--- a/results/job_matches_2026-08-22.xlsx
+++ b/results/job_matches_2026-08-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G81"/>
+  <dimension ref="A1:G76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr Databricks Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Hitachi Energy</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20.1</v>
+        <v>23.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37f9cb4e7f9e0916</t>
+          <t>https://www.indeed.com/viewjob?jk=b2bc68670e06fc48</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Analytics)</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Blob Storage, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=593e53f5fee30d60</t>
+          <t>https://www.indeed.com/viewjob?jk=e9ede359be55ea6d</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Quality Engineering (QE) Data Quality Engineer</t>
+          <t>Senior Data Engineer (Analytics)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Amida Technology Solutions</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Redshift, Azure, Data Factory, Databricks, BigQuery, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Blob Storage, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9b2b6cddab662d6</t>
+          <t>https://www.indeed.com/viewjob?jk=593e53f5fee30d60</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Engineer- Full Stack USA</t>
+          <t>Quality Engineering (QE) Data Quality Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>First Solar</t>
+          <t>Amida Technology Solutions</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Perrysburg, OH, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>Redshift, Azure, Data Factory, Databricks, BigQuery, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feaf58186fd25df4</t>
+          <t>https://www.indeed.com/viewjob?jk=b9b2b6cddab662d6</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer Microsoft Fabric</t>
+          <t>Engineer- Full Stack USA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bilzin Sumberg Baena Price &amp; Axelrod LLP</t>
+          <t>First Solar</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Perrysburg, OH, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Snowflake, SQL Server</t>
+          <t>AWS, RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=371409082795e582</t>
+          <t>https://www.indeed.com/viewjob?jk=feaf58186fd25df4</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer Microsoft Fabric</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Bilzin Sumberg Baena Price &amp; Axelrod LLP</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
+          <t>S3, RDS, Azure, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=515f3bff52abe8ea</t>
+          <t>https://www.indeed.com/viewjob?jk=371409082795e582</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f887668cf9aaf20f</t>
+          <t>https://www.indeed.com/viewjob?jk=515f3bff52abe8ea</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Guild Mortgage Company LLC</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Spark, Scala, Kafka, Snowflake, SQL Server, MySQL, MongoDB</t>
+          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd674fe067dfdd34</t>
+          <t>https://www.indeed.com/viewjob?jk=f887668cf9aaf20f</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Associate - Cloud Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Guild Mortgage Company LLC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Spark, Scala, Kafka, Snowflake, SQL Server, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce955d83d523351c</t>
+          <t>https://www.indeed.com/viewjob?jk=fd674fe067dfdd34</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI Platform System Administrator III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Boston Scientific</t>
+          <t>Entarian</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Arden Hills, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, Kinesis, Scala, Kafka, Polars, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,102 +811,102 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62388f603bbe60a4</t>
+          <t>https://www.indeed.com/viewjob?jk=97cacdd77a88ee4d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer 3 - TS clearance required - Wash DC area</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bow Wave LLC</t>
+          <t>Entarian</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, BigQuery, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Kinesis, Scala, Kafka, Polars, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61e2b94a977d2119</t>
+          <t>https://www.indeed.com/viewjob?jk=8d62e6c9bd298592</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Associate - Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f9e89b177e72a80</t>
+          <t>https://www.indeed.com/viewjob?jk=ce955d83d523351c</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr Full stack Java Developer</t>
+          <t>AI Platform System Administrator III</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Hudson Manpower</t>
+          <t>Boston Scientific</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Arden Hills, MN, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7f12b1ea10022a2</t>
+          <t>https://www.indeed.com/viewjob?jk=62388f603bbe60a4</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr Full stack Java Developer</t>
+          <t>Data Engineer 3 - TS clearance required - Wash DC area</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Hudson Manpower</t>
+          <t>Bow Wave LLC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, BigQuery, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6bc74fdfdbbca2b</t>
+          <t>https://www.indeed.com/viewjob?jk=61e2b94a977d2119</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr Full stack Java Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Hudson Manpower</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50c5bf2319077628</t>
+          <t>https://www.indeed.com/viewjob?jk=6f9e89b177e72a80</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=603c61b7cc5fe1b9</t>
+          <t>https://www.indeed.com/viewjob?jk=a7f12b1ea10022a2</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Allentown, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7340ebb5e99bf41f</t>
+          <t>https://www.indeed.com/viewjob?jk=a6bc74fdfdbbca2b</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7bb7609c20e949e</t>
+          <t>https://www.indeed.com/viewjob?jk=50c5bf2319077628</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Science Engineer</t>
+          <t>Sr Full stack Java Developer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>LegitScript</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, MLOps</t>
+          <t>AWS, S3, API Gateway, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,94 +1126,94 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ac58242095324ac</t>
+          <t>https://www.indeed.com/viewjob?jk=603c61b7cc5fe1b9</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Solution Architect (Java, Cloud &amp; AI) - FTE / Hybrid</t>
+          <t>Sr Full stack Java Developer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Allentown, PA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Databricks, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, S3, API Gateway, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cff991eacc7c642b</t>
+          <t>https://www.indeed.com/viewjob?jk=7340ebb5e99bf41f</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr. Specialist, AI CRM Engineering</t>
+          <t>Sr Full stack Java Developer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Bristol Myers Squibb</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, S3, API Gateway, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2323a1df671308a</t>
+          <t>https://www.indeed.com/viewjob?jk=e7bb7609c20e949e</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Senior Data Science Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Commence</t>
+          <t>LegitScript</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
+          <t>Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, MLOps</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=125902545a13a43c</t>
+          <t>https://www.indeed.com/viewjob?jk=0ac58242095324ac</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Solution Architect (Java, Cloud &amp; AI) - FTE / Hybrid</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Cushman &amp; Wakefield</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,69 +1256,69 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, NoSQL, ELT</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Databricks, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d93e7b1c586e6a4d</t>
+          <t>https://www.indeed.com/viewjob?jk=cff991eacc7c642b</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer 2 - TS required - Washington DC area</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Bow Wave LLC</t>
+          <t>Commence</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Google Cloud Platform, BigQuery, Hadoop, Spark, Scala, ETL</t>
+          <t>AWS, EMR, Lambda, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de40e05b432ea8b8</t>
+          <t>https://www.indeed.com/viewjob?jk=125902545a13a43c</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer 2 - TS required - Washington DC area</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>REPLY</t>
+          <t>Bow Wave LLC</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,17 +1326,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, Azure Cosmos DB, Data Modeling</t>
+          <t>AWS, Redshift, S3, Azure, Google Cloud Platform, BigQuery, Hadoop, Spark, Scala, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cc84ba97f996450</t>
+          <t>https://www.indeed.com/viewjob?jk=de40e05b432ea8b8</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9d2db7b4c8d89f8</t>
+          <t>https://www.indeed.com/viewjob?jk=5cc84ba97f996450</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74f4fee2cc3d811b</t>
+          <t>https://www.indeed.com/viewjob?jk=b9d2db7b4c8d89f8</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7ad9782930201d7</t>
+          <t>https://www.indeed.com/viewjob?jk=74f4fee2cc3d811b</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61bab526ed5bb2fe</t>
+          <t>https://www.indeed.com/viewjob?jk=b7ad9782930201d7</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Finance Solutions, Google Cloud Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>REPLY</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Spark, PySpark, Scala, Oracle, Dimensional Modeling, ETL, ELT</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, Azure Cosmos DB, Data Modeling</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c94336bbf2aab76d</t>
+          <t>https://www.indeed.com/viewjob?jk=61bab526ed5bb2fe</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data and Integration Developer</t>
+          <t>Finance Solutions, Google Cloud Platform</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Platte River Power Authority</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Fort Collins, CO, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,69 +1536,69 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, Snowflake, Oracle</t>
+          <t>RDS, Google Cloud Platform, GCP, Spark, PySpark, Scala, Oracle, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bef94e108ffe967</t>
+          <t>https://www.indeed.com/viewjob?jk=c94336bbf2aab76d</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Consultant, Data Engineer | Databricks</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Yusen Logistics</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c80455e75f43f1e</t>
+          <t>https://www.indeed.com/viewjob?jk=87fd62c345b8469e</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Consultant, Data Engineer | Databricks</t>
+          <t>Software Engineer II, Data</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Credit Acceptance</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87fd62c345b8469e</t>
+          <t>https://www.indeed.com/viewjob?jk=39dcfd9f2966d672</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Credit Acceptance</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, NoSQL</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39dcfd9f2966d672</t>
+          <t>https://www.indeed.com/viewjob?jk=8209ae3042e1b9a9</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Cloud Engineer; Platform Analytics (Contract)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Vervint</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, CI/CD</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, S3, SQS, IAM, RDS</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8209ae3042e1b9a9</t>
+          <t>https://www.indeed.com/viewjob?jk=7c0847cb6bf1b0e8</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Cloud Engineer; Platform Analytics (Contract)</t>
+          <t>Full Stack Developer - Advanced | Columbus, US</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Vervint</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, S3, SQS, IAM, RDS</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Vertex AI, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c0847cb6bf1b0e8</t>
+          <t>https://www.indeed.com/viewjob?jk=865f8a104cb006d1</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Advanced | Columbus, US</t>
+          <t>Sr Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Vertex AI, Scala, Kafka, NoSQL</t>
+          <t>AWS, Redshift, S3, Spark, Scala, Kafka, Snowflake, DynamoDB, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=865f8a104cb006d1</t>
+          <t>https://www.indeed.com/viewjob?jk=766cfaa008af94ec</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr Machine Learning Engineer</t>
+          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Platform (AWS)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Spark, Scala, Kafka, Snowflake, DynamoDB, NoSQL, MLOps</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=766cfaa008af94ec</t>
+          <t>https://www.indeed.com/viewjob?jk=7064a0875d5078f8</t>
         </is>
       </c>
     </row>
@@ -1903,17 +1903,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Devops Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Puig</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,17 +1921,17 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b295c5eb1d7771ed</t>
+          <t>https://www.indeed.com/viewjob?jk=143f81631e970888</t>
         </is>
       </c>
     </row>
@@ -2008,17 +2008,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>GCP Cloud Engineer</t>
+          <t>Azure IoT Solutions Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Ascend Technologies</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Event Hubs, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b7cc426dbd03f0e</t>
+          <t>https://www.indeed.com/viewjob?jk=48463a0b2c1a516b</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Economic Data System Engineer/Sr. Economic Data System Engineer-ITDDPED</t>
+          <t>GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Hadoop, Spark, Scala, Snowflake, NoSQL, ETL, ELT</t>
+          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a32b2285f6e0f19</t>
+          <t>https://www.indeed.com/viewjob?jk=6b7cc426dbd03f0e</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer Denodo</t>
+          <t>Economic Data System Engineer/Sr. Economic Data System Engineer-ITDDPED</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Flowserve</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Databricks, Scala, Snowflake, Oracle, SQL Server, ETL, ELT, Power BI</t>
+          <t>RDS, Databricks, BigQuery, Hadoop, Spark, Scala, Snowflake, NoSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b87d344718e073fe</t>
+          <t>https://www.indeed.com/viewjob?jk=3a32b2285f6e0f19</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer Denodo</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Flowserve</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, CI/CD, Terraform, Docker</t>
+          <t>Azure, Synapse Analytics, Databricks, Scala, Snowflake, Oracle, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae435ef03aa1b3c0</t>
+          <t>https://www.indeed.com/viewjob?jk=b87d344718e073fe</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>LTi Technology Solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,17 +2166,17 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeaa3af91b36b2cd</t>
+          <t>https://www.indeed.com/viewjob?jk=ae435ef03aa1b3c0</t>
         </is>
       </c>
     </row>
@@ -2218,17 +2218,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Hybrid Cloud Architect - (Data Center)</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Mercari</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Tableau</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=271b64578e43ebdc</t>
+          <t>https://www.indeed.com/viewjob?jk=179685542a7cf944</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>Sr Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Mercari</t>
+          <t>Pilot Flying J</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Roswell, GA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=179685542a7cf944</t>
+          <t>https://www.indeed.com/viewjob?jk=0a70d5a50e3bc2a5</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr Engineer, Data Engineering</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Pilot Flying J</t>
+          <t>Marathon Petroleum</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Roswell, GA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a70d5a50e3bc2a5</t>
+          <t>https://www.indeed.com/viewjob?jk=28293fa77ffc32bb</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Marathon Petroleum</t>
+          <t>Golden State</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, CI/CD, Git, Python, SQL</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28293fa77ffc32bb</t>
+          <t>https://www.indeed.com/viewjob?jk=1d156f80ddb5ea3e</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Golden State</t>
+          <t>American Tower</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d156f80ddb5ea3e</t>
+          <t>https://www.indeed.com/viewjob?jk=340f3540cd359821</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer – Advanced Data Integration &amp; Cloud Solutions</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>American Tower</t>
+          <t>Everforth ECS</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>ECS, RDS, Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, ETL, Python, SQL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=340f3540cd359821</t>
+          <t>https://www.indeed.com/viewjob?jk=ca1d4ee2bfb7f383</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Advanced Data Integration &amp; Cloud Solutions</t>
+          <t>AI Engineer/DevOps Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Everforth ECS</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, ETL, Python, SQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, Splunk, CI/CD, Azure DevOps, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca1d4ee2bfb7f383</t>
+          <t>https://www.indeed.com/viewjob?jk=a4e19bdfcdfa54e3</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AI Engineer/DevOps Engineer</t>
+          <t>Senior Analyst, Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Lincoln Electric</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, Splunk, CI/CD, Azure DevOps, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4e19bdfcdfa54e3</t>
+          <t>https://www.indeed.com/viewjob?jk=8382e0121c068a19</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Analyst, Data Engineer</t>
+          <t>Enterprise Data Architect - WORK FROM HOME - SELECT US STATES ONLY</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Lincoln Electric</t>
+          <t>Slavic401K</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8382e0121c068a19</t>
+          <t>https://www.indeed.com/viewjob?jk=df39dd0505c33d32</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Functional and Automation Tester</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>RDS, Dataflow, Vertex AI, Scala, Kafka, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24cf52c60da7e9ac</t>
+          <t>https://www.indeed.com/viewjob?jk=2aba83c87b4d58c3</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Engineer - Vehicle Connectivity &amp; mobility (VC&amp;M)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e67652360d9f4e9</t>
+          <t>https://www.indeed.com/viewjob?jk=14f272fafe4eb2bc</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Databricks Developer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=630a35e9cb636a94</t>
+          <t>https://www.indeed.com/viewjob?jk=ab1192abfbd7f24e</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Databricks Developer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7177817f699c500d</t>
+          <t>https://www.indeed.com/viewjob?jk=320dcd4f927cb250</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Quality Engineering (QE) Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Amida Technology Solutions</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Power BI, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96181d258407853f</t>
+          <t>https://www.indeed.com/viewjob?jk=29a7f8ff4391f120</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect - WORK FROM HOME - SELECT US STATES ONLY</t>
+          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Platform (Azure)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Slavic401K</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform, Azure Monitor</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df39dd0505c33d32</t>
+          <t>https://www.indeed.com/viewjob?jk=defb19c3b807f7fd</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer - Vehicle Connectivity &amp; mobility (VC&amp;M)</t>
+          <t>Associate, Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, DynamoDB, Azure Cosmos DB, NoSQL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14f272fafe4eb2bc</t>
+          <t>https://www.indeed.com/viewjob?jk=06fd6810514e5491</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Databricks Developer</t>
+          <t>Data Anchor</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>RDS, GCP, BigQuery, Vertex AI, Hadoop, Spark, Kafka, MongoDB, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=320dcd4f927cb250</t>
+          <t>https://www.indeed.com/viewjob?jk=3db1969fc986c5bb</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Quality Engineering (QE) Engineer</t>
+          <t>Data Engineer - Oklahoma City, OK</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Amida Technology Solutions</t>
+          <t>CFS Brands, LLC</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Power BI, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>IAM, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,59 +2841,59 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29a7f8ff4391f120</t>
+          <t>https://www.indeed.com/viewjob?jk=113fe7e3580ec298</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Data Engineer - API / Microservices</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Maven, Terraform, Kubernetes</t>
+          <t>AWS, RDS, BigQuery, Scala, Oracle, PostgreSQL, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6db805cce62a3db2</t>
+          <t>https://www.indeed.com/viewjob?jk=45eef8c152b64a60</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Associate, Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Chiesi Farmaceutici S.p.A.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, DynamoDB, Azure Cosmos DB, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06fd6810514e5491</t>
+          <t>https://www.indeed.com/viewjob?jk=78d407207abb7498</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Anchor</t>
+          <t>Apache Spark Core Java</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Vertex AI, Hadoop, Spark, Kafka, MongoDB, NoSQL, Splunk</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3db1969fc986c5bb</t>
+          <t>https://www.indeed.com/viewjob?jk=16d16eda2d514586</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr Data Engineer - API / Microservices</t>
+          <t>Senior Analytics Engineer, Marketing Sciences</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>SimplePractice</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Oracle, PostgreSQL, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, Kinesis, RDS, Scala, Kafka, Snowflake, ETL, dbt, Terraform, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45eef8c152b64a60</t>
+          <t>https://www.indeed.com/viewjob?jk=4a341479dc01b56f</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Full Stack Engineer, Agent Experience Platform</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Chiesi Farmaceutici S.p.A.</t>
+          <t>MAPFRE Insurance</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Webster, MA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, DynamoDB, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78d407207abb7498</t>
+          <t>https://www.indeed.com/viewjob?jk=73664071b95987ff</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Apache Spark Core Java</t>
+          <t>.NET Backend Developer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Inclusion Cloud</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16d16eda2d514586</t>
+          <t>https://www.indeed.com/viewjob?jk=5c9d1b0d1d29e0d2</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Marketing Sciences</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SimplePractice</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Allen Park, MI, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Scala, Kafka, Snowflake, ETL, dbt, Terraform, Docker</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,182 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a341479dc01b56f</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Engineer, Agent Experience Platform</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>MAPFRE Insurance</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Webster, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, DynamoDB, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=73664071b95987ff</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>.NET Backend Developer</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Inclusion Cloud</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5c9d1b0d1d29e0d2</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Ford Motor Company</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Allen Park, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, CI/CD, Terraform, Git</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=5cb7a428029c6a47</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer – CI/CD &amp; Cloud Infrastructure</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>General Motors (GM)</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Milford, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=24a6d7aaf0bcba34</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - CI/CD and Software Development Tools</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>General Motors (GM)</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Milford, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c07d3c81a46d8e9a</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-22.xlsx
+++ b/results/job_matches_2026-08-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G76"/>
+  <dimension ref="A1:G158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -993,17 +993,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr Full stack Java Developer</t>
+          <t>Senior Engineer, Enterprise Database</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hudson Manpower</t>
+          <t>Applied Medical</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Rancho Santa Margarita, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7f12b1ea10022a2</t>
+          <t>https://www.indeed.com/viewjob?jk=51a5d6b8454480a2</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6bc74fdfdbbca2b</t>
+          <t>https://www.indeed.com/viewjob?jk=a7f12b1ea10022a2</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50c5bf2319077628</t>
+          <t>https://www.indeed.com/viewjob?jk=a6bc74fdfdbbca2b</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=603c61b7cc5fe1b9</t>
+          <t>https://www.indeed.com/viewjob?jk=50c5bf2319077628</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Allentown, PA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7340ebb5e99bf41f</t>
+          <t>https://www.indeed.com/viewjob?jk=603c61b7cc5fe1b9</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Allentown, PA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7bb7609c20e949e</t>
+          <t>https://www.indeed.com/viewjob?jk=7340ebb5e99bf41f</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Science Engineer</t>
+          <t>Sr Full stack Java Developer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LegitScript</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, MLOps</t>
+          <t>AWS, S3, API Gateway, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,59 +1231,59 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ac58242095324ac</t>
+          <t>https://www.indeed.com/viewjob?jk=e7bb7609c20e949e</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Solution Architect (Java, Cloud &amp; AI) - FTE / Hybrid</t>
+          <t>Software Engineer, Full Stack - AI (New York)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Databricks, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cff991eacc7c642b</t>
+          <t>https://www.indeed.com/viewjob?jk=362603547d1c2a0d</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Senior Data Science Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Commence</t>
+          <t>LegitScript</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
+          <t>Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, MLOps</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,59 +1301,59 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=125902545a13a43c</t>
+          <t>https://www.indeed.com/viewjob?jk=0ac58242095324ac</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer 2 - TS required - Washington DC area</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Bow Wave LLC</t>
+          <t>Commence</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Google Cloud Platform, BigQuery, Hadoop, Spark, Scala, ETL</t>
+          <t>AWS, EMR, Lambda, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de40e05b432ea8b8</t>
+          <t>https://www.indeed.com/viewjob?jk=125902545a13a43c</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer 2 - TS required - Washington DC area</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>REPLY</t>
+          <t>Bow Wave LLC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, Azure Cosmos DB, Data Modeling</t>
+          <t>AWS, Redshift, S3, Azure, Google Cloud Platform, BigQuery, Hadoop, Spark, Scala, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cc84ba97f996450</t>
+          <t>https://www.indeed.com/viewjob?jk=de40e05b432ea8b8</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9d2db7b4c8d89f8</t>
+          <t>https://www.indeed.com/viewjob?jk=5cc84ba97f996450</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74f4fee2cc3d811b</t>
+          <t>https://www.indeed.com/viewjob?jk=b9d2db7b4c8d89f8</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7ad9782930201d7</t>
+          <t>https://www.indeed.com/viewjob?jk=74f4fee2cc3d811b</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61bab526ed5bb2fe</t>
+          <t>https://www.indeed.com/viewjob?jk=b7ad9782930201d7</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Finance Solutions, Google Cloud Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>REPLY</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Spark, PySpark, Scala, Oracle, Dimensional Modeling, ETL, ELT</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, Azure Cosmos DB, Data Modeling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c94336bbf2aab76d</t>
+          <t>https://www.indeed.com/viewjob?jk=61bab526ed5bb2fe</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Consultant, Data Engineer | Databricks</t>
+          <t>Finance Solutions, Google Cloud Platform</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ELT</t>
+          <t>RDS, Google Cloud Platform, GCP, Spark, PySpark, Scala, Oracle, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87fd62c345b8469e</t>
+          <t>https://www.indeed.com/viewjob?jk=c94336bbf2aab76d</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Credit Acceptance</t>
+          <t>Powerplan</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39dcfd9f2966d672</t>
+          <t>https://www.indeed.com/viewjob?jk=9effd2546d52cd38</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Consultant, Data Engineer | Databricks</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, CI/CD</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,19 +1651,19 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8209ae3042e1b9a9</t>
+          <t>https://www.indeed.com/viewjob?jk=87fd62c345b8469e</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Cloud Engineer; Platform Analytics (Contract)</t>
+          <t>Software Engineer II, Data</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Vervint</t>
+          <t>Credit Acceptance</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, S3, SQS, IAM, RDS</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c0847cb6bf1b0e8</t>
+          <t>https://www.indeed.com/viewjob?jk=39dcfd9f2966d672</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Advanced | Columbus, US</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Vertex AI, Scala, Kafka, NoSQL</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=865f8a104cb006d1</t>
+          <t>https://www.indeed.com/viewjob?jk=8209ae3042e1b9a9</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr Machine Learning Engineer</t>
+          <t>Cloud Engineer; Platform Analytics (Contract)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>Vervint</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Spark, Scala, Kafka, Snowflake, DynamoDB, NoSQL, MLOps</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, S3, SQS, IAM, RDS</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=766cfaa008af94ec</t>
+          <t>https://www.indeed.com/viewjob?jk=7c0847cb6bf1b0e8</t>
         </is>
       </c>
     </row>
@@ -1798,25 +1798,25 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Full Stack Developer - Advanced | Columbus, US</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, S3, RDS, Spark, Scala, PostgreSQL, NoSQL, Jenkins</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Vertex AI, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d1eabd20620b211</t>
+          <t>https://www.indeed.com/viewjob?jk=865f8a104cb006d1</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II</t>
+          <t>Sr Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>7-Eleven</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Power BI, Tableau, MLOps</t>
+          <t>AWS, Redshift, S3, Spark, Scala, Kafka, Snowflake, DynamoDB, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ef1c00bbfcfa5af</t>
+          <t>https://www.indeed.com/viewjob?jk=766cfaa008af94ec</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Five Guys</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, EMR, Kinesis, S3, RDS, Spark, Scala, PostgreSQL, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da2726835c895c54</t>
+          <t>https://www.indeed.com/viewjob?jk=5d1eabd20620b211</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Devops Engineer</t>
+          <t>Machine Learning Engineer II</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>7-Eleven</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Power BI, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=143f81631e970888</t>
+          <t>https://www.indeed.com/viewjob?jk=3ef1c00bbfcfa5af</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Full stack Java / AWS</t>
+          <t>Senior Devops Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL, DynamoDB, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=648c04000182f970</t>
+          <t>https://www.indeed.com/viewjob?jk=143f81631e970888</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Full stack Java / AWS</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SelectQuote</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,29 +1991,29 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, SQL Server, ETL, ELT, Airflow</t>
+          <t>AWS, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23f04a50e41c3404</t>
+          <t>https://www.indeed.com/viewjob?jk=648c04000182f970</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Azure IoT Solutions Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Ascend Technologies</t>
+          <t>SelectQuote</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2022,38 +2022,38 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AKS, Jenkins</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, SQL Server, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48463a0b2c1a516b</t>
+          <t>https://www.indeed.com/viewjob?jk=23f04a50e41c3404</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>GCP Cloud Engineer</t>
+          <t>Azure IoT Solutions Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Ascend Technologies</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Event Hubs, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b7cc426dbd03f0e</t>
+          <t>https://www.indeed.com/viewjob?jk=48463a0b2c1a516b</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Economic Data System Engineer/Sr. Economic Data System Engineer-ITDDPED</t>
+          <t>GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Hadoop, Spark, Scala, Snowflake, NoSQL, ETL, ELT</t>
+          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a32b2285f6e0f19</t>
+          <t>https://www.indeed.com/viewjob?jk=6b7cc426dbd03f0e</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer Denodo</t>
+          <t>Economic Data System Engineer/Sr. Economic Data System Engineer-ITDDPED</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Flowserve</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Databricks, Scala, Snowflake, Oracle, SQL Server, ETL, ELT, Power BI</t>
+          <t>RDS, Databricks, BigQuery, Hadoop, Spark, Scala, Snowflake, NoSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b87d344718e073fe</t>
+          <t>https://www.indeed.com/viewjob?jk=3a32b2285f6e0f19</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer Denodo</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Flowserve</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, CI/CD, Terraform, Docker</t>
+          <t>Azure, Synapse Analytics, Databricks, Scala, Snowflake, Oracle, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae435ef03aa1b3c0</t>
+          <t>https://www.indeed.com/viewjob?jk=b87d344718e073fe</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>QA Automation Engineer II, Officer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, NoSQL, Talend, CI/CD, Jenkins, Docker, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d73747fd9aafef8</t>
+          <t>https://www.indeed.com/viewjob?jk=ae435ef03aa1b3c0</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>QA Automation Engineer II, Officer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Mercari</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Tableau</t>
+          <t>RDS, Scala, Oracle, NoSQL, Talend, CI/CD, Jenkins, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=179685542a7cf944</t>
+          <t>https://www.indeed.com/viewjob?jk=1d73747fd9aafef8</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr Engineer, Data Engineering</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Pilot Flying J</t>
+          <t>Mercari</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Roswell, GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Tableau</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a70d5a50e3bc2a5</t>
+          <t>https://www.indeed.com/viewjob?jk=179685542a7cf944</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Sr Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Marathon Petroleum</t>
+          <t>Pilot Flying J</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Roswell, GA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, CI/CD, Git, Python, SQL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28293fa77ffc32bb</t>
+          <t>https://www.indeed.com/viewjob?jk=0a70d5a50e3bc2a5</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Golden State</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Kafka, CI/CD, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d156f80ddb5ea3e</t>
+          <t>https://www.indeed.com/viewjob?jk=9a5cbb62cc968f68</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>American Tower</t>
+          <t>Marathon Petroleum</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=340f3540cd359821</t>
+          <t>https://www.indeed.com/viewjob?jk=28293fa77ffc32bb</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Advanced Data Integration &amp; Cloud Solutions</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Everforth ECS</t>
+          <t>Golden State</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, ETL, Python, SQL</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca1d4ee2bfb7f383</t>
+          <t>https://www.indeed.com/viewjob?jk=1d156f80ddb5ea3e</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AI Engineer/DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>American Tower</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, Splunk, CI/CD, Azure DevOps, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4e19bdfcdfa54e3</t>
+          <t>https://www.indeed.com/viewjob?jk=340f3540cd359821</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Analyst, Data Engineer</t>
+          <t>Senior Data Engineer – Advanced Data Integration &amp; Cloud Solutions</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Lincoln Electric</t>
+          <t>Everforth ECS</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
+          <t>ECS, RDS, Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, ETL, Python, SQL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8382e0121c068a19</t>
+          <t>https://www.indeed.com/viewjob?jk=ca1d4ee2bfb7f383</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect - WORK FROM HOME - SELECT US STATES ONLY</t>
+          <t>AI Engineer/DevOps Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Slavic401K</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, Splunk, CI/CD, Azure DevOps, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df39dd0505c33d32</t>
+          <t>https://www.indeed.com/viewjob?jk=a4e19bdfcdfa54e3</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Functional and Automation Tester</t>
+          <t>Senior Analyst, Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Lincoln Electric</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Dataflow, Vertex AI, Scala, Kafka, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2aba83c87b4d58c3</t>
+          <t>https://www.indeed.com/viewjob?jk=8382e0121c068a19</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Engineer - Vehicle Connectivity &amp; mobility (VC&amp;M)</t>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14f272fafe4eb2bc</t>
+          <t>https://www.indeed.com/viewjob?jk=f4ab3e3c7077492c</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Databricks Developer</t>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Inglewood, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab1192abfbd7f24e</t>
+          <t>https://www.indeed.com/viewjob?jk=b0870a8c631ca3e7</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Databricks Developer</t>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=320dcd4f927cb250</t>
+          <t>https://www.indeed.com/viewjob?jk=3a8177305c7e2b4e</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Quality Engineering (QE) Engineer</t>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Amida Technology Solutions</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Power BI, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,19 +2701,19 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29a7f8ff4391f120</t>
+          <t>https://www.indeed.com/viewjob?jk=2b216035065cdcce</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Platform (Azure)</t>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform, Azure Monitor</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=defb19c3b807f7fd</t>
+          <t>https://www.indeed.com/viewjob?jk=b0d6bbe5db7dc4e3</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Associate, Data Engineer</t>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, DynamoDB, Azure Cosmos DB, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06fd6810514e5491</t>
+          <t>https://www.indeed.com/viewjob?jk=99cd5dc3d4c47201</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Anchor</t>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Vertex AI, Hadoop, Spark, Kafka, MongoDB, NoSQL, Splunk</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3db1969fc986c5bb</t>
+          <t>https://www.indeed.com/viewjob?jk=1535cff1bb626738</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer - Oklahoma City, OK</t>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>CFS Brands, LLC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Williamsville, NY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>IAM, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=113fe7e3580ec298</t>
+          <t>https://www.indeed.com/viewjob?jk=37a520fdd5e099b9</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sr Data Engineer - API / Microservices</t>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Oracle, PostgreSQL, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,102 +2876,102 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45eef8c152b64a60</t>
+          <t>https://www.indeed.com/viewjob?jk=366fcdfb585bd3be</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Chiesi Farmaceutici S.p.A.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78d407207abb7498</t>
+          <t>https://www.indeed.com/viewjob?jk=a94f1ea7f43f3649</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Apache Spark Core Java</t>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16d16eda2d514586</t>
+          <t>https://www.indeed.com/viewjob?jk=497b07468d401d8a</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Marketing Sciences</t>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SimplePractice</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Scala, Kafka, Snowflake, ETL, dbt, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a341479dc01b56f</t>
+          <t>https://www.indeed.com/viewjob?jk=8d2e49c364fa4321</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer, Agent Experience Platform</t>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>MAPFRE Insurance</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Webster, MA, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, DynamoDB, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73664071b95987ff</t>
+          <t>https://www.indeed.com/viewjob?jk=14d6f7b29ae9eb47</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>.NET Backend Developer</t>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Inclusion Cloud</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,40 +3051,2910 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c9d1b0d1d29e0d2</t>
+          <t>https://www.indeed.com/viewjob?jk=e69bf4d69267775a</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>San Antonio, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=22a4f690926575b6</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7fc8f10cc4340e38</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ed7e30adf2adc59</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Salt Lake City, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=22efcdd2b4a3dd7f</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Memphis, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4d610152102215d5</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Hermitage, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0f093d62f255edad</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=61c760c7b06ee2ec</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7e753698d58ce405</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Tulsa, OK, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=613c98d34d3a6aff</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=81eb38d16909745a</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=26aa4bbb65d7bc04</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=51eaf011bd4b3db9</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Portland, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=875b54845cacd6b4</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Louisville, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b044118f339aeefe</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Sacramento, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=79172907c08cbd27</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4072dd1e7bd9b46a</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=60e28bece0970c90</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Omaha, NE, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=337e00bdabbbf617</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Detroit, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7008c23fbe380180</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Princeton, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ef94cdec933bb8d2</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a9b3dd72c73a5c59</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>San Juan, PR, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3f362104fdb5fce0</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Rosslyn, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bb3766965503e1b0</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Boise, ID, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=01b7efd6177971eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Las Vegas, NV, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=564843cdd5d6c05d</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=38dc1e892863874b</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=36375563a2ad1043</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Honolulu, HI, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cf1ab598617115f3</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Kansas City, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bdb4d76e4c3be44c</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bd706eccacda1e1c</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>New Orleans, LA, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=606f854062c681fa</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=15ee32196b2a250e</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Midland, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c7a2ced0233034b8</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b267004acbc01cc5</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Grand Rapids, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9be2810504f2ae29</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6f0ec602c9b09a8e</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bd0e7d3dab7e604a</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Jericho, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=905c5a2344562ab8</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Dayton, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=21b0eb74cf57c4a8</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Monterey, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=127db1667ff89227</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Costa Mesa, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2a42559421200137</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Des Moines, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d6e7dd724c924aca</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Rochester, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8483d29d2dbde05b</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Mechanicsburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=824e663391dfa6bf</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3e8686e8d16dc84d</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=496d9926f80e93e9</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=57716cf6ab6ed7a5</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Tallahassee, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c418229c0f650f96</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=95121729962d91d2</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dfec58f9b4c8760a</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5153281c36740802</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Huntsville, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=310acaaa4f9f42e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Davenport, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6efe7ed3911371c4</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1a68cf132dbdec60</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Lake Mary, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8d891e75a79397a9</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Birmingham, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=117634e8f8dfb2d6</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Lansing, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b83a26f124ccdb89</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Stamford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ad88505e172120de</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c21ad262bec7ef80</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ca6810d972b1a5f1</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=27043ef345d0b8a7</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Baltimore, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=be347b278f12cb33</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Fresno, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fed8b15c04492576</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Colorado Springs, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5b12133504b24bae</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9f864d9aca9b7b27</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=76d2eb1be4c1b252</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Gilbert, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9baba2b401f1c56c</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Platform (Azure)</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform, Azure Monitor</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=defb19c3b807f7fd</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Enterprise Data Architect - WORK FROM HOME - SELECT US STATES ONLY</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Slavic401K</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Boca Raton, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=df39dd0505c33d32</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Databricks Developer</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ab1192abfbd7f24e</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Databricks Developer</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=320dcd4f927cb250</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Software Engineer - Vehicle Connectivity &amp; mobility (VC&amp;M)</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Ford Motor Company</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Dearborn, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=14f272fafe4eb2bc</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Senior Quality Engineering (QE) Engineer</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Amida Technology Solutions</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Power BI, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=29a7f8ff4391f120</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Associate, Data Engineer</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>BlackRock</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, DynamoDB, Azure Cosmos DB, NoSQL</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=06fd6810514e5491</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Data Anchor</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Ford Motor Company</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Louisville, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>RDS, GCP, BigQuery, Vertex AI, Hadoop, Spark, Kafka, MongoDB, NoSQL, Splunk</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3db1969fc986c5bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Data Engineer - Oklahoma City, OK</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>CFS Brands, LLC</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Oklahoma City, OK, US USA</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>IAM, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=113fe7e3580ec298</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Sr Data Engineer - API / Microservices</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>McLane Company</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>AWS, RDS, BigQuery, Scala, Oracle, PostgreSQL, ETL, ELT, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=45eef8c152b64a60</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Chiesi Farmaceutici S.p.A.</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Cary, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=78d407207abb7498</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Apache Spark Core Java</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=16d16eda2d514586</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Senior Analytics Engineer, Marketing Sciences</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>SimplePractice</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, RDS, Scala, Kafka, Snowflake, ETL, dbt, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4a341479dc01b56f</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer, Agent Experience Platform</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>MAPFRE Insurance</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Webster, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, DynamoDB, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=73664071b95987ff</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>.NET Backend Developer</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Inclusion Cloud</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5c9d1b0d1d29e0d2</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
           <t>Senior Software Engineer</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B158" t="inlineStr">
         <is>
           <t>Ford Motor Company</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C158" t="inlineStr">
         <is>
           <t>Allen Park, MI, US USA</t>
         </is>
       </c>
-      <c r="D76" t="n">
+      <c r="D158" t="n">
         <v>10.4</v>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="E158" t="inlineStr">
         <is>
           <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, CI/CD, Terraform, Git</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=5cb7a428029c6a47</t>
         </is>

--- a/results/job_matches_2026-08-22.xlsx
+++ b/results/job_matches_2026-08-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G158"/>
+  <dimension ref="A1:G159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Associate</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.1</v>
+        <v>22.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Delta Live Tables, Hadoop, Hive, Sqoop, MapReduce, YARN</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9ede359be55ea6d</t>
+          <t>https://www.indeed.com/viewjob?jk=48397f4e7a2d566c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Analytics)</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Blob Storage, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=593e53f5fee30d60</t>
+          <t>https://www.indeed.com/viewjob?jk=e9ede359be55ea6d</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Quality Engineering (QE) Data Quality Engineer</t>
+          <t>Senior Data Engineer (Analytics)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Amida Technology Solutions</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Redshift, Azure, Data Factory, Databricks, BigQuery, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Blob Storage, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9b2b6cddab662d6</t>
+          <t>https://www.indeed.com/viewjob?jk=593e53f5fee30d60</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Engineer- Full Stack USA</t>
+          <t>Quality Engineering (QE) Data Quality Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>First Solar</t>
+          <t>Amida Technology Solutions</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Perrysburg, OH, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>Redshift, Azure, Data Factory, Databricks, BigQuery, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feaf58186fd25df4</t>
+          <t>https://www.indeed.com/viewjob?jk=b9b2b6cddab662d6</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer Microsoft Fabric</t>
+          <t>Engineer- Full Stack USA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bilzin Sumberg Baena Price &amp; Axelrod LLP</t>
+          <t>First Solar</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Perrysburg, OH, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Snowflake, SQL Server</t>
+          <t>AWS, RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=371409082795e582</t>
+          <t>https://www.indeed.com/viewjob?jk=feaf58186fd25df4</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer Microsoft Fabric</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Bilzin Sumberg Baena Price &amp; Axelrod LLP</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
+          <t>S3, RDS, Azure, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=515f3bff52abe8ea</t>
+          <t>https://www.indeed.com/viewjob?jk=371409082795e582</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f887668cf9aaf20f</t>
+          <t>https://www.indeed.com/viewjob?jk=515f3bff52abe8ea</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Guild Mortgage Company LLC</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Spark, Scala, Kafka, Snowflake, SQL Server, MySQL, MongoDB</t>
+          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd674fe067dfdd34</t>
+          <t>https://www.indeed.com/viewjob?jk=f887668cf9aaf20f</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Entarian</t>
+          <t>Guild Mortgage Company LLC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Scala, Kafka, Polars, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Spark, Scala, Kafka, Snowflake, SQL Server, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,14 +811,14 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97cacdd77a88ee4d</t>
+          <t>https://www.indeed.com/viewjob?jk=fd674fe067dfdd34</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d62e6c9bd298592</t>
+          <t>https://www.indeed.com/viewjob?jk=97cacdd77a88ee4d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Associate - Cloud Platform Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Entarian</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Kinesis, Scala, Kafka, Polars, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce955d83d523351c</t>
+          <t>https://www.indeed.com/viewjob?jk=8d62e6c9bd298592</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI Platform System Administrator III</t>
+          <t>Senior Associate - Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Boston Scientific</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Arden Hills, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,69 +906,69 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62388f603bbe60a4</t>
+          <t>https://www.indeed.com/viewjob?jk=ce955d83d523351c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer 3 - TS clearance required - Wash DC area</t>
+          <t>AI Platform System Administrator III</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bow Wave LLC</t>
+          <t>Boston Scientific</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Arden Hills, MN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, BigQuery, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61e2b94a977d2119</t>
+          <t>https://www.indeed.com/viewjob?jk=62388f603bbe60a4</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer 3 - TS clearance required - Wash DC area</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>Bow Wave LLC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, BigQuery, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f9e89b177e72a80</t>
+          <t>https://www.indeed.com/viewjob?jk=61e2b94a977d2119</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Engineer, Enterprise Database</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Applied Medical</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Rancho Santa Margarita, CA, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51a5d6b8454480a2</t>
+          <t>https://www.indeed.com/viewjob?jk=6f9e89b177e72a80</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr Full stack Java Developer</t>
+          <t>Senior Engineer, Enterprise Database</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Hudson Manpower</t>
+          <t>Applied Medical</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Rancho Santa Margarita, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7f12b1ea10022a2</t>
+          <t>https://www.indeed.com/viewjob?jk=51a5d6b8454480a2</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6bc74fdfdbbca2b</t>
+          <t>https://www.indeed.com/viewjob?jk=a7f12b1ea10022a2</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50c5bf2319077628</t>
+          <t>https://www.indeed.com/viewjob?jk=a6bc74fdfdbbca2b</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=603c61b7cc5fe1b9</t>
+          <t>https://www.indeed.com/viewjob?jk=50c5bf2319077628</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Allentown, PA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7340ebb5e99bf41f</t>
+          <t>https://www.indeed.com/viewjob?jk=603c61b7cc5fe1b9</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Allentown, PA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7bb7609c20e949e</t>
+          <t>https://www.indeed.com/viewjob?jk=7340ebb5e99bf41f</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer, Full Stack - AI (New York)</t>
+          <t>Sr Full stack Java Developer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Fitch Group</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
+          <t>AWS, S3, API Gateway, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=362603547d1c2a0d</t>
+          <t>https://www.indeed.com/viewjob?jk=e7bb7609c20e949e</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Science Engineer</t>
+          <t>Software Engineer, Full Stack - AI (New York)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>LegitScript</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, MLOps</t>
+          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ac58242095324ac</t>
+          <t>https://www.indeed.com/viewjob?jk=362603547d1c2a0d</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Senior Data Science Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Commence</t>
+          <t>LegitScript</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
+          <t>Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, MLOps</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,59 +1336,59 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=125902545a13a43c</t>
+          <t>https://www.indeed.com/viewjob?jk=0ac58242095324ac</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer 2 - TS required - Washington DC area</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Bow Wave LLC</t>
+          <t>Commence</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Google Cloud Platform, BigQuery, Hadoop, Spark, Scala, ETL</t>
+          <t>AWS, EMR, Lambda, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de40e05b432ea8b8</t>
+          <t>https://www.indeed.com/viewjob?jk=125902545a13a43c</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer 2 - TS required - Washington DC area</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>REPLY</t>
+          <t>Bow Wave LLC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,17 +1396,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, Azure Cosmos DB, Data Modeling</t>
+          <t>AWS, Redshift, S3, Azure, Google Cloud Platform, BigQuery, Hadoop, Spark, Scala, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cc84ba97f996450</t>
+          <t>https://www.indeed.com/viewjob?jk=de40e05b432ea8b8</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9d2db7b4c8d89f8</t>
+          <t>https://www.indeed.com/viewjob?jk=5cc84ba97f996450</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74f4fee2cc3d811b</t>
+          <t>https://www.indeed.com/viewjob?jk=b9d2db7b4c8d89f8</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7ad9782930201d7</t>
+          <t>https://www.indeed.com/viewjob?jk=74f4fee2cc3d811b</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61bab526ed5bb2fe</t>
+          <t>https://www.indeed.com/viewjob?jk=b7ad9782930201d7</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Finance Solutions, Google Cloud Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>REPLY</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Spark, PySpark, Scala, Oracle, Dimensional Modeling, ETL, ELT</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, Azure Cosmos DB, Data Modeling</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c94336bbf2aab76d</t>
+          <t>https://www.indeed.com/viewjob?jk=61bab526ed5bb2fe</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Finance Solutions, Google Cloud Platform</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Powerplan</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, MLOps, CI/CD, Azure DevOps</t>
+          <t>RDS, Google Cloud Platform, GCP, Spark, PySpark, Scala, Oracle, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9effd2546d52cd38</t>
+          <t>https://www.indeed.com/viewjob?jk=c94336bbf2aab76d</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Consultant, Data Engineer | Databricks</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Powerplan</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87fd62c345b8469e</t>
+          <t>https://www.indeed.com/viewjob?jk=9effd2546d52cd38</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data</t>
+          <t>Consultant, Data Engineer | Databricks</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Credit Acceptance</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, NoSQL</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39dcfd9f2966d672</t>
+          <t>https://www.indeed.com/viewjob?jk=87fd62c345b8469e</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Software Engineer II, Data</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Credit Acceptance</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8209ae3042e1b9a9</t>
+          <t>https://www.indeed.com/viewjob?jk=39dcfd9f2966d672</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Cloud Engineer; Platform Analytics (Contract)</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Vervint</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, S3, SQS, IAM, RDS</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c0847cb6bf1b0e8</t>
+          <t>https://www.indeed.com/viewjob?jk=8209ae3042e1b9a9</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Platform (AWS)</t>
+          <t>Cloud Engineer; Platform Analytics (Contract)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Vervint</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, S3, SQS, IAM, RDS</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7064a0875d5078f8</t>
+          <t>https://www.indeed.com/viewjob?jk=7c0847cb6bf1b0e8</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Advanced | Columbus, US</t>
+          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Platform (AWS)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Vertex AI, Scala, Kafka, NoSQL</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=865f8a104cb006d1</t>
+          <t>https://www.indeed.com/viewjob?jk=7064a0875d5078f8</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr Machine Learning Engineer</t>
+          <t>Full Stack Developer - Advanced | Columbus, US</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Spark, Scala, Kafka, Snowflake, DynamoDB, NoSQL, MLOps</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Vertex AI, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=766cfaa008af94ec</t>
+          <t>https://www.indeed.com/viewjob?jk=865f8a104cb006d1</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Sr Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, S3, RDS, Spark, Scala, PostgreSQL, NoSQL, Jenkins</t>
+          <t>AWS, Redshift, S3, Spark, Scala, Kafka, Snowflake, DynamoDB, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d1eabd20620b211</t>
+          <t>https://www.indeed.com/viewjob?jk=766cfaa008af94ec</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>7-Eleven</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Power BI, Tableau, MLOps</t>
+          <t>AWS, EMR, Kinesis, S3, RDS, Spark, Scala, PostgreSQL, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ef1c00bbfcfa5af</t>
+          <t>https://www.indeed.com/viewjob?jk=5d1eabd20620b211</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Devops Engineer</t>
+          <t>Machine Learning Engineer II</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>7-Eleven</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Power BI, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=143f81631e970888</t>
+          <t>https://www.indeed.com/viewjob?jk=3ef1c00bbfcfa5af</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Full stack Java / AWS</t>
+          <t>Senior Devops Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL, DynamoDB, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=648c04000182f970</t>
+          <t>https://www.indeed.com/viewjob?jk=143f81631e970888</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Full stack Java / AWS</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SelectQuote</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,29 +2026,29 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, SQL Server, ETL, ELT, Airflow</t>
+          <t>AWS, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23f04a50e41c3404</t>
+          <t>https://www.indeed.com/viewjob?jk=648c04000182f970</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Azure IoT Solutions Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Ascend Technologies</t>
+          <t>SelectQuote</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2057,38 +2057,38 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AKS, Jenkins</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, SQL Server, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48463a0b2c1a516b</t>
+          <t>https://www.indeed.com/viewjob?jk=23f04a50e41c3404</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>GCP Cloud Engineer</t>
+          <t>Azure IoT Solutions Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Ascend Technologies</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Event Hubs, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b7cc426dbd03f0e</t>
+          <t>https://www.indeed.com/viewjob?jk=48463a0b2c1a516b</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Economic Data System Engineer/Sr. Economic Data System Engineer-ITDDPED</t>
+          <t>GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Hadoop, Spark, Scala, Snowflake, NoSQL, ETL, ELT</t>
+          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a32b2285f6e0f19</t>
+          <t>https://www.indeed.com/viewjob?jk=6b7cc426dbd03f0e</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer Denodo</t>
+          <t>Economic Data System Engineer/Sr. Economic Data System Engineer-ITDDPED</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Flowserve</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Databricks, Scala, Snowflake, Oracle, SQL Server, ETL, ELT, Power BI</t>
+          <t>RDS, Databricks, BigQuery, Hadoop, Spark, Scala, Snowflake, NoSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b87d344718e073fe</t>
+          <t>https://www.indeed.com/viewjob?jk=3a32b2285f6e0f19</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer Denodo</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Flowserve</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, CI/CD, Terraform, Docker</t>
+          <t>Azure, Synapse Analytics, Databricks, Scala, Snowflake, Oracle, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae435ef03aa1b3c0</t>
+          <t>https://www.indeed.com/viewjob?jk=b87d344718e073fe</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>QA Automation Engineer II, Officer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, NoSQL, Talend, CI/CD, Jenkins, Docker, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d73747fd9aafef8</t>
+          <t>https://www.indeed.com/viewjob?jk=ae435ef03aa1b3c0</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>QA Automation Engineer II, Officer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Mercari</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Tableau</t>
+          <t>RDS, Scala, Oracle, NoSQL, Talend, CI/CD, Jenkins, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=179685542a7cf944</t>
+          <t>https://www.indeed.com/viewjob?jk=1d73747fd9aafef8</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr Engineer, Data Engineering</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Pilot Flying J</t>
+          <t>Mercari</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Roswell, GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Tableau</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a70d5a50e3bc2a5</t>
+          <t>https://www.indeed.com/viewjob?jk=179685542a7cf944</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Sr Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Pilot Flying J</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Roswell, GA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Kafka, CI/CD, Terraform, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a5cbb62cc968f68</t>
+          <t>https://www.indeed.com/viewjob?jk=0a70d5a50e3bc2a5</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Marathon Petroleum</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, CI/CD, Git, Python, SQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Kafka, CI/CD, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28293fa77ffc32bb</t>
+          <t>https://www.indeed.com/viewjob?jk=9a5cbb62cc968f68</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Golden State</t>
+          <t>Marathon Petroleum</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d156f80ddb5ea3e</t>
+          <t>https://www.indeed.com/viewjob?jk=28293fa77ffc32bb</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>American Tower</t>
+          <t>Golden State</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=340f3540cd359821</t>
+          <t>https://www.indeed.com/viewjob?jk=1d156f80ddb5ea3e</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Advanced Data Integration &amp; Cloud Solutions</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Everforth ECS</t>
+          <t>American Tower</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, ETL, Python, SQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca1d4ee2bfb7f383</t>
+          <t>https://www.indeed.com/viewjob?jk=340f3540cd359821</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AI Engineer/DevOps Engineer</t>
+          <t>Senior Data Engineer – Advanced Data Integration &amp; Cloud Solutions</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Everforth ECS</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, Splunk, CI/CD, Azure DevOps, Kubernetes</t>
+          <t>ECS, RDS, Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, ETL, Python, SQL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4e19bdfcdfa54e3</t>
+          <t>https://www.indeed.com/viewjob?jk=ca1d4ee2bfb7f383</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Analyst, Data Engineer</t>
+          <t>AI Engineer/DevOps Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Lincoln Electric</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, Splunk, CI/CD, Azure DevOps, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8382e0121c068a19</t>
+          <t>https://www.indeed.com/viewjob?jk=a4e19bdfcdfa54e3</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+          <t>Senior Analyst, Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Lincoln Electric</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4ab3e3c7077492c</t>
+          <t>https://www.indeed.com/viewjob?jk=8382e0121c068a19</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Platform (Azure)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Inglewood, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform, Azure Monitor</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0870a8c631ca3e7</t>
+          <t>https://www.indeed.com/viewjob?jk=defb19c3b807f7fd</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+          <t>Enterprise Data Architect - WORK FROM HOME - SELECT US STATES ONLY</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Slavic401K</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a8177305c7e2b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=df39dd0505c33d32</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b216035065cdcce</t>
+          <t>https://www.indeed.com/viewjob?jk=f4ab3e3c7077492c</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Inglewood, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0d6bbe5db7dc4e3</t>
+          <t>https://www.indeed.com/viewjob?jk=b0870a8c631ca3e7</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99cd5dc3d4c47201</t>
+          <t>https://www.indeed.com/viewjob?jk=3a8177305c7e2b4e</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1535cff1bb626738</t>
+          <t>https://www.indeed.com/viewjob?jk=2b216035065cdcce</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Williamsville, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37a520fdd5e099b9</t>
+          <t>https://www.indeed.com/viewjob?jk=b0d6bbe5db7dc4e3</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=366fcdfb585bd3be</t>
+          <t>https://www.indeed.com/viewjob?jk=99cd5dc3d4c47201</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a94f1ea7f43f3649</t>
+          <t>https://www.indeed.com/viewjob?jk=1535cff1bb626738</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Williamsville, NY, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=497b07468d401d8a</t>
+          <t>https://www.indeed.com/viewjob?jk=37a520fdd5e099b9</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d2e49c364fa4321</t>
+          <t>https://www.indeed.com/viewjob?jk=366fcdfb585bd3be</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14d6f7b29ae9eb47</t>
+          <t>https://www.indeed.com/viewjob?jk=a94f1ea7f43f3649</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e69bf4d69267775a</t>
+          <t>https://www.indeed.com/viewjob?jk=497b07468d401d8a</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22a4f690926575b6</t>
+          <t>https://www.indeed.com/viewjob?jk=8d2e49c364fa4321</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fc8f10cc4340e38</t>
+          <t>https://www.indeed.com/viewjob?jk=14d6f7b29ae9eb47</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ed7e30adf2adc59</t>
+          <t>https://www.indeed.com/viewjob?jk=e69bf4d69267775a</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22efcdd2b4a3dd7f</t>
+          <t>https://www.indeed.com/viewjob?jk=22a4f690926575b6</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d610152102215d5</t>
+          <t>https://www.indeed.com/viewjob?jk=7fc8f10cc4340e38</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f093d62f255edad</t>
+          <t>https://www.indeed.com/viewjob?jk=4ed7e30adf2adc59</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61c760c7b06ee2ec</t>
+          <t>https://www.indeed.com/viewjob?jk=22efcdd2b4a3dd7f</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e753698d58ce405</t>
+          <t>https://www.indeed.com/viewjob?jk=4d610152102215d5</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=613c98d34d3a6aff</t>
+          <t>https://www.indeed.com/viewjob?jk=0f093d62f255edad</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81eb38d16909745a</t>
+          <t>https://www.indeed.com/viewjob?jk=61c760c7b06ee2ec</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26aa4bbb65d7bc04</t>
+          <t>https://www.indeed.com/viewjob?jk=7e753698d58ce405</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51eaf011bd4b3db9</t>
+          <t>https://www.indeed.com/viewjob?jk=613c98d34d3a6aff</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=875b54845cacd6b4</t>
+          <t>https://www.indeed.com/viewjob?jk=81eb38d16909745a</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b044118f339aeefe</t>
+          <t>https://www.indeed.com/viewjob?jk=26aa4bbb65d7bc04</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79172907c08cbd27</t>
+          <t>https://www.indeed.com/viewjob?jk=51eaf011bd4b3db9</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4072dd1e7bd9b46a</t>
+          <t>https://www.indeed.com/viewjob?jk=875b54845cacd6b4</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60e28bece0970c90</t>
+          <t>https://www.indeed.com/viewjob?jk=b044118f339aeefe</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=337e00bdabbbf617</t>
+          <t>https://www.indeed.com/viewjob?jk=79172907c08cbd27</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7008c23fbe380180</t>
+          <t>https://www.indeed.com/viewjob?jk=4072dd1e7bd9b46a</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef94cdec933bb8d2</t>
+          <t>https://www.indeed.com/viewjob?jk=60e28bece0970c90</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9b3dd72c73a5c59</t>
+          <t>https://www.indeed.com/viewjob?jk=337e00bdabbbf617</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>San Juan, PR, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f362104fdb5fce0</t>
+          <t>https://www.indeed.com/viewjob?jk=7008c23fbe380180</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb3766965503e1b0</t>
+          <t>https://www.indeed.com/viewjob?jk=ef94cdec933bb8d2</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01b7efd6177971eb</t>
+          <t>https://www.indeed.com/viewjob?jk=a9b3dd72c73a5c59</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>San Juan, PR, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=564843cdd5d6c05d</t>
+          <t>https://www.indeed.com/viewjob?jk=3f362104fdb5fce0</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38dc1e892863874b</t>
+          <t>https://www.indeed.com/viewjob?jk=bb3766965503e1b0</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36375563a2ad1043</t>
+          <t>https://www.indeed.com/viewjob?jk=01b7efd6177971eb</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Honolulu, HI, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf1ab598617115f3</t>
+          <t>https://www.indeed.com/viewjob?jk=564843cdd5d6c05d</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdb4d76e4c3be44c</t>
+          <t>https://www.indeed.com/viewjob?jk=38dc1e892863874b</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd706eccacda1e1c</t>
+          <t>https://www.indeed.com/viewjob?jk=36375563a2ad1043</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Honolulu, HI, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606f854062c681fa</t>
+          <t>https://www.indeed.com/viewjob?jk=cf1ab598617115f3</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15ee32196b2a250e</t>
+          <t>https://www.indeed.com/viewjob?jk=bdb4d76e4c3be44c</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7a2ced0233034b8</t>
+          <t>https://www.indeed.com/viewjob?jk=bd706eccacda1e1c</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b267004acbc01cc5</t>
+          <t>https://www.indeed.com/viewjob?jk=606f854062c681fa</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9be2810504f2ae29</t>
+          <t>https://www.indeed.com/viewjob?jk=15ee32196b2a250e</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f0ec602c9b09a8e</t>
+          <t>https://www.indeed.com/viewjob?jk=c7a2ced0233034b8</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd0e7d3dab7e604a</t>
+          <t>https://www.indeed.com/viewjob?jk=b267004acbc01cc5</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=905c5a2344562ab8</t>
+          <t>https://www.indeed.com/viewjob?jk=9be2810504f2ae29</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21b0eb74cf57c4a8</t>
+          <t>https://www.indeed.com/viewjob?jk=6f0ec602c9b09a8e</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Monterey, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127db1667ff89227</t>
+          <t>https://www.indeed.com/viewjob?jk=bd0e7d3dab7e604a</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a42559421200137</t>
+          <t>https://www.indeed.com/viewjob?jk=905c5a2344562ab8</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6e7dd724c924aca</t>
+          <t>https://www.indeed.com/viewjob?jk=21b0eb74cf57c4a8</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Monterey, CA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8483d29d2dbde05b</t>
+          <t>https://www.indeed.com/viewjob?jk=127db1667ff89227</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=824e663391dfa6bf</t>
+          <t>https://www.indeed.com/viewjob?jk=2a42559421200137</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e8686e8d16dc84d</t>
+          <t>https://www.indeed.com/viewjob?jk=d6e7dd724c924aca</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=496d9926f80e93e9</t>
+          <t>https://www.indeed.com/viewjob?jk=8483d29d2dbde05b</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57716cf6ab6ed7a5</t>
+          <t>https://www.indeed.com/viewjob?jk=824e663391dfa6bf</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c418229c0f650f96</t>
+          <t>https://www.indeed.com/viewjob?jk=3e8686e8d16dc84d</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95121729962d91d2</t>
+          <t>https://www.indeed.com/viewjob?jk=496d9926f80e93e9</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfec58f9b4c8760a</t>
+          <t>https://www.indeed.com/viewjob?jk=57716cf6ab6ed7a5</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5153281c36740802</t>
+          <t>https://www.indeed.com/viewjob?jk=c418229c0f650f96</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=310acaaa4f9f42e3</t>
+          <t>https://www.indeed.com/viewjob?jk=95121729962d91d2</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6efe7ed3911371c4</t>
+          <t>https://www.indeed.com/viewjob?jk=dfec58f9b4c8760a</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a68cf132dbdec60</t>
+          <t>https://www.indeed.com/viewjob?jk=5153281c36740802</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d891e75a79397a9</t>
+          <t>https://www.indeed.com/viewjob?jk=310acaaa4f9f42e3</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=117634e8f8dfb2d6</t>
+          <t>https://www.indeed.com/viewjob?jk=6efe7ed3911371c4</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b83a26f124ccdb89</t>
+          <t>https://www.indeed.com/viewjob?jk=1a68cf132dbdec60</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad88505e172120de</t>
+          <t>https://www.indeed.com/viewjob?jk=8d891e75a79397a9</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c21ad262bec7ef80</t>
+          <t>https://www.indeed.com/viewjob?jk=117634e8f8dfb2d6</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca6810d972b1a5f1</t>
+          <t>https://www.indeed.com/viewjob?jk=b83a26f124ccdb89</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27043ef345d0b8a7</t>
+          <t>https://www.indeed.com/viewjob?jk=ad88505e172120de</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be347b278f12cb33</t>
+          <t>https://www.indeed.com/viewjob?jk=c21ad262bec7ef80</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fed8b15c04492576</t>
+          <t>https://www.indeed.com/viewjob?jk=ca6810d972b1a5f1</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b12133504b24bae</t>
+          <t>https://www.indeed.com/viewjob?jk=27043ef345d0b8a7</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f864d9aca9b7b27</t>
+          <t>https://www.indeed.com/viewjob?jk=be347b278f12cb33</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76d2eb1be4c1b252</t>
+          <t>https://www.indeed.com/viewjob?jk=fed8b15c04492576</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9baba2b401f1c56c</t>
+          <t>https://www.indeed.com/viewjob?jk=5b12133504b24bae</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Platform (Azure)</t>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform, Azure Monitor</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=defb19c3b807f7fd</t>
+          <t>https://www.indeed.com/viewjob?jk=9f864d9aca9b7b27</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect - WORK FROM HOME - SELECT US STATES ONLY</t>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Slavic401K</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,24 +5466,24 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df39dd0505c33d32</t>
+          <t>https://www.indeed.com/viewjob?jk=76d2eb1be4c1b252</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Databricks Developer</t>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab1192abfbd7f24e</t>
+          <t>https://www.indeed.com/viewjob?jk=9baba2b401f1c56c</t>
         </is>
       </c>
     </row>
@@ -5536,24 +5536,24 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=320dcd4f927cb250</t>
+          <t>https://www.indeed.com/viewjob?jk=ab1192abfbd7f24e</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Software Engineer - Vehicle Connectivity &amp; mobility (VC&amp;M)</t>
+          <t>Databricks Developer</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5571,24 +5571,24 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14f272fafe4eb2bc</t>
+          <t>https://www.indeed.com/viewjob?jk=320dcd4f927cb250</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Senior Quality Engineering (QE) Engineer</t>
+          <t>Software Engineer - Vehicle Connectivity &amp; mobility (VC&amp;M)</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Amida Technology Solutions</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Power BI, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5606,32 +5606,32 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29a7f8ff4391f120</t>
+          <t>https://www.indeed.com/viewjob?jk=14f272fafe4eb2bc</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Associate, Data Engineer</t>
+          <t>Senior Quality Engineering (QE) Engineer</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Amida Technology Solutions</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, DynamoDB, Azure Cosmos DB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Power BI, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5641,24 +5641,24 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06fd6810514e5491</t>
+          <t>https://www.indeed.com/viewjob?jk=29a7f8ff4391f120</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Data Anchor</t>
+          <t>Associate, Data Engineer</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Vertex AI, Hadoop, Spark, Kafka, MongoDB, NoSQL, Splunk</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, DynamoDB, Azure Cosmos DB, NoSQL</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5676,24 +5676,24 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3db1969fc986c5bb</t>
+          <t>https://www.indeed.com/viewjob?jk=06fd6810514e5491</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Data Engineer - Oklahoma City, OK</t>
+          <t>Data Anchor</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>CFS Brands, LLC</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>IAM, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>RDS, GCP, BigQuery, Vertex AI, Hadoop, Spark, Kafka, MongoDB, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -5711,24 +5711,24 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=113fe7e3580ec298</t>
+          <t>https://www.indeed.com/viewjob?jk=3db1969fc986c5bb</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Sr Data Engineer - API / Microservices</t>
+          <t>Data Engineer - Oklahoma City, OK</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>CFS Brands, LLC</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5736,7 +5736,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Oracle, PostgreSQL, ETL, ELT, CI/CD, Python</t>
+          <t>IAM, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -5746,24 +5746,24 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45eef8c152b64a60</t>
+          <t>https://www.indeed.com/viewjob?jk=113fe7e3580ec298</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Data Engineer - API / Microservices</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Chiesi Farmaceutici S.p.A.</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5771,34 +5771,34 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT</t>
+          <t>AWS, RDS, BigQuery, Scala, Oracle, PostgreSQL, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78d407207abb7498</t>
+          <t>https://www.indeed.com/viewjob?jk=45eef8c152b64a60</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Apache Spark Core Java</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Chiesi Farmaceutici S.p.A.</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5806,34 +5806,34 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16d16eda2d514586</t>
+          <t>https://www.indeed.com/viewjob?jk=78d407207abb7498</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Marketing Sciences</t>
+          <t>Apache Spark Core Java</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>SimplePractice</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5841,34 +5841,34 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Scala, Kafka, Snowflake, ETL, dbt, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a341479dc01b56f</t>
+          <t>https://www.indeed.com/viewjob?jk=16d16eda2d514586</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer, Agent Experience Platform</t>
+          <t>Senior Analytics Engineer, Marketing Sciences</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>MAPFRE Insurance</t>
+          <t>SimplePractice</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Webster, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, DynamoDB, CI/CD, Docker</t>
+          <t>AWS, Kinesis, RDS, Scala, Kafka, Snowflake, ETL, dbt, Terraform, Docker</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -5886,24 +5886,24 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73664071b95987ff</t>
+          <t>https://www.indeed.com/viewjob?jk=4a341479dc01b56f</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>.NET Backend Developer</t>
+          <t>Senior Full Stack Engineer, Agent Experience Platform</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Inclusion Cloud</t>
+          <t>MAPFRE Insurance</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Webster, MA, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, DynamoDB, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -5921,24 +5921,24 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c9d1b0d1d29e0d2</t>
+          <t>https://www.indeed.com/viewjob?jk=73664071b95987ff</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>.NET Backend Developer</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Inclusion Cloud</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Allen Park, MI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5946,15 +5946,50 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
+          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5c9d1b0d1d29e0d2</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Ford Motor Company</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Allen Park, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
           <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, CI/CD, Terraform, Git</t>
         </is>
       </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=5cb7a428029c6a47</t>
         </is>

--- a/results/job_matches_2026-08-22.xlsx
+++ b/results/job_matches_2026-08-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G159"/>
+  <dimension ref="A1:G158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2603,17 +2603,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Platform (Azure)</t>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform, Azure Monitor</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=defb19c3b807f7fd</t>
+          <t>https://www.indeed.com/viewjob?jk=f4ab3e3c7077492c</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect - WORK FROM HOME - SELECT US STATES ONLY</t>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Slavic401K</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Inglewood, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df39dd0505c33d32</t>
+          <t>https://www.indeed.com/viewjob?jk=b0870a8c631ca3e7</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4ab3e3c7077492c</t>
+          <t>https://www.indeed.com/viewjob?jk=3a8177305c7e2b4e</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Inglewood, CA, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0870a8c631ca3e7</t>
+          <t>https://www.indeed.com/viewjob?jk=2b216035065cdcce</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a8177305c7e2b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=b0d6bbe5db7dc4e3</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b216035065cdcce</t>
+          <t>https://www.indeed.com/viewjob?jk=99cd5dc3d4c47201</t>
         </is>
       </c>
     </row>
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0d6bbe5db7dc4e3</t>
+          <t>https://www.indeed.com/viewjob?jk=1535cff1bb626738</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Williamsville, NY, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99cd5dc3d4c47201</t>
+          <t>https://www.indeed.com/viewjob?jk=37a520fdd5e099b9</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1535cff1bb626738</t>
+          <t>https://www.indeed.com/viewjob?jk=366fcdfb585bd3be</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Williamsville, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37a520fdd5e099b9</t>
+          <t>https://www.indeed.com/viewjob?jk=a94f1ea7f43f3649</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=366fcdfb585bd3be</t>
+          <t>https://www.indeed.com/viewjob?jk=497b07468d401d8a</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a94f1ea7f43f3649</t>
+          <t>https://www.indeed.com/viewjob?jk=8d2e49c364fa4321</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=497b07468d401d8a</t>
+          <t>https://www.indeed.com/viewjob?jk=14d6f7b29ae9eb47</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d2e49c364fa4321</t>
+          <t>https://www.indeed.com/viewjob?jk=e69bf4d69267775a</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14d6f7b29ae9eb47</t>
+          <t>https://www.indeed.com/viewjob?jk=22a4f690926575b6</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e69bf4d69267775a</t>
+          <t>https://www.indeed.com/viewjob?jk=7fc8f10cc4340e38</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22a4f690926575b6</t>
+          <t>https://www.indeed.com/viewjob?jk=4ed7e30adf2adc59</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fc8f10cc4340e38</t>
+          <t>https://www.indeed.com/viewjob?jk=22efcdd2b4a3dd7f</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ed7e30adf2adc59</t>
+          <t>https://www.indeed.com/viewjob?jk=4d610152102215d5</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22efcdd2b4a3dd7f</t>
+          <t>https://www.indeed.com/viewjob?jk=0f093d62f255edad</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d610152102215d5</t>
+          <t>https://www.indeed.com/viewjob?jk=61c760c7b06ee2ec</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f093d62f255edad</t>
+          <t>https://www.indeed.com/viewjob?jk=7e753698d58ce405</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61c760c7b06ee2ec</t>
+          <t>https://www.indeed.com/viewjob?jk=613c98d34d3a6aff</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e753698d58ce405</t>
+          <t>https://www.indeed.com/viewjob?jk=81eb38d16909745a</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=613c98d34d3a6aff</t>
+          <t>https://www.indeed.com/viewjob?jk=26aa4bbb65d7bc04</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81eb38d16909745a</t>
+          <t>https://www.indeed.com/viewjob?jk=51eaf011bd4b3db9</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26aa4bbb65d7bc04</t>
+          <t>https://www.indeed.com/viewjob?jk=875b54845cacd6b4</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51eaf011bd4b3db9</t>
+          <t>https://www.indeed.com/viewjob?jk=b044118f339aeefe</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=875b54845cacd6b4</t>
+          <t>https://www.indeed.com/viewjob?jk=79172907c08cbd27</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b044118f339aeefe</t>
+          <t>https://www.indeed.com/viewjob?jk=4072dd1e7bd9b46a</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79172907c08cbd27</t>
+          <t>https://www.indeed.com/viewjob?jk=60e28bece0970c90</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4072dd1e7bd9b46a</t>
+          <t>https://www.indeed.com/viewjob?jk=337e00bdabbbf617</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60e28bece0970c90</t>
+          <t>https://www.indeed.com/viewjob?jk=7008c23fbe380180</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=337e00bdabbbf617</t>
+          <t>https://www.indeed.com/viewjob?jk=ef94cdec933bb8d2</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7008c23fbe380180</t>
+          <t>https://www.indeed.com/viewjob?jk=a9b3dd72c73a5c59</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>San Juan, PR, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef94cdec933bb8d2</t>
+          <t>https://www.indeed.com/viewjob?jk=3f362104fdb5fce0</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9b3dd72c73a5c59</t>
+          <t>https://www.indeed.com/viewjob?jk=bb3766965503e1b0</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>San Juan, PR, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f362104fdb5fce0</t>
+          <t>https://www.indeed.com/viewjob?jk=01b7efd6177971eb</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb3766965503e1b0</t>
+          <t>https://www.indeed.com/viewjob?jk=564843cdd5d6c05d</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01b7efd6177971eb</t>
+          <t>https://www.indeed.com/viewjob?jk=38dc1e892863874b</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=564843cdd5d6c05d</t>
+          <t>https://www.indeed.com/viewjob?jk=36375563a2ad1043</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Honolulu, HI, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38dc1e892863874b</t>
+          <t>https://www.indeed.com/viewjob?jk=cf1ab598617115f3</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36375563a2ad1043</t>
+          <t>https://www.indeed.com/viewjob?jk=bdb4d76e4c3be44c</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Honolulu, HI, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf1ab598617115f3</t>
+          <t>https://www.indeed.com/viewjob?jk=bd706eccacda1e1c</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdb4d76e4c3be44c</t>
+          <t>https://www.indeed.com/viewjob?jk=606f854062c681fa</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd706eccacda1e1c</t>
+          <t>https://www.indeed.com/viewjob?jk=15ee32196b2a250e</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606f854062c681fa</t>
+          <t>https://www.indeed.com/viewjob?jk=c7a2ced0233034b8</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15ee32196b2a250e</t>
+          <t>https://www.indeed.com/viewjob?jk=b267004acbc01cc5</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7a2ced0233034b8</t>
+          <t>https://www.indeed.com/viewjob?jk=9be2810504f2ae29</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b267004acbc01cc5</t>
+          <t>https://www.indeed.com/viewjob?jk=6f0ec602c9b09a8e</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9be2810504f2ae29</t>
+          <t>https://www.indeed.com/viewjob?jk=bd0e7d3dab7e604a</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f0ec602c9b09a8e</t>
+          <t>https://www.indeed.com/viewjob?jk=905c5a2344562ab8</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd0e7d3dab7e604a</t>
+          <t>https://www.indeed.com/viewjob?jk=21b0eb74cf57c4a8</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Monterey, CA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=905c5a2344562ab8</t>
+          <t>https://www.indeed.com/viewjob?jk=127db1667ff89227</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21b0eb74cf57c4a8</t>
+          <t>https://www.indeed.com/viewjob?jk=2a42559421200137</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Monterey, CA, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127db1667ff89227</t>
+          <t>https://www.indeed.com/viewjob?jk=d6e7dd724c924aca</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a42559421200137</t>
+          <t>https://www.indeed.com/viewjob?jk=8483d29d2dbde05b</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6e7dd724c924aca</t>
+          <t>https://www.indeed.com/viewjob?jk=824e663391dfa6bf</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8483d29d2dbde05b</t>
+          <t>https://www.indeed.com/viewjob?jk=3e8686e8d16dc84d</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=824e663391dfa6bf</t>
+          <t>https://www.indeed.com/viewjob?jk=496d9926f80e93e9</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e8686e8d16dc84d</t>
+          <t>https://www.indeed.com/viewjob?jk=57716cf6ab6ed7a5</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=496d9926f80e93e9</t>
+          <t>https://www.indeed.com/viewjob?jk=c418229c0f650f96</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57716cf6ab6ed7a5</t>
+          <t>https://www.indeed.com/viewjob?jk=95121729962d91d2</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c418229c0f650f96</t>
+          <t>https://www.indeed.com/viewjob?jk=dfec58f9b4c8760a</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95121729962d91d2</t>
+          <t>https://www.indeed.com/viewjob?jk=5153281c36740802</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfec58f9b4c8760a</t>
+          <t>https://www.indeed.com/viewjob?jk=310acaaa4f9f42e3</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5153281c36740802</t>
+          <t>https://www.indeed.com/viewjob?jk=6efe7ed3911371c4</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=310acaaa4f9f42e3</t>
+          <t>https://www.indeed.com/viewjob?jk=1a68cf132dbdec60</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6efe7ed3911371c4</t>
+          <t>https://www.indeed.com/viewjob?jk=8d891e75a79397a9</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a68cf132dbdec60</t>
+          <t>https://www.indeed.com/viewjob?jk=117634e8f8dfb2d6</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d891e75a79397a9</t>
+          <t>https://www.indeed.com/viewjob?jk=b83a26f124ccdb89</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=117634e8f8dfb2d6</t>
+          <t>https://www.indeed.com/viewjob?jk=ad88505e172120de</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b83a26f124ccdb89</t>
+          <t>https://www.indeed.com/viewjob?jk=c21ad262bec7ef80</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad88505e172120de</t>
+          <t>https://www.indeed.com/viewjob?jk=ca6810d972b1a5f1</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c21ad262bec7ef80</t>
+          <t>https://www.indeed.com/viewjob?jk=27043ef345d0b8a7</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca6810d972b1a5f1</t>
+          <t>https://www.indeed.com/viewjob?jk=be347b278f12cb33</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27043ef345d0b8a7</t>
+          <t>https://www.indeed.com/viewjob?jk=fed8b15c04492576</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be347b278f12cb33</t>
+          <t>https://www.indeed.com/viewjob?jk=5b12133504b24bae</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fed8b15c04492576</t>
+          <t>https://www.indeed.com/viewjob?jk=9f864d9aca9b7b27</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b12133504b24bae</t>
+          <t>https://www.indeed.com/viewjob?jk=76d2eb1be4c1b252</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f864d9aca9b7b27</t>
+          <t>https://www.indeed.com/viewjob?jk=9baba2b401f1c56c</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Platform (Azure)</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform, Azure Monitor</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,24 +5466,24 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76d2eb1be4c1b252</t>
+          <t>https://www.indeed.com/viewjob?jk=defb19c3b807f7fd</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+          <t>Enterprise Data Architect - WORK FROM HOME - SELECT US STATES ONLY</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Slavic401K</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,24 +5501,24 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9baba2b401f1c56c</t>
+          <t>https://www.indeed.com/viewjob?jk=df39dd0505c33d32</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Databricks Developer</t>
+          <t>Software Engineer - Vehicle Connectivity &amp; mobility (VC&amp;M)</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab1192abfbd7f24e</t>
+          <t>https://www.indeed.com/viewjob?jk=14f272fafe4eb2bc</t>
         </is>
       </c>
     </row>
@@ -5571,24 +5571,24 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=320dcd4f927cb250</t>
+          <t>https://www.indeed.com/viewjob?jk=ab1192abfbd7f24e</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Software Engineer - Vehicle Connectivity &amp; mobility (VC&amp;M)</t>
+          <t>Databricks Developer</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14f272fafe4eb2bc</t>
+          <t>https://www.indeed.com/viewjob?jk=320dcd4f927cb250</t>
         </is>
       </c>
     </row>
@@ -5753,17 +5753,17 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Sr Data Engineer - API / Microservices</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Chiesi Farmaceutici S.p.A.</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5771,34 +5771,34 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Oracle, PostgreSQL, ETL, ELT, CI/CD, Python</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45eef8c152b64a60</t>
+          <t>https://www.indeed.com/viewjob?jk=78d407207abb7498</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Apache Spark Core Java</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Chiesi Farmaceutici S.p.A.</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5806,34 +5806,34 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78d407207abb7498</t>
+          <t>https://www.indeed.com/viewjob?jk=16d16eda2d514586</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Apache Spark Core Java</t>
+          <t>Senior Analytics Engineer, Marketing Sciences</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>SimplePractice</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5841,34 +5841,34 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, RDS, Scala, Kafka, Snowflake, ETL, dbt, Terraform, Docker</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16d16eda2d514586</t>
+          <t>https://www.indeed.com/viewjob?jk=4a341479dc01b56f</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Marketing Sciences</t>
+          <t>Senior Full Stack Engineer, Agent Experience Platform</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>SimplePractice</t>
+          <t>MAPFRE Insurance</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Webster, MA, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Scala, Kafka, Snowflake, ETL, dbt, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, DynamoDB, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -5886,24 +5886,24 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a341479dc01b56f</t>
+          <t>https://www.indeed.com/viewjob?jk=73664071b95987ff</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer, Agent Experience Platform</t>
+          <t>.NET Backend Developer</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>MAPFRE Insurance</t>
+          <t>Inclusion Cloud</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Webster, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, DynamoDB, CI/CD, Docker</t>
+          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -5921,24 +5921,24 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73664071b95987ff</t>
+          <t>https://www.indeed.com/viewjob?jk=5c9d1b0d1d29e0d2</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>.NET Backend Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Inclusion Cloud</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Allen Park, MI, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -5955,41 +5955,6 @@
         </is>
       </c>
       <c r="G158" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5c9d1b0d1d29e0d2</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>Ford Motor Company</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>Allen Park, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D159" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, CI/CD, Terraform, Git</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=5cb7a428029c6a47</t>
         </is>

--- a/results/job_matches_2026-08-22.xlsx
+++ b/results/job_matches_2026-08-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G158"/>
+  <dimension ref="A1:G157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -888,17 +888,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Associate - Cloud Platform Engineer</t>
+          <t>AI Platform System Administrator III</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Boston Scientific</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Arden Hills, MN, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,69 +906,69 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce955d83d523351c</t>
+          <t>https://www.indeed.com/viewjob?jk=62388f603bbe60a4</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI Platform System Administrator III</t>
+          <t>Data Engineer 3 - TS clearance required - Wash DC area</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Boston Scientific</t>
+          <t>Bow Wave LLC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Arden Hills, MN, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, BigQuery, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62388f603bbe60a4</t>
+          <t>https://www.indeed.com/viewjob?jk=61e2b94a977d2119</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer 3 - TS clearance required - Wash DC area</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bow Wave LLC</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, BigQuery, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61e2b94a977d2119</t>
+          <t>https://www.indeed.com/viewjob?jk=6f9e89b177e72a80</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Engineer, Enterprise Database</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>Applied Medical</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Rancho Santa Margarita, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f9e89b177e72a80</t>
+          <t>https://www.indeed.com/viewjob?jk=51a5d6b8454480a2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Engineer, Enterprise Database</t>
+          <t>Sr Full stack Java Developer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Applied Medical</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Rancho Santa Margarita, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, S3, API Gateway, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51a5d6b8454480a2</t>
+          <t>https://www.indeed.com/viewjob?jk=a7f12b1ea10022a2</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7f12b1ea10022a2</t>
+          <t>https://www.indeed.com/viewjob?jk=a6bc74fdfdbbca2b</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6bc74fdfdbbca2b</t>
+          <t>https://www.indeed.com/viewjob?jk=50c5bf2319077628</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50c5bf2319077628</t>
+          <t>https://www.indeed.com/viewjob?jk=603c61b7cc5fe1b9</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Allentown, PA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=603c61b7cc5fe1b9</t>
+          <t>https://www.indeed.com/viewjob?jk=7340ebb5e99bf41f</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Allentown, PA, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7340ebb5e99bf41f</t>
+          <t>https://www.indeed.com/viewjob?jk=e7bb7609c20e949e</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr Full stack Java Developer</t>
+          <t>Software Engineer, Full Stack - AI (New York)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Hudson Manpower</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7bb7609c20e949e</t>
+          <t>https://www.indeed.com/viewjob?jk=362603547d1c2a0d</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer, Full Stack - AI (New York)</t>
+          <t>Senior Data Science Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Fitch Group</t>
+          <t>LegitScript</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
+          <t>Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, MLOps</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=362603547d1c2a0d</t>
+          <t>https://www.indeed.com/viewjob?jk=0ac58242095324ac</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Science Engineer</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>LegitScript</t>
+          <t>Commence</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, MLOps</t>
+          <t>AWS, EMR, Lambda, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,59 +1336,59 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ac58242095324ac</t>
+          <t>https://www.indeed.com/viewjob?jk=125902545a13a43c</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Data Engineer 2 - TS required - Washington DC area</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Commence</t>
+          <t>Bow Wave LLC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
+          <t>AWS, Redshift, S3, Azure, Google Cloud Platform, BigQuery, Hadoop, Spark, Scala, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=125902545a13a43c</t>
+          <t>https://www.indeed.com/viewjob?jk=de40e05b432ea8b8</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer 2 - TS required - Washington DC area</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Bow Wave LLC</t>
+          <t>REPLY</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,17 +1396,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Google Cloud Platform, BigQuery, Hadoop, Spark, Scala, ETL</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, Azure Cosmos DB, Data Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de40e05b432ea8b8</t>
+          <t>https://www.indeed.com/viewjob?jk=5cc84ba97f996450</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cc84ba97f996450</t>
+          <t>https://www.indeed.com/viewjob?jk=b9d2db7b4c8d89f8</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9d2db7b4c8d89f8</t>
+          <t>https://www.indeed.com/viewjob?jk=74f4fee2cc3d811b</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74f4fee2cc3d811b</t>
+          <t>https://www.indeed.com/viewjob?jk=b7ad9782930201d7</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7ad9782930201d7</t>
+          <t>https://www.indeed.com/viewjob?jk=61bab526ed5bb2fe</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Finance Solutions, Google Cloud Platform</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>REPLY</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, Azure Cosmos DB, Data Modeling</t>
+          <t>RDS, Google Cloud Platform, GCP, Spark, PySpark, Scala, Oracle, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61bab526ed5bb2fe</t>
+          <t>https://www.indeed.com/viewjob?jk=c94336bbf2aab76d</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Finance Solutions, Google Cloud Platform</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Powerplan</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Spark, PySpark, Scala, Oracle, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c94336bbf2aab76d</t>
+          <t>https://www.indeed.com/viewjob?jk=9effd2546d52cd38</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Consultant, Data Engineer | Databricks</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Powerplan</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9effd2546d52cd38</t>
+          <t>https://www.indeed.com/viewjob?jk=87fd62c345b8469e</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Consultant, Data Engineer | Databricks</t>
+          <t>Software Engineer II, Data</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Credit Acceptance</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87fd62c345b8469e</t>
+          <t>https://www.indeed.com/viewjob?jk=39dcfd9f2966d672</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Credit Acceptance</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, NoSQL</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39dcfd9f2966d672</t>
+          <t>https://www.indeed.com/viewjob?jk=8209ae3042e1b9a9</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Cloud Engineer; Platform Analytics (Contract)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Vervint</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, CI/CD</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, S3, SQS, IAM, RDS</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8209ae3042e1b9a9</t>
+          <t>https://www.indeed.com/viewjob?jk=7c0847cb6bf1b0e8</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Cloud Engineer; Platform Analytics (Contract)</t>
+          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Platform (AWS)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Vervint</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, S3, SQS, IAM, RDS</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c0847cb6bf1b0e8</t>
+          <t>https://www.indeed.com/viewjob?jk=7064a0875d5078f8</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Platform (AWS)</t>
+          <t>Full Stack Developer - Advanced | Columbus, US</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Vertex AI, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7064a0875d5078f8</t>
+          <t>https://www.indeed.com/viewjob?jk=865f8a104cb006d1</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Advanced | Columbus, US</t>
+          <t>Sr Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Vertex AI, Scala, Kafka, NoSQL</t>
+          <t>AWS, Redshift, S3, Spark, Scala, Kafka, Snowflake, DynamoDB, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=865f8a104cb006d1</t>
+          <t>https://www.indeed.com/viewjob?jk=766cfaa008af94ec</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr Machine Learning Engineer</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Spark, Scala, Kafka, Snowflake, DynamoDB, NoSQL, MLOps</t>
+          <t>AWS, EMR, Kinesis, S3, RDS, Spark, Scala, PostgreSQL, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=766cfaa008af94ec</t>
+          <t>https://www.indeed.com/viewjob?jk=5d1eabd20620b211</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Machine Learning Engineer II</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>7-Eleven</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, S3, RDS, Spark, Scala, PostgreSQL, NoSQL, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Power BI, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d1eabd20620b211</t>
+          <t>https://www.indeed.com/viewjob?jk=3ef1c00bbfcfa5af</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II</t>
+          <t>Senior Devops Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>7-Eleven</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Power BI, Tableau, MLOps</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ef1c00bbfcfa5af</t>
+          <t>https://www.indeed.com/viewjob?jk=143f81631e970888</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Devops Engineer</t>
+          <t>Senior Full stack Java / AWS</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation</t>
+          <t>AWS, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=143f81631e970888</t>
+          <t>https://www.indeed.com/viewjob?jk=648c04000182f970</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Full stack Java / AWS</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>SelectQuote</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,29 +2026,29 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL, DynamoDB, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, SQL Server, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=648c04000182f970</t>
+          <t>https://www.indeed.com/viewjob?jk=23f04a50e41c3404</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Azure IoT Solutions Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SelectQuote</t>
+          <t>Ascend Technologies</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2057,38 +2057,38 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, SQL Server, ETL, ELT, Airflow</t>
+          <t>RDS, Azure, Event Hubs, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23f04a50e41c3404</t>
+          <t>https://www.indeed.com/viewjob?jk=48463a0b2c1a516b</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Azure IoT Solutions Engineer</t>
+          <t>GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Ascend Technologies</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AKS, Jenkins</t>
+          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48463a0b2c1a516b</t>
+          <t>https://www.indeed.com/viewjob?jk=6b7cc426dbd03f0e</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>GCP Cloud Engineer</t>
+          <t>Economic Data System Engineer/Sr. Economic Data System Engineer-ITDDPED</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD, Terraform, Docker</t>
+          <t>RDS, Databricks, BigQuery, Hadoop, Spark, Scala, Snowflake, NoSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b7cc426dbd03f0e</t>
+          <t>https://www.indeed.com/viewjob?jk=3a32b2285f6e0f19</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Economic Data System Engineer/Sr. Economic Data System Engineer-ITDDPED</t>
+          <t>Data Engineer Denodo</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Flowserve</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Hadoop, Spark, Scala, Snowflake, NoSQL, ETL, ELT</t>
+          <t>Azure, Synapse Analytics, Databricks, Scala, Snowflake, Oracle, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a32b2285f6e0f19</t>
+          <t>https://www.indeed.com/viewjob?jk=b87d344718e073fe</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer Denodo</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Flowserve</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Databricks, Scala, Snowflake, Oracle, SQL Server, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b87d344718e073fe</t>
+          <t>https://www.indeed.com/viewjob?jk=ae435ef03aa1b3c0</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>QA Automation Engineer II, Officer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, CI/CD, Terraform, Docker</t>
+          <t>RDS, Scala, Oracle, NoSQL, Talend, CI/CD, Jenkins, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae435ef03aa1b3c0</t>
+          <t>https://www.indeed.com/viewjob?jk=1d73747fd9aafef8</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>QA Automation Engineer II, Officer</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>Mercari</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, NoSQL, Talend, CI/CD, Jenkins, Docker, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Tableau</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d73747fd9aafef8</t>
+          <t>https://www.indeed.com/viewjob?jk=179685542a7cf944</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>Sr Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Mercari</t>
+          <t>Pilot Flying J</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Roswell, GA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=179685542a7cf944</t>
+          <t>https://www.indeed.com/viewjob?jk=0a70d5a50e3bc2a5</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr Engineer, Data Engineering</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Pilot Flying J</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Roswell, GA, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Kafka, CI/CD, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a70d5a50e3bc2a5</t>
+          <t>https://www.indeed.com/viewjob?jk=9a5cbb62cc968f68</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Marathon Petroleum</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Kafka, CI/CD, Terraform, Kubernetes, AKS</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a5cbb62cc968f68</t>
+          <t>https://www.indeed.com/viewjob?jk=28293fa77ffc32bb</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Marathon Petroleum</t>
+          <t>Golden State</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, CI/CD, Git, Python, SQL</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28293fa77ffc32bb</t>
+          <t>https://www.indeed.com/viewjob?jk=1d156f80ddb5ea3e</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Golden State</t>
+          <t>American Tower</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d156f80ddb5ea3e</t>
+          <t>https://www.indeed.com/viewjob?jk=340f3540cd359821</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer – Advanced Data Integration &amp; Cloud Solutions</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>American Tower</t>
+          <t>Everforth ECS</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>ECS, RDS, Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, ETL, Python, SQL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=340f3540cd359821</t>
+          <t>https://www.indeed.com/viewjob?jk=ca1d4ee2bfb7f383</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Advanced Data Integration &amp; Cloud Solutions</t>
+          <t>AI Engineer/DevOps Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Everforth ECS</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, ETL, Python, SQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, Splunk, CI/CD, Azure DevOps, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca1d4ee2bfb7f383</t>
+          <t>https://www.indeed.com/viewjob?jk=a4e19bdfcdfa54e3</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AI Engineer/DevOps Engineer</t>
+          <t>Senior Analyst, Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Lincoln Electric</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, Splunk, CI/CD, Azure DevOps, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4e19bdfcdfa54e3</t>
+          <t>https://www.indeed.com/viewjob?jk=8382e0121c068a19</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Analyst, Data Engineer</t>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Lincoln Electric</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8382e0121c068a19</t>
+          <t>https://www.indeed.com/viewjob?jk=f4ab3e3c7077492c</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Inglewood, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4ab3e3c7077492c</t>
+          <t>https://www.indeed.com/viewjob?jk=b0870a8c631ca3e7</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Inglewood, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0870a8c631ca3e7</t>
+          <t>https://www.indeed.com/viewjob?jk=3a8177305c7e2b4e</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a8177305c7e2b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=2b216035065cdcce</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b216035065cdcce</t>
+          <t>https://www.indeed.com/viewjob?jk=b0d6bbe5db7dc4e3</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0d6bbe5db7dc4e3</t>
+          <t>https://www.indeed.com/viewjob?jk=99cd5dc3d4c47201</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99cd5dc3d4c47201</t>
+          <t>https://www.indeed.com/viewjob?jk=1535cff1bb626738</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Williamsville, NY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1535cff1bb626738</t>
+          <t>https://www.indeed.com/viewjob?jk=37a520fdd5e099b9</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Williamsville, NY, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37a520fdd5e099b9</t>
+          <t>https://www.indeed.com/viewjob?jk=366fcdfb585bd3be</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=366fcdfb585bd3be</t>
+          <t>https://www.indeed.com/viewjob?jk=a94f1ea7f43f3649</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a94f1ea7f43f3649</t>
+          <t>https://www.indeed.com/viewjob?jk=497b07468d401d8a</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=497b07468d401d8a</t>
+          <t>https://www.indeed.com/viewjob?jk=8d2e49c364fa4321</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d2e49c364fa4321</t>
+          <t>https://www.indeed.com/viewjob?jk=14d6f7b29ae9eb47</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14d6f7b29ae9eb47</t>
+          <t>https://www.indeed.com/viewjob?jk=e69bf4d69267775a</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e69bf4d69267775a</t>
+          <t>https://www.indeed.com/viewjob?jk=22a4f690926575b6</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22a4f690926575b6</t>
+          <t>https://www.indeed.com/viewjob?jk=7fc8f10cc4340e38</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fc8f10cc4340e38</t>
+          <t>https://www.indeed.com/viewjob?jk=4ed7e30adf2adc59</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ed7e30adf2adc59</t>
+          <t>https://www.indeed.com/viewjob?jk=22efcdd2b4a3dd7f</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22efcdd2b4a3dd7f</t>
+          <t>https://www.indeed.com/viewjob?jk=4d610152102215d5</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d610152102215d5</t>
+          <t>https://www.indeed.com/viewjob?jk=0f093d62f255edad</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f093d62f255edad</t>
+          <t>https://www.indeed.com/viewjob?jk=61c760c7b06ee2ec</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61c760c7b06ee2ec</t>
+          <t>https://www.indeed.com/viewjob?jk=7e753698d58ce405</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e753698d58ce405</t>
+          <t>https://www.indeed.com/viewjob?jk=613c98d34d3a6aff</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=613c98d34d3a6aff</t>
+          <t>https://www.indeed.com/viewjob?jk=81eb38d16909745a</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81eb38d16909745a</t>
+          <t>https://www.indeed.com/viewjob?jk=26aa4bbb65d7bc04</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26aa4bbb65d7bc04</t>
+          <t>https://www.indeed.com/viewjob?jk=51eaf011bd4b3db9</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51eaf011bd4b3db9</t>
+          <t>https://www.indeed.com/viewjob?jk=875b54845cacd6b4</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=875b54845cacd6b4</t>
+          <t>https://www.indeed.com/viewjob?jk=b044118f339aeefe</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b044118f339aeefe</t>
+          <t>https://www.indeed.com/viewjob?jk=79172907c08cbd27</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79172907c08cbd27</t>
+          <t>https://www.indeed.com/viewjob?jk=4072dd1e7bd9b46a</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4072dd1e7bd9b46a</t>
+          <t>https://www.indeed.com/viewjob?jk=60e28bece0970c90</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60e28bece0970c90</t>
+          <t>https://www.indeed.com/viewjob?jk=337e00bdabbbf617</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=337e00bdabbbf617</t>
+          <t>https://www.indeed.com/viewjob?jk=7008c23fbe380180</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7008c23fbe380180</t>
+          <t>https://www.indeed.com/viewjob?jk=ef94cdec933bb8d2</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef94cdec933bb8d2</t>
+          <t>https://www.indeed.com/viewjob?jk=a9b3dd72c73a5c59</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>San Juan, PR, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9b3dd72c73a5c59</t>
+          <t>https://www.indeed.com/viewjob?jk=3f362104fdb5fce0</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>San Juan, PR, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f362104fdb5fce0</t>
+          <t>https://www.indeed.com/viewjob?jk=bb3766965503e1b0</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb3766965503e1b0</t>
+          <t>https://www.indeed.com/viewjob?jk=01b7efd6177971eb</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01b7efd6177971eb</t>
+          <t>https://www.indeed.com/viewjob?jk=564843cdd5d6c05d</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=564843cdd5d6c05d</t>
+          <t>https://www.indeed.com/viewjob?jk=38dc1e892863874b</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38dc1e892863874b</t>
+          <t>https://www.indeed.com/viewjob?jk=36375563a2ad1043</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Honolulu, HI, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36375563a2ad1043</t>
+          <t>https://www.indeed.com/viewjob?jk=cf1ab598617115f3</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Honolulu, HI, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf1ab598617115f3</t>
+          <t>https://www.indeed.com/viewjob?jk=bdb4d76e4c3be44c</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdb4d76e4c3be44c</t>
+          <t>https://www.indeed.com/viewjob?jk=bd706eccacda1e1c</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd706eccacda1e1c</t>
+          <t>https://www.indeed.com/viewjob?jk=606f854062c681fa</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606f854062c681fa</t>
+          <t>https://www.indeed.com/viewjob?jk=15ee32196b2a250e</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15ee32196b2a250e</t>
+          <t>https://www.indeed.com/viewjob?jk=c7a2ced0233034b8</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7a2ced0233034b8</t>
+          <t>https://www.indeed.com/viewjob?jk=b267004acbc01cc5</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b267004acbc01cc5</t>
+          <t>https://www.indeed.com/viewjob?jk=9be2810504f2ae29</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9be2810504f2ae29</t>
+          <t>https://www.indeed.com/viewjob?jk=6f0ec602c9b09a8e</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f0ec602c9b09a8e</t>
+          <t>https://www.indeed.com/viewjob?jk=bd0e7d3dab7e604a</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd0e7d3dab7e604a</t>
+          <t>https://www.indeed.com/viewjob?jk=905c5a2344562ab8</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=905c5a2344562ab8</t>
+          <t>https://www.indeed.com/viewjob?jk=21b0eb74cf57c4a8</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Monterey, CA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21b0eb74cf57c4a8</t>
+          <t>https://www.indeed.com/viewjob?jk=127db1667ff89227</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Monterey, CA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127db1667ff89227</t>
+          <t>https://www.indeed.com/viewjob?jk=2a42559421200137</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a42559421200137</t>
+          <t>https://www.indeed.com/viewjob?jk=d6e7dd724c924aca</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6e7dd724c924aca</t>
+          <t>https://www.indeed.com/viewjob?jk=8483d29d2dbde05b</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8483d29d2dbde05b</t>
+          <t>https://www.indeed.com/viewjob?jk=824e663391dfa6bf</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=824e663391dfa6bf</t>
+          <t>https://www.indeed.com/viewjob?jk=3e8686e8d16dc84d</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e8686e8d16dc84d</t>
+          <t>https://www.indeed.com/viewjob?jk=496d9926f80e93e9</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=496d9926f80e93e9</t>
+          <t>https://www.indeed.com/viewjob?jk=57716cf6ab6ed7a5</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57716cf6ab6ed7a5</t>
+          <t>https://www.indeed.com/viewjob?jk=c418229c0f650f96</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c418229c0f650f96</t>
+          <t>https://www.indeed.com/viewjob?jk=95121729962d91d2</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95121729962d91d2</t>
+          <t>https://www.indeed.com/viewjob?jk=dfec58f9b4c8760a</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfec58f9b4c8760a</t>
+          <t>https://www.indeed.com/viewjob?jk=5153281c36740802</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5153281c36740802</t>
+          <t>https://www.indeed.com/viewjob?jk=310acaaa4f9f42e3</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=310acaaa4f9f42e3</t>
+          <t>https://www.indeed.com/viewjob?jk=6efe7ed3911371c4</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6efe7ed3911371c4</t>
+          <t>https://www.indeed.com/viewjob?jk=1a68cf132dbdec60</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a68cf132dbdec60</t>
+          <t>https://www.indeed.com/viewjob?jk=8d891e75a79397a9</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d891e75a79397a9</t>
+          <t>https://www.indeed.com/viewjob?jk=117634e8f8dfb2d6</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=117634e8f8dfb2d6</t>
+          <t>https://www.indeed.com/viewjob?jk=b83a26f124ccdb89</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b83a26f124ccdb89</t>
+          <t>https://www.indeed.com/viewjob?jk=ad88505e172120de</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad88505e172120de</t>
+          <t>https://www.indeed.com/viewjob?jk=c21ad262bec7ef80</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c21ad262bec7ef80</t>
+          <t>https://www.indeed.com/viewjob?jk=ca6810d972b1a5f1</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca6810d972b1a5f1</t>
+          <t>https://www.indeed.com/viewjob?jk=27043ef345d0b8a7</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27043ef345d0b8a7</t>
+          <t>https://www.indeed.com/viewjob?jk=be347b278f12cb33</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be347b278f12cb33</t>
+          <t>https://www.indeed.com/viewjob?jk=fed8b15c04492576</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fed8b15c04492576</t>
+          <t>https://www.indeed.com/viewjob?jk=5b12133504b24bae</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b12133504b24bae</t>
+          <t>https://www.indeed.com/viewjob?jk=9f864d9aca9b7b27</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f864d9aca9b7b27</t>
+          <t>https://www.indeed.com/viewjob?jk=76d2eb1be4c1b252</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76d2eb1be4c1b252</t>
+          <t>https://www.indeed.com/viewjob?jk=9baba2b401f1c56c</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Platform (Azure)</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform, Azure Monitor</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9baba2b401f1c56c</t>
+          <t>https://www.indeed.com/viewjob?jk=defb19c3b807f7fd</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Platform (Azure)</t>
+          <t>Enterprise Data Architect - WORK FROM HOME - SELECT US STATES ONLY</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Slavic401K</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform, Azure Monitor</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,24 +5466,24 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=defb19c3b807f7fd</t>
+          <t>https://www.indeed.com/viewjob?jk=df39dd0505c33d32</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect - WORK FROM HOME - SELECT US STATES ONLY</t>
+          <t>Databricks Developer</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Slavic401K</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,24 +5501,24 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df39dd0505c33d32</t>
+          <t>https://www.indeed.com/viewjob?jk=ab1192abfbd7f24e</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Software Engineer - Vehicle Connectivity &amp; mobility (VC&amp;M)</t>
+          <t>Databricks Developer</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,24 +5536,24 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14f272fafe4eb2bc</t>
+          <t>https://www.indeed.com/viewjob?jk=320dcd4f927cb250</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Databricks Developer</t>
+          <t>Software Engineer - Vehicle Connectivity &amp; mobility (VC&amp;M)</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5571,24 +5571,24 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab1192abfbd7f24e</t>
+          <t>https://www.indeed.com/viewjob?jk=14f272fafe4eb2bc</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Databricks Developer</t>
+          <t>Senior Quality Engineering (QE) Engineer</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Amida Technology Solutions</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Power BI, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5606,32 +5606,32 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=320dcd4f927cb250</t>
+          <t>https://www.indeed.com/viewjob?jk=29a7f8ff4391f120</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Senior Quality Engineering (QE) Engineer</t>
+          <t>Associate, Data Engineer</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Amida Technology Solutions</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Power BI, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, DynamoDB, Azure Cosmos DB, NoSQL</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5641,24 +5641,24 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29a7f8ff4391f120</t>
+          <t>https://www.indeed.com/viewjob?jk=06fd6810514e5491</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Associate, Data Engineer</t>
+          <t>Data Anchor</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, DynamoDB, Azure Cosmos DB, NoSQL</t>
+          <t>RDS, GCP, BigQuery, Vertex AI, Hadoop, Spark, Kafka, MongoDB, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5676,24 +5676,24 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06fd6810514e5491</t>
+          <t>https://www.indeed.com/viewjob?jk=3db1969fc986c5bb</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Data Anchor</t>
+          <t>Data Engineer - Oklahoma City, OK</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>CFS Brands, LLC</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Vertex AI, Hadoop, Spark, Kafka, MongoDB, NoSQL, Splunk</t>
+          <t>IAM, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -5711,24 +5711,24 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3db1969fc986c5bb</t>
+          <t>https://www.indeed.com/viewjob?jk=113fe7e3580ec298</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Data Engineer - Oklahoma City, OK</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>CFS Brands, LLC</t>
+          <t>Chiesi Farmaceutici S.p.A.</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5736,34 +5736,34 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>IAM, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=113fe7e3580ec298</t>
+          <t>https://www.indeed.com/viewjob?jk=78d407207abb7498</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Apache Spark Core Java</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Chiesi Farmaceutici S.p.A.</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5771,34 +5771,34 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78d407207abb7498</t>
+          <t>https://www.indeed.com/viewjob?jk=16d16eda2d514586</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Apache Spark Core Java</t>
+          <t>Senior Analytics Engineer, Marketing Sciences</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>SimplePractice</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5806,34 +5806,34 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, RDS, Scala, Kafka, Snowflake, ETL, dbt, Terraform, Docker</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16d16eda2d514586</t>
+          <t>https://www.indeed.com/viewjob?jk=4a341479dc01b56f</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Marketing Sciences</t>
+          <t>Senior Full Stack Engineer, Agent Experience Platform</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>SimplePractice</t>
+          <t>MAPFRE Insurance</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Webster, MA, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Scala, Kafka, Snowflake, ETL, dbt, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, DynamoDB, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -5851,24 +5851,24 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a341479dc01b56f</t>
+          <t>https://www.indeed.com/viewjob?jk=73664071b95987ff</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer, Agent Experience Platform</t>
+          <t>.NET Backend Developer</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>MAPFRE Insurance</t>
+          <t>Inclusion Cloud</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Webster, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, DynamoDB, CI/CD, Docker</t>
+          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -5886,24 +5886,24 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73664071b95987ff</t>
+          <t>https://www.indeed.com/viewjob?jk=5c9d1b0d1d29e0d2</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>.NET Backend Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Inclusion Cloud</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Allen Park, MI, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -5920,41 +5920,6 @@
         </is>
       </c>
       <c r="G157" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5c9d1b0d1d29e0d2</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>Ford Motor Company</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>Allen Park, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D158" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, CI/CD, Terraform, Git</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=5cb7a428029c6a47</t>
         </is>

--- a/results/job_matches_2026-08-22.xlsx
+++ b/results/job_matches_2026-08-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G157"/>
+  <dimension ref="A1:G156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1728,17 +1728,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Cloud Engineer; Platform Analytics (Contract)</t>
+          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Platform (AWS)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Vervint</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, S3, SQS, IAM, RDS</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c0847cb6bf1b0e8</t>
+          <t>https://www.indeed.com/viewjob?jk=7064a0875d5078f8</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Platform (AWS)</t>
+          <t>Full Stack Developer - Advanced | Columbus, US</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Vertex AI, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7064a0875d5078f8</t>
+          <t>https://www.indeed.com/viewjob?jk=865f8a104cb006d1</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Advanced | Columbus, US</t>
+          <t>Sr Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Vertex AI, Scala, Kafka, NoSQL</t>
+          <t>AWS, Redshift, S3, Spark, Scala, Kafka, Snowflake, DynamoDB, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=865f8a104cb006d1</t>
+          <t>https://www.indeed.com/viewjob?jk=766cfaa008af94ec</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr Machine Learning Engineer</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Spark, Scala, Kafka, Snowflake, DynamoDB, NoSQL, MLOps</t>
+          <t>AWS, EMR, Kinesis, S3, RDS, Spark, Scala, PostgreSQL, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=766cfaa008af94ec</t>
+          <t>https://www.indeed.com/viewjob?jk=5d1eabd20620b211</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Senior Devops Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, S3, RDS, Spark, Scala, PostgreSQL, NoSQL, Jenkins</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d1eabd20620b211</t>
+          <t>https://www.indeed.com/viewjob?jk=143f81631e970888</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II</t>
+          <t>Senior Full stack Java / AWS</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>7-Eleven</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Power BI, Tableau, MLOps</t>
+          <t>AWS, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,19 +1931,19 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ef1c00bbfcfa5af</t>
+          <t>https://www.indeed.com/viewjob?jk=648c04000182f970</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Devops Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>SelectQuote</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1956,42 +1956,42 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, SQL Server, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=143f81631e970888</t>
+          <t>https://www.indeed.com/viewjob?jk=23f04a50e41c3404</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Full stack Java / AWS</t>
+          <t>Azure IoT Solutions Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Ascend Technologies</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL, DynamoDB, CI/CD</t>
+          <t>RDS, Azure, Event Hubs, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,59 +2001,59 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=648c04000182f970</t>
+          <t>https://www.indeed.com/viewjob?jk=48463a0b2c1a516b</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SelectQuote</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, SQL Server, ETL, ELT, Airflow</t>
+          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23f04a50e41c3404</t>
+          <t>https://www.indeed.com/viewjob?jk=6b7cc426dbd03f0e</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Azure IoT Solutions Engineer</t>
+          <t>Economic Data System Engineer/Sr. Economic Data System Engineer-ITDDPED</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Ascend Technologies</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AKS, Jenkins</t>
+          <t>RDS, Databricks, BigQuery, Hadoop, Spark, Scala, Snowflake, NoSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48463a0b2c1a516b</t>
+          <t>https://www.indeed.com/viewjob?jk=3a32b2285f6e0f19</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>GCP Cloud Engineer</t>
+          <t>Data Engineer Denodo</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Flowserve</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD, Terraform, Docker</t>
+          <t>Azure, Synapse Analytics, Databricks, Scala, Snowflake, Oracle, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,14 +2106,14 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b7cc426dbd03f0e</t>
+          <t>https://www.indeed.com/viewjob?jk=b87d344718e073fe</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Economic Data System Engineer/Sr. Economic Data System Engineer-ITDDPED</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Hadoop, Spark, Scala, Snowflake, NoSQL, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a32b2285f6e0f19</t>
+          <t>https://www.indeed.com/viewjob?jk=ae435ef03aa1b3c0</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer Denodo</t>
+          <t>QA Automation Engineer II, Officer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Flowserve</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Databricks, Scala, Snowflake, Oracle, SQL Server, ETL, ELT, Power BI</t>
+          <t>RDS, Scala, Oracle, NoSQL, Talend, CI/CD, Jenkins, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b87d344718e073fe</t>
+          <t>https://www.indeed.com/viewjob?jk=1d73747fd9aafef8</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Mercari</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Tableau</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae435ef03aa1b3c0</t>
+          <t>https://www.indeed.com/viewjob?jk=179685542a7cf944</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>QA Automation Engineer II, Officer</t>
+          <t>Sr Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>Pilot Flying J</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>Roswell, GA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, NoSQL, Talend, CI/CD, Jenkins, Docker, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d73747fd9aafef8</t>
+          <t>https://www.indeed.com/viewjob?jk=0a70d5a50e3bc2a5</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Mercari</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Tableau</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Kafka, CI/CD, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=179685542a7cf944</t>
+          <t>https://www.indeed.com/viewjob?jk=9a5cbb62cc968f68</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr Engineer, Data Engineering</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Pilot Flying J</t>
+          <t>Marathon Petroleum</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Roswell, GA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a70d5a50e3bc2a5</t>
+          <t>https://www.indeed.com/viewjob?jk=28293fa77ffc32bb</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Golden State</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Kafka, CI/CD, Terraform, Kubernetes, AKS</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a5cbb62cc968f68</t>
+          <t>https://www.indeed.com/viewjob?jk=1d156f80ddb5ea3e</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Marathon Petroleum</t>
+          <t>American Tower</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, CI/CD, Git, Python, SQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28293fa77ffc32bb</t>
+          <t>https://www.indeed.com/viewjob?jk=340f3540cd359821</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer – Advanced Data Integration &amp; Cloud Solutions</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Golden State</t>
+          <t>Everforth ECS</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>ECS, RDS, Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, ETL, Python, SQL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d156f80ddb5ea3e</t>
+          <t>https://www.indeed.com/viewjob?jk=ca1d4ee2bfb7f383</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Engineer/DevOps Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>American Tower</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, Splunk, CI/CD, Azure DevOps, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=340f3540cd359821</t>
+          <t>https://www.indeed.com/viewjob?jk=a4e19bdfcdfa54e3</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Advanced Data Integration &amp; Cloud Solutions</t>
+          <t>Senior Analyst, Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Everforth ECS</t>
+          <t>Lincoln Electric</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, ETL, Python, SQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca1d4ee2bfb7f383</t>
+          <t>https://www.indeed.com/viewjob?jk=8382e0121c068a19</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AI Engineer/DevOps Engineer</t>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, Splunk, CI/CD, Azure DevOps, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4e19bdfcdfa54e3</t>
+          <t>https://www.indeed.com/viewjob?jk=f4ab3e3c7077492c</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Analyst, Data Engineer</t>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Lincoln Electric</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Inglewood, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8382e0121c068a19</t>
+          <t>https://www.indeed.com/viewjob?jk=b0870a8c631ca3e7</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4ab3e3c7077492c</t>
+          <t>https://www.indeed.com/viewjob?jk=3a8177305c7e2b4e</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Inglewood, CA, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0870a8c631ca3e7</t>
+          <t>https://www.indeed.com/viewjob?jk=2b216035065cdcce</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a8177305c7e2b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=b0d6bbe5db7dc4e3</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b216035065cdcce</t>
+          <t>https://www.indeed.com/viewjob?jk=99cd5dc3d4c47201</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0d6bbe5db7dc4e3</t>
+          <t>https://www.indeed.com/viewjob?jk=1535cff1bb626738</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Williamsville, NY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99cd5dc3d4c47201</t>
+          <t>https://www.indeed.com/viewjob?jk=37a520fdd5e099b9</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1535cff1bb626738</t>
+          <t>https://www.indeed.com/viewjob?jk=366fcdfb585bd3be</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Williamsville, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37a520fdd5e099b9</t>
+          <t>https://www.indeed.com/viewjob?jk=a94f1ea7f43f3649</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=366fcdfb585bd3be</t>
+          <t>https://www.indeed.com/viewjob?jk=497b07468d401d8a</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a94f1ea7f43f3649</t>
+          <t>https://www.indeed.com/viewjob?jk=8d2e49c364fa4321</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=497b07468d401d8a</t>
+          <t>https://www.indeed.com/viewjob?jk=14d6f7b29ae9eb47</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d2e49c364fa4321</t>
+          <t>https://www.indeed.com/viewjob?jk=e69bf4d69267775a</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14d6f7b29ae9eb47</t>
+          <t>https://www.indeed.com/viewjob?jk=22a4f690926575b6</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e69bf4d69267775a</t>
+          <t>https://www.indeed.com/viewjob?jk=7fc8f10cc4340e38</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22a4f690926575b6</t>
+          <t>https://www.indeed.com/viewjob?jk=4ed7e30adf2adc59</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fc8f10cc4340e38</t>
+          <t>https://www.indeed.com/viewjob?jk=22efcdd2b4a3dd7f</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ed7e30adf2adc59</t>
+          <t>https://www.indeed.com/viewjob?jk=4d610152102215d5</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22efcdd2b4a3dd7f</t>
+          <t>https://www.indeed.com/viewjob?jk=0f093d62f255edad</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d610152102215d5</t>
+          <t>https://www.indeed.com/viewjob?jk=61c760c7b06ee2ec</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f093d62f255edad</t>
+          <t>https://www.indeed.com/viewjob?jk=7e753698d58ce405</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61c760c7b06ee2ec</t>
+          <t>https://www.indeed.com/viewjob?jk=613c98d34d3a6aff</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e753698d58ce405</t>
+          <t>https://www.indeed.com/viewjob?jk=81eb38d16909745a</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=613c98d34d3a6aff</t>
+          <t>https://www.indeed.com/viewjob?jk=26aa4bbb65d7bc04</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81eb38d16909745a</t>
+          <t>https://www.indeed.com/viewjob?jk=51eaf011bd4b3db9</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26aa4bbb65d7bc04</t>
+          <t>https://www.indeed.com/viewjob?jk=875b54845cacd6b4</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51eaf011bd4b3db9</t>
+          <t>https://www.indeed.com/viewjob?jk=b044118f339aeefe</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=875b54845cacd6b4</t>
+          <t>https://www.indeed.com/viewjob?jk=79172907c08cbd27</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b044118f339aeefe</t>
+          <t>https://www.indeed.com/viewjob?jk=4072dd1e7bd9b46a</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79172907c08cbd27</t>
+          <t>https://www.indeed.com/viewjob?jk=60e28bece0970c90</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4072dd1e7bd9b46a</t>
+          <t>https://www.indeed.com/viewjob?jk=337e00bdabbbf617</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60e28bece0970c90</t>
+          <t>https://www.indeed.com/viewjob?jk=7008c23fbe380180</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=337e00bdabbbf617</t>
+          <t>https://www.indeed.com/viewjob?jk=ef94cdec933bb8d2</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7008c23fbe380180</t>
+          <t>https://www.indeed.com/viewjob?jk=a9b3dd72c73a5c59</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>San Juan, PR, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef94cdec933bb8d2</t>
+          <t>https://www.indeed.com/viewjob?jk=3f362104fdb5fce0</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9b3dd72c73a5c59</t>
+          <t>https://www.indeed.com/viewjob?jk=bb3766965503e1b0</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>San Juan, PR, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f362104fdb5fce0</t>
+          <t>https://www.indeed.com/viewjob?jk=01b7efd6177971eb</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb3766965503e1b0</t>
+          <t>https://www.indeed.com/viewjob?jk=564843cdd5d6c05d</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01b7efd6177971eb</t>
+          <t>https://www.indeed.com/viewjob?jk=38dc1e892863874b</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=564843cdd5d6c05d</t>
+          <t>https://www.indeed.com/viewjob?jk=36375563a2ad1043</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Honolulu, HI, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38dc1e892863874b</t>
+          <t>https://www.indeed.com/viewjob?jk=cf1ab598617115f3</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36375563a2ad1043</t>
+          <t>https://www.indeed.com/viewjob?jk=bdb4d76e4c3be44c</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Honolulu, HI, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf1ab598617115f3</t>
+          <t>https://www.indeed.com/viewjob?jk=bd706eccacda1e1c</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdb4d76e4c3be44c</t>
+          <t>https://www.indeed.com/viewjob?jk=606f854062c681fa</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd706eccacda1e1c</t>
+          <t>https://www.indeed.com/viewjob?jk=15ee32196b2a250e</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606f854062c681fa</t>
+          <t>https://www.indeed.com/viewjob?jk=c7a2ced0233034b8</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15ee32196b2a250e</t>
+          <t>https://www.indeed.com/viewjob?jk=b267004acbc01cc5</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7a2ced0233034b8</t>
+          <t>https://www.indeed.com/viewjob?jk=9be2810504f2ae29</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b267004acbc01cc5</t>
+          <t>https://www.indeed.com/viewjob?jk=6f0ec602c9b09a8e</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9be2810504f2ae29</t>
+          <t>https://www.indeed.com/viewjob?jk=bd0e7d3dab7e604a</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f0ec602c9b09a8e</t>
+          <t>https://www.indeed.com/viewjob?jk=905c5a2344562ab8</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd0e7d3dab7e604a</t>
+          <t>https://www.indeed.com/viewjob?jk=21b0eb74cf57c4a8</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Monterey, CA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=905c5a2344562ab8</t>
+          <t>https://www.indeed.com/viewjob?jk=127db1667ff89227</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21b0eb74cf57c4a8</t>
+          <t>https://www.indeed.com/viewjob?jk=2a42559421200137</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Monterey, CA, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127db1667ff89227</t>
+          <t>https://www.indeed.com/viewjob?jk=d6e7dd724c924aca</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a42559421200137</t>
+          <t>https://www.indeed.com/viewjob?jk=8483d29d2dbde05b</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6e7dd724c924aca</t>
+          <t>https://www.indeed.com/viewjob?jk=824e663391dfa6bf</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8483d29d2dbde05b</t>
+          <t>https://www.indeed.com/viewjob?jk=3e8686e8d16dc84d</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=824e663391dfa6bf</t>
+          <t>https://www.indeed.com/viewjob?jk=496d9926f80e93e9</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e8686e8d16dc84d</t>
+          <t>https://www.indeed.com/viewjob?jk=57716cf6ab6ed7a5</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=496d9926f80e93e9</t>
+          <t>https://www.indeed.com/viewjob?jk=c418229c0f650f96</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57716cf6ab6ed7a5</t>
+          <t>https://www.indeed.com/viewjob?jk=95121729962d91d2</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c418229c0f650f96</t>
+          <t>https://www.indeed.com/viewjob?jk=dfec58f9b4c8760a</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95121729962d91d2</t>
+          <t>https://www.indeed.com/viewjob?jk=5153281c36740802</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfec58f9b4c8760a</t>
+          <t>https://www.indeed.com/viewjob?jk=310acaaa4f9f42e3</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5153281c36740802</t>
+          <t>https://www.indeed.com/viewjob?jk=6efe7ed3911371c4</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=310acaaa4f9f42e3</t>
+          <t>https://www.indeed.com/viewjob?jk=1a68cf132dbdec60</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6efe7ed3911371c4</t>
+          <t>https://www.indeed.com/viewjob?jk=8d891e75a79397a9</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a68cf132dbdec60</t>
+          <t>https://www.indeed.com/viewjob?jk=117634e8f8dfb2d6</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d891e75a79397a9</t>
+          <t>https://www.indeed.com/viewjob?jk=b83a26f124ccdb89</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=117634e8f8dfb2d6</t>
+          <t>https://www.indeed.com/viewjob?jk=ad88505e172120de</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b83a26f124ccdb89</t>
+          <t>https://www.indeed.com/viewjob?jk=c21ad262bec7ef80</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad88505e172120de</t>
+          <t>https://www.indeed.com/viewjob?jk=ca6810d972b1a5f1</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c21ad262bec7ef80</t>
+          <t>https://www.indeed.com/viewjob?jk=27043ef345d0b8a7</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca6810d972b1a5f1</t>
+          <t>https://www.indeed.com/viewjob?jk=be347b278f12cb33</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27043ef345d0b8a7</t>
+          <t>https://www.indeed.com/viewjob?jk=fed8b15c04492576</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be347b278f12cb33</t>
+          <t>https://www.indeed.com/viewjob?jk=5b12133504b24bae</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fed8b15c04492576</t>
+          <t>https://www.indeed.com/viewjob?jk=9f864d9aca9b7b27</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b12133504b24bae</t>
+          <t>https://www.indeed.com/viewjob?jk=76d2eb1be4c1b252</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f864d9aca9b7b27</t>
+          <t>https://www.indeed.com/viewjob?jk=9baba2b401f1c56c</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Platform (Azure)</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform, Azure Monitor</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76d2eb1be4c1b252</t>
+          <t>https://www.indeed.com/viewjob?jk=defb19c3b807f7fd</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+          <t>Enterprise Data Architect - WORK FROM HOME - SELECT US STATES ONLY</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Slavic401K</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9baba2b401f1c56c</t>
+          <t>https://www.indeed.com/viewjob?jk=df39dd0505c33d32</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Platform (Azure)</t>
+          <t>Software Engineer - Vehicle Connectivity &amp; mobility (VC&amp;M)</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform, Azure Monitor</t>
+          <t>RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=defb19c3b807f7fd</t>
+          <t>https://www.indeed.com/viewjob?jk=14f272fafe4eb2bc</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect - WORK FROM HOME - SELECT US STATES ONLY</t>
+          <t>Databricks Developer</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Slavic401K</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df39dd0505c33d32</t>
+          <t>https://www.indeed.com/viewjob?jk=ab1192abfbd7f24e</t>
         </is>
       </c>
     </row>
@@ -5501,24 +5501,24 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab1192abfbd7f24e</t>
+          <t>https://www.indeed.com/viewjob?jk=320dcd4f927cb250</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Databricks Developer</t>
+          <t>Senior Quality Engineering (QE) Engineer</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Amida Technology Solutions</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Power BI, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,32 +5536,32 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=320dcd4f927cb250</t>
+          <t>https://www.indeed.com/viewjob?jk=29a7f8ff4391f120</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Software Engineer - Vehicle Connectivity &amp; mobility (VC&amp;M)</t>
+          <t>Associate, Data Engineer</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, DynamoDB, Azure Cosmos DB, NoSQL</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5571,32 +5571,32 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14f272fafe4eb2bc</t>
+          <t>https://www.indeed.com/viewjob?jk=06fd6810514e5491</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Senior Quality Engineering (QE) Engineer</t>
+          <t>Data Anchor</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Amida Technology Solutions</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Power BI, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>RDS, GCP, BigQuery, Vertex AI, Hadoop, Spark, Kafka, MongoDB, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5606,24 +5606,24 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29a7f8ff4391f120</t>
+          <t>https://www.indeed.com/viewjob?jk=3db1969fc986c5bb</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Associate, Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, DynamoDB, Azure Cosmos DB, NoSQL</t>
+          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5641,24 +5641,24 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06fd6810514e5491</t>
+          <t>https://www.indeed.com/viewjob?jk=33b30501746ad4bf</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Data Anchor</t>
+          <t>Data Engineer - Oklahoma City, OK</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>CFS Brands, LLC</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Vertex AI, Hadoop, Spark, Kafka, MongoDB, NoSQL, Splunk</t>
+          <t>IAM, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5676,24 +5676,24 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3db1969fc986c5bb</t>
+          <t>https://www.indeed.com/viewjob?jk=113fe7e3580ec298</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Data Engineer - Oklahoma City, OK</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>CFS Brands, LLC</t>
+          <t>Chiesi Farmaceutici S.p.A.</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5701,34 +5701,34 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>IAM, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=113fe7e3580ec298</t>
+          <t>https://www.indeed.com/viewjob?jk=78d407207abb7498</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Apache Spark Core Java</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Chiesi Farmaceutici S.p.A.</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5736,34 +5736,34 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78d407207abb7498</t>
+          <t>https://www.indeed.com/viewjob?jk=16d16eda2d514586</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Apache Spark Core Java</t>
+          <t>Senior Analytics Engineer, Marketing Sciences</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>SimplePractice</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5771,34 +5771,34 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, RDS, Scala, Kafka, Snowflake, ETL, dbt, Terraform, Docker</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16d16eda2d514586</t>
+          <t>https://www.indeed.com/viewjob?jk=4a341479dc01b56f</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Marketing Sciences</t>
+          <t>Senior Full Stack Engineer, Agent Experience Platform</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>SimplePractice</t>
+          <t>MAPFRE Insurance</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Webster, MA, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Scala, Kafka, Snowflake, ETL, dbt, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, DynamoDB, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -5816,24 +5816,24 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a341479dc01b56f</t>
+          <t>https://www.indeed.com/viewjob?jk=73664071b95987ff</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer, Agent Experience Platform</t>
+          <t>.NET Backend Developer</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>MAPFRE Insurance</t>
+          <t>Inclusion Cloud</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Webster, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, DynamoDB, CI/CD, Docker</t>
+          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -5851,24 +5851,24 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73664071b95987ff</t>
+          <t>https://www.indeed.com/viewjob?jk=5c9d1b0d1d29e0d2</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>.NET Backend Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Inclusion Cloud</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Allen Park, MI, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -5885,41 +5885,6 @@
         </is>
       </c>
       <c r="G156" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5c9d1b0d1d29e0d2</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>Ford Motor Company</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>Allen Park, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D157" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, CI/CD, Terraform, Git</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=5cb7a428029c6a47</t>
         </is>

--- a/results/job_matches_2026-08-22.xlsx
+++ b/results/job_matches_2026-08-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G156"/>
+  <dimension ref="A1:G154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1098,17 +1098,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr Full stack Java Developer</t>
+          <t>Software Engineer, Full Stack - AI (New York)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Hudson Manpower</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50c5bf2319077628</t>
+          <t>https://www.indeed.com/viewjob?jk=362603547d1c2a0d</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=603c61b7cc5fe1b9</t>
+          <t>https://www.indeed.com/viewjob?jk=50c5bf2319077628</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Allentown, PA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7340ebb5e99bf41f</t>
+          <t>https://www.indeed.com/viewjob?jk=603c61b7cc5fe1b9</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Allentown, PA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7bb7609c20e949e</t>
+          <t>https://www.indeed.com/viewjob?jk=7340ebb5e99bf41f</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer, Full Stack - AI (New York)</t>
+          <t>Sr Full stack Java Developer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Fitch Group</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
+          <t>AWS, S3, API Gateway, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=362603547d1c2a0d</t>
+          <t>https://www.indeed.com/viewjob?jk=e7bb7609c20e949e</t>
         </is>
       </c>
     </row>
@@ -1693,17 +1693,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Platform (AWS)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, CI/CD</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8209ae3042e1b9a9</t>
+          <t>https://www.indeed.com/viewjob?jk=7064a0875d5078f8</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Platform (AWS)</t>
+          <t>Full Stack Developer - Advanced | Columbus, US</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Vertex AI, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7064a0875d5078f8</t>
+          <t>https://www.indeed.com/viewjob?jk=865f8a104cb006d1</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Advanced | Columbus, US</t>
+          <t>Sr Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Vertex AI, Scala, Kafka, NoSQL</t>
+          <t>AWS, Redshift, S3, Spark, Scala, Kafka, Snowflake, DynamoDB, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=865f8a104cb006d1</t>
+          <t>https://www.indeed.com/viewjob?jk=766cfaa008af94ec</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr Machine Learning Engineer</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Spark, Scala, Kafka, Snowflake, DynamoDB, NoSQL, MLOps</t>
+          <t>AWS, EMR, Kinesis, S3, RDS, Spark, Scala, PostgreSQL, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=766cfaa008af94ec</t>
+          <t>https://www.indeed.com/viewjob?jk=5d1eabd20620b211</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Senior Professional Services Consultant</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Ataccama</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, S3, RDS, Spark, Scala, PostgreSQL, NoSQL, Jenkins</t>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d1eabd20620b211</t>
+          <t>https://www.indeed.com/viewjob?jk=0f49a3f3dbcbca27</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Devops Engineer</t>
+          <t>CDP Architect</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Bounteous</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=143f81631e970888</t>
+          <t>https://www.indeed.com/viewjob?jk=f5b99e7a77983415</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Full stack Java / AWS</t>
+          <t>Senior Devops Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL, DynamoDB, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=648c04000182f970</t>
+          <t>https://www.indeed.com/viewjob?jk=143f81631e970888</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Full stack Java / AWS</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SelectQuote</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,29 +1956,29 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, SQL Server, ETL, ELT, Airflow</t>
+          <t>AWS, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23f04a50e41c3404</t>
+          <t>https://www.indeed.com/viewjob?jk=648c04000182f970</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Azure IoT Solutions Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Ascend Technologies</t>
+          <t>SelectQuote</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1987,38 +1987,38 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AKS, Jenkins</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, SQL Server, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48463a0b2c1a516b</t>
+          <t>https://www.indeed.com/viewjob?jk=23f04a50e41c3404</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>GCP Cloud Engineer</t>
+          <t>Azure IoT Solutions Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Ascend Technologies</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Event Hubs, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b7cc426dbd03f0e</t>
+          <t>https://www.indeed.com/viewjob?jk=48463a0b2c1a516b</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Economic Data System Engineer/Sr. Economic Data System Engineer-ITDDPED</t>
+          <t>GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Hadoop, Spark, Scala, Snowflake, NoSQL, ETL, ELT</t>
+          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a32b2285f6e0f19</t>
+          <t>https://www.indeed.com/viewjob?jk=6b7cc426dbd03f0e</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer Denodo</t>
+          <t>Economic Data System Engineer/Sr. Economic Data System Engineer-ITDDPED</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Flowserve</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Databricks, Scala, Snowflake, Oracle, SQL Server, ETL, ELT, Power BI</t>
+          <t>RDS, Databricks, BigQuery, Hadoop, Spark, Scala, Snowflake, NoSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b87d344718e073fe</t>
+          <t>https://www.indeed.com/viewjob?jk=3a32b2285f6e0f19</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer Denodo</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Flowserve</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, CI/CD, Terraform, Docker</t>
+          <t>Azure, Synapse Analytics, Databricks, Scala, Snowflake, Oracle, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae435ef03aa1b3c0</t>
+          <t>https://www.indeed.com/viewjob?jk=b87d344718e073fe</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>QA Automation Engineer II, Officer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, NoSQL, Talend, CI/CD, Jenkins, Docker, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d73747fd9aafef8</t>
+          <t>https://www.indeed.com/viewjob?jk=ae435ef03aa1b3c0</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>QA Automation Engineer II, Officer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Mercari</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Tableau</t>
+          <t>RDS, Scala, Oracle, NoSQL, Talend, CI/CD, Jenkins, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=179685542a7cf944</t>
+          <t>https://www.indeed.com/viewjob?jk=1d73747fd9aafef8</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr Engineer, Data Engineering</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Pilot Flying J</t>
+          <t>Mercari</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Roswell, GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Tableau</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a70d5a50e3bc2a5</t>
+          <t>https://www.indeed.com/viewjob?jk=179685542a7cf944</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Sr Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Pilot Flying J</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Roswell, GA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Kafka, CI/CD, Terraform, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a5cbb62cc968f68</t>
+          <t>https://www.indeed.com/viewjob?jk=0a70d5a50e3bc2a5</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Marathon Petroleum</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, CI/CD, Git, Python, SQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Kafka, CI/CD, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28293fa77ffc32bb</t>
+          <t>https://www.indeed.com/viewjob?jk=9a5cbb62cc968f68</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Golden State</t>
+          <t>Marathon Petroleum</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d156f80ddb5ea3e</t>
+          <t>https://www.indeed.com/viewjob?jk=28293fa77ffc32bb</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>American Tower</t>
+          <t>Golden State</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=340f3540cd359821</t>
+          <t>https://www.indeed.com/viewjob?jk=1d156f80ddb5ea3e</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Advanced Data Integration &amp; Cloud Solutions</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Everforth ECS</t>
+          <t>American Tower</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, ETL, Python, SQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca1d4ee2bfb7f383</t>
+          <t>https://www.indeed.com/viewjob?jk=340f3540cd359821</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AI Engineer/DevOps Engineer</t>
+          <t>Senior Data Engineer – Advanced Data Integration &amp; Cloud Solutions</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Everforth ECS</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, Splunk, CI/CD, Azure DevOps, Kubernetes</t>
+          <t>ECS, RDS, Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, ETL, Python, SQL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4e19bdfcdfa54e3</t>
+          <t>https://www.indeed.com/viewjob?jk=ca1d4ee2bfb7f383</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Analyst, Data Engineer</t>
+          <t>AI Engineer/DevOps Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Lincoln Electric</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, Splunk, CI/CD, Azure DevOps, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8382e0121c068a19</t>
+          <t>https://www.indeed.com/viewjob?jk=a4e19bdfcdfa54e3</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+          <t>Senior Analyst, Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Lincoln Electric</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4ab3e3c7077492c</t>
+          <t>https://www.indeed.com/viewjob?jk=8382e0121c068a19</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Platform (Azure)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Inglewood, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform, Azure Monitor</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0870a8c631ca3e7</t>
+          <t>https://www.indeed.com/viewjob?jk=defb19c3b807f7fd</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+          <t>Enterprise Data Architect - WORK FROM HOME - SELECT US STATES ONLY</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Slavic401K</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a8177305c7e2b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=df39dd0505c33d32</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b216035065cdcce</t>
+          <t>https://www.indeed.com/viewjob?jk=f4ab3e3c7077492c</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Inglewood, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0d6bbe5db7dc4e3</t>
+          <t>https://www.indeed.com/viewjob?jk=b0870a8c631ca3e7</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99cd5dc3d4c47201</t>
+          <t>https://www.indeed.com/viewjob?jk=3a8177305c7e2b4e</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1535cff1bb626738</t>
+          <t>https://www.indeed.com/viewjob?jk=2b216035065cdcce</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Williamsville, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37a520fdd5e099b9</t>
+          <t>https://www.indeed.com/viewjob?jk=b0d6bbe5db7dc4e3</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=366fcdfb585bd3be</t>
+          <t>https://www.indeed.com/viewjob?jk=99cd5dc3d4c47201</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a94f1ea7f43f3649</t>
+          <t>https://www.indeed.com/viewjob?jk=1535cff1bb626738</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Williamsville, NY, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=497b07468d401d8a</t>
+          <t>https://www.indeed.com/viewjob?jk=37a520fdd5e099b9</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d2e49c364fa4321</t>
+          <t>https://www.indeed.com/viewjob?jk=366fcdfb585bd3be</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14d6f7b29ae9eb47</t>
+          <t>https://www.indeed.com/viewjob?jk=a94f1ea7f43f3649</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e69bf4d69267775a</t>
+          <t>https://www.indeed.com/viewjob?jk=497b07468d401d8a</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22a4f690926575b6</t>
+          <t>https://www.indeed.com/viewjob?jk=8d2e49c364fa4321</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fc8f10cc4340e38</t>
+          <t>https://www.indeed.com/viewjob?jk=14d6f7b29ae9eb47</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ed7e30adf2adc59</t>
+          <t>https://www.indeed.com/viewjob?jk=e69bf4d69267775a</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22efcdd2b4a3dd7f</t>
+          <t>https://www.indeed.com/viewjob?jk=22a4f690926575b6</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d610152102215d5</t>
+          <t>https://www.indeed.com/viewjob?jk=7fc8f10cc4340e38</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f093d62f255edad</t>
+          <t>https://www.indeed.com/viewjob?jk=4ed7e30adf2adc59</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61c760c7b06ee2ec</t>
+          <t>https://www.indeed.com/viewjob?jk=22efcdd2b4a3dd7f</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e753698d58ce405</t>
+          <t>https://www.indeed.com/viewjob?jk=4d610152102215d5</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=613c98d34d3a6aff</t>
+          <t>https://www.indeed.com/viewjob?jk=0f093d62f255edad</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81eb38d16909745a</t>
+          <t>https://www.indeed.com/viewjob?jk=61c760c7b06ee2ec</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26aa4bbb65d7bc04</t>
+          <t>https://www.indeed.com/viewjob?jk=7e753698d58ce405</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51eaf011bd4b3db9</t>
+          <t>https://www.indeed.com/viewjob?jk=613c98d34d3a6aff</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=875b54845cacd6b4</t>
+          <t>https://www.indeed.com/viewjob?jk=81eb38d16909745a</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b044118f339aeefe</t>
+          <t>https://www.indeed.com/viewjob?jk=26aa4bbb65d7bc04</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79172907c08cbd27</t>
+          <t>https://www.indeed.com/viewjob?jk=51eaf011bd4b3db9</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4072dd1e7bd9b46a</t>
+          <t>https://www.indeed.com/viewjob?jk=875b54845cacd6b4</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60e28bece0970c90</t>
+          <t>https://www.indeed.com/viewjob?jk=b044118f339aeefe</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=337e00bdabbbf617</t>
+          <t>https://www.indeed.com/viewjob?jk=79172907c08cbd27</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7008c23fbe380180</t>
+          <t>https://www.indeed.com/viewjob?jk=4072dd1e7bd9b46a</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef94cdec933bb8d2</t>
+          <t>https://www.indeed.com/viewjob?jk=60e28bece0970c90</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9b3dd72c73a5c59</t>
+          <t>https://www.indeed.com/viewjob?jk=337e00bdabbbf617</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>San Juan, PR, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f362104fdb5fce0</t>
+          <t>https://www.indeed.com/viewjob?jk=7008c23fbe380180</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb3766965503e1b0</t>
+          <t>https://www.indeed.com/viewjob?jk=ef94cdec933bb8d2</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01b7efd6177971eb</t>
+          <t>https://www.indeed.com/viewjob?jk=a9b3dd72c73a5c59</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>San Juan, PR, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=564843cdd5d6c05d</t>
+          <t>https://www.indeed.com/viewjob?jk=3f362104fdb5fce0</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38dc1e892863874b</t>
+          <t>https://www.indeed.com/viewjob?jk=bb3766965503e1b0</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36375563a2ad1043</t>
+          <t>https://www.indeed.com/viewjob?jk=01b7efd6177971eb</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Honolulu, HI, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf1ab598617115f3</t>
+          <t>https://www.indeed.com/viewjob?jk=564843cdd5d6c05d</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdb4d76e4c3be44c</t>
+          <t>https://www.indeed.com/viewjob?jk=38dc1e892863874b</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd706eccacda1e1c</t>
+          <t>https://www.indeed.com/viewjob?jk=36375563a2ad1043</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Honolulu, HI, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606f854062c681fa</t>
+          <t>https://www.indeed.com/viewjob?jk=cf1ab598617115f3</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15ee32196b2a250e</t>
+          <t>https://www.indeed.com/viewjob?jk=bdb4d76e4c3be44c</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7a2ced0233034b8</t>
+          <t>https://www.indeed.com/viewjob?jk=bd706eccacda1e1c</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b267004acbc01cc5</t>
+          <t>https://www.indeed.com/viewjob?jk=606f854062c681fa</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9be2810504f2ae29</t>
+          <t>https://www.indeed.com/viewjob?jk=15ee32196b2a250e</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f0ec602c9b09a8e</t>
+          <t>https://www.indeed.com/viewjob?jk=c7a2ced0233034b8</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd0e7d3dab7e604a</t>
+          <t>https://www.indeed.com/viewjob?jk=b267004acbc01cc5</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=905c5a2344562ab8</t>
+          <t>https://www.indeed.com/viewjob?jk=9be2810504f2ae29</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21b0eb74cf57c4a8</t>
+          <t>https://www.indeed.com/viewjob?jk=6f0ec602c9b09a8e</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Monterey, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127db1667ff89227</t>
+          <t>https://www.indeed.com/viewjob?jk=bd0e7d3dab7e604a</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a42559421200137</t>
+          <t>https://www.indeed.com/viewjob?jk=905c5a2344562ab8</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6e7dd724c924aca</t>
+          <t>https://www.indeed.com/viewjob?jk=21b0eb74cf57c4a8</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Monterey, CA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8483d29d2dbde05b</t>
+          <t>https://www.indeed.com/viewjob?jk=127db1667ff89227</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=824e663391dfa6bf</t>
+          <t>https://www.indeed.com/viewjob?jk=2a42559421200137</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e8686e8d16dc84d</t>
+          <t>https://www.indeed.com/viewjob?jk=d6e7dd724c924aca</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=496d9926f80e93e9</t>
+          <t>https://www.indeed.com/viewjob?jk=8483d29d2dbde05b</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57716cf6ab6ed7a5</t>
+          <t>https://www.indeed.com/viewjob?jk=824e663391dfa6bf</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c418229c0f650f96</t>
+          <t>https://www.indeed.com/viewjob?jk=3e8686e8d16dc84d</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95121729962d91d2</t>
+          <t>https://www.indeed.com/viewjob?jk=496d9926f80e93e9</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfec58f9b4c8760a</t>
+          <t>https://www.indeed.com/viewjob?jk=57716cf6ab6ed7a5</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5153281c36740802</t>
+          <t>https://www.indeed.com/viewjob?jk=c418229c0f650f96</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=310acaaa4f9f42e3</t>
+          <t>https://www.indeed.com/viewjob?jk=95121729962d91d2</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6efe7ed3911371c4</t>
+          <t>https://www.indeed.com/viewjob?jk=dfec58f9b4c8760a</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a68cf132dbdec60</t>
+          <t>https://www.indeed.com/viewjob?jk=5153281c36740802</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d891e75a79397a9</t>
+          <t>https://www.indeed.com/viewjob?jk=310acaaa4f9f42e3</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=117634e8f8dfb2d6</t>
+          <t>https://www.indeed.com/viewjob?jk=6efe7ed3911371c4</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b83a26f124ccdb89</t>
+          <t>https://www.indeed.com/viewjob?jk=1a68cf132dbdec60</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad88505e172120de</t>
+          <t>https://www.indeed.com/viewjob?jk=8d891e75a79397a9</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c21ad262bec7ef80</t>
+          <t>https://www.indeed.com/viewjob?jk=117634e8f8dfb2d6</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca6810d972b1a5f1</t>
+          <t>https://www.indeed.com/viewjob?jk=b83a26f124ccdb89</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27043ef345d0b8a7</t>
+          <t>https://www.indeed.com/viewjob?jk=ad88505e172120de</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be347b278f12cb33</t>
+          <t>https://www.indeed.com/viewjob?jk=c21ad262bec7ef80</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fed8b15c04492576</t>
+          <t>https://www.indeed.com/viewjob?jk=ca6810d972b1a5f1</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b12133504b24bae</t>
+          <t>https://www.indeed.com/viewjob?jk=27043ef345d0b8a7</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f864d9aca9b7b27</t>
+          <t>https://www.indeed.com/viewjob?jk=be347b278f12cb33</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76d2eb1be4c1b252</t>
+          <t>https://www.indeed.com/viewjob?jk=fed8b15c04492576</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9baba2b401f1c56c</t>
+          <t>https://www.indeed.com/viewjob?jk=5b12133504b24bae</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Platform (Azure)</t>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform, Azure Monitor</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=defb19c3b807f7fd</t>
+          <t>https://www.indeed.com/viewjob?jk=9f864d9aca9b7b27</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect - WORK FROM HOME - SELECT US STATES ONLY</t>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Slavic401K</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df39dd0505c33d32</t>
+          <t>https://www.indeed.com/viewjob?jk=76d2eb1be4c1b252</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Software Engineer - Vehicle Connectivity &amp; mobility (VC&amp;M)</t>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14f272fafe4eb2bc</t>
+          <t>https://www.indeed.com/viewjob?jk=9baba2b401f1c56c</t>
         </is>
       </c>
     </row>
@@ -5578,17 +5578,17 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Data Anchor</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Vertex AI, Hadoop, Spark, Kafka, MongoDB, NoSQL, Splunk</t>
+          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5606,24 +5606,24 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3db1969fc986c5bb</t>
+          <t>https://www.indeed.com/viewjob?jk=33b30501746ad4bf</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Data Engineer - Oklahoma City, OK</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CFS Brands, LLC</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>IAM, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5641,24 +5641,24 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33b30501746ad4bf</t>
+          <t>https://www.indeed.com/viewjob?jk=113fe7e3580ec298</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Data Engineer - Oklahoma City, OK</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>CFS Brands, LLC</t>
+          <t>Chiesi Farmaceutici S.p.A.</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5666,34 +5666,34 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>IAM, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=113fe7e3580ec298</t>
+          <t>https://www.indeed.com/viewjob?jk=78d407207abb7498</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Apache Spark Core Java</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Chiesi Farmaceutici S.p.A.</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5701,34 +5701,34 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78d407207abb7498</t>
+          <t>https://www.indeed.com/viewjob?jk=16d16eda2d514586</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Apache Spark Core Java</t>
+          <t>Senior Analytics Engineer, Marketing Sciences</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>SimplePractice</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5736,34 +5736,34 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, RDS, Scala, Kafka, Snowflake, ETL, dbt, Terraform, Docker</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16d16eda2d514586</t>
+          <t>https://www.indeed.com/viewjob?jk=4a341479dc01b56f</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Marketing Sciences</t>
+          <t>Senior Full Stack Engineer, Agent Experience Platform</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>SimplePractice</t>
+          <t>MAPFRE Insurance</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Webster, MA, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Scala, Kafka, Snowflake, ETL, dbt, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, DynamoDB, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -5781,24 +5781,24 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a341479dc01b56f</t>
+          <t>https://www.indeed.com/viewjob?jk=73664071b95987ff</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer, Agent Experience Platform</t>
+          <t>.NET Backend Developer</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>MAPFRE Insurance</t>
+          <t>Inclusion Cloud</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Webster, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, DynamoDB, CI/CD, Docker</t>
+          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -5816,77 +5816,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73664071b95987ff</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>.NET Backend Developer</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>Inclusion Cloud</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D155" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=5c9d1b0d1d29e0d2</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>Ford Motor Company</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>Allen Park, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D156" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, CI/CD, Terraform, Git</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5cb7a428029c6a47</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-22.xlsx
+++ b/results/job_matches_2026-08-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G154"/>
+  <dimension ref="A1:G151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1098,17 +1098,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer, Full Stack - AI (New York)</t>
+          <t>Sr Full stack Java Developer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Fitch Group</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
+          <t>AWS, S3, API Gateway, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=362603547d1c2a0d</t>
+          <t>https://www.indeed.com/viewjob?jk=50c5bf2319077628</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr Full stack Java Developer</t>
+          <t>Software Engineer, Full Stack - AI (New York)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Hudson Manpower</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50c5bf2319077628</t>
+          <t>https://www.indeed.com/viewjob?jk=362603547d1c2a0d</t>
         </is>
       </c>
     </row>
@@ -1308,52 +1308,52 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Data Engineer 2 - TS required - Washington DC area</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Commence</t>
+          <t>Bow Wave LLC</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
+          <t>AWS, Redshift, S3, Azure, Google Cloud Platform, BigQuery, Hadoop, Spark, Scala, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=125902545a13a43c</t>
+          <t>https://www.indeed.com/viewjob?jk=de40e05b432ea8b8</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer 2 - TS required - Washington DC area</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Bow Wave LLC</t>
+          <t>REPLY</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Google Cloud Platform, BigQuery, Hadoop, Spark, Scala, ETL</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, Azure Cosmos DB, Data Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de40e05b432ea8b8</t>
+          <t>https://www.indeed.com/viewjob?jk=5cc84ba97f996450</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cc84ba97f996450</t>
+          <t>https://www.indeed.com/viewjob?jk=b9d2db7b4c8d89f8</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9d2db7b4c8d89f8</t>
+          <t>https://www.indeed.com/viewjob?jk=74f4fee2cc3d811b</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74f4fee2cc3d811b</t>
+          <t>https://www.indeed.com/viewjob?jk=b7ad9782930201d7</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7ad9782930201d7</t>
+          <t>https://www.indeed.com/viewjob?jk=61bab526ed5bb2fe</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Finance Solutions, Google Cloud Platform</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>REPLY</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, Azure Cosmos DB, Data Modeling</t>
+          <t>RDS, Google Cloud Platform, GCP, Spark, PySpark, Scala, Oracle, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61bab526ed5bb2fe</t>
+          <t>https://www.indeed.com/viewjob?jk=c94336bbf2aab76d</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Finance Solutions, Google Cloud Platform</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Powerplan</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Spark, PySpark, Scala, Oracle, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c94336bbf2aab76d</t>
+          <t>https://www.indeed.com/viewjob?jk=9effd2546d52cd38</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Consultant, Data Engineer | Databricks</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Powerplan</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9effd2546d52cd38</t>
+          <t>https://www.indeed.com/viewjob?jk=87fd62c345b8469e</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Consultant, Data Engineer | Databricks</t>
+          <t>Software Engineer II, Data</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Credit Acceptance</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87fd62c345b8469e</t>
+          <t>https://www.indeed.com/viewjob?jk=39dcfd9f2966d672</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data</t>
+          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Platform (AWS)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Credit Acceptance</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, NoSQL</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39dcfd9f2966d672</t>
+          <t>https://www.indeed.com/viewjob?jk=7064a0875d5078f8</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Platform (AWS)</t>
+          <t>Sr Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform</t>
+          <t>AWS, Redshift, S3, Spark, Scala, Kafka, Snowflake, DynamoDB, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7064a0875d5078f8</t>
+          <t>https://www.indeed.com/viewjob?jk=766cfaa008af94ec</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Advanced | Columbus, US</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Vertex AI, Scala, Kafka, NoSQL</t>
+          <t>AWS, EMR, Kinesis, S3, RDS, Spark, Scala, PostgreSQL, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,59 +1756,59 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=865f8a104cb006d1</t>
+          <t>https://www.indeed.com/viewjob?jk=5d1eabd20620b211</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr Machine Learning Engineer</t>
+          <t>Senior Professional Services Consultant</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>Ataccama</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Spark, Scala, Kafka, Snowflake, DynamoDB, NoSQL, MLOps</t>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=766cfaa008af94ec</t>
+          <t>https://www.indeed.com/viewjob?jk=0f49a3f3dbcbca27</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>CDP Architect</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Bounteous</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, S3, RDS, Spark, Scala, PostgreSQL, NoSQL, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d1eabd20620b211</t>
+          <t>https://www.indeed.com/viewjob?jk=f5b99e7a77983415</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Professional Services Consultant</t>
+          <t>Senior Devops Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Ataccama</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f49a3f3dbcbca27</t>
+          <t>https://www.indeed.com/viewjob?jk=143f81631e970888</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CDP Architect</t>
+          <t>Senior Full stack Java / AWS</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Bounteous</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake, ETL</t>
+          <t>AWS, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,19 +1896,19 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5b99e7a77983415</t>
+          <t>https://www.indeed.com/viewjob?jk=648c04000182f970</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Devops Engineer</t>
+          <t>Azure IoT Solutions Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Ascend Technologies</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1917,11 +1917,11 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation</t>
+          <t>RDS, Azure, Event Hubs, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=143f81631e970888</t>
+          <t>https://www.indeed.com/viewjob?jk=48463a0b2c1a516b</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Full stack Java / AWS</t>
+          <t>GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL, DynamoDB, CI/CD</t>
+          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,59 +1966,59 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=648c04000182f970</t>
+          <t>https://www.indeed.com/viewjob?jk=6b7cc426dbd03f0e</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Economic Data System Engineer/Sr. Economic Data System Engineer-ITDDPED</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SelectQuote</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, SQL Server, ETL, ELT, Airflow</t>
+          <t>RDS, Databricks, BigQuery, Hadoop, Spark, Scala, Snowflake, NoSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23f04a50e41c3404</t>
+          <t>https://www.indeed.com/viewjob?jk=3a32b2285f6e0f19</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Azure IoT Solutions Engineer</t>
+          <t>Data Engineer Denodo</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Ascend Technologies</t>
+          <t>Flowserve</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AKS, Jenkins</t>
+          <t>Azure, Synapse Analytics, Databricks, Scala, Snowflake, Oracle, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48463a0b2c1a516b</t>
+          <t>https://www.indeed.com/viewjob?jk=b87d344718e073fe</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>GCP Cloud Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b7cc426dbd03f0e</t>
+          <t>https://www.indeed.com/viewjob?jk=ae435ef03aa1b3c0</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Economic Data System Engineer/Sr. Economic Data System Engineer-ITDDPED</t>
+          <t>QA Automation Engineer II, Officer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Hadoop, Spark, Scala, Snowflake, NoSQL, ETL, ELT</t>
+          <t>RDS, Scala, Oracle, NoSQL, Talend, CI/CD, Jenkins, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a32b2285f6e0f19</t>
+          <t>https://www.indeed.com/viewjob?jk=1d73747fd9aafef8</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer Denodo</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Flowserve</t>
+          <t>Mercari</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Databricks, Scala, Snowflake, Oracle, SQL Server, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Tableau</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b87d344718e073fe</t>
+          <t>https://www.indeed.com/viewjob?jk=179685542a7cf944</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Pilot Flying J</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Roswell, GA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae435ef03aa1b3c0</t>
+          <t>https://www.indeed.com/viewjob?jk=0a70d5a50e3bc2a5</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>QA Automation Engineer II, Officer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, NoSQL, Talend, CI/CD, Jenkins, Docker, Jenkins, Git</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Kafka, CI/CD, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d73747fd9aafef8</t>
+          <t>https://www.indeed.com/viewjob?jk=9a5cbb62cc968f68</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Mercari</t>
+          <t>Marathon Petroleum</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Tableau</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=179685542a7cf944</t>
+          <t>https://www.indeed.com/viewjob?jk=28293fa77ffc32bb</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr Engineer, Data Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Pilot Flying J</t>
+          <t>Golden State</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Roswell, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a70d5a50e3bc2a5</t>
+          <t>https://www.indeed.com/viewjob?jk=1d156f80ddb5ea3e</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>American Tower</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Kafka, CI/CD, Terraform, Kubernetes, AKS</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a5cbb62cc968f68</t>
+          <t>https://www.indeed.com/viewjob?jk=340f3540cd359821</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Senior Data Engineer – Advanced Data Integration &amp; Cloud Solutions</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Marathon Petroleum</t>
+          <t>Everforth ECS</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, CI/CD, Git, Python, SQL</t>
+          <t>ECS, RDS, Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, ETL, Python, SQL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28293fa77ffc32bb</t>
+          <t>https://www.indeed.com/viewjob?jk=ca1d4ee2bfb7f383</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Engineer/DevOps Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Golden State</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, Splunk, CI/CD, Azure DevOps, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d156f80ddb5ea3e</t>
+          <t>https://www.indeed.com/viewjob?jk=a4e19bdfcdfa54e3</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Analyst, Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>American Tower</t>
+          <t>Lincoln Electric</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=340f3540cd359821</t>
+          <t>https://www.indeed.com/viewjob?jk=8382e0121c068a19</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Advanced Data Integration &amp; Cloud Solutions</t>
+          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Platform (Azure)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Everforth ECS</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, ETL, Python, SQL</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform, Azure Monitor</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca1d4ee2bfb7f383</t>
+          <t>https://www.indeed.com/viewjob?jk=defb19c3b807f7fd</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AI Engineer/DevOps Engineer</t>
+          <t>Enterprise Data Architect - WORK FROM HOME - SELECT US STATES ONLY</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Slavic401K</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, Splunk, CI/CD, Azure DevOps, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4e19bdfcdfa54e3</t>
+          <t>https://www.indeed.com/viewjob?jk=df39dd0505c33d32</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Analyst, Data Engineer</t>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Lincoln Electric</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8382e0121c068a19</t>
+          <t>https://www.indeed.com/viewjob?jk=f4ab3e3c7077492c</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Platform (Azure)</t>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Inglewood, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform, Azure Monitor</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=defb19c3b807f7fd</t>
+          <t>https://www.indeed.com/viewjob?jk=b0870a8c631ca3e7</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect - WORK FROM HOME - SELECT US STATES ONLY</t>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Slavic401K</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df39dd0505c33d32</t>
+          <t>https://www.indeed.com/viewjob?jk=3a8177305c7e2b4e</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4ab3e3c7077492c</t>
+          <t>https://www.indeed.com/viewjob?jk=2b216035065cdcce</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Inglewood, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0870a8c631ca3e7</t>
+          <t>https://www.indeed.com/viewjob?jk=b0d6bbe5db7dc4e3</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a8177305c7e2b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=99cd5dc3d4c47201</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b216035065cdcce</t>
+          <t>https://www.indeed.com/viewjob?jk=1535cff1bb626738</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Williamsville, NY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0d6bbe5db7dc4e3</t>
+          <t>https://www.indeed.com/viewjob?jk=37a520fdd5e099b9</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99cd5dc3d4c47201</t>
+          <t>https://www.indeed.com/viewjob?jk=366fcdfb585bd3be</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1535cff1bb626738</t>
+          <t>https://www.indeed.com/viewjob?jk=a94f1ea7f43f3649</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Williamsville, NY, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37a520fdd5e099b9</t>
+          <t>https://www.indeed.com/viewjob?jk=497b07468d401d8a</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=366fcdfb585bd3be</t>
+          <t>https://www.indeed.com/viewjob?jk=8d2e49c364fa4321</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a94f1ea7f43f3649</t>
+          <t>https://www.indeed.com/viewjob?jk=14d6f7b29ae9eb47</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=497b07468d401d8a</t>
+          <t>https://www.indeed.com/viewjob?jk=e69bf4d69267775a</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d2e49c364fa4321</t>
+          <t>https://www.indeed.com/viewjob?jk=22a4f690926575b6</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14d6f7b29ae9eb47</t>
+          <t>https://www.indeed.com/viewjob?jk=7fc8f10cc4340e38</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e69bf4d69267775a</t>
+          <t>https://www.indeed.com/viewjob?jk=4ed7e30adf2adc59</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22a4f690926575b6</t>
+          <t>https://www.indeed.com/viewjob?jk=22efcdd2b4a3dd7f</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fc8f10cc4340e38</t>
+          <t>https://www.indeed.com/viewjob?jk=4d610152102215d5</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ed7e30adf2adc59</t>
+          <t>https://www.indeed.com/viewjob?jk=0f093d62f255edad</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22efcdd2b4a3dd7f</t>
+          <t>https://www.indeed.com/viewjob?jk=61c760c7b06ee2ec</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d610152102215d5</t>
+          <t>https://www.indeed.com/viewjob?jk=7e753698d58ce405</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f093d62f255edad</t>
+          <t>https://www.indeed.com/viewjob?jk=613c98d34d3a6aff</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61c760c7b06ee2ec</t>
+          <t>https://www.indeed.com/viewjob?jk=81eb38d16909745a</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e753698d58ce405</t>
+          <t>https://www.indeed.com/viewjob?jk=26aa4bbb65d7bc04</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=613c98d34d3a6aff</t>
+          <t>https://www.indeed.com/viewjob?jk=51eaf011bd4b3db9</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81eb38d16909745a</t>
+          <t>https://www.indeed.com/viewjob?jk=875b54845cacd6b4</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26aa4bbb65d7bc04</t>
+          <t>https://www.indeed.com/viewjob?jk=b044118f339aeefe</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51eaf011bd4b3db9</t>
+          <t>https://www.indeed.com/viewjob?jk=79172907c08cbd27</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=875b54845cacd6b4</t>
+          <t>https://www.indeed.com/viewjob?jk=4072dd1e7bd9b46a</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b044118f339aeefe</t>
+          <t>https://www.indeed.com/viewjob?jk=60e28bece0970c90</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79172907c08cbd27</t>
+          <t>https://www.indeed.com/viewjob?jk=337e00bdabbbf617</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4072dd1e7bd9b46a</t>
+          <t>https://www.indeed.com/viewjob?jk=7008c23fbe380180</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60e28bece0970c90</t>
+          <t>https://www.indeed.com/viewjob?jk=ef94cdec933bb8d2</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=337e00bdabbbf617</t>
+          <t>https://www.indeed.com/viewjob?jk=a9b3dd72c73a5c59</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>San Juan, PR, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7008c23fbe380180</t>
+          <t>https://www.indeed.com/viewjob?jk=3f362104fdb5fce0</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef94cdec933bb8d2</t>
+          <t>https://www.indeed.com/viewjob?jk=bb3766965503e1b0</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9b3dd72c73a5c59</t>
+          <t>https://www.indeed.com/viewjob?jk=01b7efd6177971eb</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>San Juan, PR, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f362104fdb5fce0</t>
+          <t>https://www.indeed.com/viewjob?jk=564843cdd5d6c05d</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb3766965503e1b0</t>
+          <t>https://www.indeed.com/viewjob?jk=38dc1e892863874b</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01b7efd6177971eb</t>
+          <t>https://www.indeed.com/viewjob?jk=36375563a2ad1043</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Honolulu, HI, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=564843cdd5d6c05d</t>
+          <t>https://www.indeed.com/viewjob?jk=cf1ab598617115f3</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38dc1e892863874b</t>
+          <t>https://www.indeed.com/viewjob?jk=bdb4d76e4c3be44c</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36375563a2ad1043</t>
+          <t>https://www.indeed.com/viewjob?jk=bd706eccacda1e1c</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Honolulu, HI, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf1ab598617115f3</t>
+          <t>https://www.indeed.com/viewjob?jk=606f854062c681fa</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdb4d76e4c3be44c</t>
+          <t>https://www.indeed.com/viewjob?jk=15ee32196b2a250e</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd706eccacda1e1c</t>
+          <t>https://www.indeed.com/viewjob?jk=c7a2ced0233034b8</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606f854062c681fa</t>
+          <t>https://www.indeed.com/viewjob?jk=b267004acbc01cc5</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15ee32196b2a250e</t>
+          <t>https://www.indeed.com/viewjob?jk=9be2810504f2ae29</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7a2ced0233034b8</t>
+          <t>https://www.indeed.com/viewjob?jk=6f0ec602c9b09a8e</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b267004acbc01cc5</t>
+          <t>https://www.indeed.com/viewjob?jk=bd0e7d3dab7e604a</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9be2810504f2ae29</t>
+          <t>https://www.indeed.com/viewjob?jk=905c5a2344562ab8</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f0ec602c9b09a8e</t>
+          <t>https://www.indeed.com/viewjob?jk=21b0eb74cf57c4a8</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Monterey, CA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd0e7d3dab7e604a</t>
+          <t>https://www.indeed.com/viewjob?jk=127db1667ff89227</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=905c5a2344562ab8</t>
+          <t>https://www.indeed.com/viewjob?jk=2a42559421200137</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21b0eb74cf57c4a8</t>
+          <t>https://www.indeed.com/viewjob?jk=d6e7dd724c924aca</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Monterey, CA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127db1667ff89227</t>
+          <t>https://www.indeed.com/viewjob?jk=8483d29d2dbde05b</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a42559421200137</t>
+          <t>https://www.indeed.com/viewjob?jk=824e663391dfa6bf</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6e7dd724c924aca</t>
+          <t>https://www.indeed.com/viewjob?jk=3e8686e8d16dc84d</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8483d29d2dbde05b</t>
+          <t>https://www.indeed.com/viewjob?jk=496d9926f80e93e9</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=824e663391dfa6bf</t>
+          <t>https://www.indeed.com/viewjob?jk=57716cf6ab6ed7a5</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e8686e8d16dc84d</t>
+          <t>https://www.indeed.com/viewjob?jk=c418229c0f650f96</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=496d9926f80e93e9</t>
+          <t>https://www.indeed.com/viewjob?jk=95121729962d91d2</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57716cf6ab6ed7a5</t>
+          <t>https://www.indeed.com/viewjob?jk=dfec58f9b4c8760a</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c418229c0f650f96</t>
+          <t>https://www.indeed.com/viewjob?jk=5153281c36740802</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95121729962d91d2</t>
+          <t>https://www.indeed.com/viewjob?jk=310acaaa4f9f42e3</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfec58f9b4c8760a</t>
+          <t>https://www.indeed.com/viewjob?jk=6efe7ed3911371c4</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5153281c36740802</t>
+          <t>https://www.indeed.com/viewjob?jk=1a68cf132dbdec60</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=310acaaa4f9f42e3</t>
+          <t>https://www.indeed.com/viewjob?jk=8d891e75a79397a9</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6efe7ed3911371c4</t>
+          <t>https://www.indeed.com/viewjob?jk=117634e8f8dfb2d6</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a68cf132dbdec60</t>
+          <t>https://www.indeed.com/viewjob?jk=b83a26f124ccdb89</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d891e75a79397a9</t>
+          <t>https://www.indeed.com/viewjob?jk=ad88505e172120de</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=117634e8f8dfb2d6</t>
+          <t>https://www.indeed.com/viewjob?jk=c21ad262bec7ef80</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b83a26f124ccdb89</t>
+          <t>https://www.indeed.com/viewjob?jk=ca6810d972b1a5f1</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad88505e172120de</t>
+          <t>https://www.indeed.com/viewjob?jk=27043ef345d0b8a7</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c21ad262bec7ef80</t>
+          <t>https://www.indeed.com/viewjob?jk=be347b278f12cb33</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca6810d972b1a5f1</t>
+          <t>https://www.indeed.com/viewjob?jk=fed8b15c04492576</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27043ef345d0b8a7</t>
+          <t>https://www.indeed.com/viewjob?jk=5b12133504b24bae</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be347b278f12cb33</t>
+          <t>https://www.indeed.com/viewjob?jk=9f864d9aca9b7b27</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fed8b15c04492576</t>
+          <t>https://www.indeed.com/viewjob?jk=76d2eb1be4c1b252</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b12133504b24bae</t>
+          <t>https://www.indeed.com/viewjob?jk=9baba2b401f1c56c</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+          <t>Databricks Developer</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f864d9aca9b7b27</t>
+          <t>https://www.indeed.com/viewjob?jk=ab1192abfbd7f24e</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+          <t>Databricks Developer</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76d2eb1be4c1b252</t>
+          <t>https://www.indeed.com/viewjob?jk=320dcd4f927cb250</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+          <t>Senior Quality Engineering (QE) Engineer</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Amida Technology Solutions</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Power BI, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,32 +5431,32 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9baba2b401f1c56c</t>
+          <t>https://www.indeed.com/viewjob?jk=29a7f8ff4391f120</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Databricks Developer</t>
+          <t>Associate, Data Engineer</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, DynamoDB, Azure Cosmos DB, NoSQL</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,32 +5466,32 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab1192abfbd7f24e</t>
+          <t>https://www.indeed.com/viewjob?jk=06fd6810514e5491</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Databricks Developer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,32 +5501,32 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=320dcd4f927cb250</t>
+          <t>https://www.indeed.com/viewjob?jk=33b30501746ad4bf</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Senior Quality Engineering (QE) Engineer</t>
+          <t>Data Engineer - Oklahoma City, OK</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Amida Technology Solutions</t>
+          <t>CFS Brands, LLC</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Power BI, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>IAM, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,24 +5536,24 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29a7f8ff4391f120</t>
+          <t>https://www.indeed.com/viewjob?jk=113fe7e3580ec298</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Associate, Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Chiesi Farmaceutici S.p.A.</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,34 +5561,34 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, DynamoDB, Azure Cosmos DB, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06fd6810514e5491</t>
+          <t>https://www.indeed.com/viewjob?jk=78d407207abb7498</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Apache Spark Core Java</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,34 +5596,34 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33b30501746ad4bf</t>
+          <t>https://www.indeed.com/viewjob?jk=16d16eda2d514586</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Data Engineer - Oklahoma City, OK</t>
+          <t>Senior Analytics Engineer, Marketing Sciences</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>CFS Brands, LLC</t>
+          <t>SimplePractice</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>IAM, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Kinesis, RDS, Scala, Kafka, Snowflake, ETL, dbt, Terraform, Docker</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5641,24 +5641,24 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=113fe7e3580ec298</t>
+          <t>https://www.indeed.com/viewjob?jk=4a341479dc01b56f</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Full Stack Engineer, Agent Experience Platform</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Chiesi Farmaceutici S.p.A.</t>
+          <t>MAPFRE Insurance</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Webster, MA, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5666,34 +5666,34 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, DynamoDB, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78d407207abb7498</t>
+          <t>https://www.indeed.com/viewjob?jk=73664071b95987ff</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Apache Spark Core Java</t>
+          <t>.NET Backend Developer</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Inclusion Cloud</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5701,120 +5701,15 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=16d16eda2d514586</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>Senior Analytics Engineer, Marketing Sciences</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>SimplePractice</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D152" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, RDS, Scala, Kafka, Snowflake, ETL, dbt, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4a341479dc01b56f</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Engineer, Agent Experience Platform</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>MAPFRE Insurance</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Webster, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D153" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, DynamoDB, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=73664071b95987ff</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>.NET Backend Developer</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>Inclusion Cloud</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D154" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=5c9d1b0d1d29e0d2</t>
         </is>

--- a/results/job_matches_2026-08-22.xlsx
+++ b/results/job_matches_2026-08-22.xlsx
@@ -1028,17 +1028,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr Full stack Java Developer</t>
+          <t>Software Engineer, Full Stack - AI (New York)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Hudson Manpower</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7f12b1ea10022a2</t>
+          <t>https://www.indeed.com/viewjob?jk=362603547d1c2a0d</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6bc74fdfdbbca2b</t>
+          <t>https://www.indeed.com/viewjob?jk=a7f12b1ea10022a2</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50c5bf2319077628</t>
+          <t>https://www.indeed.com/viewjob?jk=a6bc74fdfdbbca2b</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer, Full Stack - AI (New York)</t>
+          <t>Sr Full stack Java Developer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Fitch Group</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
+          <t>AWS, S3, API Gateway, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=362603547d1c2a0d</t>
+          <t>https://www.indeed.com/viewjob?jk=50c5bf2319077628</t>
         </is>
       </c>
     </row>
@@ -1763,17 +1763,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Professional Services Consultant</t>
+          <t>Solutions Delivery Engineer (Remote)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Ataccama</t>
+          <t>RealPage Inc</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,29 +1781,29 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Redshift, RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f49a3f3dbcbca27</t>
+          <t>https://www.indeed.com/viewjob?jk=ec761fb42adb289d</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CDP Architect</t>
+          <t>Senior Professional Services Consultant</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Bounteous</t>
+          <t>Ataccama</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5b99e7a77983415</t>
+          <t>https://www.indeed.com/viewjob?jk=0f49a3f3dbcbca27</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Devops Engineer</t>
+          <t>CDP Architect</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Bounteous</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=143f81631e970888</t>
+          <t>https://www.indeed.com/viewjob?jk=f5b99e7a77983415</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Full stack Java / AWS</t>
+          <t>Senior Devops Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL, DynamoDB, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=648c04000182f970</t>
+          <t>https://www.indeed.com/viewjob?jk=143f81631e970888</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Azure IoT Solutions Engineer</t>
+          <t>Senior Full stack Java / AWS</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ascend Technologies</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AKS, Jenkins</t>
+          <t>AWS, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48463a0b2c1a516b</t>
+          <t>https://www.indeed.com/viewjob?jk=648c04000182f970</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>GCP Cloud Engineer</t>
+          <t>Azure IoT Solutions Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Ascend Technologies</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Event Hubs, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b7cc426dbd03f0e</t>
+          <t>https://www.indeed.com/viewjob?jk=48463a0b2c1a516b</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Economic Data System Engineer/Sr. Economic Data System Engineer-ITDDPED</t>
+          <t>GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Hadoop, Spark, Scala, Snowflake, NoSQL, ETL, ELT</t>
+          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a32b2285f6e0f19</t>
+          <t>https://www.indeed.com/viewjob?jk=6b7cc426dbd03f0e</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer Denodo</t>
+          <t>Economic Data System Engineer/Sr. Economic Data System Engineer-ITDDPED</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Flowserve</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Databricks, Scala, Snowflake, Oracle, SQL Server, ETL, ELT, Power BI</t>
+          <t>RDS, Databricks, BigQuery, Hadoop, Spark, Scala, Snowflake, NoSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b87d344718e073fe</t>
+          <t>https://www.indeed.com/viewjob?jk=3a32b2285f6e0f19</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer Denodo</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Flowserve</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, CI/CD, Terraform, Docker</t>
+          <t>Azure, Synapse Analytics, Databricks, Scala, Snowflake, Oracle, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae435ef03aa1b3c0</t>
+          <t>https://www.indeed.com/viewjob?jk=b87d344718e073fe</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>QA Automation Engineer II, Officer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, NoSQL, Talend, CI/CD, Jenkins, Docker, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d73747fd9aafef8</t>
+          <t>https://www.indeed.com/viewjob?jk=ae435ef03aa1b3c0</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>QA Automation Engineer II, Officer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Mercari</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Tableau</t>
+          <t>RDS, Scala, Oracle, NoSQL, Talend, CI/CD, Jenkins, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=179685542a7cf944</t>
+          <t>https://www.indeed.com/viewjob?jk=1d73747fd9aafef8</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr Engineer, Data Engineering</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Pilot Flying J</t>
+          <t>Mercari</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Roswell, GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Tableau</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a70d5a50e3bc2a5</t>
+          <t>https://www.indeed.com/viewjob?jk=179685542a7cf944</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Sr Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Pilot Flying J</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Roswell, GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Kafka, CI/CD, Terraform, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a5cbb62cc968f68</t>
+          <t>https://www.indeed.com/viewjob?jk=0a70d5a50e3bc2a5</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Marathon Petroleum</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, CI/CD, Git, Python, SQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Kafka, CI/CD, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28293fa77ffc32bb</t>
+          <t>https://www.indeed.com/viewjob?jk=9a5cbb62cc968f68</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Golden State</t>
+          <t>Marathon Petroleum</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d156f80ddb5ea3e</t>
+          <t>https://www.indeed.com/viewjob?jk=28293fa77ffc32bb</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>American Tower</t>
+          <t>Golden State</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=340f3540cd359821</t>
+          <t>https://www.indeed.com/viewjob?jk=1d156f80ddb5ea3e</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Advanced Data Integration &amp; Cloud Solutions</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Everforth ECS</t>
+          <t>American Tower</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, ETL, Python, SQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca1d4ee2bfb7f383</t>
+          <t>https://www.indeed.com/viewjob?jk=340f3540cd359821</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AI Engineer/DevOps Engineer</t>
+          <t>Senior Data Engineer – Advanced Data Integration &amp; Cloud Solutions</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Everforth ECS</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, Splunk, CI/CD, Azure DevOps, Kubernetes</t>
+          <t>ECS, RDS, Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, ETL, Python, SQL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4e19bdfcdfa54e3</t>
+          <t>https://www.indeed.com/viewjob?jk=ca1d4ee2bfb7f383</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Analyst, Data Engineer</t>
+          <t>AI Engineer/DevOps Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Lincoln Electric</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, Splunk, CI/CD, Azure DevOps, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8382e0121c068a19</t>
+          <t>https://www.indeed.com/viewjob?jk=a4e19bdfcdfa54e3</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Platform (Azure)</t>
+          <t>Senior Analyst, Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Lincoln Electric</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform, Azure Monitor</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=defb19c3b807f7fd</t>
+          <t>https://www.indeed.com/viewjob?jk=8382e0121c068a19</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect - WORK FROM HOME - SELECT US STATES ONLY</t>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Slavic401K</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df39dd0505c33d32</t>
+          <t>https://www.indeed.com/viewjob?jk=f4ab3e3c7077492c</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Inglewood, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4ab3e3c7077492c</t>
+          <t>https://www.indeed.com/viewjob?jk=b0870a8c631ca3e7</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Inglewood, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0870a8c631ca3e7</t>
+          <t>https://www.indeed.com/viewjob?jk=3a8177305c7e2b4e</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a8177305c7e2b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=2b216035065cdcce</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b216035065cdcce</t>
+          <t>https://www.indeed.com/viewjob?jk=b0d6bbe5db7dc4e3</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0d6bbe5db7dc4e3</t>
+          <t>https://www.indeed.com/viewjob?jk=99cd5dc3d4c47201</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99cd5dc3d4c47201</t>
+          <t>https://www.indeed.com/viewjob?jk=1535cff1bb626738</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Williamsville, NY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1535cff1bb626738</t>
+          <t>https://www.indeed.com/viewjob?jk=37a520fdd5e099b9</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Williamsville, NY, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37a520fdd5e099b9</t>
+          <t>https://www.indeed.com/viewjob?jk=366fcdfb585bd3be</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=366fcdfb585bd3be</t>
+          <t>https://www.indeed.com/viewjob?jk=a94f1ea7f43f3649</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a94f1ea7f43f3649</t>
+          <t>https://www.indeed.com/viewjob?jk=497b07468d401d8a</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=497b07468d401d8a</t>
+          <t>https://www.indeed.com/viewjob?jk=8d2e49c364fa4321</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d2e49c364fa4321</t>
+          <t>https://www.indeed.com/viewjob?jk=14d6f7b29ae9eb47</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14d6f7b29ae9eb47</t>
+          <t>https://www.indeed.com/viewjob?jk=e69bf4d69267775a</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e69bf4d69267775a</t>
+          <t>https://www.indeed.com/viewjob?jk=22a4f690926575b6</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22a4f690926575b6</t>
+          <t>https://www.indeed.com/viewjob?jk=7fc8f10cc4340e38</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fc8f10cc4340e38</t>
+          <t>https://www.indeed.com/viewjob?jk=4ed7e30adf2adc59</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ed7e30adf2adc59</t>
+          <t>https://www.indeed.com/viewjob?jk=22efcdd2b4a3dd7f</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22efcdd2b4a3dd7f</t>
+          <t>https://www.indeed.com/viewjob?jk=4d610152102215d5</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d610152102215d5</t>
+          <t>https://www.indeed.com/viewjob?jk=0f093d62f255edad</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f093d62f255edad</t>
+          <t>https://www.indeed.com/viewjob?jk=61c760c7b06ee2ec</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61c760c7b06ee2ec</t>
+          <t>https://www.indeed.com/viewjob?jk=7e753698d58ce405</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e753698d58ce405</t>
+          <t>https://www.indeed.com/viewjob?jk=613c98d34d3a6aff</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=613c98d34d3a6aff</t>
+          <t>https://www.indeed.com/viewjob?jk=81eb38d16909745a</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81eb38d16909745a</t>
+          <t>https://www.indeed.com/viewjob?jk=26aa4bbb65d7bc04</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26aa4bbb65d7bc04</t>
+          <t>https://www.indeed.com/viewjob?jk=51eaf011bd4b3db9</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51eaf011bd4b3db9</t>
+          <t>https://www.indeed.com/viewjob?jk=875b54845cacd6b4</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=875b54845cacd6b4</t>
+          <t>https://www.indeed.com/viewjob?jk=b044118f339aeefe</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b044118f339aeefe</t>
+          <t>https://www.indeed.com/viewjob?jk=79172907c08cbd27</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79172907c08cbd27</t>
+          <t>https://www.indeed.com/viewjob?jk=4072dd1e7bd9b46a</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4072dd1e7bd9b46a</t>
+          <t>https://www.indeed.com/viewjob?jk=60e28bece0970c90</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60e28bece0970c90</t>
+          <t>https://www.indeed.com/viewjob?jk=337e00bdabbbf617</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=337e00bdabbbf617</t>
+          <t>https://www.indeed.com/viewjob?jk=7008c23fbe380180</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7008c23fbe380180</t>
+          <t>https://www.indeed.com/viewjob?jk=ef94cdec933bb8d2</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef94cdec933bb8d2</t>
+          <t>https://www.indeed.com/viewjob?jk=a9b3dd72c73a5c59</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>San Juan, PR, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9b3dd72c73a5c59</t>
+          <t>https://www.indeed.com/viewjob?jk=3f362104fdb5fce0</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>San Juan, PR, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f362104fdb5fce0</t>
+          <t>https://www.indeed.com/viewjob?jk=bb3766965503e1b0</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb3766965503e1b0</t>
+          <t>https://www.indeed.com/viewjob?jk=01b7efd6177971eb</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01b7efd6177971eb</t>
+          <t>https://www.indeed.com/viewjob?jk=564843cdd5d6c05d</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=564843cdd5d6c05d</t>
+          <t>https://www.indeed.com/viewjob?jk=38dc1e892863874b</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38dc1e892863874b</t>
+          <t>https://www.indeed.com/viewjob?jk=36375563a2ad1043</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Honolulu, HI, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36375563a2ad1043</t>
+          <t>https://www.indeed.com/viewjob?jk=cf1ab598617115f3</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Honolulu, HI, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf1ab598617115f3</t>
+          <t>https://www.indeed.com/viewjob?jk=bdb4d76e4c3be44c</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdb4d76e4c3be44c</t>
+          <t>https://www.indeed.com/viewjob?jk=bd706eccacda1e1c</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd706eccacda1e1c</t>
+          <t>https://www.indeed.com/viewjob?jk=606f854062c681fa</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606f854062c681fa</t>
+          <t>https://www.indeed.com/viewjob?jk=15ee32196b2a250e</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15ee32196b2a250e</t>
+          <t>https://www.indeed.com/viewjob?jk=c7a2ced0233034b8</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7a2ced0233034b8</t>
+          <t>https://www.indeed.com/viewjob?jk=b267004acbc01cc5</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b267004acbc01cc5</t>
+          <t>https://www.indeed.com/viewjob?jk=9be2810504f2ae29</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9be2810504f2ae29</t>
+          <t>https://www.indeed.com/viewjob?jk=6f0ec602c9b09a8e</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f0ec602c9b09a8e</t>
+          <t>https://www.indeed.com/viewjob?jk=bd0e7d3dab7e604a</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd0e7d3dab7e604a</t>
+          <t>https://www.indeed.com/viewjob?jk=905c5a2344562ab8</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=905c5a2344562ab8</t>
+          <t>https://www.indeed.com/viewjob?jk=21b0eb74cf57c4a8</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Monterey, CA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21b0eb74cf57c4a8</t>
+          <t>https://www.indeed.com/viewjob?jk=127db1667ff89227</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Monterey, CA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127db1667ff89227</t>
+          <t>https://www.indeed.com/viewjob?jk=2a42559421200137</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a42559421200137</t>
+          <t>https://www.indeed.com/viewjob?jk=d6e7dd724c924aca</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6e7dd724c924aca</t>
+          <t>https://www.indeed.com/viewjob?jk=8483d29d2dbde05b</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8483d29d2dbde05b</t>
+          <t>https://www.indeed.com/viewjob?jk=824e663391dfa6bf</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=824e663391dfa6bf</t>
+          <t>https://www.indeed.com/viewjob?jk=3e8686e8d16dc84d</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e8686e8d16dc84d</t>
+          <t>https://www.indeed.com/viewjob?jk=496d9926f80e93e9</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=496d9926f80e93e9</t>
+          <t>https://www.indeed.com/viewjob?jk=57716cf6ab6ed7a5</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57716cf6ab6ed7a5</t>
+          <t>https://www.indeed.com/viewjob?jk=c418229c0f650f96</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c418229c0f650f96</t>
+          <t>https://www.indeed.com/viewjob?jk=95121729962d91d2</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95121729962d91d2</t>
+          <t>https://www.indeed.com/viewjob?jk=dfec58f9b4c8760a</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfec58f9b4c8760a</t>
+          <t>https://www.indeed.com/viewjob?jk=5153281c36740802</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5153281c36740802</t>
+          <t>https://www.indeed.com/viewjob?jk=310acaaa4f9f42e3</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=310acaaa4f9f42e3</t>
+          <t>https://www.indeed.com/viewjob?jk=6efe7ed3911371c4</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6efe7ed3911371c4</t>
+          <t>https://www.indeed.com/viewjob?jk=1a68cf132dbdec60</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a68cf132dbdec60</t>
+          <t>https://www.indeed.com/viewjob?jk=8d891e75a79397a9</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d891e75a79397a9</t>
+          <t>https://www.indeed.com/viewjob?jk=117634e8f8dfb2d6</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=117634e8f8dfb2d6</t>
+          <t>https://www.indeed.com/viewjob?jk=b83a26f124ccdb89</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b83a26f124ccdb89</t>
+          <t>https://www.indeed.com/viewjob?jk=ad88505e172120de</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad88505e172120de</t>
+          <t>https://www.indeed.com/viewjob?jk=c21ad262bec7ef80</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c21ad262bec7ef80</t>
+          <t>https://www.indeed.com/viewjob?jk=ca6810d972b1a5f1</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca6810d972b1a5f1</t>
+          <t>https://www.indeed.com/viewjob?jk=27043ef345d0b8a7</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27043ef345d0b8a7</t>
+          <t>https://www.indeed.com/viewjob?jk=be347b278f12cb33</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be347b278f12cb33</t>
+          <t>https://www.indeed.com/viewjob?jk=fed8b15c04492576</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fed8b15c04492576</t>
+          <t>https://www.indeed.com/viewjob?jk=5b12133504b24bae</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b12133504b24bae</t>
+          <t>https://www.indeed.com/viewjob?jk=9f864d9aca9b7b27</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f864d9aca9b7b27</t>
+          <t>https://www.indeed.com/viewjob?jk=76d2eb1be4c1b252</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76d2eb1be4c1b252</t>
+          <t>https://www.indeed.com/viewjob?jk=9baba2b401f1c56c</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Platform (Azure)</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform, Azure Monitor</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9baba2b401f1c56c</t>
+          <t>https://www.indeed.com/viewjob?jk=defb19c3b807f7fd</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Databricks Developer</t>
+          <t>Enterprise Data Architect - WORK FROM HOME - SELECT US STATES ONLY</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Slavic401K</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab1192abfbd7f24e</t>
+          <t>https://www.indeed.com/viewjob?jk=df39dd0505c33d32</t>
         </is>
       </c>
     </row>
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=320dcd4f927cb250</t>
+          <t>https://www.indeed.com/viewjob?jk=ab1192abfbd7f24e</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Senior Quality Engineering (QE) Engineer</t>
+          <t>Databricks Developer</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Amida Technology Solutions</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Power BI, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,32 +5431,32 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29a7f8ff4391f120</t>
+          <t>https://www.indeed.com/viewjob?jk=320dcd4f927cb250</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Associate, Data Engineer</t>
+          <t>Senior Quality Engineering (QE) Engineer</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Amida Technology Solutions</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, DynamoDB, Azure Cosmos DB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Power BI, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,24 +5466,24 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06fd6810514e5491</t>
+          <t>https://www.indeed.com/viewjob?jk=29a7f8ff4391f120</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Associate, Data Engineer</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, DynamoDB, Azure Cosmos DB, NoSQL</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,24 +5501,24 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33b30501746ad4bf</t>
+          <t>https://www.indeed.com/viewjob?jk=06fd6810514e5491</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Data Engineer - Oklahoma City, OK</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>CFS Brands, LLC</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>IAM, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,24 +5536,24 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=113fe7e3580ec298</t>
+          <t>https://www.indeed.com/viewjob?jk=33b30501746ad4bf</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer - Oklahoma City, OK</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Chiesi Farmaceutici S.p.A.</t>
+          <t>CFS Brands, LLC</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,34 +5561,34 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT</t>
+          <t>IAM, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78d407207abb7498</t>
+          <t>https://www.indeed.com/viewjob?jk=113fe7e3580ec298</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Apache Spark Core Java</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Chiesi Farmaceutici S.p.A.</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,34 +5596,34 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16d16eda2d514586</t>
+          <t>https://www.indeed.com/viewjob?jk=78d407207abb7498</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Marketing Sciences</t>
+          <t>Apache Spark Core Java</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>SimplePractice</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,34 +5631,34 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Scala, Kafka, Snowflake, ETL, dbt, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a341479dc01b56f</t>
+          <t>https://www.indeed.com/viewjob?jk=16d16eda2d514586</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer, Agent Experience Platform</t>
+          <t>Senior Analytics Engineer, Marketing Sciences</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>MAPFRE Insurance</t>
+          <t>SimplePractice</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Webster, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, DynamoDB, CI/CD, Docker</t>
+          <t>AWS, Kinesis, RDS, Scala, Kafka, Snowflake, ETL, dbt, Terraform, Docker</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73664071b95987ff</t>
+          <t>https://www.indeed.com/viewjob?jk=4a341479dc01b56f</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-22.xlsx
+++ b/results/job_matches_2026-08-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G151"/>
+  <dimension ref="A1:G152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1798,17 +1798,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Professional Services Consultant</t>
+          <t>Senior Software Development Engineer - LLMs, GenAI</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Ataccama</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Power BI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,19 +1826,19 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f49a3f3dbcbca27</t>
+          <t>https://www.indeed.com/viewjob?jk=7ef55c2266d41678</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CDP Architect</t>
+          <t>Senior Professional Services Consultant</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Bounteous</t>
+          <t>Ataccama</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5b99e7a77983415</t>
+          <t>https://www.indeed.com/viewjob?jk=0f49a3f3dbcbca27</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Devops Engineer</t>
+          <t>CDP Architect</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Bounteous</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=143f81631e970888</t>
+          <t>https://www.indeed.com/viewjob?jk=f5b99e7a77983415</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Full stack Java / AWS</t>
+          <t>Senior Devops Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL, DynamoDB, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=648c04000182f970</t>
+          <t>https://www.indeed.com/viewjob?jk=143f81631e970888</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Azure IoT Solutions Engineer</t>
+          <t>Senior Full stack Java / AWS</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Ascend Technologies</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AKS, Jenkins</t>
+          <t>AWS, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48463a0b2c1a516b</t>
+          <t>https://www.indeed.com/viewjob?jk=648c04000182f970</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>GCP Cloud Engineer</t>
+          <t>Azure IoT Solutions Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Ascend Technologies</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Event Hubs, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b7cc426dbd03f0e</t>
+          <t>https://www.indeed.com/viewjob?jk=48463a0b2c1a516b</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Economic Data System Engineer/Sr. Economic Data System Engineer-ITDDPED</t>
+          <t>GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Hadoop, Spark, Scala, Snowflake, NoSQL, ETL, ELT</t>
+          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a32b2285f6e0f19</t>
+          <t>https://www.indeed.com/viewjob?jk=6b7cc426dbd03f0e</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer Denodo</t>
+          <t>Economic Data System Engineer/Sr. Economic Data System Engineer-ITDDPED</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Flowserve</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Databricks, Scala, Snowflake, Oracle, SQL Server, ETL, ELT, Power BI</t>
+          <t>RDS, Databricks, BigQuery, Hadoop, Spark, Scala, Snowflake, NoSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b87d344718e073fe</t>
+          <t>https://www.indeed.com/viewjob?jk=3a32b2285f6e0f19</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer Denodo</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Flowserve</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, CI/CD, Terraform, Docker</t>
+          <t>Azure, Synapse Analytics, Databricks, Scala, Snowflake, Oracle, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae435ef03aa1b3c0</t>
+          <t>https://www.indeed.com/viewjob?jk=b87d344718e073fe</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>QA Automation Engineer II, Officer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, NoSQL, Talend, CI/CD, Jenkins, Docker, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d73747fd9aafef8</t>
+          <t>https://www.indeed.com/viewjob?jk=ae435ef03aa1b3c0</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>QA Automation Engineer II, Officer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Mercari</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Tableau</t>
+          <t>RDS, Scala, Oracle, NoSQL, Talend, CI/CD, Jenkins, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=179685542a7cf944</t>
+          <t>https://www.indeed.com/viewjob?jk=1d73747fd9aafef8</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr Engineer, Data Engineering</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Pilot Flying J</t>
+          <t>Mercari</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Roswell, GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Tableau</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a70d5a50e3bc2a5</t>
+          <t>https://www.indeed.com/viewjob?jk=179685542a7cf944</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Sr Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Pilot Flying J</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Roswell, GA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Kafka, CI/CD, Terraform, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a5cbb62cc968f68</t>
+          <t>https://www.indeed.com/viewjob?jk=0a70d5a50e3bc2a5</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Marathon Petroleum</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, CI/CD, Git, Python, SQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Kafka, CI/CD, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28293fa77ffc32bb</t>
+          <t>https://www.indeed.com/viewjob?jk=9a5cbb62cc968f68</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Golden State</t>
+          <t>Marathon Petroleum</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d156f80ddb5ea3e</t>
+          <t>https://www.indeed.com/viewjob?jk=28293fa77ffc32bb</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>American Tower</t>
+          <t>Golden State</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=340f3540cd359821</t>
+          <t>https://www.indeed.com/viewjob?jk=1d156f80ddb5ea3e</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Advanced Data Integration &amp; Cloud Solutions</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Everforth ECS</t>
+          <t>American Tower</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, ETL, Python, SQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca1d4ee2bfb7f383</t>
+          <t>https://www.indeed.com/viewjob?jk=340f3540cd359821</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AI Engineer/DevOps Engineer</t>
+          <t>Senior Data Engineer – Advanced Data Integration &amp; Cloud Solutions</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Everforth ECS</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, Splunk, CI/CD, Azure DevOps, Kubernetes</t>
+          <t>ECS, RDS, Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, ETL, Python, SQL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4e19bdfcdfa54e3</t>
+          <t>https://www.indeed.com/viewjob?jk=ca1d4ee2bfb7f383</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Analyst, Data Engineer</t>
+          <t>AI Engineer/DevOps Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Lincoln Electric</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, Splunk, CI/CD, Azure DevOps, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8382e0121c068a19</t>
+          <t>https://www.indeed.com/viewjob?jk=a4e19bdfcdfa54e3</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+          <t>Senior Analyst, Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Lincoln Electric</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4ab3e3c7077492c</t>
+          <t>https://www.indeed.com/viewjob?jk=8382e0121c068a19</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Platform (Azure)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Inglewood, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform, Azure Monitor</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0870a8c631ca3e7</t>
+          <t>https://www.indeed.com/viewjob?jk=defb19c3b807f7fd</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+          <t>Enterprise Data Architect - WORK FROM HOME - SELECT US STATES ONLY</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Slavic401K</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a8177305c7e2b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=df39dd0505c33d32</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b216035065cdcce</t>
+          <t>https://www.indeed.com/viewjob?jk=f4ab3e3c7077492c</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Inglewood, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0d6bbe5db7dc4e3</t>
+          <t>https://www.indeed.com/viewjob?jk=b0870a8c631ca3e7</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99cd5dc3d4c47201</t>
+          <t>https://www.indeed.com/viewjob?jk=3a8177305c7e2b4e</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1535cff1bb626738</t>
+          <t>https://www.indeed.com/viewjob?jk=2b216035065cdcce</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Williamsville, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37a520fdd5e099b9</t>
+          <t>https://www.indeed.com/viewjob?jk=b0d6bbe5db7dc4e3</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=366fcdfb585bd3be</t>
+          <t>https://www.indeed.com/viewjob?jk=99cd5dc3d4c47201</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a94f1ea7f43f3649</t>
+          <t>https://www.indeed.com/viewjob?jk=1535cff1bb626738</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Williamsville, NY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=497b07468d401d8a</t>
+          <t>https://www.indeed.com/viewjob?jk=37a520fdd5e099b9</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d2e49c364fa4321</t>
+          <t>https://www.indeed.com/viewjob?jk=366fcdfb585bd3be</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14d6f7b29ae9eb47</t>
+          <t>https://www.indeed.com/viewjob?jk=a94f1ea7f43f3649</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e69bf4d69267775a</t>
+          <t>https://www.indeed.com/viewjob?jk=497b07468d401d8a</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22a4f690926575b6</t>
+          <t>https://www.indeed.com/viewjob?jk=8d2e49c364fa4321</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fc8f10cc4340e38</t>
+          <t>https://www.indeed.com/viewjob?jk=14d6f7b29ae9eb47</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ed7e30adf2adc59</t>
+          <t>https://www.indeed.com/viewjob?jk=e69bf4d69267775a</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22efcdd2b4a3dd7f</t>
+          <t>https://www.indeed.com/viewjob?jk=22a4f690926575b6</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d610152102215d5</t>
+          <t>https://www.indeed.com/viewjob?jk=7fc8f10cc4340e38</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f093d62f255edad</t>
+          <t>https://www.indeed.com/viewjob?jk=4ed7e30adf2adc59</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61c760c7b06ee2ec</t>
+          <t>https://www.indeed.com/viewjob?jk=22efcdd2b4a3dd7f</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e753698d58ce405</t>
+          <t>https://www.indeed.com/viewjob?jk=4d610152102215d5</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=613c98d34d3a6aff</t>
+          <t>https://www.indeed.com/viewjob?jk=0f093d62f255edad</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81eb38d16909745a</t>
+          <t>https://www.indeed.com/viewjob?jk=61c760c7b06ee2ec</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26aa4bbb65d7bc04</t>
+          <t>https://www.indeed.com/viewjob?jk=7e753698d58ce405</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51eaf011bd4b3db9</t>
+          <t>https://www.indeed.com/viewjob?jk=613c98d34d3a6aff</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=875b54845cacd6b4</t>
+          <t>https://www.indeed.com/viewjob?jk=81eb38d16909745a</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b044118f339aeefe</t>
+          <t>https://www.indeed.com/viewjob?jk=26aa4bbb65d7bc04</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79172907c08cbd27</t>
+          <t>https://www.indeed.com/viewjob?jk=51eaf011bd4b3db9</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4072dd1e7bd9b46a</t>
+          <t>https://www.indeed.com/viewjob?jk=875b54845cacd6b4</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60e28bece0970c90</t>
+          <t>https://www.indeed.com/viewjob?jk=b044118f339aeefe</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=337e00bdabbbf617</t>
+          <t>https://www.indeed.com/viewjob?jk=79172907c08cbd27</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7008c23fbe380180</t>
+          <t>https://www.indeed.com/viewjob?jk=4072dd1e7bd9b46a</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef94cdec933bb8d2</t>
+          <t>https://www.indeed.com/viewjob?jk=60e28bece0970c90</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9b3dd72c73a5c59</t>
+          <t>https://www.indeed.com/viewjob?jk=337e00bdabbbf617</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>San Juan, PR, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f362104fdb5fce0</t>
+          <t>https://www.indeed.com/viewjob?jk=7008c23fbe380180</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb3766965503e1b0</t>
+          <t>https://www.indeed.com/viewjob?jk=ef94cdec933bb8d2</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01b7efd6177971eb</t>
+          <t>https://www.indeed.com/viewjob?jk=a9b3dd72c73a5c59</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>San Juan, PR, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=564843cdd5d6c05d</t>
+          <t>https://www.indeed.com/viewjob?jk=3f362104fdb5fce0</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38dc1e892863874b</t>
+          <t>https://www.indeed.com/viewjob?jk=bb3766965503e1b0</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36375563a2ad1043</t>
+          <t>https://www.indeed.com/viewjob?jk=01b7efd6177971eb</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Honolulu, HI, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf1ab598617115f3</t>
+          <t>https://www.indeed.com/viewjob?jk=564843cdd5d6c05d</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdb4d76e4c3be44c</t>
+          <t>https://www.indeed.com/viewjob?jk=38dc1e892863874b</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd706eccacda1e1c</t>
+          <t>https://www.indeed.com/viewjob?jk=36375563a2ad1043</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Honolulu, HI, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606f854062c681fa</t>
+          <t>https://www.indeed.com/viewjob?jk=cf1ab598617115f3</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15ee32196b2a250e</t>
+          <t>https://www.indeed.com/viewjob?jk=bdb4d76e4c3be44c</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7a2ced0233034b8</t>
+          <t>https://www.indeed.com/viewjob?jk=bd706eccacda1e1c</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b267004acbc01cc5</t>
+          <t>https://www.indeed.com/viewjob?jk=606f854062c681fa</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9be2810504f2ae29</t>
+          <t>https://www.indeed.com/viewjob?jk=15ee32196b2a250e</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f0ec602c9b09a8e</t>
+          <t>https://www.indeed.com/viewjob?jk=c7a2ced0233034b8</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd0e7d3dab7e604a</t>
+          <t>https://www.indeed.com/viewjob?jk=b267004acbc01cc5</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=905c5a2344562ab8</t>
+          <t>https://www.indeed.com/viewjob?jk=9be2810504f2ae29</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21b0eb74cf57c4a8</t>
+          <t>https://www.indeed.com/viewjob?jk=6f0ec602c9b09a8e</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Monterey, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127db1667ff89227</t>
+          <t>https://www.indeed.com/viewjob?jk=bd0e7d3dab7e604a</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a42559421200137</t>
+          <t>https://www.indeed.com/viewjob?jk=905c5a2344562ab8</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6e7dd724c924aca</t>
+          <t>https://www.indeed.com/viewjob?jk=21b0eb74cf57c4a8</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Monterey, CA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8483d29d2dbde05b</t>
+          <t>https://www.indeed.com/viewjob?jk=127db1667ff89227</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=824e663391dfa6bf</t>
+          <t>https://www.indeed.com/viewjob?jk=2a42559421200137</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e8686e8d16dc84d</t>
+          <t>https://www.indeed.com/viewjob?jk=d6e7dd724c924aca</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=496d9926f80e93e9</t>
+          <t>https://www.indeed.com/viewjob?jk=8483d29d2dbde05b</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57716cf6ab6ed7a5</t>
+          <t>https://www.indeed.com/viewjob?jk=824e663391dfa6bf</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c418229c0f650f96</t>
+          <t>https://www.indeed.com/viewjob?jk=3e8686e8d16dc84d</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95121729962d91d2</t>
+          <t>https://www.indeed.com/viewjob?jk=496d9926f80e93e9</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfec58f9b4c8760a</t>
+          <t>https://www.indeed.com/viewjob?jk=57716cf6ab6ed7a5</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5153281c36740802</t>
+          <t>https://www.indeed.com/viewjob?jk=c418229c0f650f96</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=310acaaa4f9f42e3</t>
+          <t>https://www.indeed.com/viewjob?jk=95121729962d91d2</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6efe7ed3911371c4</t>
+          <t>https://www.indeed.com/viewjob?jk=dfec58f9b4c8760a</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a68cf132dbdec60</t>
+          <t>https://www.indeed.com/viewjob?jk=5153281c36740802</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d891e75a79397a9</t>
+          <t>https://www.indeed.com/viewjob?jk=310acaaa4f9f42e3</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=117634e8f8dfb2d6</t>
+          <t>https://www.indeed.com/viewjob?jk=6efe7ed3911371c4</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b83a26f124ccdb89</t>
+          <t>https://www.indeed.com/viewjob?jk=1a68cf132dbdec60</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad88505e172120de</t>
+          <t>https://www.indeed.com/viewjob?jk=8d891e75a79397a9</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c21ad262bec7ef80</t>
+          <t>https://www.indeed.com/viewjob?jk=117634e8f8dfb2d6</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca6810d972b1a5f1</t>
+          <t>https://www.indeed.com/viewjob?jk=b83a26f124ccdb89</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27043ef345d0b8a7</t>
+          <t>https://www.indeed.com/viewjob?jk=ad88505e172120de</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be347b278f12cb33</t>
+          <t>https://www.indeed.com/viewjob?jk=c21ad262bec7ef80</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fed8b15c04492576</t>
+          <t>https://www.indeed.com/viewjob?jk=ca6810d972b1a5f1</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b12133504b24bae</t>
+          <t>https://www.indeed.com/viewjob?jk=27043ef345d0b8a7</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f864d9aca9b7b27</t>
+          <t>https://www.indeed.com/viewjob?jk=be347b278f12cb33</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76d2eb1be4c1b252</t>
+          <t>https://www.indeed.com/viewjob?jk=fed8b15c04492576</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9baba2b401f1c56c</t>
+          <t>https://www.indeed.com/viewjob?jk=5b12133504b24bae</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Platform (Azure)</t>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform, Azure Monitor</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=defb19c3b807f7fd</t>
+          <t>https://www.indeed.com/viewjob?jk=9f864d9aca9b7b27</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect - WORK FROM HOME - SELECT US STATES ONLY</t>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Slavic401K</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df39dd0505c33d32</t>
+          <t>https://www.indeed.com/viewjob?jk=76d2eb1be4c1b252</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Databricks Developer</t>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab1192abfbd7f24e</t>
+          <t>https://www.indeed.com/viewjob?jk=9baba2b401f1c56c</t>
         </is>
       </c>
     </row>
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=320dcd4f927cb250</t>
+          <t>https://www.indeed.com/viewjob?jk=ab1192abfbd7f24e</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Senior Quality Engineering (QE) Engineer</t>
+          <t>Databricks Developer</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Amida Technology Solutions</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Power BI, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,32 +5466,32 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29a7f8ff4391f120</t>
+          <t>https://www.indeed.com/viewjob?jk=320dcd4f927cb250</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Associate, Data Engineer</t>
+          <t>Senior Quality Engineering (QE) Engineer</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Amida Technology Solutions</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, DynamoDB, Azure Cosmos DB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Power BI, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,24 +5501,24 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06fd6810514e5491</t>
+          <t>https://www.indeed.com/viewjob?jk=29a7f8ff4391f120</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Associate, Data Engineer</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, DynamoDB, Azure Cosmos DB, NoSQL</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,24 +5536,24 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33b30501746ad4bf</t>
+          <t>https://www.indeed.com/viewjob?jk=06fd6810514e5491</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Data Engineer - Oklahoma City, OK</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>CFS Brands, LLC</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>IAM, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5571,24 +5571,24 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=113fe7e3580ec298</t>
+          <t>https://www.indeed.com/viewjob?jk=33b30501746ad4bf</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer - Oklahoma City, OK</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Chiesi Farmaceutici S.p.A.</t>
+          <t>CFS Brands, LLC</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,34 +5596,34 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT</t>
+          <t>IAM, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78d407207abb7498</t>
+          <t>https://www.indeed.com/viewjob?jk=113fe7e3580ec298</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Apache Spark Core Java</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Chiesi Farmaceutici S.p.A.</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,34 +5631,34 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16d16eda2d514586</t>
+          <t>https://www.indeed.com/viewjob?jk=78d407207abb7498</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Marketing Sciences</t>
+          <t>Apache Spark Core Java</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>SimplePractice</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5666,34 +5666,34 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Scala, Kafka, Snowflake, ETL, dbt, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a341479dc01b56f</t>
+          <t>https://www.indeed.com/viewjob?jk=16d16eda2d514586</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>.NET Backend Developer</t>
+          <t>Senior Analytics Engineer, Marketing Sciences</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Inclusion Cloud</t>
+          <t>SimplePractice</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5701,15 +5701,50 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
+          <t>AWS, Kinesis, RDS, Scala, Kafka, Snowflake, ETL, dbt, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4a341479dc01b56f</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>.NET Backend Developer</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Inclusion Cloud</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
           <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=5c9d1b0d1d29e0d2</t>
         </is>

--- a/results/job_matches_2026-08-22.xlsx
+++ b/results/job_matches_2026-08-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G152"/>
+  <dimension ref="A1:G153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,17 +678,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer Microsoft Fabric</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bilzin Sumberg Baena Price &amp; Axelrod LLP</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Snowflake, SQL Server</t>
+          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=371409082795e582</t>
+          <t>https://www.indeed.com/viewjob?jk=515f3bff52abe8ea</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=515f3bff52abe8ea</t>
+          <t>https://www.indeed.com/viewjob?jk=f887668cf9aaf20f</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer Microsoft Fabric</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Bilzin Sumberg Baena Price &amp; Axelrod LLP</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
+          <t>S3, RDS, Azure, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f887668cf9aaf20f</t>
+          <t>https://www.indeed.com/viewjob?jk=371409082795e582</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Guild Mortgage Company LLC</t>
+          <t>Entarian</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Spark, Scala, Kafka, Snowflake, SQL Server, MySQL, MongoDB</t>
+          <t>AWS, Kinesis, Scala, Kafka, Polars, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,14 +811,14 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd674fe067dfdd34</t>
+          <t>https://www.indeed.com/viewjob?jk=97cacdd77a88ee4d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -846,19 +846,19 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97cacdd77a88ee4d</t>
+          <t>https://www.indeed.com/viewjob?jk=8d62e6c9bd298592</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Entarian</t>
+          <t>Guild Mortgage Company LLC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Scala, Kafka, Polars, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Spark, Scala, Kafka, Snowflake, SQL Server, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d62e6c9bd298592</t>
+          <t>https://www.indeed.com/viewjob?jk=fd674fe067dfdd34</t>
         </is>
       </c>
     </row>
@@ -923,17 +923,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer 3 - TS clearance required - Wash DC area</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bow Wave LLC</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, BigQuery, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61e2b94a977d2119</t>
+          <t>https://www.indeed.com/viewjob?jk=6f9e89b177e72a80</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer 3 - TS clearance required - Wash DC area</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>Bow Wave LLC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,17 +976,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, BigQuery, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f9e89b177e72a80</t>
+          <t>https://www.indeed.com/viewjob?jk=61e2b94a977d2119</t>
         </is>
       </c>
     </row>
@@ -1308,17 +1308,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer 2 - TS required - Washington DC area</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Bow Wave LLC</t>
+          <t>REPLY</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,17 +1326,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Google Cloud Platform, BigQuery, Hadoop, Spark, Scala, ETL</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, Azure Cosmos DB, Data Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de40e05b432ea8b8</t>
+          <t>https://www.indeed.com/viewjob?jk=5cc84ba97f996450</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cc84ba97f996450</t>
+          <t>https://www.indeed.com/viewjob?jk=b9d2db7b4c8d89f8</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9d2db7b4c8d89f8</t>
+          <t>https://www.indeed.com/viewjob?jk=74f4fee2cc3d811b</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74f4fee2cc3d811b</t>
+          <t>https://www.indeed.com/viewjob?jk=b7ad9782930201d7</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7ad9782930201d7</t>
+          <t>https://www.indeed.com/viewjob?jk=61bab526ed5bb2fe</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Finance Solutions, Google Cloud Platform</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>REPLY</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, Azure Cosmos DB, Data Modeling</t>
+          <t>RDS, Google Cloud Platform, GCP, Spark, PySpark, Scala, Oracle, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61bab526ed5bb2fe</t>
+          <t>https://www.indeed.com/viewjob?jk=c94336bbf2aab76d</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Finance Solutions, Google Cloud Platform</t>
+          <t>Data Engineer 2 - TS required - Washington DC area</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Bow Wave LLC</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,17 +1536,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Spark, PySpark, Scala, Oracle, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, S3, Azure, Google Cloud Platform, BigQuery, Hadoop, Spark, Scala, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c94336bbf2aab76d</t>
+          <t>https://www.indeed.com/viewjob?jk=de40e05b432ea8b8</t>
         </is>
       </c>
     </row>
@@ -1588,17 +1588,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Consultant, Data Engineer | Databricks</t>
+          <t>Software Engineer II, Data</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Credit Acceptance</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87fd62c345b8469e</t>
+          <t>https://www.indeed.com/viewjob?jk=39dcfd9f2966d672</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data</t>
+          <t>Consultant, Data Engineer | Databricks</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Credit Acceptance</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, NoSQL</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39dcfd9f2966d672</t>
+          <t>https://www.indeed.com/viewjob?jk=87fd62c345b8469e</t>
         </is>
       </c>
     </row>
@@ -1728,17 +1728,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Solutions Delivery Engineer (Remote)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>RealPage Inc</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, S3, RDS, Spark, Scala, PostgreSQL, NoSQL, Jenkins</t>
+          <t>AWS, Redshift, RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d1eabd20620b211</t>
+          <t>https://www.indeed.com/viewjob?jk=ec761fb42adb289d</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Solutions Delivery Engineer (Remote)</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>RealPage Inc</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, EMR, Kinesis, S3, RDS, Spark, Scala, PostgreSQL, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec761fb42adb289d</t>
+          <t>https://www.indeed.com/viewjob?jk=5d1eabd20620b211</t>
         </is>
       </c>
     </row>
@@ -1833,17 +1833,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Professional Services Consultant</t>
+          <t>Senior Devops Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Ataccama</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,29 +1851,29 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f49a3f3dbcbca27</t>
+          <t>https://www.indeed.com/viewjob?jk=143f81631e970888</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CDP Architect</t>
+          <t>Senior Professional Services Consultant</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Bounteous</t>
+          <t>Ataccama</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5b99e7a77983415</t>
+          <t>https://www.indeed.com/viewjob?jk=0f49a3f3dbcbca27</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Devops Engineer</t>
+          <t>CDP Architect</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Bounteous</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=143f81631e970888</t>
+          <t>https://www.indeed.com/viewjob?jk=f5b99e7a77983415</t>
         </is>
       </c>
     </row>
@@ -2148,17 +2148,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>QA Automation Engineer II, Officer</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>Mercari</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, NoSQL, Talend, CI/CD, Jenkins, Docker, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Tableau</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d73747fd9aafef8</t>
+          <t>https://www.indeed.com/viewjob?jk=179685542a7cf944</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>QA Automation Engineer II, Officer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Mercari</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Tableau</t>
+          <t>RDS, Scala, Oracle, NoSQL, Talend, CI/CD, Jenkins, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=179685542a7cf944</t>
+          <t>https://www.indeed.com/viewjob?jk=1d73747fd9aafef8</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr Engineer, Data Engineering</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Pilot Flying J</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Roswell, GA, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Kafka, CI/CD, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a70d5a50e3bc2a5</t>
+          <t>https://www.indeed.com/viewjob?jk=9a5cbb62cc968f68</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Marathon Petroleum</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Kafka, CI/CD, Terraform, Kubernetes, AKS</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a5cbb62cc968f68</t>
+          <t>https://www.indeed.com/viewjob?jk=28293fa77ffc32bb</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Marathon Petroleum</t>
+          <t>Golden State</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, CI/CD, Git, Python, SQL</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28293fa77ffc32bb</t>
+          <t>https://www.indeed.com/viewjob?jk=1d156f80ddb5ea3e</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Golden State</t>
+          <t>American Tower</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d156f80ddb5ea3e</t>
+          <t>https://www.indeed.com/viewjob?jk=340f3540cd359821</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>American Tower</t>
+          <t>Pilot Flying J</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>Roswell, GA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=340f3540cd359821</t>
+          <t>https://www.indeed.com/viewjob?jk=0a70d5a50e3bc2a5</t>
         </is>
       </c>
     </row>
@@ -2498,17 +2498,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Platform (Azure)</t>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform, Azure Monitor</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=defb19c3b807f7fd</t>
+          <t>https://www.indeed.com/viewjob?jk=f4ab3e3c7077492c</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect - WORK FROM HOME - SELECT US STATES ONLY</t>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Slavic401K</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Inglewood, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df39dd0505c33d32</t>
+          <t>https://www.indeed.com/viewjob?jk=b0870a8c631ca3e7</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4ab3e3c7077492c</t>
+          <t>https://www.indeed.com/viewjob?jk=3a8177305c7e2b4e</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Inglewood, CA, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0870a8c631ca3e7</t>
+          <t>https://www.indeed.com/viewjob?jk=2b216035065cdcce</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a8177305c7e2b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=b0d6bbe5db7dc4e3</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b216035065cdcce</t>
+          <t>https://www.indeed.com/viewjob?jk=99cd5dc3d4c47201</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0d6bbe5db7dc4e3</t>
+          <t>https://www.indeed.com/viewjob?jk=1535cff1bb626738</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Williamsville, NY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99cd5dc3d4c47201</t>
+          <t>https://www.indeed.com/viewjob?jk=37a520fdd5e099b9</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1535cff1bb626738</t>
+          <t>https://www.indeed.com/viewjob?jk=366fcdfb585bd3be</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Williamsville, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37a520fdd5e099b9</t>
+          <t>https://www.indeed.com/viewjob?jk=a94f1ea7f43f3649</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=366fcdfb585bd3be</t>
+          <t>https://www.indeed.com/viewjob?jk=497b07468d401d8a</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a94f1ea7f43f3649</t>
+          <t>https://www.indeed.com/viewjob?jk=8d2e49c364fa4321</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=497b07468d401d8a</t>
+          <t>https://www.indeed.com/viewjob?jk=14d6f7b29ae9eb47</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d2e49c364fa4321</t>
+          <t>https://www.indeed.com/viewjob?jk=e69bf4d69267775a</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14d6f7b29ae9eb47</t>
+          <t>https://www.indeed.com/viewjob?jk=22a4f690926575b6</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e69bf4d69267775a</t>
+          <t>https://www.indeed.com/viewjob?jk=7fc8f10cc4340e38</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22a4f690926575b6</t>
+          <t>https://www.indeed.com/viewjob?jk=4ed7e30adf2adc59</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fc8f10cc4340e38</t>
+          <t>https://www.indeed.com/viewjob?jk=22efcdd2b4a3dd7f</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ed7e30adf2adc59</t>
+          <t>https://www.indeed.com/viewjob?jk=4d610152102215d5</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22efcdd2b4a3dd7f</t>
+          <t>https://www.indeed.com/viewjob?jk=0f093d62f255edad</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d610152102215d5</t>
+          <t>https://www.indeed.com/viewjob?jk=61c760c7b06ee2ec</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f093d62f255edad</t>
+          <t>https://www.indeed.com/viewjob?jk=7e753698d58ce405</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61c760c7b06ee2ec</t>
+          <t>https://www.indeed.com/viewjob?jk=613c98d34d3a6aff</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e753698d58ce405</t>
+          <t>https://www.indeed.com/viewjob?jk=81eb38d16909745a</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=613c98d34d3a6aff</t>
+          <t>https://www.indeed.com/viewjob?jk=26aa4bbb65d7bc04</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81eb38d16909745a</t>
+          <t>https://www.indeed.com/viewjob?jk=51eaf011bd4b3db9</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26aa4bbb65d7bc04</t>
+          <t>https://www.indeed.com/viewjob?jk=875b54845cacd6b4</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51eaf011bd4b3db9</t>
+          <t>https://www.indeed.com/viewjob?jk=b044118f339aeefe</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=875b54845cacd6b4</t>
+          <t>https://www.indeed.com/viewjob?jk=79172907c08cbd27</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b044118f339aeefe</t>
+          <t>https://www.indeed.com/viewjob?jk=4072dd1e7bd9b46a</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79172907c08cbd27</t>
+          <t>https://www.indeed.com/viewjob?jk=60e28bece0970c90</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4072dd1e7bd9b46a</t>
+          <t>https://www.indeed.com/viewjob?jk=337e00bdabbbf617</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60e28bece0970c90</t>
+          <t>https://www.indeed.com/viewjob?jk=7008c23fbe380180</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=337e00bdabbbf617</t>
+          <t>https://www.indeed.com/viewjob?jk=ef94cdec933bb8d2</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7008c23fbe380180</t>
+          <t>https://www.indeed.com/viewjob?jk=a9b3dd72c73a5c59</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>San Juan, PR, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef94cdec933bb8d2</t>
+          <t>https://www.indeed.com/viewjob?jk=3f362104fdb5fce0</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9b3dd72c73a5c59</t>
+          <t>https://www.indeed.com/viewjob?jk=bb3766965503e1b0</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>San Juan, PR, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f362104fdb5fce0</t>
+          <t>https://www.indeed.com/viewjob?jk=01b7efd6177971eb</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb3766965503e1b0</t>
+          <t>https://www.indeed.com/viewjob?jk=564843cdd5d6c05d</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01b7efd6177971eb</t>
+          <t>https://www.indeed.com/viewjob?jk=38dc1e892863874b</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=564843cdd5d6c05d</t>
+          <t>https://www.indeed.com/viewjob?jk=36375563a2ad1043</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Honolulu, HI, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38dc1e892863874b</t>
+          <t>https://www.indeed.com/viewjob?jk=cf1ab598617115f3</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36375563a2ad1043</t>
+          <t>https://www.indeed.com/viewjob?jk=bdb4d76e4c3be44c</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Honolulu, HI, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf1ab598617115f3</t>
+          <t>https://www.indeed.com/viewjob?jk=bd706eccacda1e1c</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdb4d76e4c3be44c</t>
+          <t>https://www.indeed.com/viewjob?jk=606f854062c681fa</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd706eccacda1e1c</t>
+          <t>https://www.indeed.com/viewjob?jk=15ee32196b2a250e</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606f854062c681fa</t>
+          <t>https://www.indeed.com/viewjob?jk=c7a2ced0233034b8</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15ee32196b2a250e</t>
+          <t>https://www.indeed.com/viewjob?jk=b267004acbc01cc5</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7a2ced0233034b8</t>
+          <t>https://www.indeed.com/viewjob?jk=9be2810504f2ae29</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b267004acbc01cc5</t>
+          <t>https://www.indeed.com/viewjob?jk=6f0ec602c9b09a8e</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9be2810504f2ae29</t>
+          <t>https://www.indeed.com/viewjob?jk=bd0e7d3dab7e604a</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f0ec602c9b09a8e</t>
+          <t>https://www.indeed.com/viewjob?jk=905c5a2344562ab8</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd0e7d3dab7e604a</t>
+          <t>https://www.indeed.com/viewjob?jk=21b0eb74cf57c4a8</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Monterey, CA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=905c5a2344562ab8</t>
+          <t>https://www.indeed.com/viewjob?jk=127db1667ff89227</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21b0eb74cf57c4a8</t>
+          <t>https://www.indeed.com/viewjob?jk=2a42559421200137</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Monterey, CA, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127db1667ff89227</t>
+          <t>https://www.indeed.com/viewjob?jk=d6e7dd724c924aca</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a42559421200137</t>
+          <t>https://www.indeed.com/viewjob?jk=8483d29d2dbde05b</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6e7dd724c924aca</t>
+          <t>https://www.indeed.com/viewjob?jk=824e663391dfa6bf</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8483d29d2dbde05b</t>
+          <t>https://www.indeed.com/viewjob?jk=3e8686e8d16dc84d</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=824e663391dfa6bf</t>
+          <t>https://www.indeed.com/viewjob?jk=496d9926f80e93e9</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e8686e8d16dc84d</t>
+          <t>https://www.indeed.com/viewjob?jk=57716cf6ab6ed7a5</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=496d9926f80e93e9</t>
+          <t>https://www.indeed.com/viewjob?jk=c418229c0f650f96</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57716cf6ab6ed7a5</t>
+          <t>https://www.indeed.com/viewjob?jk=95121729962d91d2</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c418229c0f650f96</t>
+          <t>https://www.indeed.com/viewjob?jk=dfec58f9b4c8760a</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95121729962d91d2</t>
+          <t>https://www.indeed.com/viewjob?jk=5153281c36740802</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfec58f9b4c8760a</t>
+          <t>https://www.indeed.com/viewjob?jk=310acaaa4f9f42e3</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5153281c36740802</t>
+          <t>https://www.indeed.com/viewjob?jk=6efe7ed3911371c4</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=310acaaa4f9f42e3</t>
+          <t>https://www.indeed.com/viewjob?jk=1a68cf132dbdec60</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6efe7ed3911371c4</t>
+          <t>https://www.indeed.com/viewjob?jk=8d891e75a79397a9</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a68cf132dbdec60</t>
+          <t>https://www.indeed.com/viewjob?jk=117634e8f8dfb2d6</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d891e75a79397a9</t>
+          <t>https://www.indeed.com/viewjob?jk=b83a26f124ccdb89</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=117634e8f8dfb2d6</t>
+          <t>https://www.indeed.com/viewjob?jk=ad88505e172120de</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b83a26f124ccdb89</t>
+          <t>https://www.indeed.com/viewjob?jk=c21ad262bec7ef80</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad88505e172120de</t>
+          <t>https://www.indeed.com/viewjob?jk=ca6810d972b1a5f1</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c21ad262bec7ef80</t>
+          <t>https://www.indeed.com/viewjob?jk=27043ef345d0b8a7</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca6810d972b1a5f1</t>
+          <t>https://www.indeed.com/viewjob?jk=be347b278f12cb33</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27043ef345d0b8a7</t>
+          <t>https://www.indeed.com/viewjob?jk=fed8b15c04492576</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be347b278f12cb33</t>
+          <t>https://www.indeed.com/viewjob?jk=5b12133504b24bae</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fed8b15c04492576</t>
+          <t>https://www.indeed.com/viewjob?jk=9f864d9aca9b7b27</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b12133504b24bae</t>
+          <t>https://www.indeed.com/viewjob?jk=76d2eb1be4c1b252</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f864d9aca9b7b27</t>
+          <t>https://www.indeed.com/viewjob?jk=9baba2b401f1c56c</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+          <t>Enterprise Data Architect - WORK FROM HOME - SELECT US STATES ONLY</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Slavic401K</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76d2eb1be4c1b252</t>
+          <t>https://www.indeed.com/viewjob?jk=df39dd0505c33d32</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Platform (Azure)</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform, Azure Monitor</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9baba2b401f1c56c</t>
+          <t>https://www.indeed.com/viewjob?jk=defb19c3b807f7fd</t>
         </is>
       </c>
     </row>
@@ -5508,17 +5508,17 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Associate, Data Engineer</t>
+          <t>Site Reliability Engineering (SRE) - Maryland, US</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, DynamoDB, Azure Cosmos DB, NoSQL</t>
+          <t>Azure, GCP, BigQuery, Zookeeper, Scala, Kafka, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06fd6810514e5491</t>
+          <t>https://www.indeed.com/viewjob?jk=8d51d47e65997196</t>
         </is>
       </c>
     </row>
@@ -5648,17 +5648,17 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Apache Spark Core Java</t>
+          <t>Associate, Data Engineer</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5666,34 +5666,34 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, DynamoDB, Azure Cosmos DB, NoSQL</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16d16eda2d514586</t>
+          <t>https://www.indeed.com/viewjob?jk=06fd6810514e5491</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Marketing Sciences</t>
+          <t>.NET Backend Developer</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>SimplePractice</t>
+          <t>Inclusion Cloud</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Scala, Kafka, Snowflake, ETL, dbt, Terraform, Docker</t>
+          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -5711,24 +5711,24 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a341479dc01b56f</t>
+          <t>https://www.indeed.com/viewjob?jk=5c9d1b0d1d29e0d2</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>.NET Backend Developer</t>
+          <t>Apache Spark Core Java</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Inclusion Cloud</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5736,17 +5736,52 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c9d1b0d1d29e0d2</t>
+          <t>https://www.indeed.com/viewjob?jk=16d16eda2d514586</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Senior Analytics Engineer, Marketing Sciences</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>SimplePractice</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, RDS, Scala, Kafka, Snowflake, ETL, dbt, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4a341479dc01b56f</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-22.xlsx
+++ b/results/job_matches_2026-08-22.xlsx
@@ -678,17 +678,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer Microsoft Fabric</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Bilzin Sumberg Baena Price &amp; Axelrod LLP</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
+          <t>S3, RDS, Azure, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=515f3bff52abe8ea</t>
+          <t>https://www.indeed.com/viewjob?jk=371409082795e582</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f887668cf9aaf20f</t>
+          <t>https://www.indeed.com/viewjob?jk=515f3bff52abe8ea</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer Microsoft Fabric</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bilzin Sumberg Baena Price &amp; Axelrod LLP</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Snowflake, SQL Server</t>
+          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=371409082795e582</t>
+          <t>https://www.indeed.com/viewjob?jk=f887668cf9aaf20f</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Entarian</t>
+          <t>Guild Mortgage Company LLC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Scala, Kafka, Polars, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Spark, Scala, Kafka, Snowflake, SQL Server, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,14 +811,14 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97cacdd77a88ee4d</t>
+          <t>https://www.indeed.com/viewjob?jk=fd674fe067dfdd34</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -846,19 +846,19 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d62e6c9bd298592</t>
+          <t>https://www.indeed.com/viewjob?jk=97cacdd77a88ee4d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Guild Mortgage Company LLC</t>
+          <t>Entarian</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Spark, Scala, Kafka, Snowflake, SQL Server, MySQL, MongoDB</t>
+          <t>AWS, Kinesis, Scala, Kafka, Polars, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd674fe067dfdd34</t>
+          <t>https://www.indeed.com/viewjob?jk=8d62e6c9bd298592</t>
         </is>
       </c>
     </row>
@@ -923,17 +923,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer 3 - TS clearance required - Wash DC area</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>Bow Wave LLC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, BigQuery, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f9e89b177e72a80</t>
+          <t>https://www.indeed.com/viewjob?jk=61e2b94a977d2119</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer 3 - TS clearance required - Wash DC area</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bow Wave LLC</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,17 +976,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, BigQuery, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61e2b94a977d2119</t>
+          <t>https://www.indeed.com/viewjob?jk=6f9e89b177e72a80</t>
         </is>
       </c>
     </row>
@@ -1308,17 +1308,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer 2 - TS required - Washington DC area</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>REPLY</t>
+          <t>Bow Wave LLC</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,17 +1326,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, Azure Cosmos DB, Data Modeling</t>
+          <t>AWS, Redshift, S3, Azure, Google Cloud Platform, BigQuery, Hadoop, Spark, Scala, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cc84ba97f996450</t>
+          <t>https://www.indeed.com/viewjob?jk=de40e05b432ea8b8</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9d2db7b4c8d89f8</t>
+          <t>https://www.indeed.com/viewjob?jk=5cc84ba97f996450</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74f4fee2cc3d811b</t>
+          <t>https://www.indeed.com/viewjob?jk=b9d2db7b4c8d89f8</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7ad9782930201d7</t>
+          <t>https://www.indeed.com/viewjob?jk=74f4fee2cc3d811b</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61bab526ed5bb2fe</t>
+          <t>https://www.indeed.com/viewjob?jk=b7ad9782930201d7</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Finance Solutions, Google Cloud Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>REPLY</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Spark, PySpark, Scala, Oracle, Dimensional Modeling, ETL, ELT</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, Azure Cosmos DB, Data Modeling</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c94336bbf2aab76d</t>
+          <t>https://www.indeed.com/viewjob?jk=61bab526ed5bb2fe</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer 2 - TS required - Washington DC area</t>
+          <t>Finance Solutions, Google Cloud Platform</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Bow Wave LLC</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,17 +1536,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Google Cloud Platform, BigQuery, Hadoop, Spark, Scala, ETL</t>
+          <t>RDS, Google Cloud Platform, GCP, Spark, PySpark, Scala, Oracle, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de40e05b432ea8b8</t>
+          <t>https://www.indeed.com/viewjob?jk=c94336bbf2aab76d</t>
         </is>
       </c>
     </row>
@@ -1588,17 +1588,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data</t>
+          <t>Consultant, Data Engineer | Databricks</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Credit Acceptance</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, NoSQL</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39dcfd9f2966d672</t>
+          <t>https://www.indeed.com/viewjob?jk=87fd62c345b8469e</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Consultant, Data Engineer | Databricks</t>
+          <t>Software Engineer II, Data</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Credit Acceptance</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87fd62c345b8469e</t>
+          <t>https://www.indeed.com/viewjob?jk=39dcfd9f2966d672</t>
         </is>
       </c>
     </row>
@@ -1728,17 +1728,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Solutions Delivery Engineer (Remote)</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>RealPage Inc</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, EMR, Kinesis, S3, RDS, Spark, Scala, PostgreSQL, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec761fb42adb289d</t>
+          <t>https://www.indeed.com/viewjob?jk=5d1eabd20620b211</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Solutions Delivery Engineer (Remote)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>RealPage Inc</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, S3, RDS, Spark, Scala, PostgreSQL, NoSQL, Jenkins</t>
+          <t>AWS, Redshift, RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d1eabd20620b211</t>
+          <t>https://www.indeed.com/viewjob?jk=ec761fb42adb289d</t>
         </is>
       </c>
     </row>
@@ -1833,17 +1833,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Devops Engineer</t>
+          <t>Senior Professional Services Consultant</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Ataccama</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,29 +1851,29 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation</t>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=143f81631e970888</t>
+          <t>https://www.indeed.com/viewjob?jk=0f49a3f3dbcbca27</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Professional Services Consultant</t>
+          <t>CDP Architect</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Ataccama</t>
+          <t>Bounteous</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f49a3f3dbcbca27</t>
+          <t>https://www.indeed.com/viewjob?jk=f5b99e7a77983415</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CDP Architect</t>
+          <t>Senior Devops Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Bounteous</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake, ETL</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5b99e7a77983415</t>
+          <t>https://www.indeed.com/viewjob?jk=143f81631e970888</t>
         </is>
       </c>
     </row>
@@ -2148,17 +2148,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>QA Automation Engineer II, Officer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Mercari</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Tableau</t>
+          <t>RDS, Scala, Oracle, NoSQL, Talend, CI/CD, Jenkins, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=179685542a7cf944</t>
+          <t>https://www.indeed.com/viewjob?jk=1d73747fd9aafef8</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>QA Automation Engineer II, Officer</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>Mercari</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, NoSQL, Talend, CI/CD, Jenkins, Docker, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Tableau</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d73747fd9aafef8</t>
+          <t>https://www.indeed.com/viewjob?jk=179685542a7cf944</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Sr Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Pilot Flying J</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Roswell, GA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Kafka, CI/CD, Terraform, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a5cbb62cc968f68</t>
+          <t>https://www.indeed.com/viewjob?jk=0a70d5a50e3bc2a5</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Marathon Petroleum</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, CI/CD, Git, Python, SQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Kafka, CI/CD, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28293fa77ffc32bb</t>
+          <t>https://www.indeed.com/viewjob?jk=9a5cbb62cc968f68</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Golden State</t>
+          <t>Marathon Petroleum</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d156f80ddb5ea3e</t>
+          <t>https://www.indeed.com/viewjob?jk=28293fa77ffc32bb</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>American Tower</t>
+          <t>Golden State</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=340f3540cd359821</t>
+          <t>https://www.indeed.com/viewjob?jk=1d156f80ddb5ea3e</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr Engineer, Data Engineering</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Pilot Flying J</t>
+          <t>American Tower</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Roswell, GA, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a70d5a50e3bc2a5</t>
+          <t>https://www.indeed.com/viewjob?jk=340f3540cd359821</t>
         </is>
       </c>
     </row>
@@ -2498,17 +2498,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Platform (Azure)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform, Azure Monitor</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4ab3e3c7077492c</t>
+          <t>https://www.indeed.com/viewjob?jk=defb19c3b807f7fd</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+          <t>Enterprise Data Architect - WORK FROM HOME - SELECT US STATES ONLY</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Slavic401K</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Inglewood, CA, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0870a8c631ca3e7</t>
+          <t>https://www.indeed.com/viewjob?jk=df39dd0505c33d32</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a8177305c7e2b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=f4ab3e3c7077492c</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Inglewood, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b216035065cdcce</t>
+          <t>https://www.indeed.com/viewjob?jk=b0870a8c631ca3e7</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0d6bbe5db7dc4e3</t>
+          <t>https://www.indeed.com/viewjob?jk=3a8177305c7e2b4e</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99cd5dc3d4c47201</t>
+          <t>https://www.indeed.com/viewjob?jk=2b216035065cdcce</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1535cff1bb626738</t>
+          <t>https://www.indeed.com/viewjob?jk=b0d6bbe5db7dc4e3</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Williamsville, NY, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37a520fdd5e099b9</t>
+          <t>https://www.indeed.com/viewjob?jk=99cd5dc3d4c47201</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=366fcdfb585bd3be</t>
+          <t>https://www.indeed.com/viewjob?jk=1535cff1bb626738</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Williamsville, NY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a94f1ea7f43f3649</t>
+          <t>https://www.indeed.com/viewjob?jk=37a520fdd5e099b9</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=497b07468d401d8a</t>
+          <t>https://www.indeed.com/viewjob?jk=366fcdfb585bd3be</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d2e49c364fa4321</t>
+          <t>https://www.indeed.com/viewjob?jk=a94f1ea7f43f3649</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14d6f7b29ae9eb47</t>
+          <t>https://www.indeed.com/viewjob?jk=497b07468d401d8a</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e69bf4d69267775a</t>
+          <t>https://www.indeed.com/viewjob?jk=8d2e49c364fa4321</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22a4f690926575b6</t>
+          <t>https://www.indeed.com/viewjob?jk=14d6f7b29ae9eb47</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fc8f10cc4340e38</t>
+          <t>https://www.indeed.com/viewjob?jk=e69bf4d69267775a</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ed7e30adf2adc59</t>
+          <t>https://www.indeed.com/viewjob?jk=22a4f690926575b6</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22efcdd2b4a3dd7f</t>
+          <t>https://www.indeed.com/viewjob?jk=7fc8f10cc4340e38</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d610152102215d5</t>
+          <t>https://www.indeed.com/viewjob?jk=4ed7e30adf2adc59</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f093d62f255edad</t>
+          <t>https://www.indeed.com/viewjob?jk=22efcdd2b4a3dd7f</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61c760c7b06ee2ec</t>
+          <t>https://www.indeed.com/viewjob?jk=4d610152102215d5</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e753698d58ce405</t>
+          <t>https://www.indeed.com/viewjob?jk=0f093d62f255edad</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=613c98d34d3a6aff</t>
+          <t>https://www.indeed.com/viewjob?jk=61c760c7b06ee2ec</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81eb38d16909745a</t>
+          <t>https://www.indeed.com/viewjob?jk=7e753698d58ce405</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26aa4bbb65d7bc04</t>
+          <t>https://www.indeed.com/viewjob?jk=613c98d34d3a6aff</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51eaf011bd4b3db9</t>
+          <t>https://www.indeed.com/viewjob?jk=81eb38d16909745a</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=875b54845cacd6b4</t>
+          <t>https://www.indeed.com/viewjob?jk=26aa4bbb65d7bc04</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b044118f339aeefe</t>
+          <t>https://www.indeed.com/viewjob?jk=51eaf011bd4b3db9</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79172907c08cbd27</t>
+          <t>https://www.indeed.com/viewjob?jk=875b54845cacd6b4</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4072dd1e7bd9b46a</t>
+          <t>https://www.indeed.com/viewjob?jk=b044118f339aeefe</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60e28bece0970c90</t>
+          <t>https://www.indeed.com/viewjob?jk=79172907c08cbd27</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=337e00bdabbbf617</t>
+          <t>https://www.indeed.com/viewjob?jk=4072dd1e7bd9b46a</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7008c23fbe380180</t>
+          <t>https://www.indeed.com/viewjob?jk=60e28bece0970c90</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef94cdec933bb8d2</t>
+          <t>https://www.indeed.com/viewjob?jk=337e00bdabbbf617</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9b3dd72c73a5c59</t>
+          <t>https://www.indeed.com/viewjob?jk=7008c23fbe380180</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>San Juan, PR, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f362104fdb5fce0</t>
+          <t>https://www.indeed.com/viewjob?jk=ef94cdec933bb8d2</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb3766965503e1b0</t>
+          <t>https://www.indeed.com/viewjob?jk=a9b3dd72c73a5c59</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>San Juan, PR, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01b7efd6177971eb</t>
+          <t>https://www.indeed.com/viewjob?jk=3f362104fdb5fce0</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=564843cdd5d6c05d</t>
+          <t>https://www.indeed.com/viewjob?jk=bb3766965503e1b0</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38dc1e892863874b</t>
+          <t>https://www.indeed.com/viewjob?jk=01b7efd6177971eb</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36375563a2ad1043</t>
+          <t>https://www.indeed.com/viewjob?jk=564843cdd5d6c05d</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Honolulu, HI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf1ab598617115f3</t>
+          <t>https://www.indeed.com/viewjob?jk=38dc1e892863874b</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdb4d76e4c3be44c</t>
+          <t>https://www.indeed.com/viewjob?jk=36375563a2ad1043</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Honolulu, HI, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd706eccacda1e1c</t>
+          <t>https://www.indeed.com/viewjob?jk=cf1ab598617115f3</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606f854062c681fa</t>
+          <t>https://www.indeed.com/viewjob?jk=bdb4d76e4c3be44c</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15ee32196b2a250e</t>
+          <t>https://www.indeed.com/viewjob?jk=bd706eccacda1e1c</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7a2ced0233034b8</t>
+          <t>https://www.indeed.com/viewjob?jk=606f854062c681fa</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b267004acbc01cc5</t>
+          <t>https://www.indeed.com/viewjob?jk=15ee32196b2a250e</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9be2810504f2ae29</t>
+          <t>https://www.indeed.com/viewjob?jk=c7a2ced0233034b8</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f0ec602c9b09a8e</t>
+          <t>https://www.indeed.com/viewjob?jk=b267004acbc01cc5</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd0e7d3dab7e604a</t>
+          <t>https://www.indeed.com/viewjob?jk=9be2810504f2ae29</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=905c5a2344562ab8</t>
+          <t>https://www.indeed.com/viewjob?jk=6f0ec602c9b09a8e</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21b0eb74cf57c4a8</t>
+          <t>https://www.indeed.com/viewjob?jk=bd0e7d3dab7e604a</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Monterey, CA, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127db1667ff89227</t>
+          <t>https://www.indeed.com/viewjob?jk=905c5a2344562ab8</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a42559421200137</t>
+          <t>https://www.indeed.com/viewjob?jk=21b0eb74cf57c4a8</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Monterey, CA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6e7dd724c924aca</t>
+          <t>https://www.indeed.com/viewjob?jk=127db1667ff89227</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8483d29d2dbde05b</t>
+          <t>https://www.indeed.com/viewjob?jk=2a42559421200137</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=824e663391dfa6bf</t>
+          <t>https://www.indeed.com/viewjob?jk=d6e7dd724c924aca</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e8686e8d16dc84d</t>
+          <t>https://www.indeed.com/viewjob?jk=8483d29d2dbde05b</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=496d9926f80e93e9</t>
+          <t>https://www.indeed.com/viewjob?jk=824e663391dfa6bf</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57716cf6ab6ed7a5</t>
+          <t>https://www.indeed.com/viewjob?jk=3e8686e8d16dc84d</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c418229c0f650f96</t>
+          <t>https://www.indeed.com/viewjob?jk=496d9926f80e93e9</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95121729962d91d2</t>
+          <t>https://www.indeed.com/viewjob?jk=57716cf6ab6ed7a5</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfec58f9b4c8760a</t>
+          <t>https://www.indeed.com/viewjob?jk=c418229c0f650f96</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5153281c36740802</t>
+          <t>https://www.indeed.com/viewjob?jk=95121729962d91d2</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=310acaaa4f9f42e3</t>
+          <t>https://www.indeed.com/viewjob?jk=dfec58f9b4c8760a</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6efe7ed3911371c4</t>
+          <t>https://www.indeed.com/viewjob?jk=5153281c36740802</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a68cf132dbdec60</t>
+          <t>https://www.indeed.com/viewjob?jk=310acaaa4f9f42e3</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d891e75a79397a9</t>
+          <t>https://www.indeed.com/viewjob?jk=6efe7ed3911371c4</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=117634e8f8dfb2d6</t>
+          <t>https://www.indeed.com/viewjob?jk=1a68cf132dbdec60</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b83a26f124ccdb89</t>
+          <t>https://www.indeed.com/viewjob?jk=8d891e75a79397a9</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad88505e172120de</t>
+          <t>https://www.indeed.com/viewjob?jk=117634e8f8dfb2d6</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c21ad262bec7ef80</t>
+          <t>https://www.indeed.com/viewjob?jk=b83a26f124ccdb89</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca6810d972b1a5f1</t>
+          <t>https://www.indeed.com/viewjob?jk=ad88505e172120de</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27043ef345d0b8a7</t>
+          <t>https://www.indeed.com/viewjob?jk=c21ad262bec7ef80</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be347b278f12cb33</t>
+          <t>https://www.indeed.com/viewjob?jk=ca6810d972b1a5f1</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fed8b15c04492576</t>
+          <t>https://www.indeed.com/viewjob?jk=27043ef345d0b8a7</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b12133504b24bae</t>
+          <t>https://www.indeed.com/viewjob?jk=be347b278f12cb33</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f864d9aca9b7b27</t>
+          <t>https://www.indeed.com/viewjob?jk=fed8b15c04492576</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76d2eb1be4c1b252</t>
+          <t>https://www.indeed.com/viewjob?jk=5b12133504b24bae</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9baba2b401f1c56c</t>
+          <t>https://www.indeed.com/viewjob?jk=9f864d9aca9b7b27</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect - WORK FROM HOME - SELECT US STATES ONLY</t>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Slavic401K</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df39dd0505c33d32</t>
+          <t>https://www.indeed.com/viewjob?jk=76d2eb1be4c1b252</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Platform (Azure)</t>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform, Azure Monitor</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=defb19c3b807f7fd</t>
+          <t>https://www.indeed.com/viewjob?jk=9baba2b401f1c56c</t>
         </is>
       </c>
     </row>
@@ -5508,17 +5508,17 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Site Reliability Engineering (SRE) - Maryland, US</t>
+          <t>Associate, Data Engineer</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Azure, GCP, BigQuery, Zookeeper, Scala, Kafka, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, DynamoDB, Azure Cosmos DB, NoSQL</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,24 +5536,24 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d51d47e65997196</t>
+          <t>https://www.indeed.com/viewjob?jk=06fd6810514e5491</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Site Reliability Engineering (SRE) - Maryland, US</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>Azure, GCP, BigQuery, Zookeeper, Scala, Kafka, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5571,24 +5571,24 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33b30501746ad4bf</t>
+          <t>https://www.indeed.com/viewjob?jk=8d51d47e65997196</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Data Engineer - Oklahoma City, OK</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>CFS Brands, LLC</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>IAM, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5606,24 +5606,24 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=113fe7e3580ec298</t>
+          <t>https://www.indeed.com/viewjob?jk=33b30501746ad4bf</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer - Oklahoma City, OK</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Chiesi Farmaceutici S.p.A.</t>
+          <t>CFS Brands, LLC</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,34 +5631,34 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT</t>
+          <t>IAM, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78d407207abb7498</t>
+          <t>https://www.indeed.com/viewjob?jk=113fe7e3580ec298</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Associate, Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Chiesi Farmaceutici S.p.A.</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5666,34 +5666,34 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, DynamoDB, Azure Cosmos DB, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06fd6810514e5491</t>
+          <t>https://www.indeed.com/viewjob?jk=78d407207abb7498</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>.NET Backend Developer</t>
+          <t>Apache Spark Core Java</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Inclusion Cloud</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5701,34 +5701,34 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c9d1b0d1d29e0d2</t>
+          <t>https://www.indeed.com/viewjob?jk=16d16eda2d514586</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Apache Spark Core Java</t>
+          <t>Senior Analytics Engineer, Marketing Sciences</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>SimplePractice</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5736,34 +5736,34 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, RDS, Scala, Kafka, Snowflake, ETL, dbt, Terraform, Docker</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16d16eda2d514586</t>
+          <t>https://www.indeed.com/viewjob?jk=4a341479dc01b56f</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Marketing Sciences</t>
+          <t>.NET Backend Developer</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>SimplePractice</t>
+          <t>Inclusion Cloud</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Scala, Kafka, Snowflake, ETL, dbt, Terraform, Docker</t>
+          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a341479dc01b56f</t>
+          <t>https://www.indeed.com/viewjob?jk=5c9d1b0d1d29e0d2</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-22.xlsx
+++ b/results/job_matches_2026-08-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G153"/>
+  <dimension ref="A1:G149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -923,17 +923,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer 3 - TS clearance required - Wash DC area</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bow Wave LLC</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, BigQuery, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61e2b94a977d2119</t>
+          <t>https://www.indeed.com/viewjob?jk=6f9e89b177e72a80</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Engineer, Enterprise Database</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>Applied Medical</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Rancho Santa Margarita, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f9e89b177e72a80</t>
+          <t>https://www.indeed.com/viewjob?jk=51a5d6b8454480a2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Engineer, Enterprise Database</t>
+          <t>Software Engineer, Full Stack - AI (New York)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Applied Medical</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Rancho Santa Margarita, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51a5d6b8454480a2</t>
+          <t>https://www.indeed.com/viewjob?jk=362603547d1c2a0d</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer, Full Stack - AI (New York)</t>
+          <t>Sr Full stack Java Developer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Fitch Group</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
+          <t>AWS, S3, API Gateway, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=362603547d1c2a0d</t>
+          <t>https://www.indeed.com/viewjob?jk=a7f12b1ea10022a2</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7f12b1ea10022a2</t>
+          <t>https://www.indeed.com/viewjob?jk=a6bc74fdfdbbca2b</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6bc74fdfdbbca2b</t>
+          <t>https://www.indeed.com/viewjob?jk=50c5bf2319077628</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50c5bf2319077628</t>
+          <t>https://www.indeed.com/viewjob?jk=603c61b7cc5fe1b9</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Allentown, PA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=603c61b7cc5fe1b9</t>
+          <t>https://www.indeed.com/viewjob?jk=7340ebb5e99bf41f</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Allentown, PA, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7340ebb5e99bf41f</t>
+          <t>https://www.indeed.com/viewjob?jk=e7bb7609c20e949e</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr Full stack Java Developer</t>
+          <t>Senior Data Science Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Hudson Manpower</t>
+          <t>LegitScript</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, MLOps</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7bb7609c20e949e</t>
+          <t>https://www.indeed.com/viewjob?jk=0ac58242095324ac</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Science Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>LegitScript</t>
+          <t>REPLY</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, MLOps</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, Azure Cosmos DB, Data Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ac58242095324ac</t>
+          <t>https://www.indeed.com/viewjob?jk=5cc84ba97f996450</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer 2 - TS required - Washington DC area</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Bow Wave LLC</t>
+          <t>REPLY</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,17 +1326,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Google Cloud Platform, BigQuery, Hadoop, Spark, Scala, ETL</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, Azure Cosmos DB, Data Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de40e05b432ea8b8</t>
+          <t>https://www.indeed.com/viewjob?jk=b9d2db7b4c8d89f8</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cc84ba97f996450</t>
+          <t>https://www.indeed.com/viewjob?jk=74f4fee2cc3d811b</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9d2db7b4c8d89f8</t>
+          <t>https://www.indeed.com/viewjob?jk=b7ad9782930201d7</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74f4fee2cc3d811b</t>
+          <t>https://www.indeed.com/viewjob?jk=61bab526ed5bb2fe</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Finance Solutions, Google Cloud Platform</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>REPLY</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, Azure Cosmos DB, Data Modeling</t>
+          <t>RDS, Google Cloud Platform, GCP, Spark, PySpark, Scala, Oracle, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,19 +1476,19 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7ad9782930201d7</t>
+          <t>https://www.indeed.com/viewjob?jk=c94336bbf2aab76d</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>REPLY</t>
+          <t>Powerplan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, Azure Cosmos DB, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61bab526ed5bb2fe</t>
+          <t>https://www.indeed.com/viewjob?jk=9effd2546d52cd38</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Finance Solutions, Google Cloud Platform</t>
+          <t>Consultant, Data Engineer | Databricks</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Spark, PySpark, Scala, Oracle, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c94336bbf2aab76d</t>
+          <t>https://www.indeed.com/viewjob?jk=87fd62c345b8469e</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Software Engineer II, Data</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Powerplan</t>
+          <t>Credit Acceptance</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9effd2546d52cd38</t>
+          <t>https://www.indeed.com/viewjob?jk=39dcfd9f2966d672</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Consultant, Data Engineer | Databricks</t>
+          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Platform (AWS)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87fd62c345b8469e</t>
+          <t>https://www.indeed.com/viewjob?jk=7064a0875d5078f8</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Credit Acceptance</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, NoSQL</t>
+          <t>AWS, EMR, Kinesis, S3, RDS, Spark, Scala, PostgreSQL, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39dcfd9f2966d672</t>
+          <t>https://www.indeed.com/viewjob?jk=5d1eabd20620b211</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Platform (AWS)</t>
+          <t>Solutions Delivery Engineer (Remote)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>RealPage Inc</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform</t>
+          <t>AWS, Redshift, RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,59 +1686,59 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7064a0875d5078f8</t>
+          <t>https://www.indeed.com/viewjob?jk=ec761fb42adb289d</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr Machine Learning Engineer</t>
+          <t>Senior Software Development Engineer - LLMs, GenAI</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Spark, Scala, Kafka, Snowflake, DynamoDB, NoSQL, MLOps</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Power BI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=766cfaa008af94ec</t>
+          <t>https://www.indeed.com/viewjob?jk=7ef55c2266d41678</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Senior Professional Services Consultant</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Ataccama</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, S3, RDS, Spark, Scala, PostgreSQL, NoSQL, Jenkins</t>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d1eabd20620b211</t>
+          <t>https://www.indeed.com/viewjob?jk=0f49a3f3dbcbca27</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Solutions Delivery Engineer (Remote)</t>
+          <t>CDP Architect</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>RealPage Inc</t>
+          <t>Bounteous</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec761fb42adb289d</t>
+          <t>https://www.indeed.com/viewjob?jk=f5b99e7a77983415</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer - LLMs, GenAI</t>
+          <t>Senior Devops Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Power BI, Docker, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ef55c2266d41678</t>
+          <t>https://www.indeed.com/viewjob?jk=143f81631e970888</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Professional Services Consultant</t>
+          <t>Senior Full stack Java / AWS</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Ataccama</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,42 +1851,42 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f49a3f3dbcbca27</t>
+          <t>https://www.indeed.com/viewjob?jk=648c04000182f970</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CDP Architect</t>
+          <t>Azure IoT Solutions Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Bounteous</t>
+          <t>Ascend Technologies</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake, ETL</t>
+          <t>RDS, Azure, Event Hubs, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5b99e7a77983415</t>
+          <t>https://www.indeed.com/viewjob?jk=48463a0b2c1a516b</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Devops Engineer</t>
+          <t>GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation</t>
+          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=143f81631e970888</t>
+          <t>https://www.indeed.com/viewjob?jk=6b7cc426dbd03f0e</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Full stack Java / AWS</t>
+          <t>Economic Data System Engineer/Sr. Economic Data System Engineer-ITDDPED</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL, DynamoDB, CI/CD</t>
+          <t>RDS, Databricks, BigQuery, Hadoop, Spark, Scala, Snowflake, NoSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=648c04000182f970</t>
+          <t>https://www.indeed.com/viewjob?jk=3a32b2285f6e0f19</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Azure IoT Solutions Engineer</t>
+          <t>Data Engineer Denodo</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Ascend Technologies</t>
+          <t>Flowserve</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AKS, Jenkins</t>
+          <t>Azure, Synapse Analytics, Databricks, Scala, Snowflake, Oracle, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48463a0b2c1a516b</t>
+          <t>https://www.indeed.com/viewjob?jk=b87d344718e073fe</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>GCP Cloud Engineer</t>
+          <t>QA Automation Engineer II, Officer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD, Terraform, Docker</t>
+          <t>RDS, Scala, Oracle, NoSQL, Talend, CI/CD, Jenkins, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b7cc426dbd03f0e</t>
+          <t>https://www.indeed.com/viewjob?jk=1d73747fd9aafef8</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Economic Data System Engineer/Sr. Economic Data System Engineer-ITDDPED</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Mercari</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Hadoop, Spark, Scala, Snowflake, NoSQL, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Tableau</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a32b2285f6e0f19</t>
+          <t>https://www.indeed.com/viewjob?jk=179685542a7cf944</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer Denodo</t>
+          <t>Sr Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Flowserve</t>
+          <t>Pilot Flying J</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Roswell, GA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Databricks, Scala, Snowflake, Oracle, SQL Server, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b87d344718e073fe</t>
+          <t>https://www.indeed.com/viewjob?jk=0a70d5a50e3bc2a5</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Kafka, CI/CD, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae435ef03aa1b3c0</t>
+          <t>https://www.indeed.com/viewjob?jk=9a5cbb62cc968f68</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>QA Automation Engineer II, Officer</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>Marathon Petroleum</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, NoSQL, Talend, CI/CD, Jenkins, Docker, Jenkins, Git</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d73747fd9aafef8</t>
+          <t>https://www.indeed.com/viewjob?jk=28293fa77ffc32bb</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Mercari</t>
+          <t>Golden State</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Tableau</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=179685542a7cf944</t>
+          <t>https://www.indeed.com/viewjob?jk=1d156f80ddb5ea3e</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr Engineer, Data Engineering</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Pilot Flying J</t>
+          <t>American Tower</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Roswell, GA, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a70d5a50e3bc2a5</t>
+          <t>https://www.indeed.com/viewjob?jk=340f3540cd359821</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior Data Engineer – Advanced Data Integration &amp; Cloud Solutions</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Everforth ECS</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Kafka, CI/CD, Terraform, Kubernetes, AKS</t>
+          <t>ECS, RDS, Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, ETL, Python, SQL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a5cbb62cc968f68</t>
+          <t>https://www.indeed.com/viewjob?jk=ca1d4ee2bfb7f383</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>AI Engineer/DevOps Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Marathon Petroleum</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, CI/CD, Git, Python, SQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, Splunk, CI/CD, Azure DevOps, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28293fa77ffc32bb</t>
+          <t>https://www.indeed.com/viewjob?jk=a4e19bdfcdfa54e3</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Analyst, Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Golden State</t>
+          <t>Lincoln Electric</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d156f80ddb5ea3e</t>
+          <t>https://www.indeed.com/viewjob?jk=8382e0121c068a19</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>American Tower</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=340f3540cd359821</t>
+          <t>https://www.indeed.com/viewjob?jk=f4ab3e3c7077492c</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Advanced Data Integration &amp; Cloud Solutions</t>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Everforth ECS</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Inglewood, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, ETL, Python, SQL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca1d4ee2bfb7f383</t>
+          <t>https://www.indeed.com/viewjob?jk=b0870a8c631ca3e7</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AI Engineer/DevOps Engineer</t>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, Splunk, CI/CD, Azure DevOps, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4e19bdfcdfa54e3</t>
+          <t>https://www.indeed.com/viewjob?jk=3a8177305c7e2b4e</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Analyst, Data Engineer</t>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Lincoln Electric</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,19 +2491,19 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8382e0121c068a19</t>
+          <t>https://www.indeed.com/viewjob?jk=2b216035065cdcce</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Platform (Azure)</t>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform, Azure Monitor</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=defb19c3b807f7fd</t>
+          <t>https://www.indeed.com/viewjob?jk=b0d6bbe5db7dc4e3</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect - WORK FROM HOME - SELECT US STATES ONLY</t>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Slavic401K</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df39dd0505c33d32</t>
+          <t>https://www.indeed.com/viewjob?jk=99cd5dc3d4c47201</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4ab3e3c7077492c</t>
+          <t>https://www.indeed.com/viewjob?jk=1535cff1bb626738</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Inglewood, CA, US USA</t>
+          <t>Williamsville, NY, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0870a8c631ca3e7</t>
+          <t>https://www.indeed.com/viewjob?jk=37a520fdd5e099b9</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a8177305c7e2b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=366fcdfb585bd3be</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b216035065cdcce</t>
+          <t>https://www.indeed.com/viewjob?jk=a94f1ea7f43f3649</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0d6bbe5db7dc4e3</t>
+          <t>https://www.indeed.com/viewjob?jk=497b07468d401d8a</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99cd5dc3d4c47201</t>
+          <t>https://www.indeed.com/viewjob?jk=8d2e49c364fa4321</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1535cff1bb626738</t>
+          <t>https://www.indeed.com/viewjob?jk=14d6f7b29ae9eb47</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Williamsville, NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37a520fdd5e099b9</t>
+          <t>https://www.indeed.com/viewjob?jk=e69bf4d69267775a</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=366fcdfb585bd3be</t>
+          <t>https://www.indeed.com/viewjob?jk=22a4f690926575b6</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a94f1ea7f43f3649</t>
+          <t>https://www.indeed.com/viewjob?jk=7fc8f10cc4340e38</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=497b07468d401d8a</t>
+          <t>https://www.indeed.com/viewjob?jk=4ed7e30adf2adc59</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d2e49c364fa4321</t>
+          <t>https://www.indeed.com/viewjob?jk=22efcdd2b4a3dd7f</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14d6f7b29ae9eb47</t>
+          <t>https://www.indeed.com/viewjob?jk=4d610152102215d5</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e69bf4d69267775a</t>
+          <t>https://www.indeed.com/viewjob?jk=0f093d62f255edad</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22a4f690926575b6</t>
+          <t>https://www.indeed.com/viewjob?jk=61c760c7b06ee2ec</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fc8f10cc4340e38</t>
+          <t>https://www.indeed.com/viewjob?jk=7e753698d58ce405</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ed7e30adf2adc59</t>
+          <t>https://www.indeed.com/viewjob?jk=613c98d34d3a6aff</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22efcdd2b4a3dd7f</t>
+          <t>https://www.indeed.com/viewjob?jk=81eb38d16909745a</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d610152102215d5</t>
+          <t>https://www.indeed.com/viewjob?jk=26aa4bbb65d7bc04</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f093d62f255edad</t>
+          <t>https://www.indeed.com/viewjob?jk=51eaf011bd4b3db9</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61c760c7b06ee2ec</t>
+          <t>https://www.indeed.com/viewjob?jk=875b54845cacd6b4</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e753698d58ce405</t>
+          <t>https://www.indeed.com/viewjob?jk=b044118f339aeefe</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=613c98d34d3a6aff</t>
+          <t>https://www.indeed.com/viewjob?jk=79172907c08cbd27</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81eb38d16909745a</t>
+          <t>https://www.indeed.com/viewjob?jk=4072dd1e7bd9b46a</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26aa4bbb65d7bc04</t>
+          <t>https://www.indeed.com/viewjob?jk=60e28bece0970c90</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51eaf011bd4b3db9</t>
+          <t>https://www.indeed.com/viewjob?jk=337e00bdabbbf617</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=875b54845cacd6b4</t>
+          <t>https://www.indeed.com/viewjob?jk=7008c23fbe380180</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b044118f339aeefe</t>
+          <t>https://www.indeed.com/viewjob?jk=ef94cdec933bb8d2</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79172907c08cbd27</t>
+          <t>https://www.indeed.com/viewjob?jk=a9b3dd72c73a5c59</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Juan, PR, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4072dd1e7bd9b46a</t>
+          <t>https://www.indeed.com/viewjob?jk=3f362104fdb5fce0</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60e28bece0970c90</t>
+          <t>https://www.indeed.com/viewjob?jk=bb3766965503e1b0</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=337e00bdabbbf617</t>
+          <t>https://www.indeed.com/viewjob?jk=01b7efd6177971eb</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7008c23fbe380180</t>
+          <t>https://www.indeed.com/viewjob?jk=564843cdd5d6c05d</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef94cdec933bb8d2</t>
+          <t>https://www.indeed.com/viewjob?jk=38dc1e892863874b</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9b3dd72c73a5c59</t>
+          <t>https://www.indeed.com/viewjob?jk=36375563a2ad1043</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>San Juan, PR, US USA</t>
+          <t>Honolulu, HI, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f362104fdb5fce0</t>
+          <t>https://www.indeed.com/viewjob?jk=cf1ab598617115f3</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb3766965503e1b0</t>
+          <t>https://www.indeed.com/viewjob?jk=bdb4d76e4c3be44c</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01b7efd6177971eb</t>
+          <t>https://www.indeed.com/viewjob?jk=bd706eccacda1e1c</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=564843cdd5d6c05d</t>
+          <t>https://www.indeed.com/viewjob?jk=606f854062c681fa</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38dc1e892863874b</t>
+          <t>https://www.indeed.com/viewjob?jk=15ee32196b2a250e</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36375563a2ad1043</t>
+          <t>https://www.indeed.com/viewjob?jk=c7a2ced0233034b8</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Honolulu, HI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf1ab598617115f3</t>
+          <t>https://www.indeed.com/viewjob?jk=b267004acbc01cc5</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdb4d76e4c3be44c</t>
+          <t>https://www.indeed.com/viewjob?jk=9be2810504f2ae29</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd706eccacda1e1c</t>
+          <t>https://www.indeed.com/viewjob?jk=6f0ec602c9b09a8e</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606f854062c681fa</t>
+          <t>https://www.indeed.com/viewjob?jk=bd0e7d3dab7e604a</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15ee32196b2a250e</t>
+          <t>https://www.indeed.com/viewjob?jk=905c5a2344562ab8</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7a2ced0233034b8</t>
+          <t>https://www.indeed.com/viewjob?jk=21b0eb74cf57c4a8</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Monterey, CA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b267004acbc01cc5</t>
+          <t>https://www.indeed.com/viewjob?jk=127db1667ff89227</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9be2810504f2ae29</t>
+          <t>https://www.indeed.com/viewjob?jk=2a42559421200137</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f0ec602c9b09a8e</t>
+          <t>https://www.indeed.com/viewjob?jk=d6e7dd724c924aca</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd0e7d3dab7e604a</t>
+          <t>https://www.indeed.com/viewjob?jk=8483d29d2dbde05b</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=905c5a2344562ab8</t>
+          <t>https://www.indeed.com/viewjob?jk=824e663391dfa6bf</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21b0eb74cf57c4a8</t>
+          <t>https://www.indeed.com/viewjob?jk=3e8686e8d16dc84d</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Monterey, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127db1667ff89227</t>
+          <t>https://www.indeed.com/viewjob?jk=496d9926f80e93e9</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a42559421200137</t>
+          <t>https://www.indeed.com/viewjob?jk=57716cf6ab6ed7a5</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6e7dd724c924aca</t>
+          <t>https://www.indeed.com/viewjob?jk=c418229c0f650f96</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8483d29d2dbde05b</t>
+          <t>https://www.indeed.com/viewjob?jk=95121729962d91d2</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=824e663391dfa6bf</t>
+          <t>https://www.indeed.com/viewjob?jk=dfec58f9b4c8760a</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e8686e8d16dc84d</t>
+          <t>https://www.indeed.com/viewjob?jk=5153281c36740802</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=496d9926f80e93e9</t>
+          <t>https://www.indeed.com/viewjob?jk=310acaaa4f9f42e3</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57716cf6ab6ed7a5</t>
+          <t>https://www.indeed.com/viewjob?jk=6efe7ed3911371c4</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c418229c0f650f96</t>
+          <t>https://www.indeed.com/viewjob?jk=1a68cf132dbdec60</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95121729962d91d2</t>
+          <t>https://www.indeed.com/viewjob?jk=8d891e75a79397a9</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfec58f9b4c8760a</t>
+          <t>https://www.indeed.com/viewjob?jk=117634e8f8dfb2d6</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5153281c36740802</t>
+          <t>https://www.indeed.com/viewjob?jk=b83a26f124ccdb89</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=310acaaa4f9f42e3</t>
+          <t>https://www.indeed.com/viewjob?jk=ad88505e172120de</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6efe7ed3911371c4</t>
+          <t>https://www.indeed.com/viewjob?jk=c21ad262bec7ef80</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a68cf132dbdec60</t>
+          <t>https://www.indeed.com/viewjob?jk=ca6810d972b1a5f1</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d891e75a79397a9</t>
+          <t>https://www.indeed.com/viewjob?jk=27043ef345d0b8a7</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=117634e8f8dfb2d6</t>
+          <t>https://www.indeed.com/viewjob?jk=be347b278f12cb33</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b83a26f124ccdb89</t>
+          <t>https://www.indeed.com/viewjob?jk=fed8b15c04492576</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad88505e172120de</t>
+          <t>https://www.indeed.com/viewjob?jk=5b12133504b24bae</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c21ad262bec7ef80</t>
+          <t>https://www.indeed.com/viewjob?jk=9f864d9aca9b7b27</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca6810d972b1a5f1</t>
+          <t>https://www.indeed.com/viewjob?jk=76d2eb1be4c1b252</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27043ef345d0b8a7</t>
+          <t>https://www.indeed.com/viewjob?jk=9baba2b401f1c56c</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Platform (Azure)</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform, Azure Monitor</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be347b278f12cb33</t>
+          <t>https://www.indeed.com/viewjob?jk=defb19c3b807f7fd</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+          <t>Enterprise Data Architect - WORK FROM HOME - SELECT US STATES ONLY</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Slavic401K</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fed8b15c04492576</t>
+          <t>https://www.indeed.com/viewjob?jk=df39dd0505c33d32</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+          <t>Databricks Developer</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b12133504b24bae</t>
+          <t>https://www.indeed.com/viewjob?jk=ab1192abfbd7f24e</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+          <t>Databricks Developer</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f864d9aca9b7b27</t>
+          <t>https://www.indeed.com/viewjob?jk=320dcd4f927cb250</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+          <t>Senior Quality Engineering (QE) Engineer</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Amida Technology Solutions</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Power BI, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,32 +5361,32 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76d2eb1be4c1b252</t>
+          <t>https://www.indeed.com/viewjob?jk=29a7f8ff4391f120</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+          <t>Associate, Data Engineer</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, DynamoDB, Azure Cosmos DB, NoSQL</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,32 +5396,32 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9baba2b401f1c56c</t>
+          <t>https://www.indeed.com/viewjob?jk=06fd6810514e5491</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Databricks Developer</t>
+          <t>Site Reliability Engineering (SRE) - Maryland, US</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>Azure, GCP, BigQuery, Zookeeper, Scala, Kafka, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,32 +5431,32 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab1192abfbd7f24e</t>
+          <t>https://www.indeed.com/viewjob?jk=8d51d47e65997196</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Databricks Developer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,32 +5466,32 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=320dcd4f927cb250</t>
+          <t>https://www.indeed.com/viewjob?jk=33b30501746ad4bf</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Senior Quality Engineering (QE) Engineer</t>
+          <t>Data Engineer - Oklahoma City, OK</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Amida Technology Solutions</t>
+          <t>CFS Brands, LLC</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Power BI, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>IAM, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,24 +5501,24 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29a7f8ff4391f120</t>
+          <t>https://www.indeed.com/viewjob?jk=113fe7e3580ec298</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Associate, Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Chiesi Farmaceutici S.p.A.</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,34 +5526,34 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, DynamoDB, Azure Cosmos DB, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06fd6810514e5491</t>
+          <t>https://www.indeed.com/viewjob?jk=78d407207abb7498</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Site Reliability Engineering (SRE) - Maryland, US</t>
+          <t>Apache Spark Core Java</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,34 +5561,34 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Azure, GCP, BigQuery, Zookeeper, Scala, Kafka, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d51d47e65997196</t>
+          <t>https://www.indeed.com/viewjob?jk=16d16eda2d514586</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Analytics Engineer, Marketing Sciences</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>SimplePractice</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Kinesis, RDS, Scala, Kafka, Snowflake, ETL, dbt, Terraform, Docker</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5606,24 +5606,24 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33b30501746ad4bf</t>
+          <t>https://www.indeed.com/viewjob?jk=4a341479dc01b56f</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Data Engineer - Oklahoma City, OK</t>
+          <t>.NET Backend Developer</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>CFS Brands, LLC</t>
+          <t>Inclusion Cloud</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>IAM, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5640,146 +5640,6 @@
         </is>
       </c>
       <c r="G149" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=113fe7e3580ec298</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>Chiesi Farmaceutici S.p.A.</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Cary, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D150" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=78d407207abb7498</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>Apache Spark Core Java</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D151" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>2026-08-22</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=16d16eda2d514586</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>Senior Analytics Engineer, Marketing Sciences</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>SimplePractice</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D152" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, RDS, Scala, Kafka, Snowflake, ETL, dbt, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4a341479dc01b56f</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>.NET Backend Developer</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>Inclusion Cloud</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D153" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=5c9d1b0d1d29e0d2</t>
         </is>

--- a/results/job_matches_2026-08-22.xlsx
+++ b/results/job_matches_2026-08-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G149"/>
+  <dimension ref="A1:G146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1518,17 +1518,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Consultant, Data Engineer | Databricks</t>
+          <t>Software Engineer II, Data</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Credit Acceptance</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87fd62c345b8469e</t>
+          <t>https://www.indeed.com/viewjob?jk=39dcfd9f2966d672</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data</t>
+          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Platform (AWS)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Credit Acceptance</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, NoSQL</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39dcfd9f2966d672</t>
+          <t>https://www.indeed.com/viewjob?jk=7064a0875d5078f8</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Platform (AWS)</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform</t>
+          <t>AWS, EMR, Kinesis, S3, RDS, Spark, Scala, PostgreSQL, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7064a0875d5078f8</t>
+          <t>https://www.indeed.com/viewjob?jk=5d1eabd20620b211</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Solutions Delivery Engineer (Remote)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>RealPage Inc</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, S3, RDS, Spark, Scala, PostgreSQL, NoSQL, Jenkins</t>
+          <t>AWS, Redshift, RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d1eabd20620b211</t>
+          <t>https://www.indeed.com/viewjob?jk=ec761fb42adb289d</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Solutions Delivery Engineer (Remote)</t>
+          <t>Senior Software Development Engineer - LLMs, GenAI</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>RealPage Inc</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Power BI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec761fb42adb289d</t>
+          <t>https://www.indeed.com/viewjob?jk=7ef55c2266d41678</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer - LLMs, GenAI</t>
+          <t>Senior Professional Services Consultant</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Ataccama</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Power BI, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,19 +1721,19 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ef55c2266d41678</t>
+          <t>https://www.indeed.com/viewjob?jk=0f49a3f3dbcbca27</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Professional Services Consultant</t>
+          <t>CDP Architect</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ataccama</t>
+          <t>Bounteous</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f49a3f3dbcbca27</t>
+          <t>https://www.indeed.com/viewjob?jk=f5b99e7a77983415</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CDP Architect</t>
+          <t>Senior Devops Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Bounteous</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake, ETL</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5b99e7a77983415</t>
+          <t>https://www.indeed.com/viewjob?jk=143f81631e970888</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Devops Engineer</t>
+          <t>Senior Full stack Java / AWS</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation</t>
+          <t>AWS, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=143f81631e970888</t>
+          <t>https://www.indeed.com/viewjob?jk=648c04000182f970</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Full stack Java / AWS</t>
+          <t>Azure IoT Solutions Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Ascend Technologies</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL, DynamoDB, CI/CD</t>
+          <t>RDS, Azure, Event Hubs, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=648c04000182f970</t>
+          <t>https://www.indeed.com/viewjob?jk=48463a0b2c1a516b</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Azure IoT Solutions Engineer</t>
+          <t>GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Ascend Technologies</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AKS, Jenkins</t>
+          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48463a0b2c1a516b</t>
+          <t>https://www.indeed.com/viewjob?jk=6b7cc426dbd03f0e</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>GCP Cloud Engineer</t>
+          <t>Economic Data System Engineer/Sr. Economic Data System Engineer-ITDDPED</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD, Terraform, Docker</t>
+          <t>RDS, Databricks, BigQuery, Hadoop, Spark, Scala, Snowflake, NoSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b7cc426dbd03f0e</t>
+          <t>https://www.indeed.com/viewjob?jk=3a32b2285f6e0f19</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Economic Data System Engineer/Sr. Economic Data System Engineer-ITDDPED</t>
+          <t>QA Automation Engineer II, Officer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Hadoop, Spark, Scala, Snowflake, NoSQL, ETL, ELT</t>
+          <t>RDS, Scala, Oracle, NoSQL, Talend, CI/CD, Jenkins, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a32b2285f6e0f19</t>
+          <t>https://www.indeed.com/viewjob?jk=1d73747fd9aafef8</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer Denodo</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Flowserve</t>
+          <t>Mercari</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Databricks, Scala, Snowflake, Oracle, SQL Server, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Tableau</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b87d344718e073fe</t>
+          <t>https://www.indeed.com/viewjob?jk=179685542a7cf944</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>QA Automation Engineer II, Officer</t>
+          <t>Sr Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>Pilot Flying J</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>Roswell, GA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, NoSQL, Talend, CI/CD, Jenkins, Docker, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d73747fd9aafef8</t>
+          <t>https://www.indeed.com/viewjob?jk=0a70d5a50e3bc2a5</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Mercari</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Tableau</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Kafka, CI/CD, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=179685542a7cf944</t>
+          <t>https://www.indeed.com/viewjob?jk=9a5cbb62cc968f68</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr Engineer, Data Engineering</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Pilot Flying J</t>
+          <t>Marathon Petroleum</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Roswell, GA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a70d5a50e3bc2a5</t>
+          <t>https://www.indeed.com/viewjob?jk=28293fa77ffc32bb</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Golden State</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Kafka, CI/CD, Terraform, Kubernetes, AKS</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a5cbb62cc968f68</t>
+          <t>https://www.indeed.com/viewjob?jk=1d156f80ddb5ea3e</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Marathon Petroleum</t>
+          <t>American Tower</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, CI/CD, Git, Python, SQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28293fa77ffc32bb</t>
+          <t>https://www.indeed.com/viewjob?jk=340f3540cd359821</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer – Advanced Data Integration &amp; Cloud Solutions</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Golden State</t>
+          <t>Everforth ECS</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>ECS, RDS, Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, ETL, Python, SQL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d156f80ddb5ea3e</t>
+          <t>https://www.indeed.com/viewjob?jk=ca1d4ee2bfb7f383</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Engineer/DevOps Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>American Tower</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, Splunk, CI/CD, Azure DevOps, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=340f3540cd359821</t>
+          <t>https://www.indeed.com/viewjob?jk=a4e19bdfcdfa54e3</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Advanced Data Integration &amp; Cloud Solutions</t>
+          <t>Senior Analyst, Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Everforth ECS</t>
+          <t>Lincoln Electric</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, ETL, Python, SQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca1d4ee2bfb7f383</t>
+          <t>https://www.indeed.com/viewjob?jk=8382e0121c068a19</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AI Engineer/DevOps Engineer</t>
+          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Platform (Azure)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, Splunk, CI/CD, Azure DevOps, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform, Azure Monitor</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4e19bdfcdfa54e3</t>
+          <t>https://www.indeed.com/viewjob?jk=defb19c3b807f7fd</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Analyst, Data Engineer</t>
+          <t>Enterprise Data Architect - WORK FROM HOME - SELECT US STATES ONLY</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Lincoln Electric</t>
+          <t>Slavic401K</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8382e0121c068a19</t>
+          <t>https://www.indeed.com/viewjob?jk=df39dd0505c33d32</t>
         </is>
       </c>
     </row>
@@ -5193,17 +5193,17 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Platform (Azure)</t>
+          <t>Databricks Developer</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform, Azure Monitor</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=defb19c3b807f7fd</t>
+          <t>https://www.indeed.com/viewjob?jk=ab1192abfbd7f24e</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect - WORK FROM HOME - SELECT US STATES ONLY</t>
+          <t>Databricks Developer</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Slavic401K</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df39dd0505c33d32</t>
+          <t>https://www.indeed.com/viewjob?jk=320dcd4f927cb250</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Databricks Developer</t>
+          <t>Senior Quality Engineering (QE) Engineer</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Amida Technology Solutions</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Power BI, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,32 +5291,32 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab1192abfbd7f24e</t>
+          <t>https://www.indeed.com/viewjob?jk=29a7f8ff4391f120</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Databricks Developer</t>
+          <t>Associate, Data Engineer</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, DynamoDB, Azure Cosmos DB, NoSQL</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,32 +5326,32 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=320dcd4f927cb250</t>
+          <t>https://www.indeed.com/viewjob?jk=06fd6810514e5491</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Senior Quality Engineering (QE) Engineer</t>
+          <t>Site Reliability Engineering (SRE) - Maryland, US</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Amida Technology Solutions</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Power BI, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>Azure, GCP, BigQuery, Zookeeper, Scala, Kafka, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29a7f8ff4391f120</t>
+          <t>https://www.indeed.com/viewjob?jk=8d51d47e65997196</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Associate, Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, DynamoDB, Azure Cosmos DB, NoSQL</t>
+          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06fd6810514e5491</t>
+          <t>https://www.indeed.com/viewjob?jk=33b30501746ad4bf</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Site Reliability Engineering (SRE) - Maryland, US</t>
+          <t>Data Engineer - Oklahoma City, OK</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>CFS Brands, LLC</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Azure, GCP, BigQuery, Zookeeper, Scala, Kafka, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>IAM, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d51d47e65997196</t>
+          <t>https://www.indeed.com/viewjob?jk=113fe7e3580ec298</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Chiesi Farmaceutici S.p.A.</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,34 +5456,34 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33b30501746ad4bf</t>
+          <t>https://www.indeed.com/viewjob?jk=78d407207abb7498</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Data Engineer - Oklahoma City, OK</t>
+          <t>Apache Spark Core Java</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>CFS Brands, LLC</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,34 +5491,34 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>IAM, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=113fe7e3580ec298</t>
+          <t>https://www.indeed.com/viewjob?jk=16d16eda2d514586</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Analytics Engineer, Marketing Sciences</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Chiesi Farmaceutici S.p.A.</t>
+          <t>SimplePractice</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,122 +5526,17 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT</t>
+          <t>AWS, Kinesis, RDS, Scala, Kafka, Snowflake, ETL, dbt, Terraform, Docker</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78d407207abb7498</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Apache Spark Core Java</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D147" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>2026-08-22</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=16d16eda2d514586</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Senior Analytics Engineer, Marketing Sciences</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>SimplePractice</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D148" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, RDS, Scala, Kafka, Snowflake, ETL, dbt, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=4a341479dc01b56f</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>.NET Backend Developer</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Inclusion Cloud</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D149" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5c9d1b0d1d29e0d2</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-22.xlsx
+++ b/results/job_matches_2026-08-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G146"/>
+  <dimension ref="A1:G142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,25 +643,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Engineer- Full Stack USA</t>
+          <t>Data Engineer Microsoft Fabric</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>First Solar</t>
+          <t>Bilzin Sumberg Baena Price &amp; Axelrod LLP</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Perrysburg, OH, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>S3, RDS, Azure, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feaf58186fd25df4</t>
+          <t>https://www.indeed.com/viewjob?jk=371409082795e582</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer Microsoft Fabric</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bilzin Sumberg Baena Price &amp; Axelrod LLP</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Snowflake, SQL Server</t>
+          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=371409082795e582</t>
+          <t>https://www.indeed.com/viewjob?jk=515f3bff52abe8ea</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=515f3bff52abe8ea</t>
+          <t>https://www.indeed.com/viewjob?jk=f887668cf9aaf20f</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Guild Mortgage Company LLC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, Redshift, RDS, Spark, Scala, Kafka, Snowflake, SQL Server, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f887668cf9aaf20f</t>
+          <t>https://www.indeed.com/viewjob?jk=fd674fe067dfdd34</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Guild Mortgage Company LLC</t>
+          <t>Entarian</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Spark, Scala, Kafka, Snowflake, SQL Server, MySQL, MongoDB</t>
+          <t>AWS, Kinesis, Scala, Kafka, Polars, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,14 +811,14 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd674fe067dfdd34</t>
+          <t>https://www.indeed.com/viewjob?jk=97cacdd77a88ee4d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97cacdd77a88ee4d</t>
+          <t>https://www.indeed.com/viewjob?jk=8d62e6c9bd298592</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Platform System Administrator III</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Entarian</t>
+          <t>Boston Scientific</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Arden Hills, MN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Scala, Kafka, Polars, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d62e6c9bd298592</t>
+          <t>https://www.indeed.com/viewjob?jk=62388f603bbe60a4</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI Platform System Administrator III</t>
+          <t>Senior Engineer, Enterprise Database</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Boston Scientific</t>
+          <t>Applied Medical</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Arden Hills, MN, US USA</t>
+          <t>Rancho Santa Margarita, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62388f603bbe60a4</t>
+          <t>https://www.indeed.com/viewjob?jk=51a5d6b8454480a2</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer, Full Stack - AI (New York)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f9e89b177e72a80</t>
+          <t>https://www.indeed.com/viewjob?jk=362603547d1c2a0d</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Engineer, Enterprise Database</t>
+          <t>Sr Full stack Java Developer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Applied Medical</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Rancho Santa Margarita, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, S3, API Gateway, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51a5d6b8454480a2</t>
+          <t>https://www.indeed.com/viewjob?jk=a7f12b1ea10022a2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer, Full Stack - AI (New York)</t>
+          <t>Sr Full stack Java Developer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Fitch Group</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
+          <t>AWS, S3, API Gateway, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=362603547d1c2a0d</t>
+          <t>https://www.indeed.com/viewjob?jk=a6bc74fdfdbbca2b</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7f12b1ea10022a2</t>
+          <t>https://www.indeed.com/viewjob?jk=50c5bf2319077628</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6bc74fdfdbbca2b</t>
+          <t>https://www.indeed.com/viewjob?jk=603c61b7cc5fe1b9</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Allentown, PA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50c5bf2319077628</t>
+          <t>https://www.indeed.com/viewjob?jk=7340ebb5e99bf41f</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=603c61b7cc5fe1b9</t>
+          <t>https://www.indeed.com/viewjob?jk=e7bb7609c20e949e</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr Full stack Java Developer</t>
+          <t>Senior Data Science Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Hudson Manpower</t>
+          <t>LegitScript</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Allentown, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, MLOps</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7340ebb5e99bf41f</t>
+          <t>https://www.indeed.com/viewjob?jk=0ac58242095324ac</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr Full stack Java Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Hudson Manpower</t>
+          <t>REPLY</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, Azure Cosmos DB, Data Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7bb7609c20e949e</t>
+          <t>https://www.indeed.com/viewjob?jk=5cc84ba97f996450</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Science Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>LegitScript</t>
+          <t>REPLY</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, MLOps</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, Azure Cosmos DB, Data Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ac58242095324ac</t>
+          <t>https://www.indeed.com/viewjob?jk=b9d2db7b4c8d89f8</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cc84ba97f996450</t>
+          <t>https://www.indeed.com/viewjob?jk=74f4fee2cc3d811b</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9d2db7b4c8d89f8</t>
+          <t>https://www.indeed.com/viewjob?jk=b7ad9782930201d7</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74f4fee2cc3d811b</t>
+          <t>https://www.indeed.com/viewjob?jk=61bab526ed5bb2fe</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>REPLY</t>
+          <t>Powerplan</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, Azure Cosmos DB, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7ad9782930201d7</t>
+          <t>https://www.indeed.com/viewjob?jk=9effd2546d52cd38</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer II, Data</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>REPLY</t>
+          <t>Credit Acceptance</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, Azure Cosmos DB, Data Modeling</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61bab526ed5bb2fe</t>
+          <t>https://www.indeed.com/viewjob?jk=39dcfd9f2966d672</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Finance Solutions, Google Cloud Platform</t>
+          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Platform (AWS)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Spark, PySpark, Scala, Oracle, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c94336bbf2aab76d</t>
+          <t>https://www.indeed.com/viewjob?jk=7064a0875d5078f8</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Powerplan</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, EMR, Kinesis, S3, RDS, Spark, Scala, PostgreSQL, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9effd2546d52cd38</t>
+          <t>https://www.indeed.com/viewjob?jk=5d1eabd20620b211</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data</t>
+          <t>Solutions Delivery Engineer (Remote)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Credit Acceptance</t>
+          <t>RealPage Inc</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, NoSQL</t>
+          <t>AWS, Redshift, RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,59 +1546,59 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39dcfd9f2966d672</t>
+          <t>https://www.indeed.com/viewjob?jk=ec761fb42adb289d</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Platform (AWS)</t>
+          <t>Senior Software Development Engineer - LLMs, GenAI</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Power BI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7064a0875d5078f8</t>
+          <t>https://www.indeed.com/viewjob?jk=7ef55c2266d41678</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Senior Professional Services Consultant</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Ataccama</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, S3, RDS, Spark, Scala, PostgreSQL, NoSQL, Jenkins</t>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d1eabd20620b211</t>
+          <t>https://www.indeed.com/viewjob?jk=0f49a3f3dbcbca27</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Solutions Delivery Engineer (Remote)</t>
+          <t>CDP Architect</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>RealPage Inc</t>
+          <t>Bounteous</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec761fb42adb289d</t>
+          <t>https://www.indeed.com/viewjob?jk=f5b99e7a77983415</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer - LLMs, GenAI</t>
+          <t>Senior Devops Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Power BI, Docker, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ef55c2266d41678</t>
+          <t>https://www.indeed.com/viewjob?jk=143f81631e970888</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Professional Services Consultant</t>
+          <t>Senior Full stack Java / AWS</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ataccama</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,42 +1711,42 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f49a3f3dbcbca27</t>
+          <t>https://www.indeed.com/viewjob?jk=648c04000182f970</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CDP Architect</t>
+          <t>Azure IoT Solutions Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Bounteous</t>
+          <t>Ascend Technologies</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake, ETL</t>
+          <t>RDS, Azure, Event Hubs, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5b99e7a77983415</t>
+          <t>https://www.indeed.com/viewjob?jk=48463a0b2c1a516b</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Devops Engineer</t>
+          <t>GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation</t>
+          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=143f81631e970888</t>
+          <t>https://www.indeed.com/viewjob?jk=6b7cc426dbd03f0e</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Full stack Java / AWS</t>
+          <t>Economic Data System Engineer/Sr. Economic Data System Engineer-ITDDPED</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL, DynamoDB, CI/CD</t>
+          <t>RDS, Databricks, BigQuery, Hadoop, Spark, Scala, Snowflake, NoSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=648c04000182f970</t>
+          <t>https://www.indeed.com/viewjob?jk=3a32b2285f6e0f19</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Azure IoT Solutions Engineer</t>
+          <t>QA Automation Engineer II, Officer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Ascend Technologies</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AKS, Jenkins</t>
+          <t>RDS, Scala, Oracle, NoSQL, Talend, CI/CD, Jenkins, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48463a0b2c1a516b</t>
+          <t>https://www.indeed.com/viewjob?jk=1d73747fd9aafef8</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>GCP Cloud Engineer</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Mercari</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Tableau</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b7cc426dbd03f0e</t>
+          <t>https://www.indeed.com/viewjob?jk=179685542a7cf944</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Economic Data System Engineer/Sr. Economic Data System Engineer-ITDDPED</t>
+          <t>Sr Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Pilot Flying J</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Roswell, GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Hadoop, Spark, Scala, Snowflake, NoSQL, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a32b2285f6e0f19</t>
+          <t>https://www.indeed.com/viewjob?jk=0a70d5a50e3bc2a5</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>QA Automation Engineer II, Officer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, NoSQL, Talend, CI/CD, Jenkins, Docker, Jenkins, Git</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Kafka, CI/CD, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d73747fd9aafef8</t>
+          <t>https://www.indeed.com/viewjob?jk=9a5cbb62cc968f68</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Mercari</t>
+          <t>Marathon Petroleum</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Tableau</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=179685542a7cf944</t>
+          <t>https://www.indeed.com/viewjob?jk=28293fa77ffc32bb</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr Engineer, Data Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Pilot Flying J</t>
+          <t>Golden State</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Roswell, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a70d5a50e3bc2a5</t>
+          <t>https://www.indeed.com/viewjob?jk=1d156f80ddb5ea3e</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>American Tower</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Kafka, CI/CD, Terraform, Kubernetes, AKS</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a5cbb62cc968f68</t>
+          <t>https://www.indeed.com/viewjob?jk=340f3540cd359821</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Senior Data Engineer – Advanced Data Integration &amp; Cloud Solutions</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Marathon Petroleum</t>
+          <t>Everforth ECS</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, CI/CD, Git, Python, SQL</t>
+          <t>ECS, RDS, Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, ETL, Python, SQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28293fa77ffc32bb</t>
+          <t>https://www.indeed.com/viewjob?jk=ca1d4ee2bfb7f383</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Engineer/DevOps Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Golden State</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, Splunk, CI/CD, Azure DevOps, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d156f80ddb5ea3e</t>
+          <t>https://www.indeed.com/viewjob?jk=a4e19bdfcdfa54e3</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Analyst, Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>American Tower</t>
+          <t>Lincoln Electric</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=340f3540cd359821</t>
+          <t>https://www.indeed.com/viewjob?jk=8382e0121c068a19</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Advanced Data Integration &amp; Cloud Solutions</t>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Everforth ECS</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, ETL, Python, SQL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca1d4ee2bfb7f383</t>
+          <t>https://www.indeed.com/viewjob?jk=f4ab3e3c7077492c</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AI Engineer/DevOps Engineer</t>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Inglewood, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, Splunk, CI/CD, Azure DevOps, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4e19bdfcdfa54e3</t>
+          <t>https://www.indeed.com/viewjob?jk=b0870a8c631ca3e7</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Analyst, Data Engineer</t>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Lincoln Electric</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8382e0121c068a19</t>
+          <t>https://www.indeed.com/viewjob?jk=3a8177305c7e2b4e</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Platform (Azure)</t>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform, Azure Monitor</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=defb19c3b807f7fd</t>
+          <t>https://www.indeed.com/viewjob?jk=2b216035065cdcce</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect - WORK FROM HOME - SELECT US STATES ONLY</t>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Slavic401K</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df39dd0505c33d32</t>
+          <t>https://www.indeed.com/viewjob?jk=b0d6bbe5db7dc4e3</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4ab3e3c7077492c</t>
+          <t>https://www.indeed.com/viewjob?jk=99cd5dc3d4c47201</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Inglewood, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0870a8c631ca3e7</t>
+          <t>https://www.indeed.com/viewjob?jk=1535cff1bb626738</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Williamsville, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a8177305c7e2b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=37a520fdd5e099b9</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b216035065cdcce</t>
+          <t>https://www.indeed.com/viewjob?jk=366fcdfb585bd3be</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0d6bbe5db7dc4e3</t>
+          <t>https://www.indeed.com/viewjob?jk=a94f1ea7f43f3649</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99cd5dc3d4c47201</t>
+          <t>https://www.indeed.com/viewjob?jk=497b07468d401d8a</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1535cff1bb626738</t>
+          <t>https://www.indeed.com/viewjob?jk=8d2e49c364fa4321</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Williamsville, NY, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37a520fdd5e099b9</t>
+          <t>https://www.indeed.com/viewjob?jk=14d6f7b29ae9eb47</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=366fcdfb585bd3be</t>
+          <t>https://www.indeed.com/viewjob?jk=e69bf4d69267775a</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a94f1ea7f43f3649</t>
+          <t>https://www.indeed.com/viewjob?jk=22a4f690926575b6</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=497b07468d401d8a</t>
+          <t>https://www.indeed.com/viewjob?jk=7fc8f10cc4340e38</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d2e49c364fa4321</t>
+          <t>https://www.indeed.com/viewjob?jk=4ed7e30adf2adc59</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14d6f7b29ae9eb47</t>
+          <t>https://www.indeed.com/viewjob?jk=22efcdd2b4a3dd7f</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e69bf4d69267775a</t>
+          <t>https://www.indeed.com/viewjob?jk=4d610152102215d5</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22a4f690926575b6</t>
+          <t>https://www.indeed.com/viewjob?jk=0f093d62f255edad</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fc8f10cc4340e38</t>
+          <t>https://www.indeed.com/viewjob?jk=61c760c7b06ee2ec</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ed7e30adf2adc59</t>
+          <t>https://www.indeed.com/viewjob?jk=7e753698d58ce405</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22efcdd2b4a3dd7f</t>
+          <t>https://www.indeed.com/viewjob?jk=613c98d34d3a6aff</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d610152102215d5</t>
+          <t>https://www.indeed.com/viewjob?jk=81eb38d16909745a</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f093d62f255edad</t>
+          <t>https://www.indeed.com/viewjob?jk=26aa4bbb65d7bc04</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61c760c7b06ee2ec</t>
+          <t>https://www.indeed.com/viewjob?jk=51eaf011bd4b3db9</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e753698d58ce405</t>
+          <t>https://www.indeed.com/viewjob?jk=875b54845cacd6b4</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=613c98d34d3a6aff</t>
+          <t>https://www.indeed.com/viewjob?jk=b044118f339aeefe</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81eb38d16909745a</t>
+          <t>https://www.indeed.com/viewjob?jk=79172907c08cbd27</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26aa4bbb65d7bc04</t>
+          <t>https://www.indeed.com/viewjob?jk=4072dd1e7bd9b46a</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51eaf011bd4b3db9</t>
+          <t>https://www.indeed.com/viewjob?jk=60e28bece0970c90</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=875b54845cacd6b4</t>
+          <t>https://www.indeed.com/viewjob?jk=337e00bdabbbf617</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b044118f339aeefe</t>
+          <t>https://www.indeed.com/viewjob?jk=7008c23fbe380180</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79172907c08cbd27</t>
+          <t>https://www.indeed.com/viewjob?jk=ef94cdec933bb8d2</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4072dd1e7bd9b46a</t>
+          <t>https://www.indeed.com/viewjob?jk=a9b3dd72c73a5c59</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Juan, PR, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60e28bece0970c90</t>
+          <t>https://www.indeed.com/viewjob?jk=3f362104fdb5fce0</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=337e00bdabbbf617</t>
+          <t>https://www.indeed.com/viewjob?jk=bb3766965503e1b0</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7008c23fbe380180</t>
+          <t>https://www.indeed.com/viewjob?jk=01b7efd6177971eb</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef94cdec933bb8d2</t>
+          <t>https://www.indeed.com/viewjob?jk=564843cdd5d6c05d</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9b3dd72c73a5c59</t>
+          <t>https://www.indeed.com/viewjob?jk=38dc1e892863874b</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>San Juan, PR, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f362104fdb5fce0</t>
+          <t>https://www.indeed.com/viewjob?jk=36375563a2ad1043</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Honolulu, HI, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb3766965503e1b0</t>
+          <t>https://www.indeed.com/viewjob?jk=cf1ab598617115f3</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01b7efd6177971eb</t>
+          <t>https://www.indeed.com/viewjob?jk=bdb4d76e4c3be44c</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=564843cdd5d6c05d</t>
+          <t>https://www.indeed.com/viewjob?jk=bd706eccacda1e1c</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38dc1e892863874b</t>
+          <t>https://www.indeed.com/viewjob?jk=606f854062c681fa</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36375563a2ad1043</t>
+          <t>https://www.indeed.com/viewjob?jk=15ee32196b2a250e</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Honolulu, HI, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf1ab598617115f3</t>
+          <t>https://www.indeed.com/viewjob?jk=c7a2ced0233034b8</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdb4d76e4c3be44c</t>
+          <t>https://www.indeed.com/viewjob?jk=b267004acbc01cc5</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd706eccacda1e1c</t>
+          <t>https://www.indeed.com/viewjob?jk=9be2810504f2ae29</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606f854062c681fa</t>
+          <t>https://www.indeed.com/viewjob?jk=6f0ec602c9b09a8e</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15ee32196b2a250e</t>
+          <t>https://www.indeed.com/viewjob?jk=bd0e7d3dab7e604a</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7a2ced0233034b8</t>
+          <t>https://www.indeed.com/viewjob?jk=905c5a2344562ab8</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b267004acbc01cc5</t>
+          <t>https://www.indeed.com/viewjob?jk=21b0eb74cf57c4a8</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Monterey, CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9be2810504f2ae29</t>
+          <t>https://www.indeed.com/viewjob?jk=127db1667ff89227</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f0ec602c9b09a8e</t>
+          <t>https://www.indeed.com/viewjob?jk=2a42559421200137</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd0e7d3dab7e604a</t>
+          <t>https://www.indeed.com/viewjob?jk=d6e7dd724c924aca</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=905c5a2344562ab8</t>
+          <t>https://www.indeed.com/viewjob?jk=8483d29d2dbde05b</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21b0eb74cf57c4a8</t>
+          <t>https://www.indeed.com/viewjob?jk=824e663391dfa6bf</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Monterey, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127db1667ff89227</t>
+          <t>https://www.indeed.com/viewjob?jk=3e8686e8d16dc84d</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a42559421200137</t>
+          <t>https://www.indeed.com/viewjob?jk=496d9926f80e93e9</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6e7dd724c924aca</t>
+          <t>https://www.indeed.com/viewjob?jk=57716cf6ab6ed7a5</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8483d29d2dbde05b</t>
+          <t>https://www.indeed.com/viewjob?jk=c418229c0f650f96</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=824e663391dfa6bf</t>
+          <t>https://www.indeed.com/viewjob?jk=95121729962d91d2</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e8686e8d16dc84d</t>
+          <t>https://www.indeed.com/viewjob?jk=dfec58f9b4c8760a</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=496d9926f80e93e9</t>
+          <t>https://www.indeed.com/viewjob?jk=5153281c36740802</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57716cf6ab6ed7a5</t>
+          <t>https://www.indeed.com/viewjob?jk=310acaaa4f9f42e3</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c418229c0f650f96</t>
+          <t>https://www.indeed.com/viewjob?jk=6efe7ed3911371c4</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95121729962d91d2</t>
+          <t>https://www.indeed.com/viewjob?jk=1a68cf132dbdec60</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfec58f9b4c8760a</t>
+          <t>https://www.indeed.com/viewjob?jk=8d891e75a79397a9</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5153281c36740802</t>
+          <t>https://www.indeed.com/viewjob?jk=117634e8f8dfb2d6</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=310acaaa4f9f42e3</t>
+          <t>https://www.indeed.com/viewjob?jk=b83a26f124ccdb89</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6efe7ed3911371c4</t>
+          <t>https://www.indeed.com/viewjob?jk=ad88505e172120de</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a68cf132dbdec60</t>
+          <t>https://www.indeed.com/viewjob?jk=c21ad262bec7ef80</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d891e75a79397a9</t>
+          <t>https://www.indeed.com/viewjob?jk=ca6810d972b1a5f1</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=117634e8f8dfb2d6</t>
+          <t>https://www.indeed.com/viewjob?jk=27043ef345d0b8a7</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b83a26f124ccdb89</t>
+          <t>https://www.indeed.com/viewjob?jk=be347b278f12cb33</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad88505e172120de</t>
+          <t>https://www.indeed.com/viewjob?jk=fed8b15c04492576</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c21ad262bec7ef80</t>
+          <t>https://www.indeed.com/viewjob?jk=5b12133504b24bae</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca6810d972b1a5f1</t>
+          <t>https://www.indeed.com/viewjob?jk=9f864d9aca9b7b27</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27043ef345d0b8a7</t>
+          <t>https://www.indeed.com/viewjob?jk=76d2eb1be4c1b252</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be347b278f12cb33</t>
+          <t>https://www.indeed.com/viewjob?jk=9baba2b401f1c56c</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Platform (Azure)</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform, Azure Monitor</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fed8b15c04492576</t>
+          <t>https://www.indeed.com/viewjob?jk=defb19c3b807f7fd</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+          <t>Enterprise Data Architect - WORK FROM HOME - SELECT US STATES ONLY</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Slavic401K</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b12133504b24bae</t>
+          <t>https://www.indeed.com/viewjob?jk=df39dd0505c33d32</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+          <t>Databricks Developer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f864d9aca9b7b27</t>
+          <t>https://www.indeed.com/viewjob?jk=ab1192abfbd7f24e</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+          <t>Databricks Developer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,32 +5151,32 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76d2eb1be4c1b252</t>
+          <t>https://www.indeed.com/viewjob?jk=320dcd4f927cb250</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+          <t>Associate, Data Engineer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, DynamoDB, Azure Cosmos DB, NoSQL</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,32 +5186,32 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9baba2b401f1c56c</t>
+          <t>https://www.indeed.com/viewjob?jk=06fd6810514e5491</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Databricks Developer</t>
+          <t>Site Reliability Engineering (SRE) - Maryland, US</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>Azure, GCP, BigQuery, Zookeeper, Scala, Kafka, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,32 +5221,32 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab1192abfbd7f24e</t>
+          <t>https://www.indeed.com/viewjob?jk=8d51d47e65997196</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Databricks Developer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,32 +5256,32 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=320dcd4f927cb250</t>
+          <t>https://www.indeed.com/viewjob?jk=33b30501746ad4bf</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Senior Quality Engineering (QE) Engineer</t>
+          <t>Data Engineer - Oklahoma City, OK</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Amida Technology Solutions</t>
+          <t>CFS Brands, LLC</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Power BI, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>IAM, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29a7f8ff4391f120</t>
+          <t>https://www.indeed.com/viewjob?jk=113fe7e3580ec298</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Associate, Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Chiesi Farmaceutici S.p.A.</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,34 +5316,34 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, DynamoDB, Azure Cosmos DB, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06fd6810514e5491</t>
+          <t>https://www.indeed.com/viewjob?jk=78d407207abb7498</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Site Reliability Engineering (SRE) - Maryland, US</t>
+          <t>Apache Spark Core Java</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,34 +5351,34 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Azure, GCP, BigQuery, Zookeeper, Scala, Kafka, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d51d47e65997196</t>
+          <t>https://www.indeed.com/viewjob?jk=16d16eda2d514586</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Analytics Engineer, Marketing Sciences</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>SimplePractice</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Kinesis, RDS, Scala, Kafka, Snowflake, ETL, dbt, Terraform, Docker</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5395,146 +5395,6 @@
         </is>
       </c>
       <c r="G142" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=33b30501746ad4bf</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>Data Engineer - Oklahoma City, OK</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>CFS Brands, LLC</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Oklahoma City, OK, US USA</t>
-        </is>
-      </c>
-      <c r="D143" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>IAM, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=113fe7e3580ec298</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Chiesi Farmaceutici S.p.A.</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Cary, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D144" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=78d407207abb7498</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Apache Spark Core Java</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D145" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>2026-08-22</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=16d16eda2d514586</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Senior Analytics Engineer, Marketing Sciences</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>SimplePractice</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D146" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, RDS, Scala, Kafka, Snowflake, ETL, dbt, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=4a341479dc01b56f</t>
         </is>

--- a/results/job_matches_2026-08-22.xlsx
+++ b/results/job_matches_2026-08-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G142"/>
+  <dimension ref="A1:G131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,25 +573,25 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Analytics)</t>
+          <t>Data Engineer Microsoft Fabric</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Bilzin Sumberg Baena Price &amp; Axelrod LLP</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>19.4</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Blob Storage, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>S3, RDS, Azure, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=593e53f5fee30d60</t>
+          <t>https://www.indeed.com/viewjob?jk=371409082795e582</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Quality Engineering (QE) Data Quality Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Amida Technology Solutions</t>
+          <t>Guild Mortgage Company LLC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.8</v>
+        <v>16</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Redshift, Azure, Data Factory, Databricks, BigQuery, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Redshift, RDS, Spark, Scala, Kafka, Snowflake, SQL Server, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9b2b6cddab662d6</t>
+          <t>https://www.indeed.com/viewjob?jk=fd674fe067dfdd34</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer Microsoft Fabric</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bilzin Sumberg Baena Price &amp; Axelrod LLP</t>
+          <t>Entarian</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Snowflake, SQL Server</t>
+          <t>AWS, Kinesis, Scala, Kafka, Polars, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=371409082795e582</t>
+          <t>https://www.indeed.com/viewjob?jk=97cacdd77a88ee4d</t>
         </is>
       </c>
     </row>
@@ -683,20 +683,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Entarian</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, Kinesis, Scala, Kafka, Polars, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=515f3bff52abe8ea</t>
+          <t>https://www.indeed.com/viewjob?jk=8d62e6c9bd298592</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Platform System Administrator III</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Boston Scientific</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Arden Hills, MN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f887668cf9aaf20f</t>
+          <t>https://www.indeed.com/viewjob?jk=62388f603bbe60a4</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Engineer, Enterprise Database</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Guild Mortgage Company LLC</t>
+          <t>Applied Medical</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Rancho Santa Margarita, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Spark, Scala, Kafka, Snowflake, SQL Server, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd674fe067dfdd34</t>
+          <t>https://www.indeed.com/viewjob?jk=51a5d6b8454480a2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer, Full Stack - AI (New York)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Entarian</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Scala, Kafka, Polars, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97cacdd77a88ee4d</t>
+          <t>https://www.indeed.com/viewjob?jk=362603547d1c2a0d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Science Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Entarian</t>
+          <t>LegitScript</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Scala, Kafka, Polars, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, MLOps</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d62e6c9bd298592</t>
+          <t>https://www.indeed.com/viewjob?jk=0ac58242095324ac</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI Platform System Administrator III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Boston Scientific</t>
+          <t>REPLY</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Arden Hills, MN, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>13.9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, Azure Cosmos DB, Data Modeling</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62388f603bbe60a4</t>
+          <t>https://www.indeed.com/viewjob?jk=5cc84ba97f996450</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Engineer, Enterprise Database</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Applied Medical</t>
+          <t>REPLY</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Rancho Santa Margarita, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, Azure Cosmos DB, Data Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51a5d6b8454480a2</t>
+          <t>https://www.indeed.com/viewjob?jk=b9d2db7b4c8d89f8</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer, Full Stack - AI (New York)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Fitch Group</t>
+          <t>REPLY</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, Azure Cosmos DB, Data Modeling</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=362603547d1c2a0d</t>
+          <t>https://www.indeed.com/viewjob?jk=74f4fee2cc3d811b</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr Full stack Java Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Hudson Manpower</t>
+          <t>REPLY</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, Azure Cosmos DB, Data Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7f12b1ea10022a2</t>
+          <t>https://www.indeed.com/viewjob?jk=b7ad9782930201d7</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr Full stack Java Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hudson Manpower</t>
+          <t>REPLY</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, Azure Cosmos DB, Data Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6bc74fdfdbbca2b</t>
+          <t>https://www.indeed.com/viewjob?jk=61bab526ed5bb2fe</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr Full stack Java Developer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Hudson Manpower</t>
+          <t>Powerplan</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50c5bf2319077628</t>
+          <t>https://www.indeed.com/viewjob?jk=9effd2546d52cd38</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr Full stack Java Developer</t>
+          <t>Software Engineer II, Data</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Hudson Manpower</t>
+          <t>Credit Acceptance</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>13.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=603c61b7cc5fe1b9</t>
+          <t>https://www.indeed.com/viewjob?jk=39dcfd9f2966d672</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr Full stack Java Developer</t>
+          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Platform (AWS)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Hudson Manpower</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Allentown, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7340ebb5e99bf41f</t>
+          <t>https://www.indeed.com/viewjob?jk=7064a0875d5078f8</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr Full stack Java Developer</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Hudson Manpower</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>12.5</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, EMR, Kinesis, S3, RDS, Spark, Scala, PostgreSQL, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7bb7609c20e949e</t>
+          <t>https://www.indeed.com/viewjob?jk=5d1eabd20620b211</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Science Engineer</t>
+          <t>Solutions Delivery Engineer (Remote)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>LegitScript</t>
+          <t>RealPage Inc</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, MLOps</t>
+          <t>AWS, Redshift, RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,102 +1196,102 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ac58242095324ac</t>
+          <t>https://www.indeed.com/viewjob?jk=ec761fb42adb289d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Professional Services Consultant</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>REPLY</t>
+          <t>Ataccama</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, Azure Cosmos DB, Data Modeling</t>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cc84ba97f996450</t>
+          <t>https://www.indeed.com/viewjob?jk=0f49a3f3dbcbca27</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Development Engineer - LLMs, GenAI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>REPLY</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, Azure Cosmos DB, Data Modeling</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Power BI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9d2db7b4c8d89f8</t>
+          <t>https://www.indeed.com/viewjob?jk=7ef55c2266d41678</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>CDP Architect</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>REPLY</t>
+          <t>Bounteous</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, Azure Cosmos DB, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74f4fee2cc3d811b</t>
+          <t>https://www.indeed.com/viewjob?jk=f5b99e7a77983415</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Devops Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>REPLY</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, Azure Cosmos DB, Data Modeling</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7ad9782930201d7</t>
+          <t>https://www.indeed.com/viewjob?jk=143f81631e970888</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Full stack Java / AWS</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>REPLY</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, Azure Cosmos DB, Data Modeling</t>
+          <t>AWS, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61bab526ed5bb2fe</t>
+          <t>https://www.indeed.com/viewjob?jk=648c04000182f970</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Azure IoT Solutions Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Powerplan</t>
+          <t>Ascend Technologies</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, MLOps, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Event Hubs, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9effd2546d52cd38</t>
+          <t>https://www.indeed.com/viewjob?jk=48463a0b2c1a516b</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data</t>
+          <t>GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Credit Acceptance</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, NoSQL</t>
+          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39dcfd9f2966d672</t>
+          <t>https://www.indeed.com/viewjob?jk=6b7cc426dbd03f0e</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Platform (AWS)</t>
+          <t>Economic Data System Engineer/Sr. Economic Data System Engineer-ITDDPED</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform</t>
+          <t>RDS, Databricks, BigQuery, Hadoop, Spark, Scala, Snowflake, NoSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7064a0875d5078f8</t>
+          <t>https://www.indeed.com/viewjob?jk=3a32b2285f6e0f19</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>QA Automation Engineer II, Officer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, S3, RDS, Spark, Scala, PostgreSQL, NoSQL, Jenkins</t>
+          <t>RDS, Scala, Oracle, NoSQL, Talend, CI/CD, Jenkins, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d1eabd20620b211</t>
+          <t>https://www.indeed.com/viewjob?jk=1d73747fd9aafef8</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Solutions Delivery Engineer (Remote)</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>RealPage Inc</t>
+          <t>Mercari</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Tableau</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,102 +1546,102 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec761fb42adb289d</t>
+          <t>https://www.indeed.com/viewjob?jk=179685542a7cf944</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer - LLMs, GenAI</t>
+          <t>Sr Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Pilot Flying J</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Roswell, GA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Power BI, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ef55c2266d41678</t>
+          <t>https://www.indeed.com/viewjob?jk=0a70d5a50e3bc2a5</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Professional Services Consultant</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Ataccama</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Kafka, CI/CD, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f49a3f3dbcbca27</t>
+          <t>https://www.indeed.com/viewjob?jk=9a5cbb62cc968f68</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CDP Architect</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Bounteous</t>
+          <t>Marathon Petroleum</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5b99e7a77983415</t>
+          <t>https://www.indeed.com/viewjob?jk=28293fa77ffc32bb</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Devops Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Golden State</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=143f81631e970888</t>
+          <t>https://www.indeed.com/viewjob?jk=1d156f80ddb5ea3e</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Full stack Java / AWS</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>American Tower</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL, DynamoDB, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,19 +1721,19 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=648c04000182f970</t>
+          <t>https://www.indeed.com/viewjob?jk=340f3540cd359821</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Azure IoT Solutions Engineer</t>
+          <t>Senior Data Engineer – Advanced Data Integration &amp; Cloud Solutions</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ascend Technologies</t>
+          <t>Everforth ECS</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1742,11 +1742,11 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AKS, Jenkins</t>
+          <t>ECS, RDS, Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, ETL, Python, SQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48463a0b2c1a516b</t>
+          <t>https://www.indeed.com/viewjob?jk=ca1d4ee2bfb7f383</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>GCP Cloud Engineer</t>
+          <t>AI Engineer/DevOps Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, Splunk, CI/CD, Azure DevOps, Kubernetes</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b7cc426dbd03f0e</t>
+          <t>https://www.indeed.com/viewjob?jk=a4e19bdfcdfa54e3</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Economic Data System Engineer/Sr. Economic Data System Engineer-ITDDPED</t>
+          <t>Senior Analyst, Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Lincoln Electric</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Hadoop, Spark, Scala, Snowflake, NoSQL, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a32b2285f6e0f19</t>
+          <t>https://www.indeed.com/viewjob?jk=8382e0121c068a19</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>QA Automation Engineer II, Officer</t>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, NoSQL, Talend, CI/CD, Jenkins, Docker, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d73747fd9aafef8</t>
+          <t>https://www.indeed.com/viewjob?jk=f4ab3e3c7077492c</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Mercari</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Inglewood, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=179685542a7cf944</t>
+          <t>https://www.indeed.com/viewjob?jk=b0870a8c631ca3e7</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr Engineer, Data Engineering</t>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Pilot Flying J</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Roswell, GA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a70d5a50e3bc2a5</t>
+          <t>https://www.indeed.com/viewjob?jk=3a8177305c7e2b4e</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Kafka, CI/CD, Terraform, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a5cbb62cc968f68</t>
+          <t>https://www.indeed.com/viewjob?jk=2b216035065cdcce</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Marathon Petroleum</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, CI/CD, Git, Python, SQL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28293fa77ffc32bb</t>
+          <t>https://www.indeed.com/viewjob?jk=b0d6bbe5db7dc4e3</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Golden State</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d156f80ddb5ea3e</t>
+          <t>https://www.indeed.com/viewjob?jk=99cd5dc3d4c47201</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>American Tower</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=340f3540cd359821</t>
+          <t>https://www.indeed.com/viewjob?jk=1535cff1bb626738</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Advanced Data Integration &amp; Cloud Solutions</t>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Everforth ECS</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Williamsville, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, ETL, Python, SQL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca1d4ee2bfb7f383</t>
+          <t>https://www.indeed.com/viewjob?jk=37a520fdd5e099b9</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>AI Engineer/DevOps Engineer</t>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, Splunk, CI/CD, Azure DevOps, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4e19bdfcdfa54e3</t>
+          <t>https://www.indeed.com/viewjob?jk=366fcdfb585bd3be</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Analyst, Data Engineer</t>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Lincoln Electric</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8382e0121c068a19</t>
+          <t>https://www.indeed.com/viewjob?jk=a94f1ea7f43f3649</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4ab3e3c7077492c</t>
+          <t>https://www.indeed.com/viewjob?jk=497b07468d401d8a</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Inglewood, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0870a8c631ca3e7</t>
+          <t>https://www.indeed.com/viewjob?jk=8d2e49c364fa4321</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a8177305c7e2b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=14d6f7b29ae9eb47</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b216035065cdcce</t>
+          <t>https://www.indeed.com/viewjob?jk=e69bf4d69267775a</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0d6bbe5db7dc4e3</t>
+          <t>https://www.indeed.com/viewjob?jk=22a4f690926575b6</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99cd5dc3d4c47201</t>
+          <t>https://www.indeed.com/viewjob?jk=7fc8f10cc4340e38</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1535cff1bb626738</t>
+          <t>https://www.indeed.com/viewjob?jk=4ed7e30adf2adc59</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Williamsville, NY, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37a520fdd5e099b9</t>
+          <t>https://www.indeed.com/viewjob?jk=22efcdd2b4a3dd7f</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=366fcdfb585bd3be</t>
+          <t>https://www.indeed.com/viewjob?jk=4d610152102215d5</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a94f1ea7f43f3649</t>
+          <t>https://www.indeed.com/viewjob?jk=0f093d62f255edad</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=497b07468d401d8a</t>
+          <t>https://www.indeed.com/viewjob?jk=61c760c7b06ee2ec</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d2e49c364fa4321</t>
+          <t>https://www.indeed.com/viewjob?jk=7e753698d58ce405</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14d6f7b29ae9eb47</t>
+          <t>https://www.indeed.com/viewjob?jk=613c98d34d3a6aff</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e69bf4d69267775a</t>
+          <t>https://www.indeed.com/viewjob?jk=81eb38d16909745a</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22a4f690926575b6</t>
+          <t>https://www.indeed.com/viewjob?jk=26aa4bbb65d7bc04</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fc8f10cc4340e38</t>
+          <t>https://www.indeed.com/viewjob?jk=51eaf011bd4b3db9</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ed7e30adf2adc59</t>
+          <t>https://www.indeed.com/viewjob?jk=875b54845cacd6b4</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22efcdd2b4a3dd7f</t>
+          <t>https://www.indeed.com/viewjob?jk=b044118f339aeefe</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d610152102215d5</t>
+          <t>https://www.indeed.com/viewjob?jk=79172907c08cbd27</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f093d62f255edad</t>
+          <t>https://www.indeed.com/viewjob?jk=4072dd1e7bd9b46a</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61c760c7b06ee2ec</t>
+          <t>https://www.indeed.com/viewjob?jk=60e28bece0970c90</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e753698d58ce405</t>
+          <t>https://www.indeed.com/viewjob?jk=337e00bdabbbf617</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=613c98d34d3a6aff</t>
+          <t>https://www.indeed.com/viewjob?jk=7008c23fbe380180</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81eb38d16909745a</t>
+          <t>https://www.indeed.com/viewjob?jk=ef94cdec933bb8d2</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26aa4bbb65d7bc04</t>
+          <t>https://www.indeed.com/viewjob?jk=a9b3dd72c73a5c59</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>San Juan, PR, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51eaf011bd4b3db9</t>
+          <t>https://www.indeed.com/viewjob?jk=3f362104fdb5fce0</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=875b54845cacd6b4</t>
+          <t>https://www.indeed.com/viewjob?jk=bb3766965503e1b0</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b044118f339aeefe</t>
+          <t>https://www.indeed.com/viewjob?jk=01b7efd6177971eb</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79172907c08cbd27</t>
+          <t>https://www.indeed.com/viewjob?jk=564843cdd5d6c05d</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4072dd1e7bd9b46a</t>
+          <t>https://www.indeed.com/viewjob?jk=38dc1e892863874b</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60e28bece0970c90</t>
+          <t>https://www.indeed.com/viewjob?jk=36375563a2ad1043</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Honolulu, HI, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=337e00bdabbbf617</t>
+          <t>https://www.indeed.com/viewjob?jk=cf1ab598617115f3</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7008c23fbe380180</t>
+          <t>https://www.indeed.com/viewjob?jk=bdb4d76e4c3be44c</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef94cdec933bb8d2</t>
+          <t>https://www.indeed.com/viewjob?jk=bd706eccacda1e1c</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9b3dd72c73a5c59</t>
+          <t>https://www.indeed.com/viewjob?jk=606f854062c681fa</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>San Juan, PR, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f362104fdb5fce0</t>
+          <t>https://www.indeed.com/viewjob?jk=15ee32196b2a250e</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb3766965503e1b0</t>
+          <t>https://www.indeed.com/viewjob?jk=c7a2ced0233034b8</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01b7efd6177971eb</t>
+          <t>https://www.indeed.com/viewjob?jk=b267004acbc01cc5</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=564843cdd5d6c05d</t>
+          <t>https://www.indeed.com/viewjob?jk=9be2810504f2ae29</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38dc1e892863874b</t>
+          <t>https://www.indeed.com/viewjob?jk=6f0ec602c9b09a8e</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36375563a2ad1043</t>
+          <t>https://www.indeed.com/viewjob?jk=bd0e7d3dab7e604a</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Honolulu, HI, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf1ab598617115f3</t>
+          <t>https://www.indeed.com/viewjob?jk=905c5a2344562ab8</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdb4d76e4c3be44c</t>
+          <t>https://www.indeed.com/viewjob?jk=21b0eb74cf57c4a8</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Monterey, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd706eccacda1e1c</t>
+          <t>https://www.indeed.com/viewjob?jk=127db1667ff89227</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606f854062c681fa</t>
+          <t>https://www.indeed.com/viewjob?jk=2a42559421200137</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15ee32196b2a250e</t>
+          <t>https://www.indeed.com/viewjob?jk=d6e7dd724c924aca</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7a2ced0233034b8</t>
+          <t>https://www.indeed.com/viewjob?jk=8483d29d2dbde05b</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b267004acbc01cc5</t>
+          <t>https://www.indeed.com/viewjob?jk=824e663391dfa6bf</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9be2810504f2ae29</t>
+          <t>https://www.indeed.com/viewjob?jk=3e8686e8d16dc84d</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f0ec602c9b09a8e</t>
+          <t>https://www.indeed.com/viewjob?jk=496d9926f80e93e9</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd0e7d3dab7e604a</t>
+          <t>https://www.indeed.com/viewjob?jk=57716cf6ab6ed7a5</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=905c5a2344562ab8</t>
+          <t>https://www.indeed.com/viewjob?jk=c418229c0f650f96</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21b0eb74cf57c4a8</t>
+          <t>https://www.indeed.com/viewjob?jk=95121729962d91d2</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Monterey, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127db1667ff89227</t>
+          <t>https://www.indeed.com/viewjob?jk=dfec58f9b4c8760a</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a42559421200137</t>
+          <t>https://www.indeed.com/viewjob?jk=5153281c36740802</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6e7dd724c924aca</t>
+          <t>https://www.indeed.com/viewjob?jk=310acaaa4f9f42e3</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8483d29d2dbde05b</t>
+          <t>https://www.indeed.com/viewjob?jk=6efe7ed3911371c4</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=824e663391dfa6bf</t>
+          <t>https://www.indeed.com/viewjob?jk=1a68cf132dbdec60</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e8686e8d16dc84d</t>
+          <t>https://www.indeed.com/viewjob?jk=8d891e75a79397a9</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=496d9926f80e93e9</t>
+          <t>https://www.indeed.com/viewjob?jk=117634e8f8dfb2d6</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57716cf6ab6ed7a5</t>
+          <t>https://www.indeed.com/viewjob?jk=b83a26f124ccdb89</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c418229c0f650f96</t>
+          <t>https://www.indeed.com/viewjob?jk=ad88505e172120de</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95121729962d91d2</t>
+          <t>https://www.indeed.com/viewjob?jk=c21ad262bec7ef80</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfec58f9b4c8760a</t>
+          <t>https://www.indeed.com/viewjob?jk=ca6810d972b1a5f1</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5153281c36740802</t>
+          <t>https://www.indeed.com/viewjob?jk=27043ef345d0b8a7</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=310acaaa4f9f42e3</t>
+          <t>https://www.indeed.com/viewjob?jk=be347b278f12cb33</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6efe7ed3911371c4</t>
+          <t>https://www.indeed.com/viewjob?jk=fed8b15c04492576</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a68cf132dbdec60</t>
+          <t>https://www.indeed.com/viewjob?jk=5b12133504b24bae</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d891e75a79397a9</t>
+          <t>https://www.indeed.com/viewjob?jk=9f864d9aca9b7b27</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=117634e8f8dfb2d6</t>
+          <t>https://www.indeed.com/viewjob?jk=76d2eb1be4c1b252</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b83a26f124ccdb89</t>
+          <t>https://www.indeed.com/viewjob?jk=9baba2b401f1c56c</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Platform (Azure)</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform, Azure Monitor</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad88505e172120de</t>
+          <t>https://www.indeed.com/viewjob?jk=defb19c3b807f7fd</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+          <t>Enterprise Data Architect - WORK FROM HOME - SELECT US STATES ONLY</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Slavic401K</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c21ad262bec7ef80</t>
+          <t>https://www.indeed.com/viewjob?jk=df39dd0505c33d32</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+          <t>Databricks Developer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca6810d972b1a5f1</t>
+          <t>https://www.indeed.com/viewjob?jk=ab1192abfbd7f24e</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+          <t>Databricks Developer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,32 +4801,32 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27043ef345d0b8a7</t>
+          <t>https://www.indeed.com/viewjob?jk=320dcd4f927cb250</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+          <t>Associate, Data Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, DynamoDB, Azure Cosmos DB, NoSQL</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,32 +4836,32 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be347b278f12cb33</t>
+          <t>https://www.indeed.com/viewjob?jk=06fd6810514e5491</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+          <t>Site Reliability Engineering (SRE) - Maryland, US</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+          <t>Azure, GCP, BigQuery, Zookeeper, Scala, Kafka, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,32 +4871,32 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fed8b15c04492576</t>
+          <t>https://www.indeed.com/viewjob?jk=8d51d47e65997196</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,32 +4906,32 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b12133504b24bae</t>
+          <t>https://www.indeed.com/viewjob?jk=33b30501746ad4bf</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+          <t>Data Engineer - Oklahoma City, OK</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CFS Brands, LLC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+          <t>IAM, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,67 +4941,67 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f864d9aca9b7b27</t>
+          <t>https://www.indeed.com/viewjob?jk=113fe7e3580ec298</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+          <t>Apache Spark Core Java</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76d2eb1be4c1b252</t>
+          <t>https://www.indeed.com/viewjob?jk=16d16eda2d514586</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+          <t>Senior Analytics Engineer, Marketing Sciences</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>SimplePractice</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+          <t>AWS, Kinesis, RDS, Scala, Kafka, Snowflake, ETL, dbt, Terraform, Docker</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5010,391 +5010,6 @@
         </is>
       </c>
       <c r="G131" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9baba2b401f1c56c</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Platform (Azure)</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D132" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform, Azure Monitor</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=defb19c3b807f7fd</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Enterprise Data Architect - WORK FROM HOME - SELECT US STATES ONLY</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Slavic401K</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Boca Raton, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=df39dd0505c33d32</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Databricks Developer</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ab1192abfbd7f24e</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Databricks Developer</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D135" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=320dcd4f927cb250</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Associate, Data Engineer</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>BlackRock</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D136" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, DynamoDB, Azure Cosmos DB, NoSQL</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=06fd6810514e5491</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Site Reliability Engineering (SRE) - Maryland, US</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Baltimore, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D137" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>Azure, GCP, BigQuery, Zookeeper, Scala, Kafka, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8d51d47e65997196</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>Data Engineer III</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D138" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=33b30501746ad4bf</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>Data Engineer - Oklahoma City, OK</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>CFS Brands, LLC</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Oklahoma City, OK, US USA</t>
-        </is>
-      </c>
-      <c r="D139" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>IAM, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=113fe7e3580ec298</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>Chiesi Farmaceutici S.p.A.</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Cary, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D140" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=78d407207abb7498</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>Apache Spark Core Java</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D141" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>2026-08-22</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=16d16eda2d514586</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>Senior Analytics Engineer, Marketing Sciences</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>SimplePractice</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D142" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, RDS, Scala, Kafka, Snowflake, ETL, dbt, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=4a341479dc01b56f</t>
         </is>

--- a/results/job_matches_2026-08-22.xlsx
+++ b/results/job_matches_2026-08-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G131"/>
+  <dimension ref="A1:G125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -613,7 +613,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Guild Mortgage Company LLC</t>
+          <t>Entarian</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Spark, Scala, Kafka, Snowflake, SQL Server, MySQL, MongoDB</t>
+          <t>AWS, Kinesis, Scala, Kafka, Polars, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,14 +636,14 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd674fe067dfdd34</t>
+          <t>https://www.indeed.com/viewjob?jk=97cacdd77a88ee4d</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97cacdd77a88ee4d</t>
+          <t>https://www.indeed.com/viewjob?jk=8d62e6c9bd298592</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Platform System Administrator III</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Entarian</t>
+          <t>Boston Scientific</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Arden Hills, MN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Scala, Kafka, Polars, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d62e6c9bd298592</t>
+          <t>https://www.indeed.com/viewjob?jk=62388f603bbe60a4</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI Platform System Administrator III</t>
+          <t>Senior Engineer, Enterprise Database</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Boston Scientific</t>
+          <t>Applied Medical</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Arden Hills, MN, US USA</t>
+          <t>Rancho Santa Margarita, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62388f603bbe60a4</t>
+          <t>https://www.indeed.com/viewjob?jk=51a5d6b8454480a2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Engineer, Enterprise Database</t>
+          <t>Software Engineer, Full Stack - AI (New York)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Applied Medical</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Rancho Santa Margarita, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51a5d6b8454480a2</t>
+          <t>https://www.indeed.com/viewjob?jk=362603547d1c2a0d</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer, Full Stack - AI (New York)</t>
+          <t>Senior Data Science Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Fitch Group</t>
+          <t>LegitScript</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
+          <t>Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, MLOps</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=362603547d1c2a0d</t>
+          <t>https://www.indeed.com/viewjob?jk=0ac58242095324ac</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Science Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>LegitScript</t>
+          <t>Powerplan</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, MLOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ac58242095324ac</t>
+          <t>https://www.indeed.com/viewjob?jk=9effd2546d52cd38</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer II, Data</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>REPLY</t>
+          <t>Credit Acceptance</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, Azure Cosmos DB, Data Modeling</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cc84ba97f996450</t>
+          <t>https://www.indeed.com/viewjob?jk=39dcfd9f2966d672</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Platform (AWS)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>REPLY</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, Azure Cosmos DB, Data Modeling</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9d2db7b4c8d89f8</t>
+          <t>https://www.indeed.com/viewjob?jk=7064a0875d5078f8</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>REPLY</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, Azure Cosmos DB, Data Modeling</t>
+          <t>AWS, EMR, Kinesis, S3, RDS, Spark, Scala, PostgreSQL, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74f4fee2cc3d811b</t>
+          <t>https://www.indeed.com/viewjob?jk=5d1eabd20620b211</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Solutions Delivery Engineer (Remote)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>REPLY</t>
+          <t>RealPage Inc</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, Azure Cosmos DB, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,102 +986,102 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7ad9782930201d7</t>
+          <t>https://www.indeed.com/viewjob?jk=ec761fb42adb289d</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Development Engineer - LLMs, GenAI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>REPLY</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, Azure Cosmos DB, Data Modeling</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Power BI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61bab526ed5bb2fe</t>
+          <t>https://www.indeed.com/viewjob?jk=7ef55c2266d41678</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Professional Services Consultant</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Powerplan</t>
+          <t>Ataccama</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9effd2546d52cd38</t>
+          <t>https://www.indeed.com/viewjob?jk=0f49a3f3dbcbca27</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data</t>
+          <t>CDP Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Credit Acceptance</t>
+          <t>Bounteous</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, NoSQL</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39dcfd9f2966d672</t>
+          <t>https://www.indeed.com/viewjob?jk=f5b99e7a77983415</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Platform (AWS)</t>
+          <t>Senior Devops Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7064a0875d5078f8</t>
+          <t>https://www.indeed.com/viewjob?jk=143f81631e970888</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Senior Full stack Java / AWS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, S3, RDS, Spark, Scala, PostgreSQL, NoSQL, Jenkins</t>
+          <t>AWS, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d1eabd20620b211</t>
+          <t>https://www.indeed.com/viewjob?jk=648c04000182f970</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Solutions Delivery Engineer (Remote)</t>
+          <t>Azure IoT Solutions Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>RealPage Inc</t>
+          <t>Ascend Technologies</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Event Hubs, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,102 +1196,102 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec761fb42adb289d</t>
+          <t>https://www.indeed.com/viewjob?jk=48463a0b2c1a516b</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Professional Services Consultant</t>
+          <t>GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ataccama</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
+          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f49a3f3dbcbca27</t>
+          <t>https://www.indeed.com/viewjob?jk=6b7cc426dbd03f0e</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer - LLMs, GenAI</t>
+          <t>Economic Data System Engineer/Sr. Economic Data System Engineer-ITDDPED</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Power BI, Docker, Kubernetes</t>
+          <t>RDS, Databricks, BigQuery, Hadoop, Spark, Scala, Snowflake, NoSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ef55c2266d41678</t>
+          <t>https://www.indeed.com/viewjob?jk=3a32b2285f6e0f19</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CDP Architect</t>
+          <t>QA Automation Engineer II, Officer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Bounteous</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake, ETL</t>
+          <t>RDS, Scala, Oracle, NoSQL, Talend, CI/CD, Jenkins, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5b99e7a77983415</t>
+          <t>https://www.indeed.com/viewjob?jk=1d73747fd9aafef8</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Devops Engineer</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Mercari</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Tableau</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=143f81631e970888</t>
+          <t>https://www.indeed.com/viewjob?jk=179685542a7cf944</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Full stack Java / AWS</t>
+          <t>Sr Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Pilot Flying J</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Roswell, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=648c04000182f970</t>
+          <t>https://www.indeed.com/viewjob?jk=0a70d5a50e3bc2a5</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Azure IoT Solutions Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Ascend Technologies</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AKS, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Kafka, CI/CD, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48463a0b2c1a516b</t>
+          <t>https://www.indeed.com/viewjob?jk=9a5cbb62cc968f68</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>GCP Cloud Engineer</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Marathon Petroleum</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b7cc426dbd03f0e</t>
+          <t>https://www.indeed.com/viewjob?jk=28293fa77ffc32bb</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Economic Data System Engineer/Sr. Economic Data System Engineer-ITDDPED</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Golden State</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Hadoop, Spark, Scala, Snowflake, NoSQL, ETL, ELT</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a32b2285f6e0f19</t>
+          <t>https://www.indeed.com/viewjob?jk=1d156f80ddb5ea3e</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>QA Automation Engineer II, Officer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>American Tower</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, NoSQL, Talend, CI/CD, Jenkins, Docker, Jenkins, Git</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d73747fd9aafef8</t>
+          <t>https://www.indeed.com/viewjob?jk=340f3540cd359821</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>Senior Data Engineer – Advanced Data Integration &amp; Cloud Solutions</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Mercari</t>
+          <t>Everforth ECS</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Tableau</t>
+          <t>ECS, RDS, Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, ETL, Python, SQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=179685542a7cf944</t>
+          <t>https://www.indeed.com/viewjob?jk=ca1d4ee2bfb7f383</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr Engineer, Data Engineering</t>
+          <t>AI Engineer/DevOps Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Pilot Flying J</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Roswell, GA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, Splunk, CI/CD, Azure DevOps, Kubernetes</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a70d5a50e3bc2a5</t>
+          <t>https://www.indeed.com/viewjob?jk=a4e19bdfcdfa54e3</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior Analyst, Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Lincoln Electric</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Kafka, CI/CD, Terraform, Kubernetes, AKS</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a5cbb62cc968f68</t>
+          <t>https://www.indeed.com/viewjob?jk=8382e0121c068a19</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Platform (Azure)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Marathon Petroleum</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, CI/CD, Git, Python, SQL</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform, Azure Monitor</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28293fa77ffc32bb</t>
+          <t>https://www.indeed.com/viewjob?jk=defb19c3b807f7fd</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Enterprise Data Architect - WORK FROM HOME - SELECT US STATES ONLY</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Golden State</t>
+          <t>Slavic401K</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d156f80ddb5ea3e</t>
+          <t>https://www.indeed.com/viewjob?jk=df39dd0505c33d32</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>American Tower</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=340f3540cd359821</t>
+          <t>https://www.indeed.com/viewjob?jk=f4ab3e3c7077492c</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Advanced Data Integration &amp; Cloud Solutions</t>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Everforth ECS</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Inglewood, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, ETL, Python, SQL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca1d4ee2bfb7f383</t>
+          <t>https://www.indeed.com/viewjob?jk=b0870a8c631ca3e7</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AI Engineer/DevOps Engineer</t>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, Splunk, CI/CD, Azure DevOps, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4e19bdfcdfa54e3</t>
+          <t>https://www.indeed.com/viewjob?jk=3a8177305c7e2b4e</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Analyst, Data Engineer</t>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Lincoln Electric</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8382e0121c068a19</t>
+          <t>https://www.indeed.com/viewjob?jk=2b216035065cdcce</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4ab3e3c7077492c</t>
+          <t>https://www.indeed.com/viewjob?jk=b0d6bbe5db7dc4e3</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Inglewood, CA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0870a8c631ca3e7</t>
+          <t>https://www.indeed.com/viewjob?jk=99cd5dc3d4c47201</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a8177305c7e2b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=1535cff1bb626738</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Williamsville, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b216035065cdcce</t>
+          <t>https://www.indeed.com/viewjob?jk=37a520fdd5e099b9</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0d6bbe5db7dc4e3</t>
+          <t>https://www.indeed.com/viewjob?jk=366fcdfb585bd3be</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99cd5dc3d4c47201</t>
+          <t>https://www.indeed.com/viewjob?jk=a94f1ea7f43f3649</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1535cff1bb626738</t>
+          <t>https://www.indeed.com/viewjob?jk=497b07468d401d8a</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Williamsville, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37a520fdd5e099b9</t>
+          <t>https://www.indeed.com/viewjob?jk=8d2e49c364fa4321</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=366fcdfb585bd3be</t>
+          <t>https://www.indeed.com/viewjob?jk=14d6f7b29ae9eb47</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a94f1ea7f43f3649</t>
+          <t>https://www.indeed.com/viewjob?jk=e69bf4d69267775a</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=497b07468d401d8a</t>
+          <t>https://www.indeed.com/viewjob?jk=22a4f690926575b6</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d2e49c364fa4321</t>
+          <t>https://www.indeed.com/viewjob?jk=7fc8f10cc4340e38</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14d6f7b29ae9eb47</t>
+          <t>https://www.indeed.com/viewjob?jk=4ed7e30adf2adc59</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e69bf4d69267775a</t>
+          <t>https://www.indeed.com/viewjob?jk=22efcdd2b4a3dd7f</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22a4f690926575b6</t>
+          <t>https://www.indeed.com/viewjob?jk=4d610152102215d5</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fc8f10cc4340e38</t>
+          <t>https://www.indeed.com/viewjob?jk=0f093d62f255edad</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ed7e30adf2adc59</t>
+          <t>https://www.indeed.com/viewjob?jk=61c760c7b06ee2ec</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22efcdd2b4a3dd7f</t>
+          <t>https://www.indeed.com/viewjob?jk=7e753698d58ce405</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d610152102215d5</t>
+          <t>https://www.indeed.com/viewjob?jk=613c98d34d3a6aff</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f093d62f255edad</t>
+          <t>https://www.indeed.com/viewjob?jk=81eb38d16909745a</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61c760c7b06ee2ec</t>
+          <t>https://www.indeed.com/viewjob?jk=26aa4bbb65d7bc04</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e753698d58ce405</t>
+          <t>https://www.indeed.com/viewjob?jk=51eaf011bd4b3db9</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=613c98d34d3a6aff</t>
+          <t>https://www.indeed.com/viewjob?jk=875b54845cacd6b4</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81eb38d16909745a</t>
+          <t>https://www.indeed.com/viewjob?jk=b044118f339aeefe</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26aa4bbb65d7bc04</t>
+          <t>https://www.indeed.com/viewjob?jk=79172907c08cbd27</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51eaf011bd4b3db9</t>
+          <t>https://www.indeed.com/viewjob?jk=4072dd1e7bd9b46a</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=875b54845cacd6b4</t>
+          <t>https://www.indeed.com/viewjob?jk=60e28bece0970c90</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b044118f339aeefe</t>
+          <t>https://www.indeed.com/viewjob?jk=337e00bdabbbf617</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79172907c08cbd27</t>
+          <t>https://www.indeed.com/viewjob?jk=7008c23fbe380180</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4072dd1e7bd9b46a</t>
+          <t>https://www.indeed.com/viewjob?jk=ef94cdec933bb8d2</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60e28bece0970c90</t>
+          <t>https://www.indeed.com/viewjob?jk=a9b3dd72c73a5c59</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>San Juan, PR, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=337e00bdabbbf617</t>
+          <t>https://www.indeed.com/viewjob?jk=3f362104fdb5fce0</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7008c23fbe380180</t>
+          <t>https://www.indeed.com/viewjob?jk=bb3766965503e1b0</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef94cdec933bb8d2</t>
+          <t>https://www.indeed.com/viewjob?jk=01b7efd6177971eb</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9b3dd72c73a5c59</t>
+          <t>https://www.indeed.com/viewjob?jk=564843cdd5d6c05d</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>San Juan, PR, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f362104fdb5fce0</t>
+          <t>https://www.indeed.com/viewjob?jk=38dc1e892863874b</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb3766965503e1b0</t>
+          <t>https://www.indeed.com/viewjob?jk=36375563a2ad1043</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Honolulu, HI, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01b7efd6177971eb</t>
+          <t>https://www.indeed.com/viewjob?jk=cf1ab598617115f3</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=564843cdd5d6c05d</t>
+          <t>https://www.indeed.com/viewjob?jk=bdb4d76e4c3be44c</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38dc1e892863874b</t>
+          <t>https://www.indeed.com/viewjob?jk=bd706eccacda1e1c</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36375563a2ad1043</t>
+          <t>https://www.indeed.com/viewjob?jk=606f854062c681fa</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Honolulu, HI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf1ab598617115f3</t>
+          <t>https://www.indeed.com/viewjob?jk=15ee32196b2a250e</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdb4d76e4c3be44c</t>
+          <t>https://www.indeed.com/viewjob?jk=c7a2ced0233034b8</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd706eccacda1e1c</t>
+          <t>https://www.indeed.com/viewjob?jk=b267004acbc01cc5</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606f854062c681fa</t>
+          <t>https://www.indeed.com/viewjob?jk=9be2810504f2ae29</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15ee32196b2a250e</t>
+          <t>https://www.indeed.com/viewjob?jk=6f0ec602c9b09a8e</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7a2ced0233034b8</t>
+          <t>https://www.indeed.com/viewjob?jk=bd0e7d3dab7e604a</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b267004acbc01cc5</t>
+          <t>https://www.indeed.com/viewjob?jk=905c5a2344562ab8</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9be2810504f2ae29</t>
+          <t>https://www.indeed.com/viewjob?jk=21b0eb74cf57c4a8</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Monterey, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f0ec602c9b09a8e</t>
+          <t>https://www.indeed.com/viewjob?jk=127db1667ff89227</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd0e7d3dab7e604a</t>
+          <t>https://www.indeed.com/viewjob?jk=2a42559421200137</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=905c5a2344562ab8</t>
+          <t>https://www.indeed.com/viewjob?jk=d6e7dd724c924aca</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21b0eb74cf57c4a8</t>
+          <t>https://www.indeed.com/viewjob?jk=8483d29d2dbde05b</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Monterey, CA, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127db1667ff89227</t>
+          <t>https://www.indeed.com/viewjob?jk=824e663391dfa6bf</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a42559421200137</t>
+          <t>https://www.indeed.com/viewjob?jk=3e8686e8d16dc84d</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6e7dd724c924aca</t>
+          <t>https://www.indeed.com/viewjob?jk=496d9926f80e93e9</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8483d29d2dbde05b</t>
+          <t>https://www.indeed.com/viewjob?jk=57716cf6ab6ed7a5</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=824e663391dfa6bf</t>
+          <t>https://www.indeed.com/viewjob?jk=c418229c0f650f96</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e8686e8d16dc84d</t>
+          <t>https://www.indeed.com/viewjob?jk=95121729962d91d2</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=496d9926f80e93e9</t>
+          <t>https://www.indeed.com/viewjob?jk=dfec58f9b4c8760a</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57716cf6ab6ed7a5</t>
+          <t>https://www.indeed.com/viewjob?jk=5153281c36740802</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c418229c0f650f96</t>
+          <t>https://www.indeed.com/viewjob?jk=310acaaa4f9f42e3</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95121729962d91d2</t>
+          <t>https://www.indeed.com/viewjob?jk=6efe7ed3911371c4</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfec58f9b4c8760a</t>
+          <t>https://www.indeed.com/viewjob?jk=1a68cf132dbdec60</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5153281c36740802</t>
+          <t>https://www.indeed.com/viewjob?jk=8d891e75a79397a9</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=310acaaa4f9f42e3</t>
+          <t>https://www.indeed.com/viewjob?jk=117634e8f8dfb2d6</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6efe7ed3911371c4</t>
+          <t>https://www.indeed.com/viewjob?jk=b83a26f124ccdb89</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a68cf132dbdec60</t>
+          <t>https://www.indeed.com/viewjob?jk=ad88505e172120de</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d891e75a79397a9</t>
+          <t>https://www.indeed.com/viewjob?jk=c21ad262bec7ef80</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=117634e8f8dfb2d6</t>
+          <t>https://www.indeed.com/viewjob?jk=ca6810d972b1a5f1</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b83a26f124ccdb89</t>
+          <t>https://www.indeed.com/viewjob?jk=27043ef345d0b8a7</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad88505e172120de</t>
+          <t>https://www.indeed.com/viewjob?jk=be347b278f12cb33</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c21ad262bec7ef80</t>
+          <t>https://www.indeed.com/viewjob?jk=fed8b15c04492576</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca6810d972b1a5f1</t>
+          <t>https://www.indeed.com/viewjob?jk=5b12133504b24bae</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27043ef345d0b8a7</t>
+          <t>https://www.indeed.com/viewjob?jk=9f864d9aca9b7b27</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be347b278f12cb33</t>
+          <t>https://www.indeed.com/viewjob?jk=76d2eb1be4c1b252</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fed8b15c04492576</t>
+          <t>https://www.indeed.com/viewjob?jk=9baba2b401f1c56c</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+          <t>Databricks Developer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b12133504b24bae</t>
+          <t>https://www.indeed.com/viewjob?jk=ab1192abfbd7f24e</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+          <t>Databricks Developer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,32 +4591,32 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f864d9aca9b7b27</t>
+          <t>https://www.indeed.com/viewjob?jk=320dcd4f927cb250</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+          <t>Associate, Data Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, DynamoDB, Azure Cosmos DB, NoSQL</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,32 +4626,32 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76d2eb1be4c1b252</t>
+          <t>https://www.indeed.com/viewjob?jk=06fd6810514e5491</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+          <t>Site Reliability Engineering (SRE) - Maryland, US</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+          <t>Azure, GCP, BigQuery, Zookeeper, Scala, Kafka, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,32 +4661,32 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9baba2b401f1c56c</t>
+          <t>https://www.indeed.com/viewjob?jk=8d51d47e65997196</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Platform (Azure)</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform, Azure Monitor</t>
+          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,32 +4696,32 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=defb19c3b807f7fd</t>
+          <t>https://www.indeed.com/viewjob?jk=33b30501746ad4bf</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect - WORK FROM HOME - SELECT US STATES ONLY</t>
+          <t>Data Engineer - Oklahoma City, OK</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Slavic401K</t>
+          <t>CFS Brands, LLC</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>IAM, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,19 +4731,19 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df39dd0505c33d32</t>
+          <t>https://www.indeed.com/viewjob?jk=113fe7e3580ec298</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Databricks Developer</t>
+          <t>Apache Spark Core Java</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4752,46 +4752,46 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab1192abfbd7f24e</t>
+          <t>https://www.indeed.com/viewjob?jk=16d16eda2d514586</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Databricks Developer</t>
+          <t>Senior Analytics Engineer, Marketing Sciences</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>SimplePractice</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Kinesis, RDS, Scala, Kafka, Snowflake, ETL, dbt, Terraform, Docker</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4800,216 +4800,6 @@
         </is>
       </c>
       <c r="G125" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=320dcd4f927cb250</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Associate, Data Engineer</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>BlackRock</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, DynamoDB, Azure Cosmos DB, NoSQL</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=06fd6810514e5491</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Site Reliability Engineering (SRE) - Maryland, US</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Baltimore, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>Azure, GCP, BigQuery, Zookeeper, Scala, Kafka, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8d51d47e65997196</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Data Engineer III</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=33b30501746ad4bf</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Data Engineer - Oklahoma City, OK</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>CFS Brands, LLC</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Oklahoma City, OK, US USA</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>IAM, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=113fe7e3580ec298</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Apache Spark Core Java</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>2026-08-22</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=16d16eda2d514586</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Senior Analytics Engineer, Marketing Sciences</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>SimplePractice</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, RDS, Scala, Kafka, Snowflake, ETL, dbt, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=4a341479dc01b56f</t>
         </is>

--- a/results/job_matches_2026-08-22.xlsx
+++ b/results/job_matches_2026-08-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G125"/>
+  <dimension ref="A1:G123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,60 +573,60 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer Microsoft Fabric</t>
+          <t>DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bilzin Sumberg Baena Price &amp; Axelrod LLP</t>
+          <t>Claritas Rx</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>19.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Snowflake, SQL Server</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, SQS, ECS, IAM, RDS, Spark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=371409082795e582</t>
+          <t>https://www.indeed.com/viewjob?jk=e12b8c592b8fca76</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer Microsoft Fabric</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Entarian</t>
+          <t>Bilzin Sumberg Baena Price &amp; Axelrod LLP</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Scala, Kafka, Polars, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>S3, RDS, Azure, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,14 +636,14 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97cacdd77a88ee4d</t>
+          <t>https://www.indeed.com/viewjob?jk=371409082795e582</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d62e6c9bd298592</t>
+          <t>https://www.indeed.com/viewjob?jk=97cacdd77a88ee4d</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI Platform System Administrator III</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Boston Scientific</t>
+          <t>Entarian</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Arden Hills, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, Kinesis, Scala, Kafka, Polars, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62388f603bbe60a4</t>
+          <t>https://www.indeed.com/viewjob?jk=8d62e6c9bd298592</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Engineer, Enterprise Database</t>
+          <t>AI Platform System Administrator III</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Applied Medical</t>
+          <t>Boston Scientific</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Rancho Santa Margarita, CA, US USA</t>
+          <t>Arden Hills, MN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51a5d6b8454480a2</t>
+          <t>https://www.indeed.com/viewjob?jk=62388f603bbe60a4</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer, Full Stack - AI (New York)</t>
+          <t>Senior Engineer, Enterprise Database</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Fitch Group</t>
+          <t>Applied Medical</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Rancho Santa Margarita, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=362603547d1c2a0d</t>
+          <t>https://www.indeed.com/viewjob?jk=51a5d6b8454480a2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Science Engineer</t>
+          <t>Software Engineer, Full Stack - AI (New York)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LegitScript</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, MLOps</t>
+          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ac58242095324ac</t>
+          <t>https://www.indeed.com/viewjob?jk=362603547d1c2a0d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Data Science Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Powerplan</t>
+          <t>LegitScript</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, MLOps, CI/CD, Azure DevOps</t>
+          <t>Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, MLOps</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9effd2546d52cd38</t>
+          <t>https://www.indeed.com/viewjob?jk=0ac58242095324ac</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Credit Acceptance</t>
+          <t>Powerplan</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39dcfd9f2966d672</t>
+          <t>https://www.indeed.com/viewjob?jk=9effd2546d52cd38</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Platform (AWS)</t>
+          <t>Software Engineer II, Data</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Credit Acceptance</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7064a0875d5078f8</t>
+          <t>https://www.indeed.com/viewjob?jk=39dcfd9f2966d672</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Platform (AWS)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, S3, RDS, Spark, Scala, PostgreSQL, NoSQL, Jenkins</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d1eabd20620b211</t>
+          <t>https://www.indeed.com/viewjob?jk=7064a0875d5078f8</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Solutions Delivery Engineer (Remote)</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>RealPage Inc</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, EMR, Kinesis, S3, RDS, Spark, Scala, PostgreSQL, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec761fb42adb289d</t>
+          <t>https://www.indeed.com/viewjob?jk=5d1eabd20620b211</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer - LLMs, GenAI</t>
+          <t>Solutions Delivery Engineer (Remote)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>RealPage Inc</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Power BI, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ef55c2266d41678</t>
+          <t>https://www.indeed.com/viewjob?jk=ec761fb42adb289d</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Professional Services Consultant</t>
+          <t>Senior Software Development Engineer - LLMs, GenAI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ataccama</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Power BI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,19 +1056,19 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f49a3f3dbcbca27</t>
+          <t>https://www.indeed.com/viewjob?jk=7ef55c2266d41678</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CDP Architect</t>
+          <t>Senior Professional Services Consultant</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Bounteous</t>
+          <t>Ataccama</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5b99e7a77983415</t>
+          <t>https://www.indeed.com/viewjob?jk=0f49a3f3dbcbca27</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Devops Engineer</t>
+          <t>CDP Architect</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Bounteous</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=143f81631e970888</t>
+          <t>https://www.indeed.com/viewjob?jk=f5b99e7a77983415</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Full stack Java / AWS</t>
+          <t>Senior Devops Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL, DynamoDB, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=648c04000182f970</t>
+          <t>https://www.indeed.com/viewjob?jk=143f81631e970888</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Azure IoT Solutions Engineer</t>
+          <t>Senior Full stack Java / AWS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ascend Technologies</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AKS, Jenkins</t>
+          <t>AWS, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48463a0b2c1a516b</t>
+          <t>https://www.indeed.com/viewjob?jk=648c04000182f970</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>GCP Cloud Engineer</t>
+          <t>Azure IoT Solutions Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Ascend Technologies</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Event Hubs, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b7cc426dbd03f0e</t>
+          <t>https://www.indeed.com/viewjob?jk=48463a0b2c1a516b</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Economic Data System Engineer/Sr. Economic Data System Engineer-ITDDPED</t>
+          <t>GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Hadoop, Spark, Scala, Snowflake, NoSQL, ETL, ELT</t>
+          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a32b2285f6e0f19</t>
+          <t>https://www.indeed.com/viewjob?jk=6b7cc426dbd03f0e</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>QA Automation Engineer II, Officer</t>
+          <t>Economic Data System Engineer/Sr. Economic Data System Engineer-ITDDPED</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, NoSQL, Talend, CI/CD, Jenkins, Docker, Jenkins, Git</t>
+          <t>RDS, Databricks, BigQuery, Hadoop, Spark, Scala, Snowflake, NoSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d73747fd9aafef8</t>
+          <t>https://www.indeed.com/viewjob?jk=3a32b2285f6e0f19</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>QA Automation Engineer II, Officer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Mercari</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Tableau</t>
+          <t>RDS, Scala, Oracle, NoSQL, Talend, CI/CD, Jenkins, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=179685542a7cf944</t>
+          <t>https://www.indeed.com/viewjob?jk=1d73747fd9aafef8</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr Engineer, Data Engineering</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Pilot Flying J</t>
+          <t>Mercari</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Roswell, GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Tableau</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a70d5a50e3bc2a5</t>
+          <t>https://www.indeed.com/viewjob?jk=179685542a7cf944</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Sr Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Pilot Flying J</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Roswell, GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Kafka, CI/CD, Terraform, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a5cbb62cc968f68</t>
+          <t>https://www.indeed.com/viewjob?jk=0a70d5a50e3bc2a5</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Marathon Petroleum</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, CI/CD, Git, Python, SQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Kafka, CI/CD, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28293fa77ffc32bb</t>
+          <t>https://www.indeed.com/viewjob?jk=9a5cbb62cc968f68</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Golden State</t>
+          <t>Marathon Petroleum</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d156f80ddb5ea3e</t>
+          <t>https://www.indeed.com/viewjob?jk=28293fa77ffc32bb</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>American Tower</t>
+          <t>Golden State</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=340f3540cd359821</t>
+          <t>https://www.indeed.com/viewjob?jk=1d156f80ddb5ea3e</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Advanced Data Integration &amp; Cloud Solutions</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Everforth ECS</t>
+          <t>American Tower</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, ETL, Python, SQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca1d4ee2bfb7f383</t>
+          <t>https://www.indeed.com/viewjob?jk=340f3540cd359821</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AI Engineer/DevOps Engineer</t>
+          <t>Senior Data Engineer – Advanced Data Integration &amp; Cloud Solutions</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Everforth ECS</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, Splunk, CI/CD, Azure DevOps, Kubernetes</t>
+          <t>ECS, RDS, Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, ETL, Python, SQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4e19bdfcdfa54e3</t>
+          <t>https://www.indeed.com/viewjob?jk=ca1d4ee2bfb7f383</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Analyst, Data Engineer</t>
+          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Platform (Azure)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Lincoln Electric</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform, Azure Monitor</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8382e0121c068a19</t>
+          <t>https://www.indeed.com/viewjob?jk=defb19c3b807f7fd</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Platform (Azure)</t>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform, Azure Monitor</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=defb19c3b807f7fd</t>
+          <t>https://www.indeed.com/viewjob?jk=f4ab3e3c7077492c</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect - WORK FROM HOME - SELECT US STATES ONLY</t>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Slavic401K</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Inglewood, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df39dd0505c33d32</t>
+          <t>https://www.indeed.com/viewjob?jk=b0870a8c631ca3e7</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4ab3e3c7077492c</t>
+          <t>https://www.indeed.com/viewjob?jk=3a8177305c7e2b4e</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Inglewood, CA, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0870a8c631ca3e7</t>
+          <t>https://www.indeed.com/viewjob?jk=2b216035065cdcce</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a8177305c7e2b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=b0d6bbe5db7dc4e3</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b216035065cdcce</t>
+          <t>https://www.indeed.com/viewjob?jk=99cd5dc3d4c47201</t>
         </is>
       </c>
     </row>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0d6bbe5db7dc4e3</t>
+          <t>https://www.indeed.com/viewjob?jk=1535cff1bb626738</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Williamsville, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99cd5dc3d4c47201</t>
+          <t>https://www.indeed.com/viewjob?jk=37a520fdd5e099b9</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1535cff1bb626738</t>
+          <t>https://www.indeed.com/viewjob?jk=366fcdfb585bd3be</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Williamsville, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37a520fdd5e099b9</t>
+          <t>https://www.indeed.com/viewjob?jk=a94f1ea7f43f3649</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=366fcdfb585bd3be</t>
+          <t>https://www.indeed.com/viewjob?jk=497b07468d401d8a</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a94f1ea7f43f3649</t>
+          <t>https://www.indeed.com/viewjob?jk=8d2e49c364fa4321</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=497b07468d401d8a</t>
+          <t>https://www.indeed.com/viewjob?jk=14d6f7b29ae9eb47</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d2e49c364fa4321</t>
+          <t>https://www.indeed.com/viewjob?jk=e69bf4d69267775a</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14d6f7b29ae9eb47</t>
+          <t>https://www.indeed.com/viewjob?jk=22a4f690926575b6</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e69bf4d69267775a</t>
+          <t>https://www.indeed.com/viewjob?jk=7fc8f10cc4340e38</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22a4f690926575b6</t>
+          <t>https://www.indeed.com/viewjob?jk=4ed7e30adf2adc59</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fc8f10cc4340e38</t>
+          <t>https://www.indeed.com/viewjob?jk=22efcdd2b4a3dd7f</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ed7e30adf2adc59</t>
+          <t>https://www.indeed.com/viewjob?jk=4d610152102215d5</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22efcdd2b4a3dd7f</t>
+          <t>https://www.indeed.com/viewjob?jk=0f093d62f255edad</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d610152102215d5</t>
+          <t>https://www.indeed.com/viewjob?jk=61c760c7b06ee2ec</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f093d62f255edad</t>
+          <t>https://www.indeed.com/viewjob?jk=7e753698d58ce405</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61c760c7b06ee2ec</t>
+          <t>https://www.indeed.com/viewjob?jk=613c98d34d3a6aff</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e753698d58ce405</t>
+          <t>https://www.indeed.com/viewjob?jk=81eb38d16909745a</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=613c98d34d3a6aff</t>
+          <t>https://www.indeed.com/viewjob?jk=26aa4bbb65d7bc04</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81eb38d16909745a</t>
+          <t>https://www.indeed.com/viewjob?jk=51eaf011bd4b3db9</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26aa4bbb65d7bc04</t>
+          <t>https://www.indeed.com/viewjob?jk=875b54845cacd6b4</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51eaf011bd4b3db9</t>
+          <t>https://www.indeed.com/viewjob?jk=b044118f339aeefe</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=875b54845cacd6b4</t>
+          <t>https://www.indeed.com/viewjob?jk=79172907c08cbd27</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b044118f339aeefe</t>
+          <t>https://www.indeed.com/viewjob?jk=4072dd1e7bd9b46a</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79172907c08cbd27</t>
+          <t>https://www.indeed.com/viewjob?jk=60e28bece0970c90</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4072dd1e7bd9b46a</t>
+          <t>https://www.indeed.com/viewjob?jk=337e00bdabbbf617</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60e28bece0970c90</t>
+          <t>https://www.indeed.com/viewjob?jk=7008c23fbe380180</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=337e00bdabbbf617</t>
+          <t>https://www.indeed.com/viewjob?jk=ef94cdec933bb8d2</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7008c23fbe380180</t>
+          <t>https://www.indeed.com/viewjob?jk=a9b3dd72c73a5c59</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>San Juan, PR, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef94cdec933bb8d2</t>
+          <t>https://www.indeed.com/viewjob?jk=3f362104fdb5fce0</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9b3dd72c73a5c59</t>
+          <t>https://www.indeed.com/viewjob?jk=bb3766965503e1b0</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>San Juan, PR, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f362104fdb5fce0</t>
+          <t>https://www.indeed.com/viewjob?jk=01b7efd6177971eb</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb3766965503e1b0</t>
+          <t>https://www.indeed.com/viewjob?jk=564843cdd5d6c05d</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01b7efd6177971eb</t>
+          <t>https://www.indeed.com/viewjob?jk=38dc1e892863874b</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=564843cdd5d6c05d</t>
+          <t>https://www.indeed.com/viewjob?jk=36375563a2ad1043</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Honolulu, HI, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38dc1e892863874b</t>
+          <t>https://www.indeed.com/viewjob?jk=cf1ab598617115f3</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36375563a2ad1043</t>
+          <t>https://www.indeed.com/viewjob?jk=bdb4d76e4c3be44c</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Honolulu, HI, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf1ab598617115f3</t>
+          <t>https://www.indeed.com/viewjob?jk=bd706eccacda1e1c</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdb4d76e4c3be44c</t>
+          <t>https://www.indeed.com/viewjob?jk=606f854062c681fa</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd706eccacda1e1c</t>
+          <t>https://www.indeed.com/viewjob?jk=15ee32196b2a250e</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606f854062c681fa</t>
+          <t>https://www.indeed.com/viewjob?jk=c7a2ced0233034b8</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15ee32196b2a250e</t>
+          <t>https://www.indeed.com/viewjob?jk=b267004acbc01cc5</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7a2ced0233034b8</t>
+          <t>https://www.indeed.com/viewjob?jk=9be2810504f2ae29</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b267004acbc01cc5</t>
+          <t>https://www.indeed.com/viewjob?jk=6f0ec602c9b09a8e</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9be2810504f2ae29</t>
+          <t>https://www.indeed.com/viewjob?jk=bd0e7d3dab7e604a</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f0ec602c9b09a8e</t>
+          <t>https://www.indeed.com/viewjob?jk=905c5a2344562ab8</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd0e7d3dab7e604a</t>
+          <t>https://www.indeed.com/viewjob?jk=21b0eb74cf57c4a8</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Monterey, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=905c5a2344562ab8</t>
+          <t>https://www.indeed.com/viewjob?jk=127db1667ff89227</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21b0eb74cf57c4a8</t>
+          <t>https://www.indeed.com/viewjob?jk=2a42559421200137</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Monterey, CA, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127db1667ff89227</t>
+          <t>https://www.indeed.com/viewjob?jk=d6e7dd724c924aca</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a42559421200137</t>
+          <t>https://www.indeed.com/viewjob?jk=8483d29d2dbde05b</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6e7dd724c924aca</t>
+          <t>https://www.indeed.com/viewjob?jk=824e663391dfa6bf</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8483d29d2dbde05b</t>
+          <t>https://www.indeed.com/viewjob?jk=3e8686e8d16dc84d</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=824e663391dfa6bf</t>
+          <t>https://www.indeed.com/viewjob?jk=496d9926f80e93e9</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e8686e8d16dc84d</t>
+          <t>https://www.indeed.com/viewjob?jk=57716cf6ab6ed7a5</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=496d9926f80e93e9</t>
+          <t>https://www.indeed.com/viewjob?jk=c418229c0f650f96</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57716cf6ab6ed7a5</t>
+          <t>https://www.indeed.com/viewjob?jk=95121729962d91d2</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c418229c0f650f96</t>
+          <t>https://www.indeed.com/viewjob?jk=dfec58f9b4c8760a</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95121729962d91d2</t>
+          <t>https://www.indeed.com/viewjob?jk=5153281c36740802</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfec58f9b4c8760a</t>
+          <t>https://www.indeed.com/viewjob?jk=310acaaa4f9f42e3</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5153281c36740802</t>
+          <t>https://www.indeed.com/viewjob?jk=6efe7ed3911371c4</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=310acaaa4f9f42e3</t>
+          <t>https://www.indeed.com/viewjob?jk=1a68cf132dbdec60</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6efe7ed3911371c4</t>
+          <t>https://www.indeed.com/viewjob?jk=8d891e75a79397a9</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a68cf132dbdec60</t>
+          <t>https://www.indeed.com/viewjob?jk=117634e8f8dfb2d6</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d891e75a79397a9</t>
+          <t>https://www.indeed.com/viewjob?jk=b83a26f124ccdb89</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=117634e8f8dfb2d6</t>
+          <t>https://www.indeed.com/viewjob?jk=ad88505e172120de</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b83a26f124ccdb89</t>
+          <t>https://www.indeed.com/viewjob?jk=c21ad262bec7ef80</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad88505e172120de</t>
+          <t>https://www.indeed.com/viewjob?jk=ca6810d972b1a5f1</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c21ad262bec7ef80</t>
+          <t>https://www.indeed.com/viewjob?jk=27043ef345d0b8a7</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca6810d972b1a5f1</t>
+          <t>https://www.indeed.com/viewjob?jk=be347b278f12cb33</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27043ef345d0b8a7</t>
+          <t>https://www.indeed.com/viewjob?jk=fed8b15c04492576</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be347b278f12cb33</t>
+          <t>https://www.indeed.com/viewjob?jk=5b12133504b24bae</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fed8b15c04492576</t>
+          <t>https://www.indeed.com/viewjob?jk=9f864d9aca9b7b27</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b12133504b24bae</t>
+          <t>https://www.indeed.com/viewjob?jk=76d2eb1be4c1b252</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f864d9aca9b7b27</t>
+          <t>https://www.indeed.com/viewjob?jk=9baba2b401f1c56c</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+          <t>Databricks Developer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76d2eb1be4c1b252</t>
+          <t>https://www.indeed.com/viewjob?jk=ab1192abfbd7f24e</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+          <t>Databricks Developer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,32 +4521,32 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9baba2b401f1c56c</t>
+          <t>https://www.indeed.com/viewjob?jk=320dcd4f927cb250</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Databricks Developer</t>
+          <t>Associate, Data Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, DynamoDB, Azure Cosmos DB, NoSQL</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,32 +4556,32 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab1192abfbd7f24e</t>
+          <t>https://www.indeed.com/viewjob?jk=06fd6810514e5491</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Databricks Developer</t>
+          <t>Site Reliability Engineering (SRE) - Maryland, US</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>Azure, GCP, BigQuery, Zookeeper, Scala, Kafka, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=320dcd4f927cb250</t>
+          <t>https://www.indeed.com/viewjob?jk=8d51d47e65997196</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Associate, Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, DynamoDB, Azure Cosmos DB, NoSQL</t>
+          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06fd6810514e5491</t>
+          <t>https://www.indeed.com/viewjob?jk=33b30501746ad4bf</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Site Reliability Engineering (SRE) - Maryland, US</t>
+          <t>Data Engineer - Oklahoma City, OK</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>CFS Brands, LLC</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Azure, GCP, BigQuery, Zookeeper, Scala, Kafka, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>IAM, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d51d47e65997196</t>
+          <t>https://www.indeed.com/viewjob?jk=113fe7e3580ec298</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Apache Spark Core Java</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,34 +4686,34 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33b30501746ad4bf</t>
+          <t>https://www.indeed.com/viewjob?jk=16d16eda2d514586</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Data Engineer - Oklahoma City, OK</t>
+          <t>Senior Analytics Engineer, Marketing Sciences</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>CFS Brands, LLC</t>
+          <t>SimplePractice</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>IAM, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Kinesis, RDS, Scala, Kafka, Snowflake, ETL, dbt, Terraform, Docker</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4730,76 +4730,6 @@
         </is>
       </c>
       <c r="G123" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=113fe7e3580ec298</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Apache Spark Core Java</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>2026-08-22</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=16d16eda2d514586</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Senior Analytics Engineer, Marketing Sciences</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>SimplePractice</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, RDS, Scala, Kafka, Snowflake, ETL, dbt, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=4a341479dc01b56f</t>
         </is>

--- a/results/job_matches_2026-08-22.xlsx
+++ b/results/job_matches_2026-08-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G123"/>
+  <dimension ref="A1:G118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1273,17 +1273,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Economic Data System Engineer/Sr. Economic Data System Engineer-ITDDPED</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Mercari</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Hadoop, Spark, Scala, Snowflake, NoSQL, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Tableau</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a32b2285f6e0f19</t>
+          <t>https://www.indeed.com/viewjob?jk=179685542a7cf944</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>QA Automation Engineer II, Officer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, NoSQL, Talend, CI/CD, Jenkins, Docker, Jenkins, Git</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Kafka, CI/CD, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d73747fd9aafef8</t>
+          <t>https://www.indeed.com/viewjob?jk=9a5cbb62cc968f68</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Mercari</t>
+          <t>Marathon Petroleum</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Tableau</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=179685542a7cf944</t>
+          <t>https://www.indeed.com/viewjob?jk=28293fa77ffc32bb</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr Engineer, Data Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Pilot Flying J</t>
+          <t>Golden State</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Roswell, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a70d5a50e3bc2a5</t>
+          <t>https://www.indeed.com/viewjob?jk=1d156f80ddb5ea3e</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Kafka, CI/CD, Terraform, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a5cbb62cc968f68</t>
+          <t>https://www.indeed.com/viewjob?jk=f4ab3e3c7077492c</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Marathon Petroleum</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Inglewood, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, CI/CD, Git, Python, SQL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28293fa77ffc32bb</t>
+          <t>https://www.indeed.com/viewjob?jk=b0870a8c631ca3e7</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Golden State</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d156f80ddb5ea3e</t>
+          <t>https://www.indeed.com/viewjob?jk=3a8177305c7e2b4e</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>American Tower</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=340f3540cd359821</t>
+          <t>https://www.indeed.com/viewjob?jk=2b216035065cdcce</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Advanced Data Integration &amp; Cloud Solutions</t>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Everforth ECS</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, ETL, Python, SQL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca1d4ee2bfb7f383</t>
+          <t>https://www.indeed.com/viewjob?jk=b0d6bbe5db7dc4e3</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Platform (Azure)</t>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform, Azure Monitor</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=defb19c3b807f7fd</t>
+          <t>https://www.indeed.com/viewjob?jk=99cd5dc3d4c47201</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4ab3e3c7077492c</t>
+          <t>https://www.indeed.com/viewjob?jk=1535cff1bb626738</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Inglewood, CA, US USA</t>
+          <t>Williamsville, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0870a8c631ca3e7</t>
+          <t>https://www.indeed.com/viewjob?jk=37a520fdd5e099b9</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a8177305c7e2b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=366fcdfb585bd3be</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b216035065cdcce</t>
+          <t>https://www.indeed.com/viewjob?jk=a94f1ea7f43f3649</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0d6bbe5db7dc4e3</t>
+          <t>https://www.indeed.com/viewjob?jk=497b07468d401d8a</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99cd5dc3d4c47201</t>
+          <t>https://www.indeed.com/viewjob?jk=8d2e49c364fa4321</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1535cff1bb626738</t>
+          <t>https://www.indeed.com/viewjob?jk=14d6f7b29ae9eb47</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Williamsville, NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37a520fdd5e099b9</t>
+          <t>https://www.indeed.com/viewjob?jk=e69bf4d69267775a</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=366fcdfb585bd3be</t>
+          <t>https://www.indeed.com/viewjob?jk=22a4f690926575b6</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a94f1ea7f43f3649</t>
+          <t>https://www.indeed.com/viewjob?jk=7fc8f10cc4340e38</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=497b07468d401d8a</t>
+          <t>https://www.indeed.com/viewjob?jk=4ed7e30adf2adc59</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d2e49c364fa4321</t>
+          <t>https://www.indeed.com/viewjob?jk=22efcdd2b4a3dd7f</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14d6f7b29ae9eb47</t>
+          <t>https://www.indeed.com/viewjob?jk=4d610152102215d5</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e69bf4d69267775a</t>
+          <t>https://www.indeed.com/viewjob?jk=0f093d62f255edad</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22a4f690926575b6</t>
+          <t>https://www.indeed.com/viewjob?jk=61c760c7b06ee2ec</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fc8f10cc4340e38</t>
+          <t>https://www.indeed.com/viewjob?jk=7e753698d58ce405</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ed7e30adf2adc59</t>
+          <t>https://www.indeed.com/viewjob?jk=613c98d34d3a6aff</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22efcdd2b4a3dd7f</t>
+          <t>https://www.indeed.com/viewjob?jk=81eb38d16909745a</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d610152102215d5</t>
+          <t>https://www.indeed.com/viewjob?jk=26aa4bbb65d7bc04</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f093d62f255edad</t>
+          <t>https://www.indeed.com/viewjob?jk=51eaf011bd4b3db9</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61c760c7b06ee2ec</t>
+          <t>https://www.indeed.com/viewjob?jk=875b54845cacd6b4</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e753698d58ce405</t>
+          <t>https://www.indeed.com/viewjob?jk=b044118f339aeefe</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=613c98d34d3a6aff</t>
+          <t>https://www.indeed.com/viewjob?jk=79172907c08cbd27</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81eb38d16909745a</t>
+          <t>https://www.indeed.com/viewjob?jk=4072dd1e7bd9b46a</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26aa4bbb65d7bc04</t>
+          <t>https://www.indeed.com/viewjob?jk=60e28bece0970c90</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51eaf011bd4b3db9</t>
+          <t>https://www.indeed.com/viewjob?jk=337e00bdabbbf617</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=875b54845cacd6b4</t>
+          <t>https://www.indeed.com/viewjob?jk=7008c23fbe380180</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b044118f339aeefe</t>
+          <t>https://www.indeed.com/viewjob?jk=ef94cdec933bb8d2</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79172907c08cbd27</t>
+          <t>https://www.indeed.com/viewjob?jk=a9b3dd72c73a5c59</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Juan, PR, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4072dd1e7bd9b46a</t>
+          <t>https://www.indeed.com/viewjob?jk=3f362104fdb5fce0</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60e28bece0970c90</t>
+          <t>https://www.indeed.com/viewjob?jk=bb3766965503e1b0</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=337e00bdabbbf617</t>
+          <t>https://www.indeed.com/viewjob?jk=01b7efd6177971eb</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7008c23fbe380180</t>
+          <t>https://www.indeed.com/viewjob?jk=564843cdd5d6c05d</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef94cdec933bb8d2</t>
+          <t>https://www.indeed.com/viewjob?jk=38dc1e892863874b</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9b3dd72c73a5c59</t>
+          <t>https://www.indeed.com/viewjob?jk=36375563a2ad1043</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>San Juan, PR, US USA</t>
+          <t>Honolulu, HI, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f362104fdb5fce0</t>
+          <t>https://www.indeed.com/viewjob?jk=cf1ab598617115f3</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb3766965503e1b0</t>
+          <t>https://www.indeed.com/viewjob?jk=bdb4d76e4c3be44c</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01b7efd6177971eb</t>
+          <t>https://www.indeed.com/viewjob?jk=bd706eccacda1e1c</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=564843cdd5d6c05d</t>
+          <t>https://www.indeed.com/viewjob?jk=606f854062c681fa</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38dc1e892863874b</t>
+          <t>https://www.indeed.com/viewjob?jk=15ee32196b2a250e</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36375563a2ad1043</t>
+          <t>https://www.indeed.com/viewjob?jk=c7a2ced0233034b8</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Honolulu, HI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf1ab598617115f3</t>
+          <t>https://www.indeed.com/viewjob?jk=b267004acbc01cc5</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdb4d76e4c3be44c</t>
+          <t>https://www.indeed.com/viewjob?jk=9be2810504f2ae29</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd706eccacda1e1c</t>
+          <t>https://www.indeed.com/viewjob?jk=6f0ec602c9b09a8e</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606f854062c681fa</t>
+          <t>https://www.indeed.com/viewjob?jk=bd0e7d3dab7e604a</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15ee32196b2a250e</t>
+          <t>https://www.indeed.com/viewjob?jk=905c5a2344562ab8</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7a2ced0233034b8</t>
+          <t>https://www.indeed.com/viewjob?jk=21b0eb74cf57c4a8</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Monterey, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b267004acbc01cc5</t>
+          <t>https://www.indeed.com/viewjob?jk=127db1667ff89227</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9be2810504f2ae29</t>
+          <t>https://www.indeed.com/viewjob?jk=2a42559421200137</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f0ec602c9b09a8e</t>
+          <t>https://www.indeed.com/viewjob?jk=d6e7dd724c924aca</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd0e7d3dab7e604a</t>
+          <t>https://www.indeed.com/viewjob?jk=8483d29d2dbde05b</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=905c5a2344562ab8</t>
+          <t>https://www.indeed.com/viewjob?jk=824e663391dfa6bf</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21b0eb74cf57c4a8</t>
+          <t>https://www.indeed.com/viewjob?jk=3e8686e8d16dc84d</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Monterey, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127db1667ff89227</t>
+          <t>https://www.indeed.com/viewjob?jk=496d9926f80e93e9</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a42559421200137</t>
+          <t>https://www.indeed.com/viewjob?jk=57716cf6ab6ed7a5</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6e7dd724c924aca</t>
+          <t>https://www.indeed.com/viewjob?jk=c418229c0f650f96</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8483d29d2dbde05b</t>
+          <t>https://www.indeed.com/viewjob?jk=95121729962d91d2</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=824e663391dfa6bf</t>
+          <t>https://www.indeed.com/viewjob?jk=dfec58f9b4c8760a</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e8686e8d16dc84d</t>
+          <t>https://www.indeed.com/viewjob?jk=5153281c36740802</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=496d9926f80e93e9</t>
+          <t>https://www.indeed.com/viewjob?jk=310acaaa4f9f42e3</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57716cf6ab6ed7a5</t>
+          <t>https://www.indeed.com/viewjob?jk=6efe7ed3911371c4</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c418229c0f650f96</t>
+          <t>https://www.indeed.com/viewjob?jk=1a68cf132dbdec60</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95121729962d91d2</t>
+          <t>https://www.indeed.com/viewjob?jk=8d891e75a79397a9</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfec58f9b4c8760a</t>
+          <t>https://www.indeed.com/viewjob?jk=117634e8f8dfb2d6</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5153281c36740802</t>
+          <t>https://www.indeed.com/viewjob?jk=b83a26f124ccdb89</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=310acaaa4f9f42e3</t>
+          <t>https://www.indeed.com/viewjob?jk=ad88505e172120de</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6efe7ed3911371c4</t>
+          <t>https://www.indeed.com/viewjob?jk=c21ad262bec7ef80</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a68cf132dbdec60</t>
+          <t>https://www.indeed.com/viewjob?jk=ca6810d972b1a5f1</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d891e75a79397a9</t>
+          <t>https://www.indeed.com/viewjob?jk=27043ef345d0b8a7</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=117634e8f8dfb2d6</t>
+          <t>https://www.indeed.com/viewjob?jk=be347b278f12cb33</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b83a26f124ccdb89</t>
+          <t>https://www.indeed.com/viewjob?jk=fed8b15c04492576</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad88505e172120de</t>
+          <t>https://www.indeed.com/viewjob?jk=5b12133504b24bae</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c21ad262bec7ef80</t>
+          <t>https://www.indeed.com/viewjob?jk=9f864d9aca9b7b27</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca6810d972b1a5f1</t>
+          <t>https://www.indeed.com/viewjob?jk=76d2eb1be4c1b252</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27043ef345d0b8a7</t>
+          <t>https://www.indeed.com/viewjob?jk=9baba2b401f1c56c</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Platform (Azure)</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform, Azure Monitor</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be347b278f12cb33</t>
+          <t>https://www.indeed.com/viewjob?jk=defb19c3b807f7fd</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+          <t>Databricks Developer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fed8b15c04492576</t>
+          <t>https://www.indeed.com/viewjob?jk=ab1192abfbd7f24e</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+          <t>Databricks Developer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,32 +4346,32 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b12133504b24bae</t>
+          <t>https://www.indeed.com/viewjob?jk=320dcd4f927cb250</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+          <t>Associate, Data Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, DynamoDB, Azure Cosmos DB, NoSQL</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,32 +4381,32 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f864d9aca9b7b27</t>
+          <t>https://www.indeed.com/viewjob?jk=06fd6810514e5491</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+          <t>Site Reliability Engineering (SRE) - Maryland, US</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+          <t>Azure, GCP, BigQuery, Zookeeper, Scala, Kafka, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,32 +4416,32 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76d2eb1be4c1b252</t>
+          <t>https://www.indeed.com/viewjob?jk=8d51d47e65997196</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,32 +4451,32 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9baba2b401f1c56c</t>
+          <t>https://www.indeed.com/viewjob?jk=33b30501746ad4bf</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Databricks Developer</t>
+          <t>Data Engineer - Oklahoma City, OK</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CFS Brands, LLC</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>IAM, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,19 +4486,19 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab1192abfbd7f24e</t>
+          <t>https://www.indeed.com/viewjob?jk=113fe7e3580ec298</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Databricks Developer</t>
+          <t>Apache Spark Core Java</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4507,38 +4507,38 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=320dcd4f927cb250</t>
+          <t>https://www.indeed.com/viewjob?jk=16d16eda2d514586</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Associate, Data Engineer</t>
+          <t>Senior Analytics Engineer, Marketing Sciences</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>SimplePractice</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, DynamoDB, Azure Cosmos DB, NoSQL</t>
+          <t>AWS, Kinesis, RDS, Scala, Kafka, Snowflake, ETL, dbt, Terraform, Docker</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4555,181 +4555,6 @@
         </is>
       </c>
       <c r="G118" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=06fd6810514e5491</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Site Reliability Engineering (SRE) - Maryland, US</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Baltimore, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>Azure, GCP, BigQuery, Zookeeper, Scala, Kafka, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8d51d47e65997196</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Data Engineer III</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=33b30501746ad4bf</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Data Engineer - Oklahoma City, OK</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>CFS Brands, LLC</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Oklahoma City, OK, US USA</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>IAM, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=113fe7e3580ec298</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Apache Spark Core Java</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>2026-08-22</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=16d16eda2d514586</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>Senior Analytics Engineer, Marketing Sciences</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>SimplePractice</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, RDS, Scala, Kafka, Snowflake, ETL, dbt, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=4a341479dc01b56f</t>
         </is>

--- a/results/job_matches_2026-08-22.xlsx
+++ b/results/job_matches_2026-08-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G118"/>
+  <dimension ref="A1:G111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,25 +713,25 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI Platform System Administrator III</t>
+          <t>Senior Engineer, Enterprise Database</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Boston Scientific</t>
+          <t>Applied Medical</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Arden Hills, MN, US USA</t>
+          <t>Rancho Santa Margarita, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62388f603bbe60a4</t>
+          <t>https://www.indeed.com/viewjob?jk=51a5d6b8454480a2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Engineer, Enterprise Database</t>
+          <t>Software Engineer, Full Stack - AI (New York)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Applied Medical</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Rancho Santa Margarita, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51a5d6b8454480a2</t>
+          <t>https://www.indeed.com/viewjob?jk=362603547d1c2a0d</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer, Full Stack - AI (New York)</t>
+          <t>Senior Data Science Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Fitch Group</t>
+          <t>LegitScript</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
+          <t>Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, MLOps</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=362603547d1c2a0d</t>
+          <t>https://www.indeed.com/viewjob?jk=0ac58242095324ac</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Science Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>LegitScript</t>
+          <t>Powerplan</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, MLOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ac58242095324ac</t>
+          <t>https://www.indeed.com/viewjob?jk=9effd2546d52cd38</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Software Engineer II, Data</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Powerplan</t>
+          <t>Credit Acceptance</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9effd2546d52cd38</t>
+          <t>https://www.indeed.com/viewjob?jk=39dcfd9f2966d672</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data</t>
+          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Platform (AWS)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Credit Acceptance</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, NoSQL</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39dcfd9f2966d672</t>
+          <t>https://www.indeed.com/viewjob?jk=7064a0875d5078f8</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Platform (AWS)</t>
+          <t>Solutions Delivery Engineer (Remote)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>RealPage Inc</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform</t>
+          <t>AWS, Redshift, RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7064a0875d5078f8</t>
+          <t>https://www.indeed.com/viewjob?jk=ec761fb42adb289d</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Senior Software Development Engineer - LLMs, GenAI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, S3, RDS, Spark, Scala, PostgreSQL, NoSQL, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Power BI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d1eabd20620b211</t>
+          <t>https://www.indeed.com/viewjob?jk=7ef55c2266d41678</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Solutions Delivery Engineer (Remote)</t>
+          <t>Senior Professional Services Consultant</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>RealPage Inc</t>
+          <t>Ataccama</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec761fb42adb289d</t>
+          <t>https://www.indeed.com/viewjob?jk=0f49a3f3dbcbca27</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer - LLMs, GenAI</t>
+          <t>CDP Architect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Bounteous</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Power BI, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ef55c2266d41678</t>
+          <t>https://www.indeed.com/viewjob?jk=f5b99e7a77983415</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Professional Services Consultant</t>
+          <t>Senior Devops Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ataccama</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,42 +1081,42 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f49a3f3dbcbca27</t>
+          <t>https://www.indeed.com/viewjob?jk=143f81631e970888</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CDP Architect</t>
+          <t>Azure IoT Solutions Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Bounteous</t>
+          <t>Ascend Technologies</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake, ETL</t>
+          <t>RDS, Azure, Event Hubs, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5b99e7a77983415</t>
+          <t>https://www.indeed.com/viewjob?jk=48463a0b2c1a516b</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Devops Engineer</t>
+          <t>GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation</t>
+          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=143f81631e970888</t>
+          <t>https://www.indeed.com/viewjob?jk=6b7cc426dbd03f0e</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Full stack Java / AWS</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL, DynamoDB, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Kafka, CI/CD, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=648c04000182f970</t>
+          <t>https://www.indeed.com/viewjob?jk=9a5cbb62cc968f68</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Azure IoT Solutions Engineer</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ascend Technologies</t>
+          <t>Marathon Petroleum</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AKS, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48463a0b2c1a516b</t>
+          <t>https://www.indeed.com/viewjob?jk=28293fa77ffc32bb</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>GCP Cloud Engineer</t>
+          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Platform (Azure)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform, Azure Monitor</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b7cc426dbd03f0e</t>
+          <t>https://www.indeed.com/viewjob?jk=defb19c3b807f7fd</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Mercari</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=179685542a7cf944</t>
+          <t>https://www.indeed.com/viewjob?jk=f4ab3e3c7077492c</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Inglewood, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Kafka, CI/CD, Terraform, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a5cbb62cc968f68</t>
+          <t>https://www.indeed.com/viewjob?jk=b0870a8c631ca3e7</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Marathon Petroleum</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, CI/CD, Git, Python, SQL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28293fa77ffc32bb</t>
+          <t>https://www.indeed.com/viewjob?jk=3a8177305c7e2b4e</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Golden State</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d156f80ddb5ea3e</t>
+          <t>https://www.indeed.com/viewjob?jk=2b216035065cdcce</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4ab3e3c7077492c</t>
+          <t>https://www.indeed.com/viewjob?jk=b0d6bbe5db7dc4e3</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Inglewood, CA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0870a8c631ca3e7</t>
+          <t>https://www.indeed.com/viewjob?jk=99cd5dc3d4c47201</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a8177305c7e2b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=1535cff1bb626738</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Williamsville, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b216035065cdcce</t>
+          <t>https://www.indeed.com/viewjob?jk=37a520fdd5e099b9</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0d6bbe5db7dc4e3</t>
+          <t>https://www.indeed.com/viewjob?jk=366fcdfb585bd3be</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99cd5dc3d4c47201</t>
+          <t>https://www.indeed.com/viewjob?jk=a94f1ea7f43f3649</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1535cff1bb626738</t>
+          <t>https://www.indeed.com/viewjob?jk=497b07468d401d8a</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Williamsville, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37a520fdd5e099b9</t>
+          <t>https://www.indeed.com/viewjob?jk=8d2e49c364fa4321</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=366fcdfb585bd3be</t>
+          <t>https://www.indeed.com/viewjob?jk=14d6f7b29ae9eb47</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a94f1ea7f43f3649</t>
+          <t>https://www.indeed.com/viewjob?jk=e69bf4d69267775a</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=497b07468d401d8a</t>
+          <t>https://www.indeed.com/viewjob?jk=22a4f690926575b6</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d2e49c364fa4321</t>
+          <t>https://www.indeed.com/viewjob?jk=7fc8f10cc4340e38</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14d6f7b29ae9eb47</t>
+          <t>https://www.indeed.com/viewjob?jk=4ed7e30adf2adc59</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e69bf4d69267775a</t>
+          <t>https://www.indeed.com/viewjob?jk=22efcdd2b4a3dd7f</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22a4f690926575b6</t>
+          <t>https://www.indeed.com/viewjob?jk=4d610152102215d5</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fc8f10cc4340e38</t>
+          <t>https://www.indeed.com/viewjob?jk=0f093d62f255edad</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ed7e30adf2adc59</t>
+          <t>https://www.indeed.com/viewjob?jk=61c760c7b06ee2ec</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22efcdd2b4a3dd7f</t>
+          <t>https://www.indeed.com/viewjob?jk=7e753698d58ce405</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d610152102215d5</t>
+          <t>https://www.indeed.com/viewjob?jk=613c98d34d3a6aff</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f093d62f255edad</t>
+          <t>https://www.indeed.com/viewjob?jk=81eb38d16909745a</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61c760c7b06ee2ec</t>
+          <t>https://www.indeed.com/viewjob?jk=26aa4bbb65d7bc04</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e753698d58ce405</t>
+          <t>https://www.indeed.com/viewjob?jk=51eaf011bd4b3db9</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=613c98d34d3a6aff</t>
+          <t>https://www.indeed.com/viewjob?jk=875b54845cacd6b4</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81eb38d16909745a</t>
+          <t>https://www.indeed.com/viewjob?jk=b044118f339aeefe</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26aa4bbb65d7bc04</t>
+          <t>https://www.indeed.com/viewjob?jk=79172907c08cbd27</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51eaf011bd4b3db9</t>
+          <t>https://www.indeed.com/viewjob?jk=4072dd1e7bd9b46a</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=875b54845cacd6b4</t>
+          <t>https://www.indeed.com/viewjob?jk=60e28bece0970c90</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b044118f339aeefe</t>
+          <t>https://www.indeed.com/viewjob?jk=337e00bdabbbf617</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79172907c08cbd27</t>
+          <t>https://www.indeed.com/viewjob?jk=7008c23fbe380180</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4072dd1e7bd9b46a</t>
+          <t>https://www.indeed.com/viewjob?jk=ef94cdec933bb8d2</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60e28bece0970c90</t>
+          <t>https://www.indeed.com/viewjob?jk=a9b3dd72c73a5c59</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>San Juan, PR, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=337e00bdabbbf617</t>
+          <t>https://www.indeed.com/viewjob?jk=3f362104fdb5fce0</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7008c23fbe380180</t>
+          <t>https://www.indeed.com/viewjob?jk=bb3766965503e1b0</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef94cdec933bb8d2</t>
+          <t>https://www.indeed.com/viewjob?jk=01b7efd6177971eb</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9b3dd72c73a5c59</t>
+          <t>https://www.indeed.com/viewjob?jk=564843cdd5d6c05d</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>San Juan, PR, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f362104fdb5fce0</t>
+          <t>https://www.indeed.com/viewjob?jk=38dc1e892863874b</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb3766965503e1b0</t>
+          <t>https://www.indeed.com/viewjob?jk=36375563a2ad1043</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Honolulu, HI, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01b7efd6177971eb</t>
+          <t>https://www.indeed.com/viewjob?jk=cf1ab598617115f3</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=564843cdd5d6c05d</t>
+          <t>https://www.indeed.com/viewjob?jk=bdb4d76e4c3be44c</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38dc1e892863874b</t>
+          <t>https://www.indeed.com/viewjob?jk=bd706eccacda1e1c</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36375563a2ad1043</t>
+          <t>https://www.indeed.com/viewjob?jk=606f854062c681fa</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Honolulu, HI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf1ab598617115f3</t>
+          <t>https://www.indeed.com/viewjob?jk=15ee32196b2a250e</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdb4d76e4c3be44c</t>
+          <t>https://www.indeed.com/viewjob?jk=c7a2ced0233034b8</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd706eccacda1e1c</t>
+          <t>https://www.indeed.com/viewjob?jk=b267004acbc01cc5</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606f854062c681fa</t>
+          <t>https://www.indeed.com/viewjob?jk=9be2810504f2ae29</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15ee32196b2a250e</t>
+          <t>https://www.indeed.com/viewjob?jk=6f0ec602c9b09a8e</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7a2ced0233034b8</t>
+          <t>https://www.indeed.com/viewjob?jk=bd0e7d3dab7e604a</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b267004acbc01cc5</t>
+          <t>https://www.indeed.com/viewjob?jk=905c5a2344562ab8</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9be2810504f2ae29</t>
+          <t>https://www.indeed.com/viewjob?jk=21b0eb74cf57c4a8</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Monterey, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f0ec602c9b09a8e</t>
+          <t>https://www.indeed.com/viewjob?jk=127db1667ff89227</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd0e7d3dab7e604a</t>
+          <t>https://www.indeed.com/viewjob?jk=2a42559421200137</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=905c5a2344562ab8</t>
+          <t>https://www.indeed.com/viewjob?jk=d6e7dd724c924aca</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21b0eb74cf57c4a8</t>
+          <t>https://www.indeed.com/viewjob?jk=8483d29d2dbde05b</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Monterey, CA, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127db1667ff89227</t>
+          <t>https://www.indeed.com/viewjob?jk=824e663391dfa6bf</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a42559421200137</t>
+          <t>https://www.indeed.com/viewjob?jk=3e8686e8d16dc84d</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6e7dd724c924aca</t>
+          <t>https://www.indeed.com/viewjob?jk=496d9926f80e93e9</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8483d29d2dbde05b</t>
+          <t>https://www.indeed.com/viewjob?jk=57716cf6ab6ed7a5</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=824e663391dfa6bf</t>
+          <t>https://www.indeed.com/viewjob?jk=c418229c0f650f96</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e8686e8d16dc84d</t>
+          <t>https://www.indeed.com/viewjob?jk=95121729962d91d2</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=496d9926f80e93e9</t>
+          <t>https://www.indeed.com/viewjob?jk=dfec58f9b4c8760a</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57716cf6ab6ed7a5</t>
+          <t>https://www.indeed.com/viewjob?jk=5153281c36740802</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c418229c0f650f96</t>
+          <t>https://www.indeed.com/viewjob?jk=310acaaa4f9f42e3</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95121729962d91d2</t>
+          <t>https://www.indeed.com/viewjob?jk=6efe7ed3911371c4</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfec58f9b4c8760a</t>
+          <t>https://www.indeed.com/viewjob?jk=1a68cf132dbdec60</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5153281c36740802</t>
+          <t>https://www.indeed.com/viewjob?jk=8d891e75a79397a9</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=310acaaa4f9f42e3</t>
+          <t>https://www.indeed.com/viewjob?jk=117634e8f8dfb2d6</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6efe7ed3911371c4</t>
+          <t>https://www.indeed.com/viewjob?jk=b83a26f124ccdb89</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a68cf132dbdec60</t>
+          <t>https://www.indeed.com/viewjob?jk=ad88505e172120de</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d891e75a79397a9</t>
+          <t>https://www.indeed.com/viewjob?jk=c21ad262bec7ef80</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=117634e8f8dfb2d6</t>
+          <t>https://www.indeed.com/viewjob?jk=ca6810d972b1a5f1</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b83a26f124ccdb89</t>
+          <t>https://www.indeed.com/viewjob?jk=27043ef345d0b8a7</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad88505e172120de</t>
+          <t>https://www.indeed.com/viewjob?jk=be347b278f12cb33</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c21ad262bec7ef80</t>
+          <t>https://www.indeed.com/viewjob?jk=fed8b15c04492576</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca6810d972b1a5f1</t>
+          <t>https://www.indeed.com/viewjob?jk=5b12133504b24bae</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27043ef345d0b8a7</t>
+          <t>https://www.indeed.com/viewjob?jk=9f864d9aca9b7b27</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be347b278f12cb33</t>
+          <t>https://www.indeed.com/viewjob?jk=76d2eb1be4c1b252</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fed8b15c04492576</t>
+          <t>https://www.indeed.com/viewjob?jk=9baba2b401f1c56c</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+          <t>Databricks Developer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b12133504b24bae</t>
+          <t>https://www.indeed.com/viewjob?jk=ab1192abfbd7f24e</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+          <t>Databricks Developer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,32 +4171,32 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f864d9aca9b7b27</t>
+          <t>https://www.indeed.com/viewjob?jk=320dcd4f927cb250</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+          <t>Site Reliability Engineering (SRE) - Maryland, US</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+          <t>Azure, GCP, BigQuery, Zookeeper, Scala, Kafka, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,32 +4206,32 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76d2eb1be4c1b252</t>
+          <t>https://www.indeed.com/viewjob?jk=8d51d47e65997196</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,32 +4241,32 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9baba2b401f1c56c</t>
+          <t>https://www.indeed.com/viewjob?jk=33b30501746ad4bf</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Platform (Azure)</t>
+          <t>Data Engineer - Oklahoma City, OK</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>CFS Brands, LLC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform, Azure Monitor</t>
+          <t>IAM, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,19 +4276,19 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=defb19c3b807f7fd</t>
+          <t>https://www.indeed.com/viewjob?jk=113fe7e3580ec298</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Databricks Developer</t>
+          <t>Apache Spark Core Java</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4297,266 +4297,21 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab1192abfbd7f24e</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Databricks Developer</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=320dcd4f927cb250</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Associate, Data Engineer</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>BlackRock</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, DynamoDB, Azure Cosmos DB, NoSQL</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=06fd6810514e5491</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Site Reliability Engineering (SRE) - Maryland, US</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Baltimore, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>Azure, GCP, BigQuery, Zookeeper, Scala, Kafka, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8d51d47e65997196</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Data Engineer III</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=33b30501746ad4bf</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Data Engineer - Oklahoma City, OK</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>CFS Brands, LLC</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Oklahoma City, OK, US USA</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>IAM, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=113fe7e3580ec298</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Apache Spark Core Java</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2026-08-22</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=16d16eda2d514586</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Senior Analytics Engineer, Marketing Sciences</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>SimplePractice</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, RDS, Scala, Kafka, Snowflake, ETL, dbt, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4a341479dc01b56f</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-22.xlsx
+++ b/results/job_matches_2026-08-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G111"/>
+  <dimension ref="A1:G108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,25 +608,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer Microsoft Fabric</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bilzin Sumberg Baena Price &amp; Axelrod LLP</t>
+          <t>Entarian</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Snowflake, SQL Server</t>
+          <t>AWS, Kinesis, Scala, Kafka, Polars, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,14 +636,14 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=371409082795e582</t>
+          <t>https://www.indeed.com/viewjob?jk=97cacdd77a88ee4d</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97cacdd77a88ee4d</t>
+          <t>https://www.indeed.com/viewjob?jk=8d62e6c9bd298592</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Engineer, Enterprise Database</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Entarian</t>
+          <t>Applied Medical</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Rancho Santa Margarita, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Scala, Kafka, Polars, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d62e6c9bd298592</t>
+          <t>https://www.indeed.com/viewjob?jk=51a5d6b8454480a2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Engineer, Enterprise Database</t>
+          <t>Software Engineer, Full Stack - AI (New York)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Applied Medical</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Rancho Santa Margarita, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51a5d6b8454480a2</t>
+          <t>https://www.indeed.com/viewjob?jk=362603547d1c2a0d</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer, Full Stack - AI (New York)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Fitch Group</t>
+          <t>Powerplan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=362603547d1c2a0d</t>
+          <t>https://www.indeed.com/viewjob?jk=9effd2546d52cd38</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Science Engineer</t>
+          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Platform (AWS)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LegitScript</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, MLOps</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ac58242095324ac</t>
+          <t>https://www.indeed.com/viewjob?jk=7064a0875d5078f8</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Solutions Delivery Engineer (Remote)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Powerplan</t>
+          <t>RealPage Inc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, Redshift, RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,54 +846,54 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9effd2546d52cd38</t>
+          <t>https://www.indeed.com/viewjob?jk=ec761fb42adb289d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data</t>
+          <t>Senior Software Development Engineer - LLMs, GenAI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Credit Acceptance</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, NoSQL</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Power BI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39dcfd9f2966d672</t>
+          <t>https://www.indeed.com/viewjob?jk=7ef55c2266d41678</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Platform (AWS)</t>
+          <t>Senior Professional Services Consultant</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Ataccama</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -902,38 +902,38 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform</t>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7064a0875d5078f8</t>
+          <t>https://www.indeed.com/viewjob?jk=0f49a3f3dbcbca27</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Solutions Delivery Engineer (Remote)</t>
+          <t>CDP Architect</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>RealPage Inc</t>
+          <t>Bounteous</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec761fb42adb289d</t>
+          <t>https://www.indeed.com/viewjob?jk=f5b99e7a77983415</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer - LLMs, GenAI</t>
+          <t>Senior Devops Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,77 +976,77 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Power BI, Docker, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ef55c2266d41678</t>
+          <t>https://www.indeed.com/viewjob?jk=143f81631e970888</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Professional Services Consultant</t>
+          <t>Azure IoT Solutions Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ataccama</t>
+          <t>Ascend Technologies</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
+          <t>RDS, Azure, Event Hubs, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f49a3f3dbcbca27</t>
+          <t>https://www.indeed.com/viewjob?jk=48463a0b2c1a516b</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CDP Architect</t>
+          <t>GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Bounteous</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake, ETL</t>
+          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5b99e7a77983415</t>
+          <t>https://www.indeed.com/viewjob?jk=6b7cc426dbd03f0e</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Devops Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Kafka, CI/CD, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=143f81631e970888</t>
+          <t>https://www.indeed.com/viewjob?jk=9a5cbb62cc968f68</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Azure IoT Solutions Engineer</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ascend Technologies</t>
+          <t>Marathon Petroleum</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AKS, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48463a0b2c1a516b</t>
+          <t>https://www.indeed.com/viewjob?jk=28293fa77ffc32bb</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>GCP Cloud Engineer</t>
+          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Platform (Azure)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform, Azure Monitor</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b7cc426dbd03f0e</t>
+          <t>https://www.indeed.com/viewjob?jk=defb19c3b807f7fd</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Kafka, CI/CD, Terraform, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a5cbb62cc968f68</t>
+          <t>https://www.indeed.com/viewjob?jk=f4ab3e3c7077492c</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Marathon Petroleum</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Inglewood, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, CI/CD, Git, Python, SQL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28293fa77ffc32bb</t>
+          <t>https://www.indeed.com/viewjob?jk=b0870a8c631ca3e7</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Platform (Azure)</t>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform, Azure Monitor</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=defb19c3b807f7fd</t>
+          <t>https://www.indeed.com/viewjob?jk=3a8177305c7e2b4e</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4ab3e3c7077492c</t>
+          <t>https://www.indeed.com/viewjob?jk=2b216035065cdcce</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Inglewood, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0870a8c631ca3e7</t>
+          <t>https://www.indeed.com/viewjob?jk=b0d6bbe5db7dc4e3</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a8177305c7e2b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=99cd5dc3d4c47201</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b216035065cdcce</t>
+          <t>https://www.indeed.com/viewjob?jk=1535cff1bb626738</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Williamsville, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0d6bbe5db7dc4e3</t>
+          <t>https://www.indeed.com/viewjob?jk=37a520fdd5e099b9</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99cd5dc3d4c47201</t>
+          <t>https://www.indeed.com/viewjob?jk=366fcdfb585bd3be</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1535cff1bb626738</t>
+          <t>https://www.indeed.com/viewjob?jk=a94f1ea7f43f3649</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Williamsville, NY, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37a520fdd5e099b9</t>
+          <t>https://www.indeed.com/viewjob?jk=497b07468d401d8a</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=366fcdfb585bd3be</t>
+          <t>https://www.indeed.com/viewjob?jk=8d2e49c364fa4321</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a94f1ea7f43f3649</t>
+          <t>https://www.indeed.com/viewjob?jk=14d6f7b29ae9eb47</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=497b07468d401d8a</t>
+          <t>https://www.indeed.com/viewjob?jk=e69bf4d69267775a</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d2e49c364fa4321</t>
+          <t>https://www.indeed.com/viewjob?jk=22a4f690926575b6</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14d6f7b29ae9eb47</t>
+          <t>https://www.indeed.com/viewjob?jk=7fc8f10cc4340e38</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e69bf4d69267775a</t>
+          <t>https://www.indeed.com/viewjob?jk=4ed7e30adf2adc59</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22a4f690926575b6</t>
+          <t>https://www.indeed.com/viewjob?jk=22efcdd2b4a3dd7f</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fc8f10cc4340e38</t>
+          <t>https://www.indeed.com/viewjob?jk=4d610152102215d5</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ed7e30adf2adc59</t>
+          <t>https://www.indeed.com/viewjob?jk=0f093d62f255edad</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22efcdd2b4a3dd7f</t>
+          <t>https://www.indeed.com/viewjob?jk=61c760c7b06ee2ec</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d610152102215d5</t>
+          <t>https://www.indeed.com/viewjob?jk=7e753698d58ce405</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f093d62f255edad</t>
+          <t>https://www.indeed.com/viewjob?jk=613c98d34d3a6aff</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61c760c7b06ee2ec</t>
+          <t>https://www.indeed.com/viewjob?jk=81eb38d16909745a</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e753698d58ce405</t>
+          <t>https://www.indeed.com/viewjob?jk=26aa4bbb65d7bc04</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=613c98d34d3a6aff</t>
+          <t>https://www.indeed.com/viewjob?jk=51eaf011bd4b3db9</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81eb38d16909745a</t>
+          <t>https://www.indeed.com/viewjob?jk=875b54845cacd6b4</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26aa4bbb65d7bc04</t>
+          <t>https://www.indeed.com/viewjob?jk=b044118f339aeefe</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51eaf011bd4b3db9</t>
+          <t>https://www.indeed.com/viewjob?jk=79172907c08cbd27</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=875b54845cacd6b4</t>
+          <t>https://www.indeed.com/viewjob?jk=4072dd1e7bd9b46a</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b044118f339aeefe</t>
+          <t>https://www.indeed.com/viewjob?jk=60e28bece0970c90</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79172907c08cbd27</t>
+          <t>https://www.indeed.com/viewjob?jk=337e00bdabbbf617</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4072dd1e7bd9b46a</t>
+          <t>https://www.indeed.com/viewjob?jk=7008c23fbe380180</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60e28bece0970c90</t>
+          <t>https://www.indeed.com/viewjob?jk=ef94cdec933bb8d2</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=337e00bdabbbf617</t>
+          <t>https://www.indeed.com/viewjob?jk=a9b3dd72c73a5c59</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>San Juan, PR, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7008c23fbe380180</t>
+          <t>https://www.indeed.com/viewjob?jk=3f362104fdb5fce0</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef94cdec933bb8d2</t>
+          <t>https://www.indeed.com/viewjob?jk=bb3766965503e1b0</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9b3dd72c73a5c59</t>
+          <t>https://www.indeed.com/viewjob?jk=01b7efd6177971eb</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>San Juan, PR, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f362104fdb5fce0</t>
+          <t>https://www.indeed.com/viewjob?jk=564843cdd5d6c05d</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb3766965503e1b0</t>
+          <t>https://www.indeed.com/viewjob?jk=38dc1e892863874b</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01b7efd6177971eb</t>
+          <t>https://www.indeed.com/viewjob?jk=36375563a2ad1043</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Honolulu, HI, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=564843cdd5d6c05d</t>
+          <t>https://www.indeed.com/viewjob?jk=cf1ab598617115f3</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38dc1e892863874b</t>
+          <t>https://www.indeed.com/viewjob?jk=bdb4d76e4c3be44c</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36375563a2ad1043</t>
+          <t>https://www.indeed.com/viewjob?jk=bd706eccacda1e1c</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Honolulu, HI, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf1ab598617115f3</t>
+          <t>https://www.indeed.com/viewjob?jk=606f854062c681fa</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdb4d76e4c3be44c</t>
+          <t>https://www.indeed.com/viewjob?jk=15ee32196b2a250e</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd706eccacda1e1c</t>
+          <t>https://www.indeed.com/viewjob?jk=c7a2ced0233034b8</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606f854062c681fa</t>
+          <t>https://www.indeed.com/viewjob?jk=b267004acbc01cc5</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15ee32196b2a250e</t>
+          <t>https://www.indeed.com/viewjob?jk=9be2810504f2ae29</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7a2ced0233034b8</t>
+          <t>https://www.indeed.com/viewjob?jk=6f0ec602c9b09a8e</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b267004acbc01cc5</t>
+          <t>https://www.indeed.com/viewjob?jk=bd0e7d3dab7e604a</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9be2810504f2ae29</t>
+          <t>https://www.indeed.com/viewjob?jk=905c5a2344562ab8</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f0ec602c9b09a8e</t>
+          <t>https://www.indeed.com/viewjob?jk=21b0eb74cf57c4a8</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Monterey, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd0e7d3dab7e604a</t>
+          <t>https://www.indeed.com/viewjob?jk=127db1667ff89227</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=905c5a2344562ab8</t>
+          <t>https://www.indeed.com/viewjob?jk=2a42559421200137</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21b0eb74cf57c4a8</t>
+          <t>https://www.indeed.com/viewjob?jk=d6e7dd724c924aca</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Monterey, CA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127db1667ff89227</t>
+          <t>https://www.indeed.com/viewjob?jk=8483d29d2dbde05b</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a42559421200137</t>
+          <t>https://www.indeed.com/viewjob?jk=824e663391dfa6bf</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6e7dd724c924aca</t>
+          <t>https://www.indeed.com/viewjob?jk=3e8686e8d16dc84d</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8483d29d2dbde05b</t>
+          <t>https://www.indeed.com/viewjob?jk=496d9926f80e93e9</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=824e663391dfa6bf</t>
+          <t>https://www.indeed.com/viewjob?jk=57716cf6ab6ed7a5</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e8686e8d16dc84d</t>
+          <t>https://www.indeed.com/viewjob?jk=c418229c0f650f96</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=496d9926f80e93e9</t>
+          <t>https://www.indeed.com/viewjob?jk=95121729962d91d2</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57716cf6ab6ed7a5</t>
+          <t>https://www.indeed.com/viewjob?jk=dfec58f9b4c8760a</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c418229c0f650f96</t>
+          <t>https://www.indeed.com/viewjob?jk=5153281c36740802</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95121729962d91d2</t>
+          <t>https://www.indeed.com/viewjob?jk=310acaaa4f9f42e3</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfec58f9b4c8760a</t>
+          <t>https://www.indeed.com/viewjob?jk=6efe7ed3911371c4</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5153281c36740802</t>
+          <t>https://www.indeed.com/viewjob?jk=1a68cf132dbdec60</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=310acaaa4f9f42e3</t>
+          <t>https://www.indeed.com/viewjob?jk=8d891e75a79397a9</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6efe7ed3911371c4</t>
+          <t>https://www.indeed.com/viewjob?jk=117634e8f8dfb2d6</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a68cf132dbdec60</t>
+          <t>https://www.indeed.com/viewjob?jk=b83a26f124ccdb89</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d891e75a79397a9</t>
+          <t>https://www.indeed.com/viewjob?jk=ad88505e172120de</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=117634e8f8dfb2d6</t>
+          <t>https://www.indeed.com/viewjob?jk=c21ad262bec7ef80</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b83a26f124ccdb89</t>
+          <t>https://www.indeed.com/viewjob?jk=ca6810d972b1a5f1</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad88505e172120de</t>
+          <t>https://www.indeed.com/viewjob?jk=27043ef345d0b8a7</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c21ad262bec7ef80</t>
+          <t>https://www.indeed.com/viewjob?jk=be347b278f12cb33</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca6810d972b1a5f1</t>
+          <t>https://www.indeed.com/viewjob?jk=fed8b15c04492576</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27043ef345d0b8a7</t>
+          <t>https://www.indeed.com/viewjob?jk=5b12133504b24bae</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be347b278f12cb33</t>
+          <t>https://www.indeed.com/viewjob?jk=9f864d9aca9b7b27</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fed8b15c04492576</t>
+          <t>https://www.indeed.com/viewjob?jk=76d2eb1be4c1b252</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b12133504b24bae</t>
+          <t>https://www.indeed.com/viewjob?jk=9baba2b401f1c56c</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+          <t>Databricks Developer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f864d9aca9b7b27</t>
+          <t>https://www.indeed.com/viewjob?jk=ab1192abfbd7f24e</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+          <t>Databricks Developer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,32 +4066,32 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76d2eb1be4c1b252</t>
+          <t>https://www.indeed.com/viewjob?jk=320dcd4f927cb250</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+          <t>Site Reliability Engineering (SRE) - Maryland, US</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+          <t>Azure, GCP, BigQuery, Zookeeper, Scala, Kafka, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,32 +4101,32 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9baba2b401f1c56c</t>
+          <t>https://www.indeed.com/viewjob?jk=8d51d47e65997196</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Databricks Developer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,32 +4136,32 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab1192abfbd7f24e</t>
+          <t>https://www.indeed.com/viewjob?jk=33b30501746ad4bf</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Databricks Developer</t>
+          <t>Data Engineer - Oklahoma City, OK</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CFS Brands, LLC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>IAM, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=320dcd4f927cb250</t>
+          <t>https://www.indeed.com/viewjob?jk=113fe7e3580ec298</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Site Reliability Engineering (SRE) - Maryland, US</t>
+          <t>Apache Spark Core Java</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,120 +4196,15 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Azure, GCP, BigQuery, Zookeeper, Scala, Kafka, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8d51d47e65997196</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Data Engineer III</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=33b30501746ad4bf</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Data Engineer - Oklahoma City, OK</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>CFS Brands, LLC</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Oklahoma City, OK, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>IAM, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=113fe7e3580ec298</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Apache Spark Core Java</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-08-22</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=16d16eda2d514586</t>
         </is>

--- a/results/job_matches_2026-08-22.xlsx
+++ b/results/job_matches_2026-08-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G108"/>
+  <dimension ref="A1:G105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1028,25 +1028,25 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GCP Cloud Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Kafka, CI/CD, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b7cc426dbd03f0e</t>
+          <t>https://www.indeed.com/viewjob?jk=9a5cbb62cc968f68</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Marathon Petroleum</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Kafka, CI/CD, Terraform, Kubernetes, AKS</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a5cbb62cc968f68</t>
+          <t>https://www.indeed.com/viewjob?jk=28293fa77ffc32bb</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Platform (Azure)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Marathon Petroleum</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, CI/CD, Git, Python, SQL</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform, Azure Monitor</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28293fa77ffc32bb</t>
+          <t>https://www.indeed.com/viewjob?jk=defb19c3b807f7fd</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Cloud Infrastructure &amp; Platform (Azure)</t>
+          <t>Senior Data Product Analyst - Data Management Engineer III</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform, Azure Monitor</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=defb19c3b807f7fd</t>
+          <t>https://www.indeed.com/viewjob?jk=f4ab3e3c7077492c</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Inglewood, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4ab3e3c7077492c</t>
+          <t>https://www.indeed.com/viewjob?jk=b0870a8c631ca3e7</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Inglewood, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0870a8c631ca3e7</t>
+          <t>https://www.indeed.com/viewjob?jk=3a8177305c7e2b4e</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a8177305c7e2b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=2b216035065cdcce</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b216035065cdcce</t>
+          <t>https://www.indeed.com/viewjob?jk=b0d6bbe5db7dc4e3</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0d6bbe5db7dc4e3</t>
+          <t>https://www.indeed.com/viewjob?jk=99cd5dc3d4c47201</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99cd5dc3d4c47201</t>
+          <t>https://www.indeed.com/viewjob?jk=1535cff1bb626738</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Williamsville, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1535cff1bb626738</t>
+          <t>https://www.indeed.com/viewjob?jk=37a520fdd5e099b9</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Williamsville, NY, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37a520fdd5e099b9</t>
+          <t>https://www.indeed.com/viewjob?jk=366fcdfb585bd3be</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=366fcdfb585bd3be</t>
+          <t>https://www.indeed.com/viewjob?jk=a94f1ea7f43f3649</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a94f1ea7f43f3649</t>
+          <t>https://www.indeed.com/viewjob?jk=497b07468d401d8a</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=497b07468d401d8a</t>
+          <t>https://www.indeed.com/viewjob?jk=8d2e49c364fa4321</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d2e49c364fa4321</t>
+          <t>https://www.indeed.com/viewjob?jk=14d6f7b29ae9eb47</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14d6f7b29ae9eb47</t>
+          <t>https://www.indeed.com/viewjob?jk=e69bf4d69267775a</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e69bf4d69267775a</t>
+          <t>https://www.indeed.com/viewjob?jk=22a4f690926575b6</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22a4f690926575b6</t>
+          <t>https://www.indeed.com/viewjob?jk=7fc8f10cc4340e38</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fc8f10cc4340e38</t>
+          <t>https://www.indeed.com/viewjob?jk=4ed7e30adf2adc59</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ed7e30adf2adc59</t>
+          <t>https://www.indeed.com/viewjob?jk=22efcdd2b4a3dd7f</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22efcdd2b4a3dd7f</t>
+          <t>https://www.indeed.com/viewjob?jk=4d610152102215d5</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d610152102215d5</t>
+          <t>https://www.indeed.com/viewjob?jk=0f093d62f255edad</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f093d62f255edad</t>
+          <t>https://www.indeed.com/viewjob?jk=61c760c7b06ee2ec</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61c760c7b06ee2ec</t>
+          <t>https://www.indeed.com/viewjob?jk=7e753698d58ce405</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e753698d58ce405</t>
+          <t>https://www.indeed.com/viewjob?jk=613c98d34d3a6aff</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=613c98d34d3a6aff</t>
+          <t>https://www.indeed.com/viewjob?jk=81eb38d16909745a</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81eb38d16909745a</t>
+          <t>https://www.indeed.com/viewjob?jk=26aa4bbb65d7bc04</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26aa4bbb65d7bc04</t>
+          <t>https://www.indeed.com/viewjob?jk=51eaf011bd4b3db9</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51eaf011bd4b3db9</t>
+          <t>https://www.indeed.com/viewjob?jk=875b54845cacd6b4</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=875b54845cacd6b4</t>
+          <t>https://www.indeed.com/viewjob?jk=b044118f339aeefe</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b044118f339aeefe</t>
+          <t>https://www.indeed.com/viewjob?jk=79172907c08cbd27</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79172907c08cbd27</t>
+          <t>https://www.indeed.com/viewjob?jk=4072dd1e7bd9b46a</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4072dd1e7bd9b46a</t>
+          <t>https://www.indeed.com/viewjob?jk=60e28bece0970c90</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60e28bece0970c90</t>
+          <t>https://www.indeed.com/viewjob?jk=337e00bdabbbf617</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=337e00bdabbbf617</t>
+          <t>https://www.indeed.com/viewjob?jk=7008c23fbe380180</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7008c23fbe380180</t>
+          <t>https://www.indeed.com/viewjob?jk=ef94cdec933bb8d2</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef94cdec933bb8d2</t>
+          <t>https://www.indeed.com/viewjob?jk=a9b3dd72c73a5c59</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>San Juan, PR, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9b3dd72c73a5c59</t>
+          <t>https://www.indeed.com/viewjob?jk=3f362104fdb5fce0</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>San Juan, PR, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f362104fdb5fce0</t>
+          <t>https://www.indeed.com/viewjob?jk=bb3766965503e1b0</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb3766965503e1b0</t>
+          <t>https://www.indeed.com/viewjob?jk=01b7efd6177971eb</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01b7efd6177971eb</t>
+          <t>https://www.indeed.com/viewjob?jk=564843cdd5d6c05d</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=564843cdd5d6c05d</t>
+          <t>https://www.indeed.com/viewjob?jk=38dc1e892863874b</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38dc1e892863874b</t>
+          <t>https://www.indeed.com/viewjob?jk=36375563a2ad1043</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Honolulu, HI, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36375563a2ad1043</t>
+          <t>https://www.indeed.com/viewjob?jk=cf1ab598617115f3</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Honolulu, HI, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf1ab598617115f3</t>
+          <t>https://www.indeed.com/viewjob?jk=bdb4d76e4c3be44c</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdb4d76e4c3be44c</t>
+          <t>https://www.indeed.com/viewjob?jk=bd706eccacda1e1c</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd706eccacda1e1c</t>
+          <t>https://www.indeed.com/viewjob?jk=606f854062c681fa</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606f854062c681fa</t>
+          <t>https://www.indeed.com/viewjob?jk=15ee32196b2a250e</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15ee32196b2a250e</t>
+          <t>https://www.indeed.com/viewjob?jk=c7a2ced0233034b8</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7a2ced0233034b8</t>
+          <t>https://www.indeed.com/viewjob?jk=b267004acbc01cc5</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b267004acbc01cc5</t>
+          <t>https://www.indeed.com/viewjob?jk=9be2810504f2ae29</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9be2810504f2ae29</t>
+          <t>https://www.indeed.com/viewjob?jk=6f0ec602c9b09a8e</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f0ec602c9b09a8e</t>
+          <t>https://www.indeed.com/viewjob?jk=bd0e7d3dab7e604a</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd0e7d3dab7e604a</t>
+          <t>https://www.indeed.com/viewjob?jk=905c5a2344562ab8</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=905c5a2344562ab8</t>
+          <t>https://www.indeed.com/viewjob?jk=21b0eb74cf57c4a8</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Monterey, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21b0eb74cf57c4a8</t>
+          <t>https://www.indeed.com/viewjob?jk=127db1667ff89227</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Monterey, CA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127db1667ff89227</t>
+          <t>https://www.indeed.com/viewjob?jk=2a42559421200137</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a42559421200137</t>
+          <t>https://www.indeed.com/viewjob?jk=d6e7dd724c924aca</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6e7dd724c924aca</t>
+          <t>https://www.indeed.com/viewjob?jk=8483d29d2dbde05b</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8483d29d2dbde05b</t>
+          <t>https://www.indeed.com/viewjob?jk=824e663391dfa6bf</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=824e663391dfa6bf</t>
+          <t>https://www.indeed.com/viewjob?jk=3e8686e8d16dc84d</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e8686e8d16dc84d</t>
+          <t>https://www.indeed.com/viewjob?jk=496d9926f80e93e9</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=496d9926f80e93e9</t>
+          <t>https://www.indeed.com/viewjob?jk=57716cf6ab6ed7a5</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57716cf6ab6ed7a5</t>
+          <t>https://www.indeed.com/viewjob?jk=c418229c0f650f96</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c418229c0f650f96</t>
+          <t>https://www.indeed.com/viewjob?jk=95121729962d91d2</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95121729962d91d2</t>
+          <t>https://www.indeed.com/viewjob?jk=dfec58f9b4c8760a</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfec58f9b4c8760a</t>
+          <t>https://www.indeed.com/viewjob?jk=5153281c36740802</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5153281c36740802</t>
+          <t>https://www.indeed.com/viewjob?jk=310acaaa4f9f42e3</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=310acaaa4f9f42e3</t>
+          <t>https://www.indeed.com/viewjob?jk=6efe7ed3911371c4</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6efe7ed3911371c4</t>
+          <t>https://www.indeed.com/viewjob?jk=1a68cf132dbdec60</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a68cf132dbdec60</t>
+          <t>https://www.indeed.com/viewjob?jk=8d891e75a79397a9</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d891e75a79397a9</t>
+          <t>https://www.indeed.com/viewjob?jk=117634e8f8dfb2d6</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=117634e8f8dfb2d6</t>
+          <t>https://www.indeed.com/viewjob?jk=b83a26f124ccdb89</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b83a26f124ccdb89</t>
+          <t>https://www.indeed.com/viewjob?jk=ad88505e172120de</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad88505e172120de</t>
+          <t>https://www.indeed.com/viewjob?jk=c21ad262bec7ef80</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c21ad262bec7ef80</t>
+          <t>https://www.indeed.com/viewjob?jk=ca6810d972b1a5f1</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca6810d972b1a5f1</t>
+          <t>https://www.indeed.com/viewjob?jk=27043ef345d0b8a7</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27043ef345d0b8a7</t>
+          <t>https://www.indeed.com/viewjob?jk=be347b278f12cb33</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be347b278f12cb33</t>
+          <t>https://www.indeed.com/viewjob?jk=fed8b15c04492576</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fed8b15c04492576</t>
+          <t>https://www.indeed.com/viewjob?jk=5b12133504b24bae</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b12133504b24bae</t>
+          <t>https://www.indeed.com/viewjob?jk=9f864d9aca9b7b27</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f864d9aca9b7b27</t>
+          <t>https://www.indeed.com/viewjob?jk=76d2eb1be4c1b252</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76d2eb1be4c1b252</t>
+          <t>https://www.indeed.com/viewjob?jk=9baba2b401f1c56c</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Data Product Analyst - Data Management Engineer III</t>
+          <t>Databricks Developer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,32 +3996,32 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9baba2b401f1c56c</t>
+          <t>https://www.indeed.com/viewjob?jk=ab1192abfbd7f24e</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Databricks Developer</t>
+          <t>Site Reliability Engineering (SRE) - Maryland, US</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>Azure, GCP, BigQuery, Zookeeper, Scala, Kafka, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,32 +4031,32 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab1192abfbd7f24e</t>
+          <t>https://www.indeed.com/viewjob?jk=8d51d47e65997196</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Databricks Developer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=320dcd4f927cb250</t>
+          <t>https://www.indeed.com/viewjob?jk=33b30501746ad4bf</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Site Reliability Engineering (SRE) - Maryland, US</t>
+          <t>Data Engineer - Oklahoma City, OK</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>CFS Brands, LLC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Azure, GCP, BigQuery, Zookeeper, Scala, Kafka, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>IAM, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,112 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d51d47e65997196</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Data Engineer III</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=33b30501746ad4bf</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Data Engineer - Oklahoma City, OK</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>CFS Brands, LLC</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Oklahoma City, OK, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>IAM, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=113fe7e3580ec298</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Apache Spark Core Java</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-08-22</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=16d16eda2d514586</t>
         </is>
       </c>
     </row>
